--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CA52FD-68F5-461A-91AA-494660226D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -86,9 +87,6 @@
   </si>
   <si>
     <t>From the concerns table only. The processing of the questionnaire responses may be deterministic. Vidit to create the core logic of Questionnaire processing and get it reviewed with Lindsey/ business.</t>
-  </si>
-  <si>
-    <t>Concern fusion</t>
   </si>
   <si>
     <t>RAG-based base &amp; active retrieval</t>
@@ -143,12 +141,72 @@
       <t xml:space="preserve"> research.</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">Add exclusion table </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contains allergens and contraindictions which users answer in questionnaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vision LLM concern extraction prompt &amp; json design </t>
+  </si>
+  <si>
+    <t>SQL Candidate Shortlist Query</t>
+  </si>
+  <si>
+    <t>Formulation LLM call prompt and json design</t>
+  </si>
+  <si>
+    <t>Questionnaire concern extraction prompt &amp; json design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design json structure to send shortlist package and get active, base , dosage and explanation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concern fusion </t>
+  </si>
+  <si>
+    <t>1. Use exclusion table (item 9) to filter out allergens and contraindications
+2.From the user's confirmed concerns, join concern_benefit with active_benefit_score and base_active_compatability, to give filtered, structured json packet</t>
+  </si>
+  <si>
+    <t>Post Generation safety re-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final check to see if returned formulation contains any exclusions or incompatabilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLM interaction auditing </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write to existing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>audit_log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — no new table needed</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,8 +222,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,8 +261,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -187,11 +282,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -202,6 +312,40 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -220,9 +364,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -260,9 +404,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -297,7 +441,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -332,7 +476,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,20 +649,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" style="1"/>
-    <col min="2" max="2" width="3.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="1"/>
+    <col min="2" max="2" width="3.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.19921875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.06640625" style="1"/>
+    <col min="4" max="4" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.21875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="28.8">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -541,7 +685,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="28.8">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -561,12 +705,12 @@
         <v>46245</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="57.6">
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -581,7 +725,7 @@
         <v>46245</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="28.8">
       <c r="B4" s="1">
         <v>3</v>
       </c>
@@ -589,7 +733,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3">
         <v>46240</v>
@@ -598,7 +742,7 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="28.8">
       <c r="B5" s="1">
         <v>4</v>
       </c>
@@ -606,7 +750,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3">
         <v>46240</v>
@@ -615,7 +759,7 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="28.8">
       <c r="B6" s="1">
         <v>5</v>
       </c>
@@ -623,7 +767,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" s="3">
         <v>46240</v>
@@ -632,7 +776,7 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="28.8">
       <c r="B7" s="1">
         <v>6</v>
       </c>
@@ -640,7 +784,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3">
         <v>46240</v>
@@ -649,15 +793,15 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="28.8">
       <c r="B8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3">
         <v>46240</v>
@@ -666,7 +810,7 @@
         <v>46262</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="28.8">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -677,7 +821,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" s="3">
         <v>46240</v>
@@ -689,180 +833,281 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="42.75" x14ac:dyDescent="0.45">
-      <c r="B10" s="1">
+    <row r="10" spans="1:7" s="12" customFormat="1" ht="28.8">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="3">
-        <v>46240</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="3">
-        <v>46248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="C10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" ht="43.2">
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="3">
         <v>46240</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3">
         <v>46248</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="57" x14ac:dyDescent="0.45">
-      <c r="B12" s="1">
+    <row r="12" spans="1:7" s="4" customFormat="1" ht="28.8">
+      <c r="B12" s="4">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="5">
+        <v>46240</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="5">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="12" customFormat="1">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10">
         <v>11</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:7" s="4" customFormat="1" ht="57.6">
+      <c r="B14" s="4">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="5">
         <v>46240</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G14" s="5">
         <v>46248</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B13" s="1">
+    <row r="15" spans="1:7" s="13" customFormat="1" ht="28.8">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8">
         <v>12</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="1:7" ht="28.8">
+      <c r="B16" s="1">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="3">
+        <v>46246</v>
+      </c>
+      <c r="G16" s="3">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="4" customFormat="1" ht="28.8">
+      <c r="B17" s="4">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="3">
-        <v>46246</v>
-      </c>
-      <c r="G13" s="3">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="1">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="5">
+        <v>46251</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="G17" s="5">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="14" customFormat="1" ht="72">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6">
+        <v>14</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" s="14" customFormat="1" ht="28.8">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6">
+        <v>15</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" s="4" customFormat="1" ht="28.8">
+      <c r="B20" s="4">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="5">
         <v>46251</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="F20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="5">
         <v>46255</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="1">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1" t="s">
+    <row r="21" spans="1:7" s="4" customFormat="1" ht="28.8">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6">
+        <v>16</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" s="4" customFormat="1" ht="28.8">
+      <c r="B22" s="4">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="D22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="5">
         <v>46251</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="F22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="5">
         <v>46255</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="1">
-        <v>15</v>
-      </c>
-      <c r="C16" s="1" t="s">
+    <row r="23" spans="1:7" s="4" customFormat="1" ht="28.8">
+      <c r="B23" s="4">
+        <v>16</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="3">
-        <v>46251</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="3">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="1">
-        <v>16</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="5">
+        <v>46258</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="5">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="4" customFormat="1">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6">
+        <v>17</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" ht="28.8">
+      <c r="B25" s="1">
+        <v>18</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="3">
         <v>46258</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="3">
-        <v>46262</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B18" s="1">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="3">
-        <v>46258</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="F25" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="3">
         <v>46262</v>
       </c>
     </row>

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,19 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CA52FD-68F5-461A-91AA-494660226D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA007FAD-25E6-4D83-859A-BCF323A566AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint Plan" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="88">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -201,12 +202,263 @@
       <t xml:space="preserve"> — no new table needed</t>
     </r>
   </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Add exclusion table</t>
+  </si>
+  <si>
+    <t>Design schema (allergen/exclusion master + active link table)</t>
+  </si>
+  <si>
+    <t>Map questionnaire allergen field → exclusion table (structured, not free-text)</t>
+  </si>
+  <si>
+    <t>Write DDL migration</t>
+  </si>
+  <si>
+    <t>Seed exclusion data from workbook/domain input</t>
+  </si>
+  <si>
+    <t>Write QA query to validate coverage (e.g. every active has been assessed against every known allergen category)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image Preprocessing &amp; Quality Validation </t>
+  </si>
+  <si>
+    <t>Define acceptance thresholds (blur, lighting,resolution)</t>
+  </si>
+  <si>
+    <t>Implement preprocessing pipeline</t>
+  </si>
+  <si>
+    <t>Quality gate + reject/retry module</t>
+  </si>
+  <si>
+    <t>Vision LLM Concern Extraction</t>
+  </si>
+  <si>
+    <t>Define prompt structure</t>
+  </si>
+  <si>
+    <t>Questionnaire Concern Extraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concern Fusion </t>
+  </si>
+  <si>
+    <t>Fuse questionnaire &amp; image skin detected skin concerns using OR  logic i.e
+skin_concerns = questionnaire_concerns OR image_concerns</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Update </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>session_skin_concern_score</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> table</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">join </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>concern_benefit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>active_benefit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>score+base_active_compatability</t>
+    </r>
+  </si>
+  <si>
+    <t>Apply exclusion filter</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define JSON package shape for LLM call - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shortlist_json</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulation LLM Call </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Draft prompt template consuming </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">shortlist_json </t>
+    </r>
+  </si>
+  <si>
+    <t>Define output Json Schema</t>
+  </si>
+  <si>
+    <t>Work Serial</t>
+  </si>
+  <si>
+    <t>Desginated Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend Sprint </t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>LLM Interaction auditing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>audit_log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> payload shape per event_type (image, questionnaire,formulation)</t>
+    </r>
+  </si>
+  <si>
+    <t>Implement logging calls at each LLM touchpoint</t>
+  </si>
+  <si>
+    <t>Define final response schema (formulation,actives,bases,explanation, formulation_id,etc)</t>
+  </si>
+  <si>
+    <t>Implement DB -&gt; Json serialization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define error/fallback response </t>
+  </si>
+  <si>
+    <t>Shopify integration test</t>
+  </si>
+  <si>
+    <t>Work Sub Serial</t>
+  </si>
+  <si>
+    <t>Sprint Serial</t>
+  </si>
+  <si>
+    <t>SQL Candidate Shortlist Query (Optional)</t>
+  </si>
+  <si>
+    <t>Audit final candidate table</t>
+  </si>
+  <si>
+    <t>Sprint Start</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define output JSON structure </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,13 +468,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -248,7 +493,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,8 +518,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -297,11 +554,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -312,22 +649,10 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -336,16 +661,61 @@
     <xf numFmtId="16" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,20 +1203,20 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="12" customFormat="1" ht="28.8">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10">
+    <row r="10" spans="1:7" s="10" customFormat="1" ht="28.8">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6">
         <v>9</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="10" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="11"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="43.2">
       <c r="B11" s="1">
@@ -888,18 +1258,18 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="12" customFormat="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10">
+    <row r="13" spans="1:7" s="10" customFormat="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6">
         <v>11</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" s="4" customFormat="1" ht="57.6">
       <c r="B14" s="4">
@@ -921,7 +1291,7 @@
         <v>46248</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="13" customFormat="1" ht="28.8">
+    <row r="15" spans="1:7" s="11" customFormat="1" ht="28.8">
       <c r="A15" s="8"/>
       <c r="B15" s="8">
         <v>12</v>
@@ -971,7 +1341,7 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="14" customFormat="1" ht="72">
+    <row r="18" spans="1:7" s="10" customFormat="1" ht="72">
       <c r="A18" s="6"/>
       <c r="B18" s="6">
         <v>14</v>
@@ -986,7 +1356,7 @@
       </c>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" spans="1:7" s="14" customFormat="1" ht="28.8">
+    <row r="19" spans="1:7" s="10" customFormat="1" ht="28.8">
       <c r="A19" s="6"/>
       <c r="B19" s="6">
         <v>15</v>
@@ -1086,7 +1456,7 @@
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="12" t="s">
         <v>46</v>
       </c>
       <c r="G24" s="7"/>
@@ -1104,7 +1474,7 @@
       <c r="E25" s="3">
         <v>46258</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G25" s="3">
@@ -1115,4 +1485,463 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B28C61C-1A55-4D93-BE97-335A9CE60726}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="32"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="58.8" customHeight="1">
+      <c r="A3" s="24"/>
+      <c r="B3" s="28">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="1:9" ht="54.6" customHeight="1">
+      <c r="A4" s="24"/>
+      <c r="B4" s="28"/>
+      <c r="C4">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="25"/>
+    </row>
+    <row r="5" spans="1:9" ht="33.6" customHeight="1">
+      <c r="A5" s="24"/>
+      <c r="B5" s="28"/>
+      <c r="C5">
+        <v>1.3</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="25"/>
+    </row>
+    <row r="6" spans="1:9" ht="26.4" customHeight="1">
+      <c r="A6" s="24"/>
+      <c r="B6" s="28"/>
+      <c r="C6">
+        <v>1.4</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="25"/>
+    </row>
+    <row r="7" spans="1:9" ht="72.599999999999994" customHeight="1">
+      <c r="A7" s="24"/>
+      <c r="B7" s="28"/>
+      <c r="C7">
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:9" ht="28.8">
+      <c r="A8" s="24"/>
+      <c r="B8" s="28">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>2.1</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="25"/>
+    </row>
+    <row r="9" spans="1:9" ht="28.8">
+      <c r="A9" s="24"/>
+      <c r="B9" s="28"/>
+      <c r="C9">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="25"/>
+    </row>
+    <row r="10" spans="1:9" ht="28.8">
+      <c r="A10" s="24"/>
+      <c r="B10" s="28"/>
+      <c r="C10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="25"/>
+    </row>
+    <row r="11" spans="1:9" ht="28.8">
+      <c r="A11" s="24"/>
+      <c r="B11" s="28">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>3.1</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="25"/>
+    </row>
+    <row r="12" spans="1:9" ht="28.8">
+      <c r="A12" s="24"/>
+      <c r="B12" s="28"/>
+      <c r="C12">
+        <v>3.2</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="25"/>
+    </row>
+    <row r="13" spans="1:9" ht="28.8">
+      <c r="A13" s="24"/>
+      <c r="B13" s="28">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="25"/>
+    </row>
+    <row r="14" spans="1:9" ht="28.8">
+      <c r="A14" s="24"/>
+      <c r="B14" s="28"/>
+      <c r="C14">
+        <v>4.2</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="25"/>
+    </row>
+    <row r="15" spans="1:9" ht="86.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="28">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16" spans="1:9" ht="28.8">
+      <c r="A16" s="24"/>
+      <c r="B16" s="28"/>
+      <c r="C16">
+        <v>5.2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="1:9" ht="28.8">
+      <c r="A17" s="24"/>
+      <c r="B17" s="28">
+        <v>6</v>
+      </c>
+      <c r="C17">
+        <v>6.1</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="25"/>
+    </row>
+    <row r="18" spans="1:9" ht="28.8">
+      <c r="A18" s="24"/>
+      <c r="B18" s="28"/>
+      <c r="C18">
+        <v>6.2</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="25"/>
+    </row>
+    <row r="19" spans="1:9" ht="43.8" customHeight="1">
+      <c r="A19" s="24"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="18">
+        <v>6.3</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" s="25"/>
+    </row>
+    <row r="20" spans="1:9" ht="28.8">
+      <c r="A20" s="24"/>
+      <c r="B20" s="28"/>
+      <c r="C20">
+        <v>6.4</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="25"/>
+    </row>
+    <row r="21" spans="1:9" ht="28.8">
+      <c r="A21" s="24"/>
+      <c r="B21" s="28">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>7.1</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" s="25"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="24"/>
+      <c r="B22" s="28"/>
+      <c r="C22">
+        <v>7.2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="25"/>
+    </row>
+    <row r="23" spans="1:9" ht="43.2">
+      <c r="A23" s="24"/>
+      <c r="B23" s="28">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>8.1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="25"/>
+    </row>
+    <row r="24" spans="1:9" ht="28.8">
+      <c r="A24" s="24"/>
+      <c r="B24" s="28"/>
+      <c r="C24">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="25"/>
+    </row>
+    <row r="25" spans="1:9" ht="43.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="28">
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <v>9.1</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="25"/>
+    </row>
+    <row r="26" spans="1:9" ht="28.8">
+      <c r="A26" s="24"/>
+      <c r="B26" s="28"/>
+      <c r="C26">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="25"/>
+    </row>
+    <row r="27" spans="1:9" ht="28.8">
+      <c r="A27" s="24"/>
+      <c r="B27" s="28"/>
+      <c r="C27">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I27" s="25"/>
+    </row>
+    <row r="28" spans="1:9" ht="28.8">
+      <c r="A28" s="26"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="20">
+        <v>9.4</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B17:B20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA007FAD-25E6-4D83-859A-BCF323A566AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0A7BEF-6168-491A-AFA1-D9354CA73BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,12 +11,25 @@
     <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint Plan" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="104">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -230,12 +243,6 @@
     <t>Define acceptance thresholds (blur, lighting,resolution)</t>
   </si>
   <si>
-    <t>Implement preprocessing pipeline</t>
-  </si>
-  <si>
-    <t>Quality gate + reject/retry module</t>
-  </si>
-  <si>
     <t>Vision LLM Concern Extraction</t>
   </si>
   <si>
@@ -278,6 +285,158 @@
     </r>
   </si>
   <si>
+    <t>Apply exclusion filter</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define JSON package shape for LLM call - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shortlist_json</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulation LLM Call </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Draft prompt template consuming </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">shortlist_json </t>
+    </r>
+  </si>
+  <si>
+    <t>Define output Json Schema</t>
+  </si>
+  <si>
+    <t>Work Serial</t>
+  </si>
+  <si>
+    <t>Desginated Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend Sprint </t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>LLM Interaction auditing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>audit_log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> payload shape per event_type (image, questionnaire,formulation)</t>
+    </r>
+  </si>
+  <si>
+    <t>Implement logging calls at each LLM touchpoint</t>
+  </si>
+  <si>
+    <t>Define final response schema (formulation,actives,bases,explanation, formulation_id,etc)</t>
+  </si>
+  <si>
+    <t>Implement DB -&gt; Json serialization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define error/fallback response </t>
+  </si>
+  <si>
+    <t>Shopify integration test</t>
+  </si>
+  <si>
+    <t>Work Sub Serial</t>
+  </si>
+  <si>
+    <t>Sprint Serial</t>
+  </si>
+  <si>
+    <t>SQL Candidate Shortlist Query (Optional)</t>
+  </si>
+  <si>
+    <t>Audit final candidate table</t>
+  </si>
+  <si>
+    <t>Sprint Start</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define output JSON structure </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement preprocessing pipeline </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(update in detail)</t>
+    </r>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quality gate + reject/retry module
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(capture status code from backend and display in the frontend in a UX shell)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">join </t>
     </r>
@@ -321,7 +480,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> + </t>
+      <t xml:space="preserve"> _</t>
     </r>
     <r>
       <rPr>
@@ -332,126 +491,64 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>score+base_active_compatability</t>
-    </r>
-  </si>
-  <si>
-    <t>Apply exclusion filter</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Define JSON package shape for LLM call - </t>
+      <t xml:space="preserve">score+base_active_compatability
+</t>
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>shortlist_json</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulation LLM Call </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Draft prompt template consuming </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">shortlist_json </t>
-    </r>
-  </si>
-  <si>
-    <t>Define output Json Schema</t>
-  </si>
-  <si>
-    <t>Work Serial</t>
-  </si>
-  <si>
-    <t>Desginated Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend Sprint </t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>LLM Interaction auditing</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Define </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>audit_log</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> payload shape per event_type (image, questionnaire,formulation)</t>
-    </r>
-  </si>
-  <si>
-    <t>Implement logging calls at each LLM touchpoint</t>
-  </si>
-  <si>
-    <t>Define final response schema (formulation,actives,bases,explanation, formulation_id,etc)</t>
-  </si>
-  <si>
-    <t>Implement DB -&gt; Json serialization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define error/fallback response </t>
-  </si>
-  <si>
-    <t>Shopify integration test</t>
-  </si>
-  <si>
-    <t>Work Sub Serial</t>
-  </si>
-  <si>
-    <t>Sprint Serial</t>
-  </si>
-  <si>
-    <t>SQL Candidate Shortlist Query (Optional)</t>
-  </si>
-  <si>
-    <t>Audit final candidate table</t>
-  </si>
-  <si>
-    <t>Sprint Start</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define output JSON structure </t>
+      <t>(climate, skin type {oily,semi-oily,dry,etc},acne suitable)</t>
+    </r>
+  </si>
+  <si>
+    <t>Rajanya , Azad</t>
+  </si>
+  <si>
+    <t>Vidit</t>
+  </si>
+  <si>
+    <t>6 days</t>
+  </si>
+  <si>
+    <t>Soubhanik</t>
+  </si>
+  <si>
+    <t>3 days</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>7 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint Review </t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Blocker</t>
+  </si>
+  <si>
+    <t>Client yet to mail back</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>2 days</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Rajanya, Azad and Vidit</t>
   </si>
 </sst>
 </file>
@@ -531,7 +628,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -554,91 +651,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -691,29 +708,54 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1489,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B28C61C-1A55-4D93-BE97-335A9CE60726}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
@@ -1498,32 +1540,37 @@
     <col min="4" max="4" width="21.44140625" style="13" customWidth="1"/>
     <col min="5" max="5" width="33.33203125" style="13" customWidth="1"/>
     <col min="6" max="6" width="11.77734375" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="7" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="32"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="22" t="s">
-        <v>82</v>
+    <row r="1" spans="1:12">
+      <c r="A1" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>5</v>
@@ -1532,21 +1579,32 @@
         <v>47</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="58.8" customHeight="1">
-      <c r="A3" s="24"/>
-      <c r="B3" s="28">
+      <c r="L2" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="58.8" customHeight="1">
+      <c r="A3" s="32">
+        <v>1</v>
+      </c>
+      <c r="B3" s="32">
         <v>1</v>
       </c>
       <c r="C3">
@@ -1558,11 +1616,25 @@
       <c r="E3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="1:9" ht="54.6" customHeight="1">
-      <c r="A4" s="24"/>
-      <c r="B4" s="28"/>
+      <c r="F3" s="35">
+        <v>46252</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="35">
+        <v>46259</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="54.6" customHeight="1">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
       <c r="C4">
         <v>1.2</v>
       </c>
@@ -1572,11 +1644,15 @@
       <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="25"/>
-    </row>
-    <row r="5" spans="1:9" ht="33.6" customHeight="1">
-      <c r="A5" s="24"/>
-      <c r="B5" s="28"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" spans="1:12" ht="33.6" customHeight="1">
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
       <c r="C5">
         <v>1.3</v>
       </c>
@@ -1586,11 +1662,15 @@
       <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="25"/>
-    </row>
-    <row r="6" spans="1:9" ht="26.4" customHeight="1">
-      <c r="A6" s="24"/>
-      <c r="B6" s="28"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+    </row>
+    <row r="6" spans="1:12" ht="26.4" customHeight="1">
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
       <c r="C6">
         <v>1.4</v>
       </c>
@@ -1600,11 +1680,15 @@
       <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="25"/>
-    </row>
-    <row r="7" spans="1:9" ht="72.599999999999994" customHeight="1">
-      <c r="A7" s="24"/>
-      <c r="B7" s="28"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+    </row>
+    <row r="7" spans="1:12" ht="72.599999999999994" customHeight="1">
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
       <c r="C7">
         <v>1.5</v>
       </c>
@@ -1614,11 +1698,15 @@
       <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="25"/>
-    </row>
-    <row r="8" spans="1:9" ht="28.8">
-      <c r="A8" s="24"/>
-      <c r="B8" s="28">
+      <c r="F7" s="35"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+    </row>
+    <row r="8" spans="1:12" ht="28.8">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32">
         <v>2</v>
       </c>
       <c r="C8">
@@ -1630,11 +1718,23 @@
       <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="25"/>
-    </row>
-    <row r="9" spans="1:9" ht="28.8">
-      <c r="A9" s="24"/>
-      <c r="B9" s="28"/>
+      <c r="F8" s="35">
+        <v>46252</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="35">
+        <v>46258</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="32"/>
+    </row>
+    <row r="9" spans="1:12" ht="28.8">
+      <c r="A9" s="32"/>
+      <c r="B9" s="32"/>
       <c r="C9">
         <v>2.2000000000000002</v>
       </c>
@@ -1642,13 +1742,17 @@
         <v>54</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="25"/>
-    </row>
-    <row r="10" spans="1:9" ht="28.8">
-      <c r="A10" s="24"/>
-      <c r="B10" s="28"/>
+        <v>85</v>
+      </c>
+      <c r="F9" s="35"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+    </row>
+    <row r="10" spans="1:12" ht="43.2">
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
       <c r="C10">
         <v>2.2999999999999998</v>
       </c>
@@ -1656,292 +1760,500 @@
         <v>54</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="25"/>
-    </row>
-    <row r="11" spans="1:9" ht="28.8">
-      <c r="A11" s="24"/>
-      <c r="B11" s="28">
+        <v>87</v>
+      </c>
+      <c r="F10" s="35"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+    </row>
+    <row r="11" spans="1:12" ht="28.8">
+      <c r="A11" s="32"/>
+      <c r="B11" s="32">
         <v>3</v>
       </c>
       <c r="C11">
         <v>3.1</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="25"/>
-    </row>
-    <row r="12" spans="1:9" ht="28.8">
-      <c r="A12" s="24"/>
-      <c r="B12" s="28"/>
+        <v>84</v>
+      </c>
+      <c r="F11" s="35"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+    </row>
+    <row r="12" spans="1:12" ht="28.8">
+      <c r="A12" s="32"/>
+      <c r="B12" s="32"/>
       <c r="C12">
         <v>3.2</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="25"/>
-    </row>
-    <row r="13" spans="1:9" ht="28.8">
-      <c r="A13" s="24"/>
-      <c r="B13" s="28">
+        <v>57</v>
+      </c>
+      <c r="F12" s="22">
+        <v>46255</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="22">
+        <v>46259</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J12" s="32"/>
+    </row>
+    <row r="13" spans="1:12" ht="28.8">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32">
         <v>4</v>
       </c>
       <c r="C13">
         <v>4.0999999999999996</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" s="25"/>
-    </row>
-    <row r="14" spans="1:9" ht="28.8">
-      <c r="A14" s="24"/>
-      <c r="B14" s="28"/>
+        <v>84</v>
+      </c>
+      <c r="F13" s="22">
+        <v>46252</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="22">
+        <v>46258</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="32"/>
+    </row>
+    <row r="14" spans="1:12" ht="28.8">
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
       <c r="C14">
         <v>4.2</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="22">
+        <v>46255</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="22">
+        <v>46259</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" spans="1:12" ht="28.8">
+      <c r="A15" s="32"/>
+      <c r="B15" s="14">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>9.4</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="32"/>
+      <c r="L15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="36"/>
+      <c r="F16" s="26">
+        <v>46198</v>
+      </c>
+      <c r="G16" s="27">
+        <v>0.625</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="I16" s="24"/>
+    </row>
+    <row r="17" spans="1:9" ht="86.4">
+      <c r="A17" s="32">
+        <v>2</v>
+      </c>
+      <c r="B17" s="32">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F17" s="21">
+        <v>46260</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="33">
+        <v>46262</v>
+      </c>
+      <c r="I17" s="31" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.8">
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18">
+        <v>5.2</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I14" s="25"/>
-    </row>
-    <row r="15" spans="1:9" ht="86.4">
-      <c r="A15" s="24"/>
-      <c r="B15" s="28">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" s="25"/>
-    </row>
-    <row r="16" spans="1:9" ht="28.8">
-      <c r="A16" s="24"/>
-      <c r="B16" s="28"/>
-      <c r="C16">
-        <v>5.2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="I16" s="25"/>
-    </row>
-    <row r="17" spans="1:9" ht="28.8">
-      <c r="A17" s="24"/>
-      <c r="B17" s="28">
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+    </row>
+    <row r="19" spans="1:9" ht="57.6">
+      <c r="A19" s="32"/>
+      <c r="B19" s="32">
         <v>6</v>
       </c>
-      <c r="C17">
+      <c r="C19">
         <v>6.1</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="25"/>
-    </row>
-    <row r="18" spans="1:9" ht="28.8">
-      <c r="A18" s="24"/>
-      <c r="B18" s="28"/>
-      <c r="C18">
+      <c r="E19" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="33">
+        <v>46260</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="33">
+        <v>46267</v>
+      </c>
+      <c r="I19" s="31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20">
         <v>6.2</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9" ht="43.8" customHeight="1">
-      <c r="A19" s="24"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="18">
-        <v>6.3</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9" ht="28.8">
-      <c r="A20" s="24"/>
-      <c r="B20" s="28"/>
-      <c r="C20">
-        <v>6.4</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>37</v>
       </c>
       <c r="E20" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+    </row>
+    <row r="21" spans="1:9" ht="43.8" customHeight="1">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="18">
+        <v>6.3</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+    </row>
+    <row r="22" spans="1:9" ht="28.8">
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22">
+        <v>6.4</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+    </row>
+    <row r="23" spans="1:9" ht="28.8">
+      <c r="A23" s="32"/>
+      <c r="B23" s="32">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>7.1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="33">
+        <v>46260</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="33">
+        <v>46267</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24">
+        <v>7.2</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="I20" s="25"/>
-    </row>
-    <row r="21" spans="1:9" ht="28.8">
-      <c r="A21" s="24"/>
-      <c r="B21" s="28">
-        <v>7</v>
-      </c>
-      <c r="C21">
-        <v>7.1</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" s="25"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="24"/>
-      <c r="B22" s="28"/>
-      <c r="C22">
-        <v>7.2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="25"/>
-    </row>
-    <row r="23" spans="1:9" ht="43.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="28">
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+    </row>
+    <row r="25" spans="1:9" ht="43.2">
+      <c r="A25" s="32"/>
+      <c r="B25" s="32">
         <v>8</v>
       </c>
-      <c r="C23">
+      <c r="C25">
         <v>8.1</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="34">
+        <v>46260</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="33">
+        <v>46267</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="28.8">
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
+      <c r="C26">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="34"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="29">
+        <v>46266</v>
+      </c>
+      <c r="G27" s="30">
+        <v>0.625</v>
+      </c>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+    </row>
+    <row r="28" spans="1:9" ht="43.2">
+      <c r="A28" s="32">
+        <v>3</v>
+      </c>
+      <c r="B28" s="32">
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <v>9.1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="F28" s="33">
+        <v>46268</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="33">
+        <v>46275</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="28.8">
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
+      <c r="C29">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="I23" s="25"/>
-    </row>
-    <row r="24" spans="1:9" ht="28.8">
-      <c r="A24" s="24"/>
-      <c r="B24" s="28"/>
-      <c r="C24">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="13" t="s">
+      <c r="F29" s="33"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="31"/>
+    </row>
+    <row r="30" spans="1:9" ht="28.8">
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I24" s="25"/>
-    </row>
-    <row r="25" spans="1:9" ht="43.2">
-      <c r="A25" s="24"/>
-      <c r="B25" s="28">
-        <v>9</v>
-      </c>
-      <c r="C25">
-        <v>9.1</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I25" s="25"/>
-    </row>
-    <row r="26" spans="1:9" ht="28.8">
-      <c r="A26" s="24"/>
-      <c r="B26" s="28"/>
-      <c r="C26">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="25"/>
-    </row>
-    <row r="27" spans="1:9" ht="28.8">
-      <c r="A27" s="24"/>
-      <c r="B27" s="28"/>
-      <c r="C27">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I27" s="25"/>
-    </row>
-    <row r="28" spans="1:9" ht="28.8">
-      <c r="A28" s="26"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="20">
-        <v>9.4</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="27"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="31"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="32"/>
+      <c r="B31" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B21:B22"/>
+  <mergeCells count="43">
     <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B28:B31"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="F3:F7"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J3:J15"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="G3:G7"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="A17:A26"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I17:I18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0A7BEF-6168-491A-AFA1-D9354CA73BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0CC603-084A-495E-8B76-D4533DDF2B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -437,6 +437,51 @@
     </r>
   </si>
   <si>
+    <t>Rajanya , Azad</t>
+  </si>
+  <si>
+    <t>Vidit</t>
+  </si>
+  <si>
+    <t>6 days</t>
+  </si>
+  <si>
+    <t>Soubhanik</t>
+  </si>
+  <si>
+    <t>3 days</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>7 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint Review </t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Blocker</t>
+  </si>
+  <si>
+    <t>Client yet to mail back</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>2 days</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Rajanya, Azad and Vidit</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">join </t>
     </r>
@@ -497,65 +542,31 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(climate, skin type {oily,semi-oily,dry,etc},acne suitable)</t>
-    </r>
-  </si>
-  <si>
-    <t>Rajanya , Azad</t>
-  </si>
-  <si>
-    <t>Vidit</t>
-  </si>
-  <si>
-    <t>6 days</t>
-  </si>
-  <si>
-    <t>Soubhanik</t>
-  </si>
-  <si>
-    <t>3 days</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>7 days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint Review </t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Blocker</t>
-  </si>
-  <si>
-    <t>Client yet to mail back</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>2 days</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Rajanya, Azad and Vidit</t>
+      <t xml:space="preserve">(climate, skin type {oily,semi-oily,dry,etc},acne suitable) -&gt; bases
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(vector db query ; no deterministic logic)</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,6 +599,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -738,24 +756,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1547,20 +1565,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="15" t="s">
@@ -1585,7 +1603,7 @@
         <v>83</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I2" s="15" t="s">
         <v>68</v>
@@ -1597,14 +1615,14 @@
         <v>86</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="58.8" customHeight="1">
-      <c r="A3" s="32">
+      <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="32">
+      <c r="B3" s="31">
         <v>1</v>
       </c>
       <c r="C3">
@@ -1616,25 +1634,25 @@
       <c r="E3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="33">
         <v>46252</v>
       </c>
-      <c r="G3" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="H3" s="35">
+      <c r="G3" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="33">
         <v>46259</v>
       </c>
-      <c r="I3" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>100</v>
+      <c r="I3" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="54.6" customHeight="1">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
       <c r="C4">
         <v>1.2</v>
       </c>
@@ -1644,15 +1662,15 @@
       <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="35"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
       <c r="C5">
         <v>1.3</v>
       </c>
@@ -1662,15 +1680,15 @@
       <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:12" ht="26.4" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
       <c r="C6">
         <v>1.4</v>
       </c>
@@ -1680,15 +1698,15 @@
       <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
     </row>
     <row r="7" spans="1:12" ht="72.599999999999994" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
       <c r="C7">
         <v>1.5</v>
       </c>
@@ -1698,15 +1716,15 @@
       <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32">
+      <c r="A8" s="31"/>
+      <c r="B8" s="31">
         <v>2</v>
       </c>
       <c r="C8">
@@ -1718,23 +1736,23 @@
       <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="33">
         <v>46252</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="35">
+      <c r="G8" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="33">
         <v>46258</v>
       </c>
-      <c r="I8" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="J8" s="32"/>
+      <c r="I8" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="28.8">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="31"/>
       <c r="C9">
         <v>2.2000000000000002</v>
       </c>
@@ -1744,15 +1762,15 @@
       <c r="E9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
       <c r="C10">
         <v>2.2999999999999998</v>
       </c>
@@ -1762,15 +1780,15 @@
       <c r="E10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" spans="1:12" ht="28.8">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32">
+      <c r="A11" s="31"/>
+      <c r="B11" s="31">
         <v>3</v>
       </c>
       <c r="C11">
@@ -1782,15 +1800,15 @@
       <c r="E11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
       <c r="C12">
         <v>3.2</v>
       </c>
@@ -1804,19 +1822,19 @@
         <v>46255</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H12" s="22">
         <v>46259</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="J12" s="32"/>
+        <v>91</v>
+      </c>
+      <c r="J12" s="31"/>
     </row>
     <row r="13" spans="1:12" ht="28.8">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32">
+      <c r="A13" s="31"/>
+      <c r="B13" s="31">
         <v>4</v>
       </c>
       <c r="C13">
@@ -1832,19 +1850,19 @@
         <v>46252</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H13" s="22">
         <v>46258</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="J13" s="32"/>
+        <v>89</v>
+      </c>
+      <c r="J13" s="31"/>
     </row>
     <row r="14" spans="1:12" ht="28.8">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
       <c r="C14">
         <v>4.2</v>
       </c>
@@ -1858,18 +1876,18 @@
         <v>46255</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H14" s="22">
         <v>46259</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="32"/>
+        <v>91</v>
+      </c>
+      <c r="J14" s="31"/>
     </row>
     <row r="15" spans="1:12" ht="28.8">
-      <c r="A15" s="32"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="14">
         <v>9</v>
       </c>
@@ -1882,27 +1900,27 @@
       <c r="E15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
+      <c r="F15" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="32"/>
+      <c r="J15" s="31"/>
       <c r="L15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" s="36"/>
+      <c r="D16" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="34"/>
       <c r="F16" s="26">
         <v>46198</v>
       </c>
@@ -1913,10 +1931,10 @@
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="86.4">
-      <c r="A17" s="32">
+      <c r="A17" s="31">
         <v>2</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="31">
         <v>5</v>
       </c>
       <c r="C17">
@@ -1931,19 +1949,19 @@
       <c r="F17" s="21">
         <v>46260</v>
       </c>
-      <c r="G17" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="H17" s="33">
+      <c r="G17" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="36">
         <v>46262</v>
       </c>
-      <c r="I17" s="31" t="s">
-        <v>90</v>
+      <c r="I17" s="32" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="31"/>
       <c r="C18">
         <v>5.2</v>
       </c>
@@ -1953,13 +1971,13 @@
       <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-    </row>
-    <row r="19" spans="1:9" ht="57.6">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32">
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+    </row>
+    <row r="19" spans="1:9" ht="86.4">
+      <c r="A19" s="31"/>
+      <c r="B19" s="31">
         <v>6</v>
       </c>
       <c r="C19">
@@ -1969,24 +1987,24 @@
         <v>37</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="33">
+        <v>103</v>
+      </c>
+      <c r="F19" s="36">
         <v>46260</v>
       </c>
-      <c r="G19" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="33">
+      <c r="G19" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="36">
         <v>46267</v>
       </c>
-      <c r="I19" s="31" t="s">
-        <v>102</v>
+      <c r="I19" s="32" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
       <c r="C20">
         <v>6.2</v>
       </c>
@@ -1996,14 +2014,14 @@
       <c r="E20" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
     </row>
     <row r="21" spans="1:9" ht="43.8" customHeight="1">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="18">
         <v>6.3</v>
       </c>
@@ -2013,14 +2031,14 @@
       <c r="E21" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
     </row>
     <row r="22" spans="1:9" ht="28.8">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
       <c r="C22">
         <v>6.4</v>
       </c>
@@ -2030,14 +2048,14 @@
       <c r="E22" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
     </row>
     <row r="23" spans="1:9" ht="28.8">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32">
+      <c r="A23" s="31"/>
+      <c r="B23" s="31">
         <v>7</v>
       </c>
       <c r="C23">
@@ -2049,22 +2067,22 @@
       <c r="E23" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="36">
         <v>46260</v>
       </c>
-      <c r="G23" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="33">
+      <c r="G23" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="36">
         <v>46267</v>
       </c>
-      <c r="I23" s="31" t="s">
-        <v>92</v>
+      <c r="I23" s="32" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="31"/>
       <c r="C24">
         <v>7.2</v>
       </c>
@@ -2074,14 +2092,14 @@
       <c r="E24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
     </row>
     <row r="25" spans="1:9" ht="43.2">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32">
+      <c r="A25" s="31"/>
+      <c r="B25" s="31">
         <v>8</v>
       </c>
       <c r="C25">
@@ -2093,22 +2111,22 @@
       <c r="E25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="37">
         <v>46260</v>
       </c>
-      <c r="G25" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="H25" s="33">
+      <c r="G25" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="36">
         <v>46267</v>
       </c>
-      <c r="I25" s="31" t="s">
-        <v>103</v>
+      <c r="I25" s="32" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28.8">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
+      <c r="A26" s="31"/>
+      <c r="B26" s="31"/>
       <c r="C26">
         <v>8.1999999999999993</v>
       </c>
@@ -2118,10 +2136,10 @@
       <c r="E26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="24"/>
@@ -2129,7 +2147,7 @@
       <c r="C27" s="25"/>
       <c r="D27" s="28"/>
       <c r="E27" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F27" s="29">
         <v>46266</v>
@@ -2141,10 +2159,10 @@
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="43.2">
-      <c r="A28" s="32">
+      <c r="A28" s="31">
         <v>3</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="31">
         <v>9</v>
       </c>
       <c r="C28">
@@ -2156,22 +2174,22 @@
       <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="36">
         <v>46268</v>
       </c>
-      <c r="G28" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="H28" s="33">
+      <c r="G28" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="36">
         <v>46275</v>
       </c>
-      <c r="I28" s="31" t="s">
-        <v>97</v>
+      <c r="I28" s="32" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.8">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="31"/>
       <c r="C29">
         <v>9.1999999999999993</v>
       </c>
@@ -2181,14 +2199,14 @@
       <c r="E29" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="33"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="31"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="32"/>
     </row>
     <row r="30" spans="1:9" ht="28.8">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
       <c r="C30">
         <v>9.3000000000000007</v>
       </c>
@@ -2198,26 +2216,35 @@
       <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="33"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="31"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="32"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="A17:A26"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
     <mergeCell ref="I19:I22"/>
     <mergeCell ref="F3:F7"/>
     <mergeCell ref="D16:E16"/>
@@ -2234,24 +2261,15 @@
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="F19:F22"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0CC603-084A-495E-8B76-D4533DDF2B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8E2665-D8D7-4719-A55A-FBF7991E0138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint Plan" sheetId="2" r:id="rId2"/>
+    <sheet name="Agile Sprint" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="133">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -560,6 +561,219 @@
       </rPr>
       <t>(vector db query ; no deterministic logic)</t>
     </r>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>User Story</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Story Points</t>
+  </si>
+  <si>
+    <t>Designated Team</t>
+  </si>
+  <si>
+    <t>Must</t>
+  </si>
+  <si>
+    <t>Image Preprocessing &amp; Quality</t>
+  </si>
+  <si>
+    <t>Questionnaire concern extraction</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Concern Fusion</t>
+  </si>
+  <si>
+    <t>As a customer, I want the system to shortlist compatible actives and bases based on my combined image and questionnaire concerns, so that only relevant, safe candidates feed into my formulation.</t>
+  </si>
+  <si>
+    <t>As a customer, I want to receive a formulation — recommended
+ actives, bases, dosage and explanation — based on my shortlisted 
+candidates, so that I get a personalised, safe product recommendation.</t>
+  </si>
+  <si>
+    <t>Formulation LLM Call</t>
+  </si>
+  <si>
+    <t>LLM interaction auditing</t>
+  </si>
+  <si>
+    <t>Internal Review</t>
+  </si>
+  <si>
+    <t>Client Review</t>
+  </si>
+  <si>
+    <t>Shopify Integration Feasibility Test</t>
+  </si>
+  <si>
+    <t>Test the feasibility of shopify api integration</t>
+  </si>
+  <si>
+    <t>pending access to client shopify store</t>
+  </si>
+  <si>
+    <t>Quality Testing</t>
+  </si>
+  <si>
+    <t>Create a test dataset</t>
+  </si>
+  <si>
+    <t>Validate System with test dataset</t>
+  </si>
+  <si>
+    <t>MVP_SPRINT_PLAN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>As a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> customer,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I want to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> upload a picture of my skin , and after processing receive the detected skin concerns, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>so that</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the system has a basis for formulation reccomendation(actives)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>As a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> customer, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I want to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> answer a questionnaire, and after processing, receive my detected skin concerns, allergies, contraindications and skin properties (?),</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>so that</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> system understands my entire skin profile for formulation reccomendation ( bases)</t>
+    </r>
+  </si>
+  <si>
+    <t>Response to frontend</t>
+  </si>
+  <si>
+    <t>Return json containing detected skin concerns, allergies , and other relevant properties , to the front end.</t>
+  </si>
+  <si>
+    <t>Expected MVP showcase</t>
+  </si>
+  <si>
+    <t>Expected Skin concern detection showcase</t>
   </si>
 </sst>
 </file>
@@ -608,7 +822,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,8 +859,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -669,11 +907,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -756,9 +1040,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -770,10 +1060,88 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1565,20 +1933,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="15" t="s">
@@ -1619,10 +1987,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="58.8" customHeight="1">
-      <c r="A3" s="31">
+      <c r="A3" s="33">
         <v>1</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="33">
         <v>1</v>
       </c>
       <c r="C3">
@@ -1634,25 +2002,25 @@
       <c r="E3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="35">
         <v>46252</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="35">
         <v>46259</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="33" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="54.6" customHeight="1">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
       <c r="C4">
         <v>1.2</v>
       </c>
@@ -1662,15 +2030,15 @@
       <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
     </row>
     <row r="5" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
       <c r="C5">
         <v>1.3</v>
       </c>
@@ -1680,15 +2048,15 @@
       <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
     </row>
     <row r="6" spans="1:12" ht="26.4" customHeight="1">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
       <c r="C6">
         <v>1.4</v>
       </c>
@@ -1698,15 +2066,15 @@
       <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="33"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
     </row>
     <row r="7" spans="1:12" ht="72.599999999999994" customHeight="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
       <c r="C7">
         <v>1.5</v>
       </c>
@@ -1716,15 +2084,15 @@
       <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="33"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="31"/>
-      <c r="B8" s="31">
+      <c r="A8" s="33"/>
+      <c r="B8" s="33">
         <v>2</v>
       </c>
       <c r="C8">
@@ -1736,23 +2104,23 @@
       <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="35">
         <v>46252</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="35">
         <v>46258</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="31"/>
+      <c r="J8" s="33"/>
     </row>
     <row r="9" spans="1:12" ht="28.8">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
       <c r="C9">
         <v>2.2000000000000002</v>
       </c>
@@ -1762,15 +2130,15 @@
       <c r="E9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
       <c r="C10">
         <v>2.2999999999999998</v>
       </c>
@@ -1780,15 +2148,15 @@
       <c r="E10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="33"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
     </row>
     <row r="11" spans="1:12" ht="28.8">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31">
+      <c r="A11" s="33"/>
+      <c r="B11" s="33">
         <v>3</v>
       </c>
       <c r="C11">
@@ -1800,15 +2168,15 @@
       <c r="E11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
-      <c r="A12" s="31"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
       <c r="C12">
         <v>3.2</v>
       </c>
@@ -1830,11 +2198,11 @@
       <c r="I12" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="31"/>
+      <c r="J12" s="33"/>
     </row>
     <row r="13" spans="1:12" ht="28.8">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33">
         <v>4</v>
       </c>
       <c r="C13">
@@ -1858,11 +2226,11 @@
       <c r="I13" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="31"/>
+      <c r="J13" s="33"/>
     </row>
     <row r="14" spans="1:12" ht="28.8">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
       <c r="C14">
         <v>4.2</v>
       </c>
@@ -1884,10 +2252,10 @@
       <c r="I14" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="31"/>
+      <c r="J14" s="33"/>
     </row>
     <row r="15" spans="1:12" ht="28.8">
-      <c r="A15" s="31"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="14">
         <v>9</v>
       </c>
@@ -1900,15 +2268,15 @@
       <c r="E15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="31"/>
+      <c r="J15" s="33"/>
       <c r="L15" t="s">
         <v>98</v>
       </c>
@@ -1917,10 +2285,10 @@
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="34"/>
+      <c r="E16" s="36"/>
       <c r="F16" s="26">
         <v>46198</v>
       </c>
@@ -1931,10 +2299,10 @@
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="86.4">
-      <c r="A17" s="31">
+      <c r="A17" s="33">
         <v>2</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="33">
         <v>5</v>
       </c>
       <c r="C17">
@@ -1949,19 +2317,19 @@
       <c r="F17" s="21">
         <v>46260</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="32">
         <v>46262</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="31" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8">
-      <c r="A18" s="31"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
       <c r="C18">
         <v>5.2</v>
       </c>
@@ -1971,13 +2339,13 @@
       <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
     </row>
     <row r="19" spans="1:9" ht="86.4">
-      <c r="A19" s="31"/>
-      <c r="B19" s="31">
+      <c r="A19" s="33"/>
+      <c r="B19" s="33">
         <v>6</v>
       </c>
       <c r="C19">
@@ -1989,22 +2357,22 @@
       <c r="E19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="32">
         <v>46260</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="32">
         <v>46267</v>
       </c>
-      <c r="I19" s="32" t="s">
+      <c r="I19" s="31" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8">
-      <c r="A20" s="31"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
       <c r="C20">
         <v>6.2</v>
       </c>
@@ -2014,14 +2382,14 @@
       <c r="E20" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
     </row>
     <row r="21" spans="1:9" ht="43.8" customHeight="1">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
       <c r="C21" s="18">
         <v>6.3</v>
       </c>
@@ -2031,14 +2399,14 @@
       <c r="E21" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
     </row>
     <row r="22" spans="1:9" ht="28.8">
-      <c r="A22" s="31"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
       <c r="C22">
         <v>6.4</v>
       </c>
@@ -2048,14 +2416,14 @@
       <c r="E22" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
     </row>
     <row r="23" spans="1:9" ht="28.8">
-      <c r="A23" s="31"/>
-      <c r="B23" s="31">
+      <c r="A23" s="33"/>
+      <c r="B23" s="33">
         <v>7</v>
       </c>
       <c r="C23">
@@ -2067,22 +2435,22 @@
       <c r="E23" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="36">
+      <c r="F23" s="32">
         <v>46260</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="32">
         <v>46267</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" s="31" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="31"/>
-      <c r="B24" s="31"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="33"/>
       <c r="C24">
         <v>7.2</v>
       </c>
@@ -2092,14 +2460,14 @@
       <c r="E24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
     </row>
     <row r="25" spans="1:9" ht="43.2">
-      <c r="A25" s="31"/>
-      <c r="B25" s="31">
+      <c r="A25" s="33"/>
+      <c r="B25" s="33">
         <v>8</v>
       </c>
       <c r="C25">
@@ -2111,22 +2479,22 @@
       <c r="E25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="34">
         <v>46260</v>
       </c>
-      <c r="G25" s="32" t="s">
+      <c r="G25" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="32">
         <v>46267</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" s="31" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28.8">
-      <c r="A26" s="31"/>
-      <c r="B26" s="31"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="33"/>
       <c r="C26">
         <v>8.1999999999999993</v>
       </c>
@@ -2136,10 +2504,10 @@
       <c r="E26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="24"/>
@@ -2159,10 +2527,10 @@
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="43.2">
-      <c r="A28" s="31">
+      <c r="A28" s="33">
         <v>3</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="33">
         <v>9</v>
       </c>
       <c r="C28">
@@ -2174,22 +2542,22 @@
       <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="32">
         <v>46268</v>
       </c>
-      <c r="G28" s="32" t="s">
+      <c r="G28" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="36">
+      <c r="H28" s="32">
         <v>46275</v>
       </c>
-      <c r="I28" s="32" t="s">
+      <c r="I28" s="31" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.8">
-      <c r="A29" s="31"/>
-      <c r="B29" s="31"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="33"/>
       <c r="C29">
         <v>9.1999999999999993</v>
       </c>
@@ -2199,14 +2567,14 @@
       <c r="E29" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="36"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="31"/>
     </row>
     <row r="30" spans="1:9" ht="28.8">
-      <c r="A30" s="31"/>
-      <c r="B30" s="31"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="33"/>
       <c r="C30">
         <v>9.3000000000000007</v>
       </c>
@@ -2216,50 +2584,17 @@
       <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="36"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="31"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="31"/>
-      <c r="B31" s="31"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="F3:F7"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J3:J15"/>
-    <mergeCell ref="H3:H7"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="I3:I7"/>
-    <mergeCell ref="G3:G7"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:H18"/>
     <mergeCell ref="F19:F22"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
@@ -2270,8 +2605,613 @@
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="B19:B22"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J3:J15"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="G3:G7"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="A17:A26"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="F3:F7"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="H17:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B077794A-BDEC-4305-8F7F-332456871660}">
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="63.77734375" customWidth="1"/>
+    <col min="4" max="5" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="38" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" style="39" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.44140625" customWidth="1"/>
+    <col min="11" max="11" width="32.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+    </row>
+    <row r="2" spans="1:11" s="15" customFormat="1">
+      <c r="A2" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="63" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" s="63" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="43.2" customHeight="1">
+      <c r="A3" s="33">
+        <v>1</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="33">
+        <v>8</v>
+      </c>
+      <c r="E3" s="35">
+        <v>46254</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="28.8">
+      <c r="A4" s="33"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="48" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="72">
+      <c r="A5" s="33"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="48" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="33"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="33"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="28.8">
+      <c r="A8" s="33"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="K8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="43"/>
+      <c r="B9" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="47">
+        <v>46261</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+    </row>
+    <row r="10" spans="1:11" ht="57.6" customHeight="1">
+      <c r="A10" s="42">
+        <v>2</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="33">
+        <v>8</v>
+      </c>
+      <c r="E10" s="35">
+        <v>46261</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="43.2">
+      <c r="A11" s="42"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="42"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="28.8">
+      <c r="A13" s="42"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="57.6">
+      <c r="A14" s="42"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="42"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="42"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="57.6">
+      <c r="A17" s="42"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="15" customFormat="1">
+      <c r="A18" s="57"/>
+      <c r="B18" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="59">
+        <v>46268</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18" s="60"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+      <c r="K18" s="61"/>
+    </row>
+    <row r="19" spans="1:11" ht="86.4">
+      <c r="A19" s="33">
+        <v>3</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="33">
+        <v>5</v>
+      </c>
+      <c r="E19" s="35">
+        <v>46268</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="54" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="43.2">
+      <c r="A20" s="33"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="48" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="129.6">
+      <c r="A21" s="33"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="33"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="33"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="49" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="28.8">
+      <c r="A24" s="33"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="52" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="43"/>
+      <c r="B25" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="47">
+        <v>46275</v>
+      </c>
+      <c r="F25" s="45"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+    </row>
+    <row r="26" spans="1:11" ht="43.2" customHeight="1">
+      <c r="A26" s="33">
+        <v>4</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="33">
+        <v>8</v>
+      </c>
+      <c r="E26" s="35">
+        <v>46275</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="33"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="50" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="43.2">
+      <c r="A28" s="33"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="28.8">
+      <c r="A29" s="33"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="43.2">
+      <c r="A30" s="33"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="28.8">
+      <c r="A31" s="33"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="50" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="33"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="33"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="33"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="28.8">
+      <c r="A35" s="33"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="51" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" s="15" customFormat="1">
+      <c r="A36" s="57"/>
+      <c r="B36" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="59">
+        <v>46282</v>
+      </c>
+      <c r="F36" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36" s="62"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="E3:E8"/>
+    <mergeCell ref="E19:E24"/>
+    <mergeCell ref="E26:E35"/>
+    <mergeCell ref="E10:E17"/>
+    <mergeCell ref="D10:D17"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:C8"/>
+    <mergeCell ref="D3:D8"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="D26:D35"/>
+    <mergeCell ref="C26:C35"/>
+    <mergeCell ref="B26:B35"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A26:A35"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="D19:D24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="F10:F14"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="C10:C17"/>
+    <mergeCell ref="B10:B17"/>
+    <mergeCell ref="A10:A17"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="F6:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,14 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8E2665-D8D7-4719-A55A-FBF7991E0138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41AF736-7A6A-4AF4-9A10-88AD80BDA3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint Plan" sheetId="2" r:id="rId2"/>
-    <sheet name="Agile Sprint" sheetId="3" r:id="rId3"/>
+    <sheet name="Sprint Backlog" sheetId="3" r:id="rId3"/>
+    <sheet name="Product Backlog" sheetId="4" r:id="rId4"/>
+    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="164">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -578,16 +580,10 @@
     <t>Designated Team</t>
   </si>
   <si>
-    <t>Must</t>
-  </si>
-  <si>
     <t>Image Preprocessing &amp; Quality</t>
   </si>
   <si>
     <t>Questionnaire concern extraction</t>
-  </si>
-  <si>
-    <t>Should</t>
   </si>
   <si>
     <t>Concern Fusion</t>
@@ -629,9 +625,6 @@
   </si>
   <si>
     <t>Validate System with test dataset</t>
-  </si>
-  <si>
-    <t>MVP_SPRINT_PLAN</t>
   </si>
   <si>
     <r>
@@ -653,7 +646,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> customer,</t>
+      <t xml:space="preserve"> customer, </t>
     </r>
     <r>
       <rPr>
@@ -664,7 +657,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> I want to</t>
+      <t>I want to</t>
     </r>
     <r>
       <rPr>
@@ -674,7 +667,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> upload a picture of my skin , and after processing receive the detected skin concerns, </t>
+      <t xml:space="preserve"> answer a questionnaire, and after processing, receive my detected skin concerns, allergies, contraindications and skin properties (?),</t>
     </r>
     <r>
       <rPr>
@@ -695,10 +688,51 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> the system has a basis for formulation reccomendation(actives)</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve"> system understands my entire skin profile for formulation reccomendation ( bases)</t>
+    </r>
+  </si>
+  <si>
+    <t>Response to frontend</t>
+  </si>
+  <si>
+    <t>Return json containing detected skin concerns, allergies , and other relevant properties , to the front end.</t>
+  </si>
+  <si>
+    <t>Expected MVP showcase</t>
+  </si>
+  <si>
+    <t>Expected Skin concern detection showcase</t>
+  </si>
+  <si>
+    <t>Return Frontend Response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return response </t>
+  </si>
+  <si>
+    <t>As a User</t>
+  </si>
+  <si>
+    <t>I want to</t>
+  </si>
+  <si>
+    <t>So that</t>
+  </si>
+  <si>
+    <t>Logged in Customer</t>
+  </si>
+  <si>
+    <t>I can view my reccomendation page with the following fields:
+1. Hello "user_full_name"! 
+2. Skin analysis results : Primary Concerns : only those detected through selfie
+3. Reccomended for you : Active Ingredients: only those detected through selfie skin concerns.
+4. Reccomended for you: Why this formula: explained by LLM for selected actives detected through selfie skin concerns</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">upload a poor quality picture of my skin 
+and press on </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -708,7 +742,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>As a</t>
+      <t>submit</t>
     </r>
     <r>
       <rPr>
@@ -718,7 +752,32 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> customer, </t>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I am redirected to the selfie capture page with an error message saying :
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Your image is not valid. Take another image with better quality"</t>
+    </r>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">upload an acceptable quality picture of my skin 
+and press on </t>
     </r>
     <r>
       <rPr>
@@ -729,7 +788,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>I want to</t>
+      <t>submit</t>
     </r>
     <r>
       <rPr>
@@ -739,7 +798,21 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> answer a questionnaire, and after processing, receive my detected skin concerns, allergies, contraindications and skin properties (?),</t>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <t>Identify User ID &amp; Session ID</t>
+  </si>
+  <si>
+    <t>Product Backlog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptance Criteria </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">answer the provided questionnaire and press the </t>
     </r>
     <r>
       <rPr>
@@ -750,7 +823,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>so that</t>
+      <t>submit</t>
     </r>
     <r>
       <rPr>
@@ -760,20 +833,134 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> system understands my entire skin profile for formulation reccomendation ( bases)</t>
-    </r>
-  </si>
-  <si>
-    <t>Response to frontend</t>
-  </si>
-  <si>
-    <t>Return json containing detected skin concerns, allergies , and other relevant properties , to the front end.</t>
-  </si>
-  <si>
-    <t>Expected MVP showcase</t>
-  </si>
-  <si>
-    <t>Expected Skin concern detection showcase</t>
+      <t xml:space="preserve"> button</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view my reccomendation page with the following fields:
+1. Hello "user_full_name"! 
+2. Skin analysis results : Primary Concerns :  those detected through the combination of skin concerns from both image and questionnaire.
+3.Skin analysis results: Skin Type: detected through questionnaire answers.
+4. Skin analysis results: Allergens: detected through questionnaire answers.
+5. Skin analysis results: Sensitivity Level: detected through questionnaire input
+6. Reccomended for you: Base :
+selected through questionnaire answers.
+7. Reccomended for you : Active Ingredients: those detected through selfie and questionnaire skin concerns.
+8. Reccomended for you: Why this formula: explained by LLM for selected actives detected through selfie and questionnaire skin concerns</t>
+  </si>
+  <si>
+    <t>Wireframe Reference</t>
+  </si>
+  <si>
+    <t>1. Blurry image should be rejected.
+2. A low lighting image should be rejected.
+3. A low resolution image should be rejected
+4. A combination of any/all of the above three should be rejected
+4. A proper image should not be rejected</t>
+  </si>
+  <si>
+    <t>I can view my reccomendation page with the following fields:
+1. Hello "user_full_name"! 
+2. Skin analysis results : Primary Concerns : only those detected through selfie.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Detected skin concerns should be from the series:
+SC0001 - SC0019 &amp; SC1001 - SC1009
+2. If no skin concern is detected (perfectly fit skin) then Skin analysis results should show the following message:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Your skin looks perfect!".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. If the image contains one or multiple particular skin concerns that should all be shown in the Skin analysis results: Primary Concerns.
+4. No other skin concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images.</t>
+    </r>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>XXXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSHIRT SIZING </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add to cart 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button </t>
+    </r>
+  </si>
+  <si>
+    <t>todo/wip/done - states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a </t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>Scale : 1-5</t>
+  </si>
+  <si>
+    <t>Final Weightage</t>
+  </si>
+  <si>
+    <t>Ease</t>
   </si>
 </sst>
 </file>
@@ -822,7 +1009,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -880,6 +1067,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -957,7 +1156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1040,27 +1239,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1069,23 +1247,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1109,10 +1281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1141,9 +1310,56 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1933,20 +2149,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="15" t="s">
@@ -1987,10 +2203,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="58.8" customHeight="1">
-      <c r="A3" s="33">
+      <c r="A3" s="58">
         <v>1</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="58">
         <v>1</v>
       </c>
       <c r="C3">
@@ -2002,25 +2218,25 @@
       <c r="E3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="57">
         <v>46252</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="57">
         <v>46259</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="58" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="54.6" customHeight="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
       <c r="C4">
         <v>1.2</v>
       </c>
@@ -2030,15 +2246,15 @@
       <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="35"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
       <c r="C5">
         <v>1.3</v>
       </c>
@@ -2048,15 +2264,15 @@
       <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:12" ht="26.4" customHeight="1">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
       <c r="C6">
         <v>1.4</v>
       </c>
@@ -2066,15 +2282,15 @@
       <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:12" ht="72.599999999999994" customHeight="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
       <c r="C7">
         <v>1.5</v>
       </c>
@@ -2084,15 +2300,15 @@
       <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33">
+      <c r="A8" s="58"/>
+      <c r="B8" s="58">
         <v>2</v>
       </c>
       <c r="C8">
@@ -2104,23 +2320,23 @@
       <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="57">
         <v>46252</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="57">
         <v>46258</v>
       </c>
-      <c r="I8" s="33" t="s">
+      <c r="I8" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="33"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:12" ht="28.8">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
       <c r="C9">
         <v>2.2000000000000002</v>
       </c>
@@ -2130,15 +2346,15 @@
       <c r="E9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="35"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
       <c r="C10">
         <v>2.2999999999999998</v>
       </c>
@@ -2148,15 +2364,15 @@
       <c r="E10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:12" ht="28.8">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58">
         <v>3</v>
       </c>
       <c r="C11">
@@ -2168,15 +2384,15 @@
       <c r="E11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
       <c r="C12">
         <v>3.2</v>
       </c>
@@ -2198,11 +2414,11 @@
       <c r="I12" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="33"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:12" ht="28.8">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33">
+      <c r="A13" s="58"/>
+      <c r="B13" s="58">
         <v>4</v>
       </c>
       <c r="C13">
@@ -2226,11 +2442,11 @@
       <c r="I13" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="33"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:12" ht="28.8">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
       <c r="C14">
         <v>4.2</v>
       </c>
@@ -2252,10 +2468,10 @@
       <c r="I14" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="33"/>
+      <c r="J14" s="58"/>
     </row>
     <row r="15" spans="1:12" ht="28.8">
-      <c r="A15" s="33"/>
+      <c r="A15" s="58"/>
       <c r="B15" s="14">
         <v>9</v>
       </c>
@@ -2268,15 +2484,15 @@
       <c r="E15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="33"/>
+      <c r="J15" s="58"/>
       <c r="L15" t="s">
         <v>98</v>
       </c>
@@ -2285,10 +2501,10 @@
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="64"/>
       <c r="F16" s="26">
         <v>46198</v>
       </c>
@@ -2299,10 +2515,10 @@
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="86.4">
-      <c r="A17" s="33">
+      <c r="A17" s="58">
         <v>2</v>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="58">
         <v>5</v>
       </c>
       <c r="C17">
@@ -2317,19 +2533,19 @@
       <c r="F17" s="21">
         <v>46260</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="60">
         <v>46262</v>
       </c>
-      <c r="I17" s="31" t="s">
+      <c r="I17" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="58"/>
+      <c r="B18" s="58"/>
       <c r="C18">
         <v>5.2</v>
       </c>
@@ -2339,13 +2555,13 @@
       <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
     </row>
     <row r="19" spans="1:9" ht="86.4">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33">
+      <c r="A19" s="58"/>
+      <c r="B19" s="58">
         <v>6</v>
       </c>
       <c r="C19">
@@ -2357,22 +2573,22 @@
       <c r="E19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="60">
         <v>46260</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="60">
         <v>46267</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="61" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
       <c r="C20">
         <v>6.2</v>
       </c>
@@ -2382,14 +2598,14 @@
       <c r="E20" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
     </row>
     <row r="21" spans="1:9" ht="43.8" customHeight="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="58"/>
       <c r="C21" s="18">
         <v>6.3</v>
       </c>
@@ -2399,14 +2615,14 @@
       <c r="E21" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
     </row>
     <row r="22" spans="1:9" ht="28.8">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
       <c r="C22">
         <v>6.4</v>
       </c>
@@ -2416,14 +2632,14 @@
       <c r="E22" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
     </row>
     <row r="23" spans="1:9" ht="28.8">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33">
+      <c r="A23" s="58"/>
+      <c r="B23" s="58">
         <v>7</v>
       </c>
       <c r="C23">
@@ -2435,22 +2651,22 @@
       <c r="E23" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="60">
         <v>46260</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="60">
         <v>46267</v>
       </c>
-      <c r="I23" s="31" t="s">
+      <c r="I23" s="61" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
       <c r="C24">
         <v>7.2</v>
       </c>
@@ -2460,14 +2676,14 @@
       <c r="E24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
     </row>
     <row r="25" spans="1:9" ht="43.2">
-      <c r="A25" s="33"/>
-      <c r="B25" s="33">
+      <c r="A25" s="58"/>
+      <c r="B25" s="58">
         <v>8</v>
       </c>
       <c r="C25">
@@ -2479,22 +2695,22 @@
       <c r="E25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="63">
         <v>46260</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="60">
         <v>46267</v>
       </c>
-      <c r="I25" s="31" t="s">
+      <c r="I25" s="61" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28.8">
-      <c r="A26" s="33"/>
-      <c r="B26" s="33"/>
+      <c r="A26" s="58"/>
+      <c r="B26" s="58"/>
       <c r="C26">
         <v>8.1999999999999993</v>
       </c>
@@ -2504,10 +2720,10 @@
       <c r="E26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="24"/>
@@ -2527,10 +2743,10 @@
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="43.2">
-      <c r="A28" s="33">
+      <c r="A28" s="58">
         <v>3</v>
       </c>
-      <c r="B28" s="33">
+      <c r="B28" s="58">
         <v>9</v>
       </c>
       <c r="C28">
@@ -2542,22 +2758,22 @@
       <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="60">
         <v>46268</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="G28" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="60">
         <v>46275</v>
       </c>
-      <c r="I28" s="31" t="s">
+      <c r="I28" s="61" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.8">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
+      <c r="A29" s="58"/>
+      <c r="B29" s="58"/>
       <c r="C29">
         <v>9.1999999999999993</v>
       </c>
@@ -2567,14 +2783,14 @@
       <c r="E29" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="32"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="31"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="61"/>
     </row>
     <row r="30" spans="1:9" ht="28.8">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
+      <c r="A30" s="58"/>
+      <c r="B30" s="58"/>
       <c r="C30">
         <v>9.3000000000000007</v>
       </c>
@@ -2584,37 +2800,25 @@
       <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="32"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="31"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="61"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
+      <c r="A31" s="58"/>
+      <c r="B31" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J3:J15"/>
-    <mergeCell ref="H3:H7"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="I3:I7"/>
-    <mergeCell ref="G3:G7"/>
-    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="H17:H18"/>
     <mergeCell ref="A17:A26"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="F28:F30"/>
@@ -2626,18 +2830,30 @@
     <mergeCell ref="F25:F26"/>
     <mergeCell ref="G25:G26"/>
     <mergeCell ref="H25:H26"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J3:J15"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="G3:G7"/>
+    <mergeCell ref="A3:A15"/>
     <mergeCell ref="F3:F7"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B22"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="H17:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2646,571 +2862,1130 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B077794A-BDEC-4305-8F7F-332456871660}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="2" max="2" width="63.77734375" customWidth="1"/>
-    <col min="4" max="5" width="10.88671875" customWidth="1"/>
-    <col min="6" max="6" width="38" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.109375" style="39" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" customWidth="1"/>
-    <col min="11" max="11" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.77734375" customWidth="1"/>
+    <col min="5" max="5" width="65.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="38" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.109375" style="32" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.44140625" customWidth="1"/>
+    <col min="13" max="13" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="68"/>
+      <c r="B2" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+    </row>
+    <row r="3" spans="1:14" s="15" customFormat="1" ht="16.2" customHeight="1">
+      <c r="A3" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="43.2">
+      <c r="A4" s="33"/>
+      <c r="B4" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="33"/>
+      <c r="G4" s="70"/>
+      <c r="I4" s="39"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="33"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="33"/>
+      <c r="G5" s="70"/>
+      <c r="I5" s="39"/>
+    </row>
+    <row r="6" spans="1:14" ht="42" customHeight="1">
+      <c r="A6" s="33"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="33"/>
+      <c r="G6" s="70"/>
+      <c r="I6" s="39"/>
+    </row>
+    <row r="7" spans="1:14" ht="115.2">
+      <c r="A7" s="33">
+        <v>1</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="33">
+        <v>8</v>
+      </c>
+      <c r="G7" s="70">
+        <v>46254</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="39"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="33"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="33"/>
+      <c r="G8" s="70"/>
+      <c r="I8" s="39"/>
+    </row>
+    <row r="9" spans="1:14" ht="28.8">
+      <c r="A9" s="33"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="33"/>
+      <c r="G9" s="70"/>
+      <c r="I9" s="39"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="33"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" s="33"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="33"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="70"/>
+      <c r="I11" s="39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8">
+      <c r="A12" s="33"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="M12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="31"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" s="65" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="65"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="38">
+        <v>46261</v>
+      </c>
+      <c r="H15" s="36"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+    </row>
+    <row r="16" spans="1:14" ht="57.6" customHeight="1">
+      <c r="A16" s="33">
+        <v>2</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" s="67"/>
+      <c r="F16" s="33">
+        <v>8</v>
+      </c>
+      <c r="G16" s="70">
+        <v>46261</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="43.2">
+      <c r="A17" s="33"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="70"/>
+      <c r="I17" s="39" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="33"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="70"/>
+      <c r="I18" s="39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="28.8">
+      <c r="A19" s="33"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="70"/>
+      <c r="I19" s="39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="57.6">
+      <c r="A20" s="33"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="70"/>
+      <c r="I20" s="39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="33"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="39" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="33"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="70"/>
+      <c r="I22" s="43" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="57.6">
+      <c r="A23" s="33"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I23" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-    </row>
-    <row r="2" spans="1:11" s="15" customFormat="1">
-      <c r="A2" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" s="63" t="s">
+    </row>
+    <row r="24" spans="1:13" s="15" customFormat="1">
+      <c r="A24" s="47"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="48"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="49">
+        <v>46268</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="50"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+    </row>
+    <row r="25" spans="1:13" ht="86.4">
+      <c r="A25" s="33">
+        <v>3</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="67"/>
+      <c r="F25" s="33">
+        <v>5</v>
+      </c>
+      <c r="G25" s="70">
+        <v>46268</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="I25" s="45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="43.2">
+      <c r="A26" s="33"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="70"/>
+      <c r="I26" s="39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="129.6">
+      <c r="A27" s="33"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="33"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="70"/>
+      <c r="I28" s="39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="33"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="70"/>
+      <c r="I29" s="40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="28.8">
+      <c r="A30" s="33"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="70"/>
+      <c r="I30" s="43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="34"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="35"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="38">
+        <v>46275</v>
+      </c>
+      <c r="H31" s="36"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
+    </row>
+    <row r="32" spans="1:13" ht="43.2" customHeight="1">
+      <c r="A32" s="33">
+        <v>4</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="67" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="67"/>
+      <c r="F32" s="33">
+        <v>8</v>
+      </c>
+      <c r="G32" s="70">
+        <v>46275</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="33"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="70"/>
+      <c r="I33" s="41" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="43.2">
+      <c r="A34" s="33"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="I34" s="41" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="28.8">
+      <c r="A35" s="33"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="70"/>
+      <c r="I35" s="41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="43.2">
+      <c r="A36" s="33"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="41" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="28.8">
+      <c r="A37" s="33"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="70"/>
+      <c r="I37" s="41" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="33"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="70"/>
+      <c r="I38" s="41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="33"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="70"/>
+      <c r="I39" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="33"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="28.8">
+      <c r="A41" s="33"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="70"/>
+      <c r="I41" s="42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="15" customFormat="1">
+      <c r="A42" s="47"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42" s="48"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="49">
+        <v>46282</v>
+      </c>
+      <c r="H42" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="I42" s="52"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="51"/>
+      <c r="M42" s="51"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D13B384-1725-40B5-B0F7-A3A77A0F68B1}">
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="35.77734375" customWidth="1"/>
+    <col min="5" max="5" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="68"/>
+      <c r="B1" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D2" s="63" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="63" t="s">
-        <v>108</v>
-      </c>
-      <c r="I2" s="63" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="K2" s="63" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="43.2" customHeight="1">
+      <c r="H2" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="J2" s="53" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="115.2">
       <c r="A3" s="33">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="33">
+      <c r="B3" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <f>6-H3</f>
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <f>SQRT(G3*I3)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="230.4">
+      <c r="A4" s="33">
+        <v>2</v>
+      </c>
+      <c r="B4" s="72" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="66" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="316.8">
+      <c r="A5" s="33">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.8">
+      <c r="A6" s="33">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="33"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="33"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="33"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="31"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="31"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="100.8">
+      <c r="A13" s="33">
+        <v>2</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="67" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="33"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="67"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="33"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="67"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="33"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="67"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="33"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="67"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="33"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="67"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="33"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="67"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="33"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="67"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="86.4">
+      <c r="A22" s="33">
+        <v>3</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="67" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="33"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="67"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="67"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="33"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="67"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="33"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="67"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="33"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="67"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="86.4">
+      <c r="A29" s="33">
+        <v>4</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="67" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="33"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="67"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="33"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="67"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="33"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="67"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="33"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="67"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="33"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="67"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="33"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="67"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="33"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="67"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="33"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="67"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="33"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="67"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="47"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF11110B-B1A6-47E4-BCEC-C2B4CA62D5BE}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="74" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="74" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="74" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="74" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="74" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="74">
+        <v>1</v>
+      </c>
+      <c r="B3" s="74">
+        <v>2</v>
+      </c>
+      <c r="C3" s="74">
+        <f>A3+B3</f>
+        <v>3</v>
+      </c>
+      <c r="D3" s="74">
+        <f t="shared" ref="D3:G3" si="0">B3+C3</f>
+        <v>5</v>
+      </c>
+      <c r="E3" s="74">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E3" s="35">
-        <v>46254</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="28.8">
-      <c r="A4" s="33"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="72">
-      <c r="A5" s="33"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="48" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="33"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="33"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="28.8">
-      <c r="A8" s="33"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="K8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="43"/>
-      <c r="B9" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="47">
-        <v>46261</v>
-      </c>
-      <c r="F9" s="45"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-    </row>
-    <row r="10" spans="1:11" ht="57.6" customHeight="1">
-      <c r="A10" s="42">
-        <v>2</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="33">
-        <v>8</v>
-      </c>
-      <c r="E10" s="35">
-        <v>46261</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="43.2">
-      <c r="A11" s="42"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="48" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="42"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="48" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="28.8">
-      <c r="A13" s="42"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="48" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="57.6">
-      <c r="A14" s="42"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="42"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="G15" s="48" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="42"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="57.6">
-      <c r="A17" s="42"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" s="48" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="15" customFormat="1">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="59">
-        <v>46268</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>132</v>
-      </c>
-      <c r="G18" s="60"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-    </row>
-    <row r="19" spans="1:11" ht="86.4">
-      <c r="A19" s="33">
-        <v>3</v>
-      </c>
-      <c r="B19" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="33">
-        <v>5</v>
-      </c>
-      <c r="E19" s="35">
-        <v>46268</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="43.2">
-      <c r="A20" s="33"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="129.6">
-      <c r="A21" s="33"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="48" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="33"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="33"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="49" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="28.8">
-      <c r="A24" s="33"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="47">
-        <v>46275</v>
-      </c>
-      <c r="F25" s="45"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-    </row>
-    <row r="26" spans="1:11" ht="43.2" customHeight="1">
-      <c r="A26" s="33">
-        <v>4</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="C26" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="33">
-        <v>8</v>
-      </c>
-      <c r="E26" s="35">
-        <v>46275</v>
-      </c>
-      <c r="F26" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="G26" s="53" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="33"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="50" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="43.2">
-      <c r="A28" s="33"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" s="50" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="28.8">
-      <c r="A29" s="33"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="50" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="43.2">
-      <c r="A30" s="33"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="G30" s="50" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="28.8">
-      <c r="A31" s="33"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="50" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="33"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="50" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="33"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="50" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="33"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="G34" s="50" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="28.8">
-      <c r="A35" s="33"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="51" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" s="15" customFormat="1">
-      <c r="A36" s="57"/>
-      <c r="B36" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="59">
-        <v>46282</v>
-      </c>
-      <c r="F36" s="57" t="s">
-        <v>131</v>
-      </c>
-      <c r="G36" s="62"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
+      <c r="F3" s="75">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G3" s="76">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="E3:E8"/>
-    <mergeCell ref="E19:E24"/>
-    <mergeCell ref="E26:E35"/>
-    <mergeCell ref="E10:E17"/>
-    <mergeCell ref="D10:D17"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="C3:C8"/>
-    <mergeCell ref="D3:D8"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="D26:D35"/>
-    <mergeCell ref="C26:C35"/>
-    <mergeCell ref="B26:B35"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A26:A35"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="D19:D24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="F10:F14"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="C10:C17"/>
-    <mergeCell ref="B10:B17"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="F6:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41AF736-7A6A-4AF4-9A10-88AD80BDA3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228B6D37-7B31-4E3F-9D51-F31DB87662ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={233094A3-3D2A-436A-904F-A8273DA397F5}</author>
+    <author>tc={08942A35-04A9-4798-9BE7-511ACD0FC8D0}</author>
+  </authors>
+  <commentList>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{233094A3-3D2A-436A-904F-A8273DA397F5}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Should all skin concerns be listed when we are only addressing top n.</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="1" shapeId="0" xr:uid="{08942A35-04A9-4798-9BE7-511ACD0FC8D0}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Upto what limit can a user repeat the process? </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="171">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -837,7 +864,164 @@
     </r>
   </si>
   <si>
+    <t>Wireframe Reference</t>
+  </si>
+  <si>
+    <t>1. Blurry image should be rejected.
+2. A low lighting image should be rejected.
+3. A low resolution image should be rejected
+4. A combination of any/all of the above three should be rejected
+4. A proper image should not be rejected</t>
+  </si>
+  <si>
     <t>I can view my reccomendation page with the following fields:
+1. Hello "user_full_name"! 
+2. Skin analysis results : Primary Concerns : only those detected through selfie.</t>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>XXXL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSHIRT SIZING </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add to cart 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button </t>
+    </r>
+  </si>
+  <si>
+    <t>todo/wip/done - states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As a </t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>Scale : 1-5</t>
+  </si>
+  <si>
+    <t>Final Weightage</t>
+  </si>
+  <si>
+    <t>Ease</t>
+  </si>
+  <si>
+    <t>I can add the reccomended formulation to my shopping cart .</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Detected skin concerns should be from the series:
+SC0001 - SC0019 &amp; SC1001 - SC1009
+2. If no skin concern is detected (perfectly fit skin) then Skin analysis results should show the following message:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Your skin looks perfect!".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. If the image contains one or multiple particular skin concerns then, all of those should be shown in the Skin analysis results: Primary Concerns.
+4. No other skin concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Detected skin concerns should be from the series:
+SC0001-SC0019 , SC1001-SC1009 &amp;
+SC2001-SC2004.
+2. If no skin concern is detected(perfectly fit skin) then Skin analysis results should show the following message:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Your skin looks perfect!"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">3.If the image &amp; questionnaire contains one or multiple particular skin concerns then, all of those should be shown in the Skin analysis results: Primary Concerns.
+4.No other skins concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images and questionnaire.
+5. The total formulation must always weigh 100g total.
+6. The percentage of actives in formulation must be listed.
+7. The formulation explanation must correctly reflect the reason for choosing the actives and bases.
+8. Skin analysis result:Skin Type, Sensitive Level, Allergens: must exactly match the answers provided by the user via the questionnaire.
+9. The reccomended formula must not contain any harmful or unsuitable ingredients as per the answers provided by the user via the questionnaire.
+10. The actives and base comprising the reccomended formulation must be compatible with each other, and relevant to the user's skin concerns.
+11. The cost of actives and base comprising the reccomended formulation must be calculated with their accurate cost/g.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view my reccomendation page with the following fields:
 1. Hello "user_full_name"! 
 2. Skin analysis results : Primary Concerns :  those detected through the combination of skin concerns from both image and questionnaire.
 3.Skin analysis results: Skin Type: detected through questionnaire answers.
@@ -846,128 +1030,91 @@
 6. Reccomended for you: Base :
 selected through questionnaire answers.
 7. Reccomended for you : Active Ingredients: those detected through selfie and questionnaire skin concerns.
-8. Reccomended for you: Why this formula: explained by LLM for selected actives detected through selfie and questionnaire skin concerns</t>
-  </si>
-  <si>
-    <t>Wireframe Reference</t>
-  </si>
-  <si>
-    <t>1. Blurry image should be rejected.
-2. A low lighting image should be rejected.
-3. A low resolution image should be rejected
-4. A combination of any/all of the above three should be rejected
-4. A proper image should not be rejected</t>
-  </si>
-  <si>
-    <t>I can view my reccomendation page with the following fields:
-1. Hello "user_full_name"! 
-2. Skin analysis results : Primary Concerns : only those detected through selfie.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Detected skin concerns should be from the series:
-SC0001 - SC0019 &amp; SC1001 - SC1009
-2. If no skin concern is detected (perfectly fit skin) then Skin analysis results should show the following message:
+8. Reccomended for you: Why this formula: explained by LLM for selected actives detected through selfie and questionnaire skin concerns
+9.Reccomended for you: Cost: Total cost of the reccomended formulation. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[add in wireframes]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">I can repeat my AI skin analysis. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.Upon </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add to cart </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button being clicked, the reccomended formulation along with cost , should be saved for the user and added to their shopping cart, allowing them to buy later at their convenience. 
+2. The saved formulation in [1] must exactly match the reccomended formulation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">press the 
 </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Your skin looks perfect!".
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">[repeat reccomendation process] 
 </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3. If the image contains one or multiple particular skin concerns that should all be shown in the Skin analysis results: Primary Concerns.
-4. No other skin concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images.</t>
-    </r>
-  </si>
-  <si>
-    <t>XS</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>XXL</t>
-  </si>
-  <si>
-    <t>XXXL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSHIRT SIZING </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">press the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">add to cart 
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">button
 </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">button </t>
-    </r>
-  </si>
-  <si>
-    <t>todo/wip/done - states</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As a </t>
-  </si>
-  <si>
-    <t>Difficulty</t>
-  </si>
-  <si>
-    <t>Scale : 1-5</t>
-  </si>
-  <si>
-    <t>Final Weightage</t>
-  </si>
-  <si>
-    <t>Ease</t>
+  </si>
+  <si>
+    <t>Sprint Id</t>
+  </si>
+  <si>
+    <t>Story Point</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1002,6 +1149,20 @@
       <name val="Arial Unicode MS"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
@@ -1156,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1310,30 +1471,6 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1343,8 +1480,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1353,13 +1490,50 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1375,6 +1549,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1662,6 +1840,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E5" dT="2026-08-20T15:41:46.67" personId="{00000000-0000-0000-0000-000000000000}" id="{233094A3-3D2A-436A-904F-A8273DA397F5}">
+    <text>Should all skin concerns be listed when we are only addressing top n.</text>
+  </threadedComment>
+  <threadedComment ref="D7" dT="2026-08-20T15:38:33.80" personId="{00000000-0000-0000-0000-000000000000}" id="{08942A35-04A9-4798-9BE7-511ACD0FC8D0}">
+    <text xml:space="preserve">Upto what limit can a user repeat the process? </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G25"/>
@@ -2149,20 +2338,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="15" t="s">
@@ -2203,10 +2392,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="58.8" customHeight="1">
-      <c r="A3" s="58">
+      <c r="A3" s="71">
         <v>1</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="71">
         <v>1</v>
       </c>
       <c r="C3">
@@ -2218,25 +2407,25 @@
       <c r="E3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="57">
+      <c r="F3" s="74">
         <v>46252</v>
       </c>
-      <c r="G3" s="58" t="s">
+      <c r="G3" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="57">
+      <c r="H3" s="74">
         <v>46259</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="58" t="s">
+      <c r="J3" s="71" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="54.6" customHeight="1">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
+      <c r="A4" s="71"/>
+      <c r="B4" s="71"/>
       <c r="C4">
         <v>1.2</v>
       </c>
@@ -2246,15 +2435,15 @@
       <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="57"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A5" s="58"/>
-      <c r="B5" s="58"/>
+      <c r="A5" s="71"/>
+      <c r="B5" s="71"/>
       <c r="C5">
         <v>1.3</v>
       </c>
@@ -2264,15 +2453,15 @@
       <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
     </row>
     <row r="6" spans="1:12" ht="26.4" customHeight="1">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="71"/>
       <c r="C6">
         <v>1.4</v>
       </c>
@@ -2282,15 +2471,15 @@
       <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="57"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
     </row>
     <row r="7" spans="1:12" ht="72.599999999999994" customHeight="1">
-      <c r="A7" s="58"/>
-      <c r="B7" s="58"/>
+      <c r="A7" s="71"/>
+      <c r="B7" s="71"/>
       <c r="C7">
         <v>1.5</v>
       </c>
@@ -2300,15 +2489,15 @@
       <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="57"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="58"/>
-      <c r="B8" s="58">
+      <c r="A8" s="71"/>
+      <c r="B8" s="71">
         <v>2</v>
       </c>
       <c r="C8">
@@ -2320,23 +2509,23 @@
       <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="74">
         <v>46252</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="74">
         <v>46258</v>
       </c>
-      <c r="I8" s="58" t="s">
+      <c r="I8" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="58"/>
+      <c r="J8" s="71"/>
     </row>
     <row r="9" spans="1:12" ht="28.8">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="71"/>
       <c r="C9">
         <v>2.2000000000000002</v>
       </c>
@@ -2346,15 +2535,15 @@
       <c r="E9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="57"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
-      <c r="A10" s="58"/>
-      <c r="B10" s="58"/>
+      <c r="A10" s="71"/>
+      <c r="B10" s="71"/>
       <c r="C10">
         <v>2.2999999999999998</v>
       </c>
@@ -2364,15 +2553,15 @@
       <c r="E10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="57"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
     </row>
     <row r="11" spans="1:12" ht="28.8">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58">
+      <c r="A11" s="71"/>
+      <c r="B11" s="71">
         <v>3</v>
       </c>
       <c r="C11">
@@ -2384,15 +2573,15 @@
       <c r="E11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="57"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
-      <c r="A12" s="58"/>
-      <c r="B12" s="58"/>
+      <c r="A12" s="71"/>
+      <c r="B12" s="71"/>
       <c r="C12">
         <v>3.2</v>
       </c>
@@ -2414,11 +2603,11 @@
       <c r="I12" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="58"/>
+      <c r="J12" s="71"/>
     </row>
     <row r="13" spans="1:12" ht="28.8">
-      <c r="A13" s="58"/>
-      <c r="B13" s="58">
+      <c r="A13" s="71"/>
+      <c r="B13" s="71">
         <v>4</v>
       </c>
       <c r="C13">
@@ -2442,11 +2631,11 @@
       <c r="I13" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="58"/>
+      <c r="J13" s="71"/>
     </row>
     <row r="14" spans="1:12" ht="28.8">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
       <c r="C14">
         <v>4.2</v>
       </c>
@@ -2468,10 +2657,10 @@
       <c r="I14" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="58"/>
+      <c r="J14" s="71"/>
     </row>
     <row r="15" spans="1:12" ht="28.8">
-      <c r="A15" s="58"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="14">
         <v>9</v>
       </c>
@@ -2484,15 +2673,15 @@
       <c r="E15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="57" t="s">
+      <c r="F15" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="58"/>
+      <c r="J15" s="71"/>
       <c r="L15" t="s">
         <v>98</v>
       </c>
@@ -2501,10 +2690,10 @@
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="64" t="s">
+      <c r="D16" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="64"/>
+      <c r="E16" s="75"/>
       <c r="F16" s="26">
         <v>46198</v>
       </c>
@@ -2515,10 +2704,10 @@
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="86.4">
-      <c r="A17" s="58">
+      <c r="A17" s="71">
         <v>2</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="71">
         <v>5</v>
       </c>
       <c r="C17">
@@ -2533,19 +2722,19 @@
       <c r="F17" s="21">
         <v>46260</v>
       </c>
-      <c r="G17" s="61" t="s">
+      <c r="G17" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="60">
+      <c r="H17" s="70">
         <v>46262</v>
       </c>
-      <c r="I17" s="61" t="s">
+      <c r="I17" s="69" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8">
-      <c r="A18" s="58"/>
-      <c r="B18" s="58"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
       <c r="C18">
         <v>5.2</v>
       </c>
@@ -2555,13 +2744,13 @@
       <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
     </row>
     <row r="19" spans="1:9" ht="86.4">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58">
+      <c r="A19" s="71"/>
+      <c r="B19" s="71">
         <v>6</v>
       </c>
       <c r="C19">
@@ -2573,22 +2762,22 @@
       <c r="E19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="60">
+      <c r="F19" s="70">
         <v>46260</v>
       </c>
-      <c r="G19" s="61" t="s">
+      <c r="G19" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="60">
+      <c r="H19" s="70">
         <v>46267</v>
       </c>
-      <c r="I19" s="61" t="s">
+      <c r="I19" s="69" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8">
-      <c r="A20" s="58"/>
-      <c r="B20" s="58"/>
+      <c r="A20" s="71"/>
+      <c r="B20" s="71"/>
       <c r="C20">
         <v>6.2</v>
       </c>
@@ -2598,14 +2787,14 @@
       <c r="E20" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
     </row>
     <row r="21" spans="1:9" ht="43.8" customHeight="1">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
+      <c r="A21" s="71"/>
+      <c r="B21" s="71"/>
       <c r="C21" s="18">
         <v>6.3</v>
       </c>
@@ -2615,14 +2804,14 @@
       <c r="E21" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
     </row>
     <row r="22" spans="1:9" ht="28.8">
-      <c r="A22" s="58"/>
-      <c r="B22" s="58"/>
+      <c r="A22" s="71"/>
+      <c r="B22" s="71"/>
       <c r="C22">
         <v>6.4</v>
       </c>
@@ -2632,14 +2821,14 @@
       <c r="E22" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
     </row>
     <row r="23" spans="1:9" ht="28.8">
-      <c r="A23" s="58"/>
-      <c r="B23" s="58">
+      <c r="A23" s="71"/>
+      <c r="B23" s="71">
         <v>7</v>
       </c>
       <c r="C23">
@@ -2651,22 +2840,22 @@
       <c r="E23" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="60">
+      <c r="F23" s="70">
         <v>46260</v>
       </c>
-      <c r="G23" s="61" t="s">
+      <c r="G23" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="60">
+      <c r="H23" s="70">
         <v>46267</v>
       </c>
-      <c r="I23" s="61" t="s">
+      <c r="I23" s="69" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="58"/>
-      <c r="B24" s="58"/>
+      <c r="A24" s="71"/>
+      <c r="B24" s="71"/>
       <c r="C24">
         <v>7.2</v>
       </c>
@@ -2676,14 +2865,14 @@
       <c r="E24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
     </row>
     <row r="25" spans="1:9" ht="43.2">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58">
+      <c r="A25" s="71"/>
+      <c r="B25" s="71">
         <v>8</v>
       </c>
       <c r="C25">
@@ -2695,22 +2884,22 @@
       <c r="E25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="63">
+      <c r="F25" s="72">
         <v>46260</v>
       </c>
-      <c r="G25" s="61" t="s">
+      <c r="G25" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="60">
+      <c r="H25" s="70">
         <v>46267</v>
       </c>
-      <c r="I25" s="61" t="s">
+      <c r="I25" s="69" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28.8">
-      <c r="A26" s="58"/>
-      <c r="B26" s="58"/>
+      <c r="A26" s="71"/>
+      <c r="B26" s="71"/>
       <c r="C26">
         <v>8.1999999999999993</v>
       </c>
@@ -2720,10 +2909,10 @@
       <c r="E26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="63"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="24"/>
@@ -2743,10 +2932,10 @@
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="43.2">
-      <c r="A28" s="58">
+      <c r="A28" s="71">
         <v>3</v>
       </c>
-      <c r="B28" s="58">
+      <c r="B28" s="71">
         <v>9</v>
       </c>
       <c r="C28">
@@ -2758,22 +2947,22 @@
       <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="60">
+      <c r="F28" s="70">
         <v>46268</v>
       </c>
-      <c r="G28" s="61" t="s">
+      <c r="G28" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="60">
+      <c r="H28" s="70">
         <v>46275</v>
       </c>
-      <c r="I28" s="61" t="s">
+      <c r="I28" s="69" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.8">
-      <c r="A29" s="58"/>
-      <c r="B29" s="58"/>
+      <c r="A29" s="71"/>
+      <c r="B29" s="71"/>
       <c r="C29">
         <v>9.1999999999999993</v>
       </c>
@@ -2783,14 +2972,14 @@
       <c r="E29" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="60"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="61"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="69"/>
     </row>
     <row r="30" spans="1:9" ht="28.8">
-      <c r="A30" s="58"/>
-      <c r="B30" s="58"/>
+      <c r="A30" s="71"/>
+      <c r="B30" s="71"/>
       <c r="C30">
         <v>9.3000000000000007</v>
       </c>
@@ -2800,25 +2989,36 @@
       <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="60"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="61"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="69"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="58"/>
-      <c r="B31" s="58"/>
+      <c r="A31" s="71"/>
+      <c r="B31" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="J3:J15"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="G3:G7"/>
+    <mergeCell ref="A3:A15"/>
+    <mergeCell ref="F3:F7"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A17:A26"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="F28:F30"/>
@@ -2831,29 +3031,18 @@
     <mergeCell ref="G25:G26"/>
     <mergeCell ref="H25:H26"/>
     <mergeCell ref="G17:G18"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="J3:J15"/>
-    <mergeCell ref="H3:H7"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="I3:I7"/>
-    <mergeCell ref="G3:G7"/>
-    <mergeCell ref="A3:A15"/>
-    <mergeCell ref="F3:F7"/>
-    <mergeCell ref="F15:H15"/>
     <mergeCell ref="F19:F22"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="H17:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2862,7 +3051,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B077794A-BDEC-4305-8F7F-332456871660}">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.44140625" customWidth="1"/>
@@ -2877,43 +3066,44 @@
     <col min="11" max="11" width="7.44140625" customWidth="1"/>
     <col min="13" max="13" width="32.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:22">
+      <c r="A1" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="69"/>
-      <c r="M1" s="69"/>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="68"/>
-      <c r="B2" s="59" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="60"/>
+      <c r="B2" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-    </row>
-    <row r="3" spans="1:14" s="15" customFormat="1" ht="16.2" customHeight="1">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+    </row>
+    <row r="3" spans="1:22" s="15" customFormat="1" ht="16.2" customHeight="1">
       <c r="A3" s="53" t="s">
         <v>104</v>
       </c>
@@ -2954,59 +3144,77 @@
         <v>97</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="43.2">
+        <v>156</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="43.2">
       <c r="A4" s="33"/>
       <c r="B4" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="58" t="s">
         <v>137</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="33"/>
-      <c r="G4" s="70"/>
+      <c r="G4" s="62"/>
       <c r="I4" s="39"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:22">
       <c r="A5" s="33"/>
       <c r="B5" s="14"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="39" t="s">
         <v>85</v>
       </c>
       <c r="F5" s="33"/>
-      <c r="G5" s="70"/>
+      <c r="G5" s="62"/>
       <c r="I5" s="39"/>
     </row>
-    <row r="6" spans="1:14" ht="42" customHeight="1">
+    <row r="6" spans="1:22" ht="42" customHeight="1">
       <c r="A6" s="33"/>
       <c r="B6" s="14"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="39" t="s">
         <v>87</v>
       </c>
       <c r="F6" s="33"/>
-      <c r="G6" s="70"/>
+      <c r="G6" s="62"/>
       <c r="I6" s="39"/>
     </row>
-    <row r="7" spans="1:14" ht="115.2">
+    <row r="7" spans="1:22" ht="115.2">
       <c r="A7" s="33">
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="58" t="s">
         <v>139</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -3018,7 +3226,7 @@
       <c r="F7" s="33">
         <v>8</v>
       </c>
-      <c r="G7" s="70">
+      <c r="G7" s="62">
         <v>46254</v>
       </c>
       <c r="H7" s="33" t="s">
@@ -3026,7 +3234,7 @@
       </c>
       <c r="I7" s="39"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:22">
       <c r="A8" s="33"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -3035,10 +3243,10 @@
         <v>85</v>
       </c>
       <c r="F8" s="33"/>
-      <c r="G8" s="70"/>
+      <c r="G8" s="62"/>
       <c r="I8" s="39"/>
     </row>
-    <row r="9" spans="1:14" ht="28.8">
+    <row r="9" spans="1:22" ht="28.8">
       <c r="A9" s="33"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -3047,10 +3255,10 @@
         <v>87</v>
       </c>
       <c r="F9" s="33"/>
-      <c r="G9" s="70"/>
+      <c r="G9" s="62"/>
       <c r="I9" s="39"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:22">
       <c r="A10" s="33"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -3059,7 +3267,7 @@
         <v>140</v>
       </c>
       <c r="F10" s="33"/>
-      <c r="G10" s="70"/>
+      <c r="G10" s="62"/>
       <c r="H10" s="33" t="s">
         <v>56</v>
       </c>
@@ -3067,26 +3275,26 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:22">
       <c r="A11" s="33"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="33"/>
-      <c r="G11" s="70"/>
+      <c r="G11" s="62"/>
       <c r="I11" s="39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28.8">
+    <row r="12" spans="1:22" ht="28.8">
       <c r="A12" s="33"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="33"/>
-      <c r="G12" s="70"/>
+      <c r="G12" s="62"/>
       <c r="H12" s="14" t="s">
         <v>118</v>
       </c>
@@ -3097,7 +3305,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:22">
       <c r="A13" s="14"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -3107,11 +3315,11 @@
       <c r="H13" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="I13" s="65" t="s">
+      <c r="I13" s="57" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:22">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -3120,9 +3328,9 @@
       <c r="F14" s="14"/>
       <c r="G14" s="22"/>
       <c r="H14" s="14"/>
-      <c r="I14" s="65"/>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="I14" s="57"/>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
@@ -3141,20 +3349,20 @@
       <c r="L15" s="37"/>
       <c r="M15" s="37"/>
     </row>
-    <row r="16" spans="1:14" ht="57.6" customHeight="1">
+    <row r="16" spans="1:22" ht="57.6" customHeight="1">
       <c r="A16" s="33">
         <v>2</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="67"/>
+      <c r="E16" s="59"/>
       <c r="F16" s="33">
         <v>8</v>
       </c>
-      <c r="G16" s="70">
+      <c r="G16" s="62">
         <v>46261</v>
       </c>
       <c r="H16" s="33" t="s">
@@ -3168,10 +3376,10 @@
       <c r="A17" s="33"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
       <c r="F17" s="33"/>
-      <c r="G17" s="70"/>
+      <c r="G17" s="62"/>
       <c r="I17" s="39" t="s">
         <v>50</v>
       </c>
@@ -3180,10 +3388,10 @@
       <c r="A18" s="33"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
       <c r="F18" s="33"/>
-      <c r="G18" s="70"/>
+      <c r="G18" s="62"/>
       <c r="I18" s="39" t="s">
         <v>51</v>
       </c>
@@ -3192,10 +3400,10 @@
       <c r="A19" s="33"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
       <c r="F19" s="33"/>
-      <c r="G19" s="70"/>
+      <c r="G19" s="62"/>
       <c r="I19" s="39" t="s">
         <v>52</v>
       </c>
@@ -3204,10 +3412,10 @@
       <c r="A20" s="33"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
       <c r="F20" s="33"/>
-      <c r="G20" s="70"/>
+      <c r="G20" s="62"/>
       <c r="I20" s="39" t="s">
         <v>53</v>
       </c>
@@ -3216,10 +3424,10 @@
       <c r="A21" s="33"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
       <c r="F21" s="33"/>
-      <c r="G21" s="70"/>
+      <c r="G21" s="62"/>
       <c r="H21" s="33" t="s">
         <v>110</v>
       </c>
@@ -3231,10 +3439,10 @@
       <c r="A22" s="33"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
       <c r="F22" s="33"/>
-      <c r="G22" s="70"/>
+      <c r="G22" s="62"/>
       <c r="I22" s="43" t="s">
         <v>57</v>
       </c>
@@ -3243,10 +3451,10 @@
       <c r="A23" s="33"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
       <c r="F23" s="33"/>
-      <c r="G23" s="70"/>
+      <c r="G23" s="62"/>
       <c r="H23" s="14" t="s">
         <v>125</v>
       </c>
@@ -3281,14 +3489,14 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="E25" s="67"/>
+      <c r="E25" s="59"/>
       <c r="F25" s="33">
         <v>5</v>
       </c>
-      <c r="G25" s="70">
+      <c r="G25" s="62">
         <v>46268</v>
       </c>
       <c r="H25" s="33" t="s">
@@ -3302,10 +3510,10 @@
       <c r="A26" s="33"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
       <c r="F26" s="33"/>
-      <c r="G26" s="70"/>
+      <c r="G26" s="62"/>
       <c r="I26" s="39" t="s">
         <v>61</v>
       </c>
@@ -3314,10 +3522,10 @@
       <c r="A27" s="33"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
       <c r="F27" s="33"/>
-      <c r="G27" s="70"/>
+      <c r="G27" s="62"/>
       <c r="H27" s="33" t="s">
         <v>37</v>
       </c>
@@ -3329,10 +3537,10 @@
       <c r="A28" s="33"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
       <c r="F28" s="33"/>
-      <c r="G28" s="70"/>
+      <c r="G28" s="62"/>
       <c r="I28" s="39" t="s">
         <v>62</v>
       </c>
@@ -3341,10 +3549,10 @@
       <c r="A29" s="33"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
       <c r="F29" s="33"/>
-      <c r="G29" s="70"/>
+      <c r="G29" s="62"/>
       <c r="I29" s="40" t="s">
         <v>81</v>
       </c>
@@ -3353,10 +3561,10 @@
       <c r="A30" s="33"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
       <c r="F30" s="33"/>
-      <c r="G30" s="70"/>
+      <c r="G30" s="62"/>
       <c r="I30" s="43" t="s">
         <v>63</v>
       </c>
@@ -3386,14 +3594,14 @@
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="67"/>
+      <c r="E32" s="59"/>
       <c r="F32" s="33">
         <v>8</v>
       </c>
-      <c r="G32" s="70">
+      <c r="G32" s="62">
         <v>46275</v>
       </c>
       <c r="H32" s="33" t="s">
@@ -3407,10 +3615,10 @@
       <c r="A33" s="33"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
       <c r="F33" s="33"/>
-      <c r="G33" s="70"/>
+      <c r="G33" s="62"/>
       <c r="I33" s="41" t="s">
         <v>66</v>
       </c>
@@ -3419,10 +3627,10 @@
       <c r="A34" s="33"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
       <c r="F34" s="33"/>
-      <c r="G34" s="70"/>
+      <c r="G34" s="62"/>
       <c r="H34" s="33" t="s">
         <v>115</v>
       </c>
@@ -3434,10 +3642,10 @@
       <c r="A35" s="33"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
-      <c r="D35" s="67"/>
-      <c r="E35" s="67"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
       <c r="F35" s="33"/>
-      <c r="G35" s="70"/>
+      <c r="G35" s="62"/>
       <c r="I35" s="41" t="s">
         <v>73</v>
       </c>
@@ -3446,10 +3654,10 @@
       <c r="A36" s="33"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
       <c r="F36" s="33"/>
-      <c r="G36" s="70"/>
+      <c r="G36" s="62"/>
       <c r="H36" s="33" t="s">
         <v>29</v>
       </c>
@@ -3461,10 +3669,10 @@
       <c r="A37" s="33"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
       <c r="F37" s="33"/>
-      <c r="G37" s="70"/>
+      <c r="G37" s="62"/>
       <c r="I37" s="41" t="s">
         <v>75</v>
       </c>
@@ -3473,10 +3681,10 @@
       <c r="A38" s="33"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
       <c r="F38" s="33"/>
-      <c r="G38" s="70"/>
+      <c r="G38" s="62"/>
       <c r="I38" s="41" t="s">
         <v>76</v>
       </c>
@@ -3485,10 +3693,10 @@
       <c r="A39" s="33"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
       <c r="F39" s="33"/>
-      <c r="G39" s="70"/>
+      <c r="G39" s="62"/>
       <c r="I39" s="41" t="s">
         <v>77</v>
       </c>
@@ -3497,10 +3705,10 @@
       <c r="A40" s="33"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
       <c r="F40" s="33"/>
-      <c r="G40" s="70"/>
+      <c r="G40" s="62"/>
       <c r="H40" s="33" t="s">
         <v>121</v>
       </c>
@@ -3512,10 +3720,10 @@
       <c r="A41" s="33"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
       <c r="F41" s="33"/>
-      <c r="G41" s="70"/>
+      <c r="G41" s="62"/>
       <c r="I41" s="42" t="s">
         <v>123</v>
       </c>
@@ -3550,15 +3758,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D13B384-1725-40B5-B0F7-A3A77A0F68B1}">
-  <dimension ref="A1:J39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D13B384-1725-40B5-B0F7-A3A77A0F68B1}">
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="35.77734375" customWidth="1"/>
-    <col min="5" max="5" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.109375" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5546875" bestFit="1" customWidth="1"/>
@@ -3567,29 +3775,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="68"/>
-      <c r="B1" s="59" t="s">
+      <c r="A1" s="60"/>
+      <c r="B1" s="68" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
       <c r="G1" s="56" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H1" s="56" t="s">
-        <v>161</v>
-      </c>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
+        <v>159</v>
+      </c>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="53" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C2" s="53" t="s">
         <v>132</v>
@@ -3601,36 +3809,36 @@
         <v>142</v>
       </c>
       <c r="F2" s="53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G2" s="53" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="J2" s="53" t="s">
         <v>160</v>
-      </c>
-      <c r="I2" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="J2" s="53" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="115.2">
       <c r="A3" s="33">
         <v>1</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="66" t="s">
-        <v>146</v>
+      <c r="E3" s="58" t="s">
+        <v>145</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3651,50 +3859,67 @@
       <c r="A4" s="33">
         <v>2</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="58" t="s">
         <v>139</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E4" s="66" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="316.8">
-      <c r="A5" s="33">
+        <v>146</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="13" customFormat="1" ht="409.2" customHeight="1">
+      <c r="A5" s="59">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="63" t="s">
         <v>143</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="28.8">
+        <v>165</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="86.4">
       <c r="A6" s="33">
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="66" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="33"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="1"/>
+      <c r="C6" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="86.4">
+      <c r="A7" s="77">
+        <v>5</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="81"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="33"/>
@@ -3720,199 +3945,12 @@
       <c r="C11" s="14"/>
       <c r="D11" s="31"/>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="35" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="100.8">
-      <c r="A13" s="33">
-        <v>2</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="67" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="33"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="67"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="33"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="67"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="33"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="67"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="33"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="67"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="33"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="67"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="33"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="67"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="33"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="67"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="48" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="86.4">
-      <c r="A22" s="33">
-        <v>3</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="67" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="33"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="67"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="33"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="67"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="33"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="67"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="33"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="67"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="67"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="35" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="86.4">
-      <c r="A29" s="33">
-        <v>4</v>
-      </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="67" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="33"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="67"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="33"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="67"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="33"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="67"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="33"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="67"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="33"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="67"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="33"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="67"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="33"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="67"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="33"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="67"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="33"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="67"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="47"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="48" t="s">
-        <v>117</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3922,63 +3960,63 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="73" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="A1" s="76" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="D2" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="E2" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="F2" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="G2" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="74" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" s="74" t="s">
-        <v>155</v>
-      </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="74">
+      <c r="A3" s="65">
         <v>1</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="65">
         <v>2</v>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="65">
         <f>A3+B3</f>
         <v>3</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="65">
         <f t="shared" ref="D3:G3" si="0">B3+C3</f>
         <v>5</v>
       </c>
-      <c r="E3" s="74">
+      <c r="E3" s="65">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F3" s="75">
+      <c r="F3" s="66">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="G3" s="76">
+      <c r="G3" s="67">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228B6D37-7B31-4E3F-9D51-F31DB87662ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E048262-4033-466D-81BD-28D4485F8381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint Plan" sheetId="2" r:id="rId2"/>
     <sheet name="Sprint Backlog" sheetId="3" r:id="rId3"/>
-    <sheet name="Product Backlog" sheetId="4" r:id="rId4"/>
-    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId4"/>
+    <sheet name="Product Backlog" sheetId="4" r:id="rId5"/>
+    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,6 +33,35 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={7A857420-A344-4A5B-B5A5-8DCCE0278C3D}</author>
+    <author>tc={62DF36E2-EA7C-49D8-8C48-B87BDEFAC85F}</author>
+  </authors>
+  <commentList>
+    <comment ref="D55" authorId="0" shapeId="0" xr:uid="{7A857420-A344-4A5B-B5A5-8DCCE0278C3D}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Do we display all concerns or just top n 
+</t>
+      </text>
+    </comment>
+    <comment ref="D153" authorId="1" shapeId="0" xr:uid="{62DF36E2-EA7C-49D8-8C48-B87BDEFAC85F}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Do we need for MVP?
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={233094A3-3D2A-436A-904F-A8273DA397F5}</author>
@@ -59,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="425">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -737,9 +767,6 @@
     <t xml:space="preserve">return response </t>
   </si>
   <si>
-    <t>As a User</t>
-  </si>
-  <si>
     <t>I want to</t>
   </si>
   <si>
@@ -1104,17 +1131,835 @@
     </r>
   </si>
   <si>
-    <t>Sprint Id</t>
-  </si>
-  <si>
     <t>Story Point</t>
+  </si>
+  <si>
+    <t>User Story Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Story Id </t>
+  </si>
+  <si>
+    <t>User Story ID</t>
+  </si>
+  <si>
+    <t>Story points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receive image from frontend </t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Validate Image filetype</t>
+  </si>
+  <si>
+    <t>Validate image can be decoded/read</t>
+  </si>
+  <si>
+    <t>Validate image resolution</t>
+  </si>
+  <si>
+    <t>Calculate Image sharpness score</t>
+  </si>
+  <si>
+    <t>Define blur rejection threshold</t>
+  </si>
+  <si>
+    <t>Calculate image brightness/lighting score</t>
+  </si>
+  <si>
+    <t>Define low light rejection threshold</t>
+  </si>
+  <si>
+    <t>Define minimum resolution threshold</t>
+  </si>
+  <si>
+    <t>Combine image quality checks into a single validation test</t>
+  </si>
+  <si>
+    <t>Implement blurry image rejection</t>
+  </si>
+  <si>
+    <t>Implement low light rejection</t>
+  </si>
+  <si>
+    <t>Implement low resolution rejection</t>
+  </si>
+  <si>
+    <t>Implement combined-quality rejection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implement valid-image acceptance </t>
+  </si>
+  <si>
+    <t>Define image validation response schema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return validation response to frontend </t>
+  </si>
+  <si>
+    <t>Map invalid image-response to frontend error message</t>
+  </si>
+  <si>
+    <t>Redirect user to selfie capture page after rejection</t>
+  </si>
+  <si>
+    <t>Display "Your image is not valid. Take another image with better quality"</t>
+  </si>
+  <si>
+    <t>Normalize accepted image</t>
+  </si>
+  <si>
+    <t>Resize Image for Vission LLM input</t>
+  </si>
+  <si>
+    <t>Apply required image format conversion</t>
+  </si>
+  <si>
+    <t>Validate preprocessing output</t>
+  </si>
+  <si>
+    <t>Store/forward processed image to vision LLM</t>
+  </si>
+  <si>
+    <t>Define Vision LLM Output JSON</t>
+  </si>
+  <si>
+    <t>Define image analysis instructions</t>
+  </si>
+  <si>
+    <t>Define Vision LLM System Prompt</t>
+  </si>
+  <si>
+    <t>Define skin concern detection rules</t>
+  </si>
+  <si>
+    <t>Restrict model output to supported skin concern IDS</t>
+  </si>
+  <si>
+    <t>Define "no concern" behaviors</t>
+  </si>
+  <si>
+    <t>Add hallucination prevention instructions</t>
+  </si>
+  <si>
+    <t>Add JSON only response instruction</t>
+  </si>
+  <si>
+    <t>Implement Vision LLM API Call</t>
+  </si>
+  <si>
+    <t>Pass preprocessed image to Vision LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate Vision LLM response against JSON Schema </t>
+  </si>
+  <si>
+    <t>Handle malformed LLM response</t>
+  </si>
+  <si>
+    <t>Handle LLM timeout/API failure</t>
+  </si>
+  <si>
+    <t>Store/audit Vision LLM request and response</t>
+  </si>
+  <si>
+    <t>Validate returned concern IDs against SC0001-SC0019</t>
+  </si>
+  <si>
+    <t>Validate returned concern IDs against SC1001-SC1009</t>
+  </si>
+  <si>
+    <t>Remove unsupported concern IDs</t>
+  </si>
+  <si>
+    <t>Handle duplicate concern IDs</t>
+  </si>
+  <si>
+    <t>Handle empty concern list</t>
+  </si>
+  <si>
+    <t>Define Skin analysis response schema</t>
+  </si>
+  <si>
+    <t>Serialize detected concerns to JSON</t>
+  </si>
+  <si>
+    <t>Return detected concerns to frontend</t>
+  </si>
+  <si>
+    <t>Return user full name</t>
+  </si>
+  <si>
+    <t>Return "Your skin looks perfect!" when no concerns exist</t>
+  </si>
+  <si>
+    <t>Return detected concerns under Primary Concerns</t>
+  </si>
+  <si>
+    <t>Map concern IDs to display names</t>
+  </si>
+  <si>
+    <t>Display primary concerns on reccomendation page</t>
+  </si>
+  <si>
+    <t>Display perfect skin message when concern list is empty</t>
+  </si>
+  <si>
+    <t>Verify only model-detected concerns are displayed</t>
+  </si>
+  <si>
+    <t>Define Questionnaire concern extraction JSON schema</t>
+  </si>
+  <si>
+    <t>Define skin concern field</t>
+  </si>
+  <si>
+    <t>Define skin type field</t>
+  </si>
+  <si>
+    <t>Define sensitivity field</t>
+  </si>
+  <si>
+    <t>Define Allergen field</t>
+  </si>
+  <si>
+    <t>Define base preference field</t>
+  </si>
+  <si>
+    <t>Define allowed values for each field</t>
+  </si>
+  <si>
+    <t>Define Questionnaire concern extraction prompt</t>
+  </si>
+  <si>
+    <t>Map questionnaire answers into prompt variables</t>
+  </si>
+  <si>
+    <t>Define concern extraction rules</t>
+  </si>
+  <si>
+    <t>Define allergen extraction rules</t>
+  </si>
+  <si>
+    <t>Define skin type extraction rules</t>
+  </si>
+  <si>
+    <t>Define sensitivity extraction rules</t>
+  </si>
+  <si>
+    <t>Add JSON only output instruction</t>
+  </si>
+  <si>
+    <t>Implement Questionnaire LLM call</t>
+  </si>
+  <si>
+    <t>Validate questionnaire response schema</t>
+  </si>
+  <si>
+    <t>Handle LLM failure</t>
+  </si>
+  <si>
+    <t>Store/audit questionnaire extraction event</t>
+  </si>
+  <si>
+    <t>Define active-to-exclusion relationsip table</t>
+  </si>
+  <si>
+    <t>Write database migration</t>
+  </si>
+  <si>
+    <t>Seed allergen/exclusion master data</t>
+  </si>
+  <si>
+    <t>Validate seed data</t>
+  </si>
+  <si>
+    <t>Map questionnaire allergen values to master allergen IDs</t>
+  </si>
+  <si>
+    <t>Define concern-fusion input schema</t>
+  </si>
+  <si>
+    <t>Normalize concern IDs</t>
+  </si>
+  <si>
+    <t>Merge questionnaire and image concern lists</t>
+  </si>
+  <si>
+    <t>Remove duplicate concerns</t>
+  </si>
+  <si>
+    <t>Validate merged concerns</t>
+  </si>
+  <si>
+    <t>Store final fused concern list</t>
+  </si>
+  <si>
+    <t>Define empty-concern behaviour</t>
+  </si>
+  <si>
+    <t>Define vector-search input</t>
+  </si>
+  <si>
+    <t>Implement vector DB candidate retrieval</t>
+  </si>
+  <si>
+    <t>Define candidate top-K</t>
+  </si>
+  <si>
+    <t>Validate retrieved candidates</t>
+  </si>
+  <si>
+    <t>Filter candidates by skin type</t>
+  </si>
+  <si>
+    <t>Filter candidates by climate</t>
+  </si>
+  <si>
+    <t>Filter candidates by acne suitability</t>
+  </si>
+  <si>
+    <t>Filter incompatible active/base combinations</t>
+  </si>
+  <si>
+    <t>Load user's normalized exclusions</t>
+  </si>
+  <si>
+    <t>Match exclusions against candidate ingredients</t>
+  </si>
+  <si>
+    <t>Remove excluded actives</t>
+  </si>
+  <si>
+    <t>Remove excluded bases</t>
+  </si>
+  <si>
+    <t>Record exclusion reason</t>
+  </si>
+  <si>
+    <t>Verify no excluded ingredient remains</t>
+  </si>
+  <si>
+    <t>Create candidate audit structure</t>
+  </si>
+  <si>
+    <t>Store retrieved candidates</t>
+  </si>
+  <si>
+    <t>Store removed candidates</t>
+  </si>
+  <si>
+    <t>Store exclusion reasons</t>
+  </si>
+  <si>
+    <t>Store final candidate set</t>
+  </si>
+  <si>
+    <t>Validate final candidate set</t>
+  </si>
+  <si>
+    <t>Define active ingredient representation</t>
+  </si>
+  <si>
+    <t>Define base representation</t>
+  </si>
+  <si>
+    <t>Define concern representation</t>
+  </si>
+  <si>
+    <t>Define compatibility information</t>
+  </si>
+  <si>
+    <t>Define exclusion information</t>
+  </si>
+  <si>
+    <t>Define cost information</t>
+  </si>
+  <si>
+    <t>Serialize candidate shortlist to JSON</t>
+  </si>
+  <si>
+    <t>Draft formulation prompt template</t>
+  </si>
+  <si>
+    <t>Define formulation constraints</t>
+  </si>
+  <si>
+    <t>Define 100g formulation requirement</t>
+  </si>
+  <si>
+    <t>Define active percentage requirements</t>
+  </si>
+  <si>
+    <t>Define compatibility requirements</t>
+  </si>
+  <si>
+    <t>Define exclusion requirements</t>
+  </si>
+  <si>
+    <t>Define concern-to-active reasoning requirements</t>
+  </si>
+  <si>
+    <t>Define cost calculation requirements</t>
+  </si>
+  <si>
+    <t>Add JSON-only output instruction</t>
+  </si>
+  <si>
+    <t>Define formulation output JSON schema</t>
+  </si>
+  <si>
+    <t>Define formulation ID</t>
+  </si>
+  <si>
+    <t>Define selected actives</t>
+  </si>
+  <si>
+    <t>Define active percentages</t>
+  </si>
+  <si>
+    <t>Define selected base</t>
+  </si>
+  <si>
+    <t>Define quantities</t>
+  </si>
+  <si>
+    <t>Define formulation weight</t>
+  </si>
+  <si>
+    <t>Define formulation cost</t>
+  </si>
+  <si>
+    <t>Define explanation</t>
+  </si>
+  <si>
+    <t>Define validation/error fields</t>
+  </si>
+  <si>
+    <t>Validate output against schema</t>
+  </si>
+  <si>
+    <t>Handle malformed response</t>
+  </si>
+  <si>
+    <t>Implement formulation LLM call</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shortlist_json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> schema</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Validate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shortlist_json</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pass </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shortlist_json</t>
+    </r>
+  </si>
+  <si>
+    <t>Validate formulation total weight = 100g</t>
+  </si>
+  <si>
+    <t>Validate active percentages</t>
+  </si>
+  <si>
+    <t>Validate active quantities</t>
+  </si>
+  <si>
+    <t>Validate base quantity</t>
+  </si>
+  <si>
+    <t>Validate active/base compatibility</t>
+  </si>
+  <si>
+    <t>Validate skin-concern relevance</t>
+  </si>
+  <si>
+    <t>Validate allergen exclusions</t>
+  </si>
+  <si>
+    <t>Validate ingredient suitability</t>
+  </si>
+  <si>
+    <t>Calculate total formulation cost</t>
+  </si>
+  <si>
+    <t>Validate LLM-calculated cost against DB cost</t>
+  </si>
+  <si>
+    <t>Reject invalid formulation</t>
+  </si>
+  <si>
+    <t>Trigger formulation regeneration/fallback for invalid formulation</t>
+  </si>
+  <si>
+    <t>Define audit event types</t>
+  </si>
+  <si>
+    <t>Define image-analysis audit payload</t>
+  </si>
+  <si>
+    <t>Define questionnaire-analysis audit payload</t>
+  </si>
+  <si>
+    <t>Define formulation audit payload</t>
+  </si>
+  <si>
+    <t>Define request metadata</t>
+  </si>
+  <si>
+    <t>Define response metadata</t>
+  </si>
+  <si>
+    <t>Define model/version metadata</t>
+  </si>
+  <si>
+    <t>Define timestamp/session identifiers</t>
+  </si>
+  <si>
+    <t>Implement image LLM logging</t>
+  </si>
+  <si>
+    <t>Implement questionnaire LLM logging</t>
+  </si>
+  <si>
+    <t>Implement formulation LLM logging</t>
+  </si>
+  <si>
+    <t>Implement LLM error logging</t>
+  </si>
+  <si>
+    <t>Define final recommendation response schema</t>
+  </si>
+  <si>
+    <t>Add user full name</t>
+  </si>
+  <si>
+    <t>Add primary skin concerns</t>
+  </si>
+  <si>
+    <t>Add skin type</t>
+  </si>
+  <si>
+    <t>Add sensitivity level</t>
+  </si>
+  <si>
+    <t>Add allergens</t>
+  </si>
+  <si>
+    <t>Add recommended base</t>
+  </si>
+  <si>
+    <t>Add active ingredients</t>
+  </si>
+  <si>
+    <t>Add active percentages</t>
+  </si>
+  <si>
+    <t>Add ingredient quantities</t>
+  </si>
+  <si>
+    <t>Add formulation weight</t>
+  </si>
+  <si>
+    <t>Add formulation cost</t>
+  </si>
+  <si>
+    <t>Add formulation explanation</t>
+  </si>
+  <si>
+    <t>Add formulation ID</t>
+  </si>
+  <si>
+    <t>Implement DB → response serialization</t>
+  </si>
+  <si>
+    <t>Serialize formulation data</t>
+  </si>
+  <si>
+    <t>Serialize concern data</t>
+  </si>
+  <si>
+    <t>Serialize questionnaire data</t>
+  </si>
+  <si>
+    <t>Serialize cost data</t>
+  </si>
+  <si>
+    <t>Validate final response schema</t>
+  </si>
+  <si>
+    <t>Define recommendation error schema</t>
+  </si>
+  <si>
+    <t>Define no-compatible-formulation response</t>
+  </si>
+  <si>
+    <t>Define LLM failure response</t>
+  </si>
+  <si>
+    <t>Define database failure response</t>
+  </si>
+  <si>
+    <t>Define invalid-formulation response</t>
+  </si>
+  <si>
+    <t>Implement fallback response</t>
+  </si>
+  <si>
+    <t>Display user name</t>
+  </si>
+  <si>
+    <t>Display primary skin concerns</t>
+  </si>
+  <si>
+    <t>Display perfect-skin message when applicable</t>
+  </si>
+  <si>
+    <t>Display skin type</t>
+  </si>
+  <si>
+    <t>Display allergens</t>
+  </si>
+  <si>
+    <t>Display sensitivity level</t>
+  </si>
+  <si>
+    <t>Display recommended base</t>
+  </si>
+  <si>
+    <t>Display active ingredients</t>
+  </si>
+  <si>
+    <t>Display active percentages</t>
+  </si>
+  <si>
+    <t>Display formulation explanation</t>
+  </si>
+  <si>
+    <t>Display total cost</t>
+  </si>
+  <si>
+    <t>Display formulation ID/status if required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2
+</t>
+  </si>
+  <si>
+    <t>Identify required Shopify API capabilities</t>
+  </si>
+  <si>
+    <t>Identify Shopify product/cart model</t>
+  </si>
+  <si>
+    <t>Determine how formulation metadata can be stored</t>
+  </si>
+  <si>
+    <t>Determine authentication requirements</t>
+  </si>
+  <si>
+    <t>Create Shopify API proof of concept</t>
+  </si>
+  <si>
+    <t>Create test product/variant</t>
+  </si>
+  <si>
+    <t>Add test item to cart</t>
+  </si>
+  <si>
+    <t>Retrieve cart</t>
+  </si>
+  <si>
+    <t>Confirm custom formulation data can be persisted</t>
+  </si>
+  <si>
+    <t>Define saved formulation schema</t>
+  </si>
+  <si>
+    <t>Define formulation-to-user relationship</t>
+  </si>
+  <si>
+    <t>Define formulation-to-cart relationship</t>
+  </si>
+  <si>
+    <t>Store formulation ID</t>
+  </si>
+  <si>
+    <t>Store formulation ingredients</t>
+  </si>
+  <si>
+    <t>Store ingredient quantities</t>
+  </si>
+  <si>
+    <t>Store base</t>
+  </si>
+  <si>
+    <t>Store formulation cost</t>
+  </si>
+  <si>
+    <t>Store formulation snapshot/version</t>
+  </si>
+  <si>
+    <t>Implement formulation persistence</t>
+  </si>
+  <si>
+    <t>Define add-to-cart request schema</t>
+  </si>
+  <si>
+    <t>Validate formulation ID</t>
+  </si>
+  <si>
+    <t>Retrieve formulation</t>
+  </si>
+  <si>
+    <t>Verify formulation belongs to logged-in user</t>
+  </si>
+  <si>
+    <t>Verify formulation is valid</t>
+  </si>
+  <si>
+    <t>Create Shopify cart item</t>
+  </si>
+  <si>
+    <t>Attach formulation metadata</t>
+  </si>
+  <si>
+    <t>Save cart/formulation relationship</t>
+  </si>
+  <si>
+    <t>Return cart response</t>
+  </si>
+  <si>
+    <t>Implement Add to Cart button</t>
+  </si>
+  <si>
+    <t>Disable button while request is processing</t>
+  </si>
+  <si>
+    <t>Call add-to-cart API</t>
+  </si>
+  <si>
+    <t>Handle successful response</t>
+  </si>
+  <si>
+    <t>Display success state</t>
+  </si>
+  <si>
+    <t>Handle add-to-cart failure</t>
+  </si>
+  <si>
+    <t>Prevent duplicate submissions</t>
+  </si>
+  <si>
+    <t>Define allergen/exclusion master table</t>
+  </si>
+  <si>
+    <t>Define base-to-exclusion relationship table</t>
+  </si>
+  <si>
+    <t>Seed active ingredient -&gt; exclusion mapping</t>
+  </si>
+  <si>
+    <t>Seed base -&gt; exclusion mappings</t>
+  </si>
+  <si>
+    <t>Store image analysis result against current session</t>
+  </si>
+  <si>
+    <t>Store questionnaire extraction result against current session</t>
+  </si>
+  <si>
+    <t>Store questionnaire-derived exclusions for the current session</t>
+  </si>
+  <si>
+    <t>Define candidate retrieval query</t>
+  </si>
+  <si>
+    <t>Retrieve candidate actives</t>
+  </si>
+  <si>
+    <t>Retrieve candidate bases</t>
+  </si>
+  <si>
+    <t>Verify formulation references only ingredients present in shortlist</t>
+  </si>
+  <si>
+    <t>Store formulation explanation</t>
+  </si>
+  <si>
+    <t>Validate selected base exists in shortlist</t>
+  </si>
+  <si>
+    <t>Store active ingredient percentages</t>
+  </si>
+  <si>
+    <t>Retrieve and validate ingredient cost/g from db</t>
+  </si>
+  <si>
+    <t>SPRINT BACKLOG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1156,15 +2001,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1317,7 +2176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1494,6 +2353,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1509,31 +2381,53 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1842,6 +2736,19 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D55" dT="2026-08-21T09:15:33.65" personId="{00000000-0000-0000-0000-000000000000}" id="{7A857420-A344-4A5B-B5A5-8DCCE0278C3D}">
+    <text xml:space="preserve">Do we display all concerns or just top n 
+</text>
+  </threadedComment>
+  <threadedComment ref="D153" dT="2026-08-21T10:26:11.01" personId="{00000000-0000-0000-0000-000000000000}" id="{62DF36E2-EA7C-49D8-8C48-B87BDEFAC85F}">
+    <text xml:space="preserve">Do we need for MVP?
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E5" dT="2026-08-20T15:41:46.67" personId="{00000000-0000-0000-0000-000000000000}" id="{233094A3-3D2A-436A-904F-A8273DA397F5}">
     <text>Should all skin concerns be listed when we are only addressing top n.</text>
   </threadedComment>
@@ -2338,20 +3245,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="15" t="s">
@@ -2392,10 +3299,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="58.8" customHeight="1">
-      <c r="A3" s="71">
+      <c r="A3" s="76">
         <v>1</v>
       </c>
-      <c r="B3" s="71">
+      <c r="B3" s="76">
         <v>1</v>
       </c>
       <c r="C3">
@@ -2407,25 +3314,25 @@
       <c r="E3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="74">
+      <c r="F3" s="80">
         <v>46252</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="74">
+      <c r="H3" s="80">
         <v>46259</v>
       </c>
-      <c r="I3" s="71" t="s">
+      <c r="I3" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="76" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="54.6" customHeight="1">
-      <c r="A4" s="71"/>
-      <c r="B4" s="71"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="76"/>
       <c r="C4">
         <v>1.2</v>
       </c>
@@ -2435,15 +3342,15 @@
       <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
     </row>
     <row r="5" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A5" s="71"/>
-      <c r="B5" s="71"/>
+      <c r="A5" s="76"/>
+      <c r="B5" s="76"/>
       <c r="C5">
         <v>1.3</v>
       </c>
@@ -2453,15 +3360,15 @@
       <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="74"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
     </row>
     <row r="6" spans="1:12" ht="26.4" customHeight="1">
-      <c r="A6" s="71"/>
-      <c r="B6" s="71"/>
+      <c r="A6" s="76"/>
+      <c r="B6" s="76"/>
       <c r="C6">
         <v>1.4</v>
       </c>
@@ -2471,15 +3378,15 @@
       <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="74"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
     </row>
     <row r="7" spans="1:12" ht="72.599999999999994" customHeight="1">
-      <c r="A7" s="71"/>
-      <c r="B7" s="71"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="76"/>
       <c r="C7">
         <v>1.5</v>
       </c>
@@ -2489,15 +3396,15 @@
       <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="74"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="71"/>
-      <c r="B8" s="71">
+      <c r="A8" s="76"/>
+      <c r="B8" s="76">
         <v>2</v>
       </c>
       <c r="C8">
@@ -2509,23 +3416,23 @@
       <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="74">
+      <c r="F8" s="80">
         <v>46252</v>
       </c>
-      <c r="G8" s="71" t="s">
+      <c r="G8" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="74">
+      <c r="H8" s="80">
         <v>46258</v>
       </c>
-      <c r="I8" s="71" t="s">
+      <c r="I8" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="71"/>
+      <c r="J8" s="76"/>
     </row>
     <row r="9" spans="1:12" ht="28.8">
-      <c r="A9" s="71"/>
-      <c r="B9" s="71"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="76"/>
       <c r="C9">
         <v>2.2000000000000002</v>
       </c>
@@ -2535,15 +3442,15 @@
       <c r="E9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="74"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
-      <c r="A10" s="71"/>
-      <c r="B10" s="71"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
       <c r="C10">
         <v>2.2999999999999998</v>
       </c>
@@ -2553,15 +3460,15 @@
       <c r="E10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="74"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
     </row>
     <row r="11" spans="1:12" ht="28.8">
-      <c r="A11" s="71"/>
-      <c r="B11" s="71">
+      <c r="A11" s="76"/>
+      <c r="B11" s="76">
         <v>3</v>
       </c>
       <c r="C11">
@@ -2573,15 +3480,15 @@
       <c r="E11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="74"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="76"/>
+      <c r="J11" s="76"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
-      <c r="A12" s="71"/>
-      <c r="B12" s="71"/>
+      <c r="A12" s="76"/>
+      <c r="B12" s="76"/>
       <c r="C12">
         <v>3.2</v>
       </c>
@@ -2603,11 +3510,11 @@
       <c r="I12" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="71"/>
+      <c r="J12" s="76"/>
     </row>
     <row r="13" spans="1:12" ht="28.8">
-      <c r="A13" s="71"/>
-      <c r="B13" s="71">
+      <c r="A13" s="76"/>
+      <c r="B13" s="76">
         <v>4</v>
       </c>
       <c r="C13">
@@ -2631,11 +3538,11 @@
       <c r="I13" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="71"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="1:12" ht="28.8">
-      <c r="A14" s="71"/>
-      <c r="B14" s="71"/>
+      <c r="A14" s="76"/>
+      <c r="B14" s="76"/>
       <c r="C14">
         <v>4.2</v>
       </c>
@@ -2657,10 +3564,10 @@
       <c r="I14" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="71"/>
+      <c r="J14" s="76"/>
     </row>
     <row r="15" spans="1:12" ht="28.8">
-      <c r="A15" s="71"/>
+      <c r="A15" s="76"/>
       <c r="B15" s="14">
         <v>9</v>
       </c>
@@ -2673,15 +3580,15 @@
       <c r="E15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="74" t="s">
+      <c r="F15" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="71"/>
+      <c r="J15" s="76"/>
       <c r="L15" t="s">
         <v>98</v>
       </c>
@@ -2690,10 +3597,10 @@
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="75"/>
+      <c r="E16" s="78"/>
       <c r="F16" s="26">
         <v>46198</v>
       </c>
@@ -2704,10 +3611,10 @@
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="86.4">
-      <c r="A17" s="71">
+      <c r="A17" s="76">
         <v>2</v>
       </c>
-      <c r="B17" s="71">
+      <c r="B17" s="76">
         <v>5</v>
       </c>
       <c r="C17">
@@ -2722,19 +3629,19 @@
       <c r="F17" s="21">
         <v>46260</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="70">
+      <c r="H17" s="75">
         <v>46262</v>
       </c>
-      <c r="I17" s="69" t="s">
+      <c r="I17" s="74" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8">
-      <c r="A18" s="71"/>
-      <c r="B18" s="71"/>
+      <c r="A18" s="76"/>
+      <c r="B18" s="76"/>
       <c r="C18">
         <v>5.2</v>
       </c>
@@ -2744,13 +3651,13 @@
       <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
     </row>
     <row r="19" spans="1:9" ht="86.4">
-      <c r="A19" s="71"/>
-      <c r="B19" s="71">
+      <c r="A19" s="76"/>
+      <c r="B19" s="76">
         <v>6</v>
       </c>
       <c r="C19">
@@ -2762,22 +3669,22 @@
       <c r="E19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="70">
+      <c r="F19" s="75">
         <v>46260</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="70">
+      <c r="H19" s="75">
         <v>46267</v>
       </c>
-      <c r="I19" s="69" t="s">
+      <c r="I19" s="74" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8">
-      <c r="A20" s="71"/>
-      <c r="B20" s="71"/>
+      <c r="A20" s="76"/>
+      <c r="B20" s="76"/>
       <c r="C20">
         <v>6.2</v>
       </c>
@@ -2787,14 +3694,14 @@
       <c r="E20" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="69"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="69"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
     </row>
     <row r="21" spans="1:9" ht="43.8" customHeight="1">
-      <c r="A21" s="71"/>
-      <c r="B21" s="71"/>
+      <c r="A21" s="76"/>
+      <c r="B21" s="76"/>
       <c r="C21" s="18">
         <v>6.3</v>
       </c>
@@ -2804,14 +3711,14 @@
       <c r="E21" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
     </row>
     <row r="22" spans="1:9" ht="28.8">
-      <c r="A22" s="71"/>
-      <c r="B22" s="71"/>
+      <c r="A22" s="76"/>
+      <c r="B22" s="76"/>
       <c r="C22">
         <v>6.4</v>
       </c>
@@ -2821,14 +3728,14 @@
       <c r="E22" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
     </row>
     <row r="23" spans="1:9" ht="28.8">
-      <c r="A23" s="71"/>
-      <c r="B23" s="71">
+      <c r="A23" s="76"/>
+      <c r="B23" s="76">
         <v>7</v>
       </c>
       <c r="C23">
@@ -2840,22 +3747,22 @@
       <c r="E23" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F23" s="75">
         <v>46260</v>
       </c>
-      <c r="G23" s="69" t="s">
+      <c r="G23" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="70">
+      <c r="H23" s="75">
         <v>46267</v>
       </c>
-      <c r="I23" s="69" t="s">
+      <c r="I23" s="74" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="71"/>
-      <c r="B24" s="71"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="76"/>
       <c r="C24">
         <v>7.2</v>
       </c>
@@ -2865,14 +3772,14 @@
       <c r="E24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="69"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="69"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
     </row>
     <row r="25" spans="1:9" ht="43.2">
-      <c r="A25" s="71"/>
-      <c r="B25" s="71">
+      <c r="A25" s="76"/>
+      <c r="B25" s="76">
         <v>8</v>
       </c>
       <c r="C25">
@@ -2884,22 +3791,22 @@
       <c r="E25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="72">
+      <c r="F25" s="77">
         <v>46260</v>
       </c>
-      <c r="G25" s="69" t="s">
+      <c r="G25" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="70">
+      <c r="H25" s="75">
         <v>46267</v>
       </c>
-      <c r="I25" s="69" t="s">
+      <c r="I25" s="74" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28.8">
-      <c r="A26" s="71"/>
-      <c r="B26" s="71"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="76"/>
       <c r="C26">
         <v>8.1999999999999993</v>
       </c>
@@ -2909,10 +3816,10 @@
       <c r="E26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="72"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="69"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="24"/>
@@ -2932,10 +3839,10 @@
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="43.2">
-      <c r="A28" s="71">
+      <c r="A28" s="76">
         <v>3</v>
       </c>
-      <c r="B28" s="71">
+      <c r="B28" s="76">
         <v>9</v>
       </c>
       <c r="C28">
@@ -2947,22 +3854,22 @@
       <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="70">
+      <c r="F28" s="75">
         <v>46268</v>
       </c>
-      <c r="G28" s="69" t="s">
+      <c r="G28" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="70">
+      <c r="H28" s="75">
         <v>46275</v>
       </c>
-      <c r="I28" s="69" t="s">
+      <c r="I28" s="74" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.8">
-      <c r="A29" s="71"/>
-      <c r="B29" s="71"/>
+      <c r="A29" s="76"/>
+      <c r="B29" s="76"/>
       <c r="C29">
         <v>9.1999999999999993</v>
       </c>
@@ -2972,14 +3879,14 @@
       <c r="E29" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="70"/>
-      <c r="G29" s="69"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="69"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="74"/>
     </row>
     <row r="30" spans="1:9" ht="28.8">
-      <c r="A30" s="71"/>
-      <c r="B30" s="71"/>
+      <c r="A30" s="76"/>
+      <c r="B30" s="76"/>
       <c r="C30">
         <v>9.3000000000000007</v>
       </c>
@@ -2989,19 +3896,17 @@
       <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="70"/>
-      <c r="G30" s="69"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="69"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="74"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="71"/>
-      <c r="B31" s="71"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B22"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="J3:J15"/>
@@ -3021,20 +3926,15 @@
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A17:A26"/>
     <mergeCell ref="A28:A31"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B22"/>
     <mergeCell ref="F19:F22"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B28:B31"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="G19:G22"/>
@@ -3043,6 +3943,13 @@
     <mergeCell ref="I23:I24"/>
     <mergeCell ref="I19:I22"/>
     <mergeCell ref="H17:H18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3066,12 +3973,13 @@
     <col min="11" max="11" width="7.44140625" customWidth="1"/>
     <col min="13" max="13" width="32.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B1" s="60"/>
       <c r="C1" s="60"/>
@@ -3088,11 +3996,11 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="60"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
       <c r="E2" s="61"/>
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
@@ -3108,16 +4016,16 @@
         <v>104</v>
       </c>
       <c r="B3" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="D3" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="53" t="s">
-        <v>133</v>
-      </c>
       <c r="E3" s="53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F3" s="53" t="s">
         <v>107</v>
@@ -3144,16 +4052,19 @@
         <v>97</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>104</v>
       </c>
       <c r="Q3" s="15" t="s">
         <v>169</v>
       </c>
       <c r="R3" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T3" s="15" t="s">
         <v>101</v>
@@ -3168,13 +4079,13 @@
     <row r="4" spans="1:22" ht="43.2">
       <c r="A4" s="33"/>
       <c r="B4" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="58" t="s">
         <v>136</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>137</v>
       </c>
       <c r="E4" s="39" t="s">
         <v>55</v>
@@ -3182,6 +4093,9 @@
       <c r="F4" s="33"/>
       <c r="G4" s="62"/>
       <c r="I4" s="39"/>
+      <c r="Q4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="33"/>
@@ -3212,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="E7" s="39" t="s">
         <v>55</v>
@@ -3264,7 +4178,7 @@
       <c r="C10" s="14"/>
       <c r="D10" s="1"/>
       <c r="E10" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F10" s="33"/>
       <c r="G10" s="62"/>
@@ -3758,6 +4672,1929 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B102D4C0-1656-4F6E-9BC2-A7E4DB44885F}">
+  <dimension ref="A1:I253"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="61.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="92" t="s">
+        <v>424</v>
+      </c>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+    </row>
+    <row r="2" spans="1:9" s="15" customFormat="1">
+      <c r="A2" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="94" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="H2" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" s="60" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="B3" s="83">
+        <v>1</v>
+      </c>
+      <c r="C3" s="84">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="83"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="13" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="83"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="83"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.4" customHeight="1">
+      <c r="B13" s="83"/>
+      <c r="C13" s="87" t="s">
+        <v>373</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="B14" s="83"/>
+      <c r="C14" s="87"/>
+      <c r="D14" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="B15" s="83"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="B16" s="83"/>
+      <c r="C16" s="87"/>
+      <c r="D16" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="83"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="83"/>
+      <c r="C18" s="84">
+        <v>1.3</v>
+      </c>
+      <c r="D18" s="89" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="83"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="89" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B20" s="83"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="13" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B21" s="83"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B22" s="83"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23" s="83"/>
+      <c r="C23" s="83">
+        <v>1.4</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="83"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B27" s="83"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="83">
+        <v>2</v>
+      </c>
+      <c r="C28" s="86">
+        <v>2.1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="83"/>
+      <c r="C29" s="83">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" s="83"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B32" s="83"/>
+      <c r="C32" s="83"/>
+      <c r="D32" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="83"/>
+      <c r="C35" s="83"/>
+      <c r="D35" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="83"/>
+      <c r="C36" s="83">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="13" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="83"/>
+      <c r="C41" s="83"/>
+      <c r="D41" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B43" s="83"/>
+      <c r="C43" s="83">
+        <v>2.4</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B44" s="83"/>
+      <c r="C44" s="83"/>
+      <c r="D44" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="83"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="83"/>
+      <c r="C48" s="83">
+        <v>2.5</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="83"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="83"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="83"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B53" s="83"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="83"/>
+      <c r="C54" s="83">
+        <v>2.6</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="85" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B56" s="83"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="83"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="83">
+        <v>3</v>
+      </c>
+      <c r="C58" s="83">
+        <v>3.1</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="83"/>
+      <c r="C59" s="83"/>
+      <c r="D59" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="83"/>
+      <c r="C60" s="83"/>
+      <c r="D60" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="83"/>
+      <c r="C61" s="83"/>
+      <c r="D61" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="83"/>
+      <c r="C62" s="83"/>
+      <c r="D62" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="83"/>
+      <c r="C63" s="83"/>
+      <c r="D63" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="83"/>
+      <c r="C64" s="83"/>
+      <c r="D64" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="83"/>
+      <c r="C65" s="83">
+        <v>3.2</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B66" s="83"/>
+      <c r="C66" s="83"/>
+      <c r="D66" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="83"/>
+      <c r="C67" s="83"/>
+      <c r="D67" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" s="83"/>
+      <c r="C68" s="83"/>
+      <c r="D68" s="13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" s="83"/>
+      <c r="C69" s="83"/>
+      <c r="D69" s="13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="83"/>
+      <c r="C70" s="83"/>
+      <c r="D70" s="13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" s="83"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="83"/>
+      <c r="C72" s="83">
+        <v>3.3</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="83"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="83"/>
+      <c r="C74" s="83"/>
+      <c r="D74" s="13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="83"/>
+      <c r="C75" s="83"/>
+      <c r="D75" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="83"/>
+      <c r="C76" s="83"/>
+      <c r="D76" s="13" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B77" s="83"/>
+      <c r="C77" s="83"/>
+      <c r="D77" s="13" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" s="83"/>
+      <c r="C78" s="83">
+        <v>3.4</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B79" s="83"/>
+      <c r="C79" s="83"/>
+      <c r="D79" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" s="83"/>
+      <c r="C80" s="83"/>
+      <c r="D80" s="13" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" s="83"/>
+      <c r="C81" s="83"/>
+      <c r="D81" s="13" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="83"/>
+      <c r="C82" s="83"/>
+      <c r="D82" s="89" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B83" s="83"/>
+      <c r="C83" s="83"/>
+      <c r="D83" s="89" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" s="83"/>
+      <c r="C84" s="83"/>
+      <c r="D84" s="89" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" s="83"/>
+      <c r="C85" s="83"/>
+      <c r="D85" s="89" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B86" s="83"/>
+      <c r="C86" s="83"/>
+      <c r="D86" s="13" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B87" s="83"/>
+      <c r="C87" s="83"/>
+      <c r="D87" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4">
+      <c r="B88" s="83"/>
+      <c r="C88" s="83">
+        <v>3.5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" s="83"/>
+      <c r="C89" s="83"/>
+      <c r="D89" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="83"/>
+      <c r="C90" s="83"/>
+      <c r="D90" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="83"/>
+      <c r="C91" s="83"/>
+      <c r="D91" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" s="83"/>
+      <c r="C92" s="83"/>
+      <c r="D92" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" s="83"/>
+      <c r="C93" s="83"/>
+      <c r="D93" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" s="83"/>
+      <c r="C94" s="83"/>
+      <c r="D94" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" s="83"/>
+      <c r="C95" s="83">
+        <v>3.6</v>
+      </c>
+      <c r="D95" s="82" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" s="83"/>
+      <c r="C96" s="83"/>
+      <c r="D96" s="82" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" s="83"/>
+      <c r="C97" s="83"/>
+      <c r="D97" s="82" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" s="83"/>
+      <c r="C98" s="83"/>
+      <c r="D98" s="82" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" s="83"/>
+      <c r="C99" s="83"/>
+      <c r="D99" s="82" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" s="83"/>
+      <c r="C100" s="83"/>
+      <c r="D100" s="82" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="83"/>
+      <c r="C101" s="83"/>
+      <c r="D101" s="82" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" s="83"/>
+      <c r="C102" s="83"/>
+      <c r="D102" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" s="83"/>
+      <c r="C103" s="83"/>
+      <c r="D103" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" s="83"/>
+      <c r="C104" s="83"/>
+      <c r="D104" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" s="83"/>
+      <c r="C105" s="83"/>
+      <c r="D105" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="83"/>
+      <c r="C106" s="83"/>
+      <c r="D106" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" s="83"/>
+      <c r="C107" s="83"/>
+      <c r="D107" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="83"/>
+      <c r="C108" s="83"/>
+      <c r="D108" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" s="83"/>
+      <c r="C109" s="83"/>
+      <c r="D109" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" s="83"/>
+      <c r="C110" s="83"/>
+      <c r="D110" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" s="83"/>
+      <c r="C111" s="83"/>
+      <c r="D111" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" s="83"/>
+      <c r="C112" s="83">
+        <v>3.7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" s="83"/>
+      <c r="C113" s="83"/>
+      <c r="D113" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="83"/>
+      <c r="C114" s="83"/>
+      <c r="D114" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" s="83"/>
+      <c r="C115" s="83"/>
+      <c r="D115" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="83"/>
+      <c r="C116" s="83"/>
+      <c r="D116" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="83"/>
+      <c r="C117" s="83"/>
+      <c r="D117" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="83"/>
+      <c r="C118" s="83">
+        <v>3.8</v>
+      </c>
+      <c r="D118" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="83"/>
+      <c r="C119" s="83"/>
+      <c r="D119" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" s="83"/>
+      <c r="C120" s="83"/>
+      <c r="D120" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" s="83"/>
+      <c r="C121" s="83"/>
+      <c r="D121" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" s="83"/>
+      <c r="C122" s="83"/>
+      <c r="D122" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" s="83"/>
+      <c r="C123" s="83"/>
+      <c r="D123" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" s="83"/>
+      <c r="C124" s="83"/>
+      <c r="D124" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" s="83"/>
+      <c r="C125" s="83"/>
+      <c r="D125" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" s="83"/>
+      <c r="C126" s="83"/>
+      <c r="D126" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" s="83"/>
+      <c r="C127" s="91">
+        <v>3.9</v>
+      </c>
+      <c r="D127" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="83"/>
+      <c r="C128" s="91"/>
+      <c r="D128" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="83"/>
+      <c r="C129" s="91"/>
+      <c r="D129" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="83"/>
+      <c r="C130" s="91"/>
+      <c r="D130" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" s="83"/>
+      <c r="C131" s="91"/>
+      <c r="D131" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" s="83"/>
+      <c r="C132" s="91"/>
+      <c r="D132" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" s="83"/>
+      <c r="C133" s="91"/>
+      <c r="D133" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" s="83"/>
+      <c r="C134" s="91"/>
+      <c r="D134" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" s="83"/>
+      <c r="C135" s="91"/>
+      <c r="D135" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" s="83"/>
+      <c r="C136" s="91"/>
+      <c r="D136" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" s="83"/>
+      <c r="C137" s="91"/>
+      <c r="D137" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" s="83"/>
+      <c r="C138" s="88">
+        <v>3.1</v>
+      </c>
+      <c r="D138" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="83"/>
+      <c r="C139" s="88"/>
+      <c r="D139" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="83"/>
+      <c r="C140" s="88"/>
+      <c r="D140" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141" s="83"/>
+      <c r="C141" s="88"/>
+      <c r="D141" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="83"/>
+      <c r="C142" s="88"/>
+      <c r="D142" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="83"/>
+      <c r="C143" s="88"/>
+      <c r="D143" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="83"/>
+      <c r="C144" s="88"/>
+      <c r="D144" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="83"/>
+      <c r="C145" s="88"/>
+      <c r="D145" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="83"/>
+      <c r="C146" s="88"/>
+      <c r="D146" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="83"/>
+      <c r="C147" s="88"/>
+      <c r="D147" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="83"/>
+      <c r="C148" s="83">
+        <v>3.11</v>
+      </c>
+      <c r="D148" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="83"/>
+      <c r="C149" s="83"/>
+      <c r="D149" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="83"/>
+      <c r="C150" s="83"/>
+      <c r="D150" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="83"/>
+      <c r="C151" s="83"/>
+      <c r="D151" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" s="83"/>
+      <c r="C152" s="83"/>
+      <c r="D152" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="83"/>
+      <c r="C153" s="83">
+        <v>3.12</v>
+      </c>
+      <c r="D153" s="90" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="83"/>
+      <c r="C154" s="83"/>
+      <c r="D154" s="90" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="83"/>
+      <c r="C155" s="83"/>
+      <c r="D155" s="90" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="83"/>
+      <c r="C156" s="83"/>
+      <c r="D156" s="90" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="83"/>
+      <c r="C157" s="83"/>
+      <c r="D157" s="90" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="83"/>
+      <c r="C158" s="83"/>
+      <c r="D158" s="90" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="83"/>
+      <c r="C159" s="83"/>
+      <c r="D159" s="90" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="83"/>
+      <c r="C160" s="83"/>
+      <c r="D160" s="90" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="83"/>
+      <c r="C161" s="83"/>
+      <c r="D161" s="90" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="83"/>
+      <c r="C162" s="83"/>
+      <c r="D162" s="90" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="83"/>
+      <c r="C163" s="83"/>
+      <c r="D163" s="90" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="83"/>
+      <c r="C164" s="83"/>
+      <c r="D164" s="90" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="83"/>
+      <c r="C165" s="83"/>
+      <c r="D165" s="90" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="83"/>
+      <c r="C166" s="83">
+        <v>3.13</v>
+      </c>
+      <c r="D166" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="83"/>
+      <c r="C167" s="83"/>
+      <c r="D167" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="B168" s="83"/>
+      <c r="C168" s="83"/>
+      <c r="D168" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="83"/>
+      <c r="C169" s="83"/>
+      <c r="D169" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="83"/>
+      <c r="C170" s="83"/>
+      <c r="D170" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="83"/>
+      <c r="C171" s="83"/>
+      <c r="D171" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="83"/>
+      <c r="C172" s="83"/>
+      <c r="D172" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="83"/>
+      <c r="C173" s="83"/>
+      <c r="D173" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="83"/>
+      <c r="C174" s="83"/>
+      <c r="D174" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="83"/>
+      <c r="C175" s="83"/>
+      <c r="D175" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="B176" s="83"/>
+      <c r="C176" s="83"/>
+      <c r="D176" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="B177" s="83"/>
+      <c r="C177" s="83"/>
+      <c r="D177" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4">
+      <c r="B178" s="83"/>
+      <c r="C178" s="83"/>
+      <c r="D178" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" s="83"/>
+      <c r="C179" s="83">
+        <v>3.14</v>
+      </c>
+      <c r="D179" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4">
+      <c r="B180" s="83"/>
+      <c r="C180" s="83"/>
+      <c r="D180" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4">
+      <c r="B181" s="83"/>
+      <c r="C181" s="83"/>
+      <c r="D181" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" s="83"/>
+      <c r="C182" s="83"/>
+      <c r="D182" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" s="83"/>
+      <c r="C183" s="83"/>
+      <c r="D183" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" s="83"/>
+      <c r="C184" s="83"/>
+      <c r="D184" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" s="83"/>
+      <c r="C185" s="83"/>
+      <c r="D185" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" s="83"/>
+      <c r="C186" s="83"/>
+      <c r="D186" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="B187" s="83"/>
+      <c r="C187" s="83"/>
+      <c r="D187" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="B188" s="83"/>
+      <c r="C188" s="83"/>
+      <c r="D188" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="B189" s="83"/>
+      <c r="C189" s="83"/>
+      <c r="D189" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190" s="83"/>
+      <c r="C190" s="83"/>
+      <c r="D190" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="B191" s="83"/>
+      <c r="C191" s="83">
+        <v>3.15</v>
+      </c>
+      <c r="D191" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="B192" s="83"/>
+      <c r="C192" s="83"/>
+      <c r="D192" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="83"/>
+      <c r="C193" s="83"/>
+      <c r="D193" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="B194" s="83"/>
+      <c r="C194" s="83"/>
+      <c r="D194" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="B195" s="83"/>
+      <c r="C195" s="83"/>
+      <c r="D195" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4">
+      <c r="B196" s="83"/>
+      <c r="C196" s="83"/>
+      <c r="D196" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="B197" s="83"/>
+      <c r="C197" s="83"/>
+      <c r="D197" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="B198" s="83"/>
+      <c r="C198" s="83"/>
+      <c r="D198" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4">
+      <c r="B199" s="83"/>
+      <c r="C199" s="83"/>
+      <c r="D199" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="B200" s="83"/>
+      <c r="C200" s="83"/>
+      <c r="D200" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4">
+      <c r="B201" s="83"/>
+      <c r="C201" s="83"/>
+      <c r="D201" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4">
+      <c r="B202" s="83"/>
+      <c r="C202" s="83"/>
+      <c r="D202" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4">
+      <c r="B203" s="83"/>
+      <c r="C203" s="83"/>
+      <c r="D203" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="B204" s="83"/>
+      <c r="C204" s="83"/>
+      <c r="D204" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="B205" s="83"/>
+      <c r="C205" s="83">
+        <v>3.16</v>
+      </c>
+      <c r="D205" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="B206" s="83"/>
+      <c r="C206" s="83"/>
+      <c r="D206" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="B207" s="83"/>
+      <c r="C207" s="83"/>
+      <c r="D207" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4">
+      <c r="B208" s="83"/>
+      <c r="C208" s="83"/>
+      <c r="D208" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4">
+      <c r="B209" s="83"/>
+      <c r="C209" s="83"/>
+      <c r="D209" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4">
+      <c r="B210" s="83"/>
+      <c r="C210" s="83"/>
+      <c r="D210" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4">
+      <c r="B211" s="83"/>
+      <c r="C211" s="83">
+        <v>3.17</v>
+      </c>
+      <c r="D211" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4">
+      <c r="B212" s="83"/>
+      <c r="C212" s="83"/>
+      <c r="D212" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4">
+      <c r="B213" s="83"/>
+      <c r="C213" s="83"/>
+      <c r="D213" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4">
+      <c r="B214" s="83"/>
+      <c r="C214" s="83"/>
+      <c r="D214" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4">
+      <c r="B215" s="83"/>
+      <c r="C215" s="83"/>
+      <c r="D215" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4">
+      <c r="B216" s="83"/>
+      <c r="C216" s="83"/>
+      <c r="D216" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4">
+      <c r="B217" s="83"/>
+      <c r="C217" s="83">
+        <v>3.18</v>
+      </c>
+      <c r="D217" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4">
+      <c r="B218" s="83"/>
+      <c r="C218" s="83"/>
+      <c r="D218" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4">
+      <c r="B219" s="83"/>
+      <c r="C219" s="83"/>
+      <c r="D219" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4">
+      <c r="B220" s="83"/>
+      <c r="C220" s="83"/>
+      <c r="D220" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4">
+      <c r="B221" s="83"/>
+      <c r="C221" s="83"/>
+      <c r="D221" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4">
+      <c r="B222" s="83"/>
+      <c r="C222" s="83"/>
+      <c r="D222" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4">
+      <c r="B223" s="83"/>
+      <c r="C223" s="83"/>
+      <c r="D223" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="B224" s="83"/>
+      <c r="C224" s="83"/>
+      <c r="D224" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="B225" s="83"/>
+      <c r="C225" s="83"/>
+      <c r="D225" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="B226" s="83"/>
+      <c r="C226" s="83"/>
+      <c r="D226" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="B227" s="83"/>
+      <c r="C227" s="83"/>
+      <c r="D227" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="B228" s="83"/>
+      <c r="C228" s="83"/>
+      <c r="D228" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" s="83">
+        <v>4</v>
+      </c>
+      <c r="C229" s="83">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D229" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="B230" s="83"/>
+      <c r="C230" s="83"/>
+      <c r="D230" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231" s="83"/>
+      <c r="C231" s="83"/>
+      <c r="D231" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="B232" s="83"/>
+      <c r="C232" s="83"/>
+      <c r="D232" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" s="83"/>
+      <c r="C233" s="83"/>
+      <c r="D233" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234" s="83"/>
+      <c r="C234" s="83"/>
+      <c r="D234" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235" s="83"/>
+      <c r="C235" s="83"/>
+      <c r="D235" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236" s="83"/>
+      <c r="C236" s="83"/>
+      <c r="D236" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" s="83"/>
+      <c r="C237" s="83"/>
+      <c r="D237" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4">
+      <c r="B238" s="83"/>
+      <c r="C238" s="83">
+        <v>4.2</v>
+      </c>
+      <c r="D238" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239" s="83"/>
+      <c r="C239" s="83"/>
+      <c r="D239" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="B240" s="83"/>
+      <c r="C240" s="83"/>
+      <c r="D240" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4">
+      <c r="B241" s="83"/>
+      <c r="C241" s="83"/>
+      <c r="D241" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4">
+      <c r="B242" s="83"/>
+      <c r="C242" s="83"/>
+      <c r="D242" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4">
+      <c r="B243" s="83"/>
+      <c r="C243" s="83"/>
+      <c r="D243" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4">
+      <c r="B244" s="83"/>
+      <c r="C244" s="83"/>
+      <c r="D244" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4">
+      <c r="B245" s="83"/>
+      <c r="C245" s="83"/>
+      <c r="D245" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4">
+      <c r="B246" s="83"/>
+      <c r="C246" s="83"/>
+      <c r="D246" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4">
+      <c r="B247" s="83"/>
+      <c r="C247" s="83">
+        <v>4.3</v>
+      </c>
+      <c r="D247" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4">
+      <c r="B248" s="83"/>
+      <c r="C248" s="83"/>
+      <c r="D248" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4">
+      <c r="B249" s="83"/>
+      <c r="C249" s="83"/>
+      <c r="D249" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4">
+      <c r="B250" s="83"/>
+      <c r="C250" s="83"/>
+      <c r="D250" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4">
+      <c r="B251" s="83"/>
+      <c r="C251" s="83"/>
+      <c r="D251" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4">
+      <c r="B252" s="83"/>
+      <c r="C252" s="83"/>
+      <c r="D252" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4">
+      <c r="B253" s="83"/>
+      <c r="C253" s="83"/>
+      <c r="D253" t="s">
+        <v>408</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="C247:C253"/>
+    <mergeCell ref="B229:B253"/>
+    <mergeCell ref="B58:B228"/>
+    <mergeCell ref="B28:B57"/>
+    <mergeCell ref="B3:B27"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C166:C178"/>
+    <mergeCell ref="C179:C190"/>
+    <mergeCell ref="C191:C204"/>
+    <mergeCell ref="C205:C210"/>
+    <mergeCell ref="C211:C216"/>
+    <mergeCell ref="C217:C228"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="C58:C64"/>
+    <mergeCell ref="C65:C71"/>
+    <mergeCell ref="C72:C77"/>
+    <mergeCell ref="C78:C87"/>
+    <mergeCell ref="C88:C94"/>
+    <mergeCell ref="C95:C111"/>
+    <mergeCell ref="C112:C117"/>
+    <mergeCell ref="C118:C126"/>
+    <mergeCell ref="C229:C237"/>
+    <mergeCell ref="C238:C246"/>
+    <mergeCell ref="C127:C137"/>
+    <mergeCell ref="C138:C147"/>
+    <mergeCell ref="C148:C152"/>
+    <mergeCell ref="C153:C165"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C42"/>
+    <mergeCell ref="C43:C47"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="C3:C12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C23:C27"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D13B384-1725-40B5-B0F7-A3A77A0F68B1}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -3776,18 +6613,18 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="60"/>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="73" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
       <c r="E1" s="60"/>
       <c r="F1" s="60"/>
       <c r="G1" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H1" s="56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I1" s="60"/>
       <c r="J1" s="60"/>
@@ -3797,48 +6634,48 @@
         <v>10</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="53" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="53" t="s">
-        <v>133</v>
-      </c>
       <c r="E2" s="53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F2" s="53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G2" s="53" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I2" s="53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J2" s="53" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="115.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="86.4">
       <c r="A3" s="33">
         <v>1</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C3" s="58" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="58" t="s">
-        <v>137</v>
-      </c>
       <c r="E3" s="58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3855,21 +6692,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="230.4">
+    <row r="4" spans="1:10" ht="158.4">
       <c r="A4" s="33">
         <v>2</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" ht="409.2" customHeight="1">
@@ -3877,16 +6714,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="86.4">
@@ -3894,32 +6731,32 @@
         <v>4</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E6" s="58" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="86.4">
+      <c r="A7" s="68">
+        <v>5</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="70" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="86.4">
-      <c r="A7" s="77">
-        <v>5</v>
-      </c>
-      <c r="B7" s="78" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="79" t="s">
-        <v>168</v>
-      </c>
-      <c r="D7" s="80" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="81"/>
+      <c r="D7" s="71" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="72"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="33"/>
@@ -3954,43 +6791,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF11110B-B1A6-47E4-BCEC-C2B4CA62D5BE}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="76" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="A1" s="81" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="65" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="C2" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="D2" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="E2" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="F2" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="G2" s="65" t="s">
         <v>152</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAEFD4B-48EF-4F3C-A8E1-26F7304E8A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B654A3AA-0EFB-4706-BEDD-3A863B0FA3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint Plan" sheetId="2" r:id="rId2"/>
     <sheet name="Sprint Backlog" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId4"/>
-    <sheet name="Product Backlog" sheetId="4" r:id="rId5"/>
-    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId5"/>
+    <sheet name="Product Backlog" sheetId="4" r:id="rId6"/>
+    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,6 +65,593 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{3BEE7270-9E5D-4C3B-88E0-91F05B9BD669}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Receive &amp; Validate Image</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{D5A9F85E-92E8-4B8A-B751-650E1FE2569F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Image Quality Decision</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{EFBBA07C-E254-4781-9933-E074E562E094}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Rejection Flow</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{08C2F3F8-DE97-42AE-B963-708E64840735}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Testing</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{98BE6294-CAA3-4259-A595-9BA237237285}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Image Session Storage
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{140A5E96-154A-4162-A239-1DBD3E41810C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Visual AI Output</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0" shapeId="0" xr:uid="{E3A3B5A0-0F07-42D5-9D6D-8B8281899F6E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Visual AI Prompt</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="0" shapeId="0" xr:uid="{FDDD7F68-C10A-4FC9-9764-CDD59417EB55}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Visual AI Integration</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0" xr:uid="{51C480C2-E212-4A32-86A1-5F704BCFF728}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ Store Visual Analysis</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{52553FD1-E265-4535-9DD2-2EA05E499E51}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Testing</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C59" authorId="0" shapeId="0" xr:uid="{E4589DAE-73CB-47AB-AD0F-AB8AF18DDD65}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Questionnaire Collection</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{D05C5BAE-0CC4-4ED2-88B6-98BF1ED2B235}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Questionnaire LLM Analysis</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{8C37B025-1BDA-457E-ADB8-C6B979CBD1B1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Concern Fusion</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C88" authorId="0" shapeId="0" xr:uid="{D1A59F32-F52A-4554-9D45-7BAAF46B83A7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Candidate Generation</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C101" authorId="0" shapeId="0" xr:uid="{29757E96-410A-48C6-A86D-C6221515FA91}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Recommendation Generation</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C110" authorId="0" shapeId="0" xr:uid="{C9E3522F-95B1-4BD8-BE53-4B604FDEA74C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Recommendation Persistence</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C116" authorId="0" shapeId="0" xr:uid="{87018544-F456-4F26-A7A5-F72A08475131}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Final Recommendation Response</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C127" authorId="0" shapeId="0" xr:uid="{EC2B78D7-751C-44BB-9D07-F55A82442F1A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Recommendation Screen</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C137" authorId="0" shapeId="0" xr:uid="{99C81342-5268-4323-82B8-DCB2C87D9E02}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Recommendation Error Handling</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{73BA3055-4675-4813-88D0-50B14C092AF1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Testing</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{706E98C8-4B35-46F2-B926-68F27F8F78A4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Shopify Cart Integration</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{A79A220B-8C29-48AD-9825-8780EE217E6A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Add to Cart Backend</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{C4E0F00C-6245-4423-9EA8-8A42808307DE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Add to Cart UI</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{D8702894-1958-4EC2-ACC6-FDE92A697344}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Testing</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={233094A3-3D2A-436A-904F-A8273DA397F5}</author>
   </authors>
   <commentList>
@@ -102,7 +690,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="577">
   <si>
     <t>Gain access to the Dev pannel of Shopify website for CelRevive from client.</t>
   </si>
@@ -904,11 +1492,6 @@
     <t>Wireframe Reference</t>
   </si>
   <si>
-    <t>I can view my reccomendation page with the following fields:
-1. Hello "user_full_name"! 
-2. Skin analysis results : Primary Concerns : only those detected through selfie.</t>
-  </si>
-  <si>
     <t>XS</t>
   </si>
   <si>
@@ -967,36 +1550,6 @@
   </si>
   <si>
     <t>I can add the reccomended formulation to my shopping cart .</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Detected skin concerns should be from the series:
-SC0001 - SC0019 &amp; SC1001 - SC1009
-2. If no skin concern is detected (perfectly fit skin) then Skin analysis results should show the following message:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Your skin looks perfect!".
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3. If the image contains one or multiple particular skin concerns then, all of those should be shown in the Skin analysis results: Primary Concerns.
-4. No other skin concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images.</t>
-    </r>
   </si>
   <si>
     <t>Story Point</t>
@@ -1917,6 +2470,765 @@
   <si>
     <t>T Shirt Sizing</t>
   </si>
+  <si>
+    <t>upload an acceptable quality picture of my skin 
+and press on submit button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I can have my skin image analysed for visible skin concerns and proceed to the questionnaire to provide additional information about my skin. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user should only be allowed to proceed if the uploaded image passes all image-quality checks for blurriness, lighting, and resolution.
+2. Once the image passes the quality checks, the image should be submitted to the Visual AI component for skin-concern analysis.
+3. The Visual AI component should return the visible skin concerns detected from the uploaded image along with an AI-generated explanation for each detected concern.
+4. Detected image-based skin concerns must belong only to the valid concern series SC0001–SC0019 and SC1001–SC1009.
+5. If no skin concern is detected from the image, the Visual AI result should indicate that no visible skin concern was detected rather than assigning an unrelated concern.
+6. The image-analysis results should be retained and passed to the concern fusion stage so that they can later be combined with the questionnaire results.
+7. After successful Visual AI analysis, the user should be redirected to the skin questionnaire.
+</t>
+  </si>
+  <si>
+    <t>Test User Story 1 acceptance criteria</t>
+  </si>
+  <si>
+    <t>Test User Story 2 acceptance criteria</t>
+  </si>
+  <si>
+    <t>Test User Story 3 acceptance criteria</t>
+  </si>
+  <si>
+    <t>Test User Story 4 acceptance criteria</t>
+  </si>
+  <si>
+    <t>Receive image from Shopify widget</t>
+  </si>
+  <si>
+    <t>Validate image file type</t>
+  </si>
+  <si>
+    <t>Calculate image sharpness</t>
+  </si>
+  <si>
+    <t>Calculate image brightness/lighting</t>
+  </si>
+  <si>
+    <t>Define/configure blur rejection threshold</t>
+  </si>
+  <si>
+    <t>Define/configure low-light rejection threshold</t>
+  </si>
+  <si>
+    <t>Define/configure minimum resolution threshold</t>
+  </si>
+  <si>
+    <t>Combine all image-quality checks</t>
+  </si>
+  <si>
+    <t>Reject image if any required quality check fails</t>
+  </si>
+  <si>
+    <t>Accept image only if all required checks pass</t>
+  </si>
+  <si>
+    <t>Return image-validation result to frontend</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Display </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>"Your image is not valid. Take another image with better quality"</t>
+    </r>
+  </si>
+  <si>
+    <t>Redirect user back to selfie capture</t>
+  </si>
+  <si>
+    <t>Test invalid file type</t>
+  </si>
+  <si>
+    <t>Test unreadable image</t>
+  </si>
+  <si>
+    <t>Test low-resolution image</t>
+  </si>
+  <si>
+    <t>Test blurry image</t>
+  </si>
+  <si>
+    <t>Test low-light image</t>
+  </si>
+  <si>
+    <t>Test combinations of quality failures</t>
+  </si>
+  <si>
+    <t>Test valid image</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define Visual AI response JSON schema based on </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>image_detection.json</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define supported image-detectable concern IDs: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SC0001–SC0019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>SC1001–SC1009</t>
+    </r>
+  </si>
+  <si>
+    <t>Define Visual AI system prompt</t>
+  </si>
+  <si>
+    <t>Define image-analysis instructions</t>
+  </si>
+  <si>
+    <t>Define skin-concern detection rules</t>
+  </si>
+  <si>
+    <t>Restrict output to supported concern IDs</t>
+  </si>
+  <si>
+    <t>Define no-concern behaviour</t>
+  </si>
+  <si>
+    <t>Require AI explanation for detected concerns</t>
+  </si>
+  <si>
+    <t>Require JSON-only response</t>
+  </si>
+  <si>
+    <t>Send accepted image to Visual AI</t>
+  </si>
+  <si>
+    <t>Validate Visual AI response against JSON schema</t>
+  </si>
+  <si>
+    <t>Validate returned concern IDs</t>
+  </si>
+  <si>
+    <t>Handle unsupported concern IDs</t>
+  </si>
+  <si>
+    <t>Handle empty/no-concern response</t>
+  </si>
+  <si>
+    <t>Handle malformed AI response</t>
+  </si>
+  <si>
+    <t>Handle AI/API failure</t>
+  </si>
+  <si>
+    <t>Store detected concern IDs</t>
+  </si>
+  <si>
+    <t>Store AI-generated explanations</t>
+  </si>
+  <si>
+    <t>Store raw detection JSON</t>
+  </si>
+  <si>
+    <t>Redirect user to questionnaire after successful Visual AI analysis</t>
+  </si>
+  <si>
+    <t>Test Visual AI response validation</t>
+  </si>
+  <si>
+    <t>Test supported concern IDs</t>
+  </si>
+  <si>
+    <t>Test unsupported concern IDs</t>
+  </si>
+  <si>
+    <t>Test duplicate concern handling</t>
+  </si>
+  <si>
+    <t>Test multiple detected concerns</t>
+  </si>
+  <si>
+    <t>Test no visible concern</t>
+  </si>
+  <si>
+    <t>Test malformed AI response</t>
+  </si>
+  <si>
+    <t>Test AI/API failure</t>
+  </si>
+  <si>
+    <t>Display questionnaire to user</t>
+  </si>
+  <si>
+    <t>Collect questionnaire answers</t>
+  </si>
+  <si>
+    <t>Validate required questionnaire fields</t>
+  </si>
+  <si>
+    <t>Submit questionnaire for LLM analysis</t>
+  </si>
+  <si>
+    <t>Define questionnaire-analysis LLM prompt</t>
+  </si>
+  <si>
+    <t>Pass questionnaire JSON to LLM</t>
+  </si>
+  <si>
+    <t>Define skin-type extraction</t>
+  </si>
+  <si>
+    <t>Define sensitivity extraction</t>
+  </si>
+  <si>
+    <t>Define questionnaire-only concern handling</t>
+  </si>
+  <si>
+    <t>Validate LLM response</t>
+  </si>
+  <si>
+    <t>Handle LLM/API failure</t>
+  </si>
+  <si>
+    <t>Store LLM-generated explanations</t>
+  </si>
+  <si>
+    <t>Retrieve image-based detection results</t>
+  </si>
+  <si>
+    <t>Retrieve questionnaire-based detection results</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Match results using </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>skin_concern_id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Calculate </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>image_skin_concern_exists OR questionnaire_skin_concern_exists</t>
+    </r>
+  </si>
+  <si>
+    <t>Combine image and questionnaire explanations</t>
+  </si>
+  <si>
+    <t>Handle concerns detected only from image</t>
+  </si>
+  <si>
+    <t>Handle concerns detected only from questionnaire</t>
+  </si>
+  <si>
+    <t>Handle concerns detected by both</t>
+  </si>
+  <si>
+    <t>Handle no detected concerns</t>
+  </si>
+  <si>
+    <t>Validate final combined concern set</t>
+  </si>
+  <si>
+    <t>Retrieve combined skin concerns</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Retrieve </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>active_benefit_score</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> data</t>
+    </r>
+  </si>
+  <si>
+    <t>Calculate/rank active candidates</t>
+  </si>
+  <si>
+    <t>Retrieve applicable bases using questionnaire/session information</t>
+  </si>
+  <si>
+    <t>Apply age suitability</t>
+  </si>
+  <si>
+    <t>Apply skin-type suitability</t>
+  </si>
+  <si>
+    <t>Apply climate/location considerations</t>
+  </si>
+  <si>
+    <t>Apply acne-suitability requirements</t>
+  </si>
+  <si>
+    <t>Apply questionnaire preferences</t>
+  </si>
+  <si>
+    <t>Check base-active compatibility</t>
+  </si>
+  <si>
+    <t>Produce candidate bases</t>
+  </si>
+  <si>
+    <t>Produce candidate actives</t>
+  </si>
+  <si>
+    <t>Pass candidate information and relevant RAG information to LLM</t>
+  </si>
+  <si>
+    <t>Generate recommended base</t>
+  </si>
+  <si>
+    <t>Generate recommended active ingredients</t>
+  </si>
+  <si>
+    <t>Generate explanation for selected base</t>
+  </si>
+  <si>
+    <t>Generate explanation for selected actives</t>
+  </si>
+  <si>
+    <t>Ensure selected actives address detected concerns</t>
+  </si>
+  <si>
+    <t>Ensure selected actives are compatible with selected base</t>
+  </si>
+  <si>
+    <t>Generate formulation information</t>
+  </si>
+  <si>
+    <t>Validate recommendation output</t>
+  </si>
+  <si>
+    <t>Store recommendation explanations</t>
+  </si>
+  <si>
+    <t>Store recommendation scores/ranks where applicable</t>
+  </si>
+  <si>
+    <t>Build final response containing user full name</t>
+  </si>
+  <si>
+    <t>Include combined primary skin concerns</t>
+  </si>
+  <si>
+    <t>Include skin type</t>
+  </si>
+  <si>
+    <t>Include sensitivity level</t>
+  </si>
+  <si>
+    <t>Include recommended base</t>
+  </si>
+  <si>
+    <t>Include recommended active ingredients</t>
+  </si>
+  <si>
+    <t>Include active percentages/quantities</t>
+  </si>
+  <si>
+    <t>Include formulation weight</t>
+  </si>
+  <si>
+    <t>Include formulation explanation</t>
+  </si>
+  <si>
+    <t>Include formulation/recommendation ID</t>
+  </si>
+  <si>
+    <t>Return recommendation response to Shopify widget</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Display </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>"Your skin looks perfect!"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when no concern is detected</t>
+    </r>
+  </si>
+  <si>
+    <t>Display formulation information</t>
+  </si>
+  <si>
+    <t>Handle no-compatible-recommendation case</t>
+  </si>
+  <si>
+    <t>Handle database failure</t>
+  </si>
+  <si>
+    <t>Handle invalid recommendation/formulation</t>
+  </si>
+  <si>
+    <t>Return appropriate frontend error response</t>
+  </si>
+  <si>
+    <t>Test questionnaire submission</t>
+  </si>
+  <si>
+    <t>Test questionnaire LLM analysis</t>
+  </si>
+  <si>
+    <t>Test concern fusion</t>
+  </si>
+  <si>
+    <t>Test image/questionnaire OR logic</t>
+  </si>
+  <si>
+    <t>Test candidate generation</t>
+  </si>
+  <si>
+    <t>Test base selection</t>
+  </si>
+  <si>
+    <t>Test active selection</t>
+  </si>
+  <si>
+    <t>Test base-active compatibility</t>
+  </si>
+  <si>
+    <t>Test formulation validation</t>
+  </si>
+  <si>
+    <t>Test 100 g formulation requirement</t>
+  </si>
+  <si>
+    <t>Test recommendation persistence</t>
+  </si>
+  <si>
+    <t>Test final recommendation response</t>
+  </si>
+  <si>
+    <t>Test no-concern scenario</t>
+  </si>
+  <si>
+    <t>Test recommendation error handling</t>
+  </si>
+  <si>
+    <t>Identify required Shopify cart/API capability</t>
+  </si>
+  <si>
+    <t>Identify Shopify product/variant representing the formulation</t>
+  </si>
+  <si>
+    <t>Define formulation metadata required by Shopify cart</t>
+  </si>
+  <si>
+    <t>Create/test Shopify product or variant</t>
+  </si>
+  <si>
+    <t>Receive formulation ID from frontend</t>
+  </si>
+  <si>
+    <t>Retrieve saved formulation</t>
+  </si>
+  <si>
+    <t>Verify formulation belongs to the logged-in customer/session</t>
+  </si>
+  <si>
+    <t>Add recommended formulation/product to Shopify cart</t>
+  </si>
+  <si>
+    <t>Attach required formulation metadata</t>
+  </si>
+  <si>
+    <t>Call Add to Cart API</t>
+  </si>
+  <si>
+    <t>Display successful cart-addition state</t>
+  </si>
+  <si>
+    <t>Handle Add to Cart failure</t>
+  </si>
+  <si>
+    <t>Test formulation ID validation</t>
+  </si>
+  <si>
+    <t>Test customer/formulation ownership</t>
+  </si>
+  <si>
+    <t>Test Shopify cart item creation</t>
+  </si>
+  <si>
+    <t>Test formulation metadata</t>
+  </si>
+  <si>
+    <t>Test successful Add to Cart</t>
+  </si>
+  <si>
+    <t>Test Add to Cart failure</t>
+  </si>
+  <si>
+    <t>Test duplicate submission prevention</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Associate image with current </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customer_session</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note accepted image in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skin_image</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store Visual AI result in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>session_skin_concern_detection</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store questionnaire answers in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>questionnaire_response</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Associate questionnaire response with current</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>customer_session</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store questionnaire detection result in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>session_skin_concern_detection</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store combined result in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>session_skin_concern</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Retrieve relevant </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>concern_benefit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mappings</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>recommendation_run</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store selected base in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>recommendation_base</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store selected actives in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>recommendation_active</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store final formatted response in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>recommendation_output</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1925,7 +3237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1979,6 +3291,38 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2128,7 +3472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2313,6 +3657,22 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2328,10 +3688,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2339,20 +3705,8 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2360,16 +3714,38 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3180,20 +4556,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="87" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+      <c r="J1" s="87"/>
+      <c r="K1" s="87"/>
+      <c r="L1" s="87"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="15" t="s">
@@ -3234,10 +4610,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="58.8" customHeight="1">
-      <c r="A3" s="80">
+      <c r="A3" s="84">
         <v>1</v>
       </c>
-      <c r="B3" s="80">
+      <c r="B3" s="84">
         <v>1</v>
       </c>
       <c r="C3">
@@ -3249,25 +4625,25 @@
       <c r="E3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="81">
+      <c r="F3" s="88">
         <v>46252</v>
       </c>
-      <c r="G3" s="80" t="s">
+      <c r="G3" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="88">
         <v>46259</v>
       </c>
-      <c r="I3" s="80" t="s">
+      <c r="I3" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="80" t="s">
+      <c r="J3" s="84" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="54.6" customHeight="1">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
       <c r="C4">
         <v>1.2</v>
       </c>
@@ -3277,15 +4653,15 @@
       <c r="E4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="81"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
     </row>
     <row r="5" spans="1:12" ht="33.6" customHeight="1">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
+      <c r="A5" s="84"/>
+      <c r="B5" s="84"/>
       <c r="C5">
         <v>1.3</v>
       </c>
@@ -3295,15 +4671,15 @@
       <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="81"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="J5" s="84"/>
     </row>
     <row r="6" spans="1:12" ht="26.4" customHeight="1">
-      <c r="A6" s="80"/>
-      <c r="B6" s="80"/>
+      <c r="A6" s="84"/>
+      <c r="B6" s="84"/>
       <c r="C6">
         <v>1.4</v>
       </c>
@@ -3313,15 +4689,15 @@
       <c r="E6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:12" ht="72.599999999999994" customHeight="1">
-      <c r="A7" s="80"/>
-      <c r="B7" s="80"/>
+      <c r="A7" s="84"/>
+      <c r="B7" s="84"/>
       <c r="C7">
         <v>1.5</v>
       </c>
@@ -3331,15 +4707,15 @@
       <c r="E7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="81"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
     </row>
     <row r="8" spans="1:12" ht="28.8">
-      <c r="A8" s="80"/>
-      <c r="B8" s="80">
+      <c r="A8" s="84"/>
+      <c r="B8" s="84">
         <v>2</v>
       </c>
       <c r="C8">
@@ -3351,23 +4727,23 @@
       <c r="E8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="81">
+      <c r="F8" s="88">
         <v>46252</v>
       </c>
-      <c r="G8" s="80" t="s">
+      <c r="G8" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="88">
         <v>46258</v>
       </c>
-      <c r="I8" s="80" t="s">
+      <c r="I8" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="80"/>
+      <c r="J8" s="84"/>
     </row>
     <row r="9" spans="1:12" ht="28.8">
-      <c r="A9" s="80"/>
-      <c r="B9" s="80"/>
+      <c r="A9" s="84"/>
+      <c r="B9" s="84"/>
       <c r="C9">
         <v>2.2000000000000002</v>
       </c>
@@ -3377,15 +4753,15 @@
       <c r="E9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="81"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="80"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
     </row>
     <row r="10" spans="1:12" ht="43.2">
-      <c r="A10" s="80"/>
-      <c r="B10" s="80"/>
+      <c r="A10" s="84"/>
+      <c r="B10" s="84"/>
       <c r="C10">
         <v>2.2999999999999998</v>
       </c>
@@ -3395,15 +4771,15 @@
       <c r="E10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="81"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="80"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
     </row>
     <row r="11" spans="1:12" ht="28.8">
-      <c r="A11" s="80"/>
-      <c r="B11" s="80">
+      <c r="A11" s="84"/>
+      <c r="B11" s="84">
         <v>3</v>
       </c>
       <c r="C11">
@@ -3415,15 +4791,15 @@
       <c r="E11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="81"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
     </row>
     <row r="12" spans="1:12" ht="28.8">
-      <c r="A12" s="80"/>
-      <c r="B12" s="80"/>
+      <c r="A12" s="84"/>
+      <c r="B12" s="84"/>
       <c r="C12">
         <v>3.2</v>
       </c>
@@ -3445,11 +4821,11 @@
       <c r="I12" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="80"/>
+      <c r="J12" s="84"/>
     </row>
     <row r="13" spans="1:12" ht="28.8">
-      <c r="A13" s="80"/>
-      <c r="B13" s="80">
+      <c r="A13" s="84"/>
+      <c r="B13" s="84">
         <v>4</v>
       </c>
       <c r="C13">
@@ -3473,11 +4849,11 @@
       <c r="I13" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="80"/>
+      <c r="J13" s="84"/>
     </row>
     <row r="14" spans="1:12" ht="28.8">
-      <c r="A14" s="80"/>
-      <c r="B14" s="80"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="84"/>
       <c r="C14">
         <v>4.2</v>
       </c>
@@ -3499,10 +4875,10 @@
       <c r="I14" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="80"/>
+      <c r="J14" s="84"/>
     </row>
     <row r="15" spans="1:12" ht="28.8">
-      <c r="A15" s="80"/>
+      <c r="A15" s="84"/>
       <c r="B15" s="14">
         <v>9</v>
       </c>
@@ -3515,15 +4891,15 @@
       <c r="E15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="81" t="s">
+      <c r="F15" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
       <c r="I15" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="J15" s="80"/>
+      <c r="J15" s="84"/>
       <c r="L15" t="s">
         <v>98</v>
       </c>
@@ -3532,10 +4908,10 @@
       <c r="A16" s="23"/>
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="78" t="s">
+      <c r="D16" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="78"/>
+      <c r="E16" s="86"/>
       <c r="F16" s="26">
         <v>46198</v>
       </c>
@@ -3546,10 +4922,10 @@
       <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="86.4">
-      <c r="A17" s="80">
+      <c r="A17" s="84">
         <v>2</v>
       </c>
-      <c r="B17" s="80">
+      <c r="B17" s="84">
         <v>5</v>
       </c>
       <c r="C17">
@@ -3564,19 +4940,19 @@
       <c r="F17" s="21">
         <v>46260</v>
       </c>
-      <c r="G17" s="83" t="s">
+      <c r="G17" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="82">
+      <c r="H17" s="83">
         <v>46262</v>
       </c>
-      <c r="I17" s="83" t="s">
+      <c r="I17" s="82" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8">
-      <c r="A18" s="80"/>
-      <c r="B18" s="80"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="84"/>
       <c r="C18">
         <v>5.2</v>
       </c>
@@ -3586,13 +4962,13 @@
       <c r="E18" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
     </row>
     <row r="19" spans="1:9" ht="86.4">
-      <c r="A19" s="80"/>
-      <c r="B19" s="80">
+      <c r="A19" s="84"/>
+      <c r="B19" s="84">
         <v>6</v>
       </c>
       <c r="C19">
@@ -3604,22 +4980,22 @@
       <c r="E19" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="82">
+      <c r="F19" s="83">
         <v>46260</v>
       </c>
-      <c r="G19" s="83" t="s">
+      <c r="G19" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="82">
+      <c r="H19" s="83">
         <v>46267</v>
       </c>
-      <c r="I19" s="83" t="s">
+      <c r="I19" s="82" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8">
-      <c r="A20" s="80"/>
-      <c r="B20" s="80"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="84"/>
       <c r="C20">
         <v>6.2</v>
       </c>
@@ -3629,14 +5005,14 @@
       <c r="E20" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
+      <c r="I20" s="82"/>
     </row>
     <row r="21" spans="1:9" ht="43.8" customHeight="1">
-      <c r="A21" s="80"/>
-      <c r="B21" s="80"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="18">
         <v>6.3</v>
       </c>
@@ -3646,14 +5022,14 @@
       <c r="E21" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="82"/>
     </row>
     <row r="22" spans="1:9" ht="28.8">
-      <c r="A22" s="80"/>
-      <c r="B22" s="80"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="84"/>
       <c r="C22">
         <v>6.4</v>
       </c>
@@ -3663,14 +5039,14 @@
       <c r="E22" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
     </row>
     <row r="23" spans="1:9" ht="28.8">
-      <c r="A23" s="80"/>
-      <c r="B23" s="80">
+      <c r="A23" s="84"/>
+      <c r="B23" s="84">
         <v>7</v>
       </c>
       <c r="C23">
@@ -3682,22 +5058,22 @@
       <c r="E23" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="82">
+      <c r="F23" s="83">
         <v>46260</v>
       </c>
-      <c r="G23" s="83" t="s">
+      <c r="G23" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="82">
+      <c r="H23" s="83">
         <v>46267</v>
       </c>
-      <c r="I23" s="83" t="s">
+      <c r="I23" s="82" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="80"/>
-      <c r="B24" s="80"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="84"/>
       <c r="C24">
         <v>7.2</v>
       </c>
@@ -3707,14 +5083,14 @@
       <c r="E24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
     </row>
     <row r="25" spans="1:9" ht="43.2">
-      <c r="A25" s="80"/>
-      <c r="B25" s="80">
+      <c r="A25" s="84"/>
+      <c r="B25" s="84">
         <v>8</v>
       </c>
       <c r="C25">
@@ -3726,22 +5102,22 @@
       <c r="E25" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="84">
+      <c r="F25" s="85">
         <v>46260</v>
       </c>
-      <c r="G25" s="83" t="s">
+      <c r="G25" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="82">
+      <c r="H25" s="83">
         <v>46267</v>
       </c>
-      <c r="I25" s="83" t="s">
+      <c r="I25" s="82" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28.8">
-      <c r="A26" s="80"/>
-      <c r="B26" s="80"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="84"/>
       <c r="C26">
         <v>8.1999999999999993</v>
       </c>
@@ -3751,10 +5127,10 @@
       <c r="E26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F26" s="84"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="24"/>
@@ -3774,10 +5150,10 @@
       <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9" ht="43.2">
-      <c r="A28" s="80">
+      <c r="A28" s="84">
         <v>3</v>
       </c>
-      <c r="B28" s="80">
+      <c r="B28" s="84">
         <v>9</v>
       </c>
       <c r="C28">
@@ -3789,22 +5165,22 @@
       <c r="E28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="82">
+      <c r="F28" s="83">
         <v>46268</v>
       </c>
-      <c r="G28" s="83" t="s">
+      <c r="G28" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="82">
+      <c r="H28" s="83">
         <v>46275</v>
       </c>
-      <c r="I28" s="83" t="s">
+      <c r="I28" s="82" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.8">
-      <c r="A29" s="80"/>
-      <c r="B29" s="80"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="84"/>
       <c r="C29">
         <v>9.1999999999999993</v>
       </c>
@@ -3814,14 +5190,14 @@
       <c r="E29" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="82"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="82"/>
-      <c r="I29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="82"/>
     </row>
     <row r="30" spans="1:9" ht="28.8">
-      <c r="A30" s="80"/>
-      <c r="B30" s="80"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="84"/>
       <c r="C30">
         <v>9.3000000000000007</v>
       </c>
@@ -3831,44 +5207,17 @@
       <c r="E30" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F30" s="82"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="82"/>
-      <c r="I30" s="83"/>
+      <c r="F30" s="83"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="82"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="80"/>
-      <c r="B31" s="80"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="G19:G22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I19:I22"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A17:A26"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B22"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="J3:J15"/>
@@ -3885,6 +5234,33 @@
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A17:A26"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="H19:H22"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I19:I22"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3931,11 +5307,11 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="59"/>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
       <c r="E2" s="60"/>
       <c r="F2" s="60"/>
       <c r="G2" s="60"/>
@@ -3951,7 +5327,7 @@
         <v>104</v>
       </c>
       <c r="B3" s="53" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C3" s="53" t="s">
         <v>130</v>
@@ -3987,19 +5363,19 @@
         <v>97</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P3" s="15" t="s">
         <v>104</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R3" s="15" t="s">
         <v>136</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="T3" s="15" t="s">
         <v>101</v>
@@ -4620,25 +5996,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="72" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
+      <c r="A1" s="78" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
     </row>
     <row r="2" spans="1:10" s="15" customFormat="1">
       <c r="A2" s="59" t="s">
         <v>104</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2" s="59" t="s">
         <v>5</v>
@@ -4647,7 +6023,7 @@
         <v>136</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F2" s="59" t="s">
         <v>106</v>
@@ -4656,7 +6032,7 @@
         <v>101</v>
       </c>
       <c r="H2" s="59" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I2" s="59" t="s">
         <v>97</v>
@@ -4666,1914 +6042,1889 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="B3" s="71">
+      <c r="B3" s="77">
         <v>1</v>
       </c>
       <c r="C3" s="76">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="90" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="90" cm="1">
+        <v>160</v>
+      </c>
+      <c r="E3" s="74" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="74" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="71"/>
+      <c r="B4" s="77"/>
       <c r="C4" s="76"/>
       <c r="D4" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
+        <v>161</v>
+      </c>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="B5" s="71"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="76"/>
       <c r="D5" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
+        <v>162</v>
+      </c>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="B6" s="71"/>
+      <c r="B6" s="77"/>
       <c r="C6" s="76"/>
       <c r="D6" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
+        <v>163</v>
+      </c>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="B7" s="71"/>
+      <c r="B7" s="77"/>
       <c r="C7" s="76"/>
       <c r="D7" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="90"/>
-      <c r="F7" s="90"/>
+        <v>164</v>
+      </c>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="71"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="76"/>
       <c r="D8" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
+        <v>165</v>
+      </c>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="B9" s="71"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="76"/>
       <c r="D9" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
+        <v>166</v>
+      </c>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="B10" s="71"/>
+      <c r="B10" s="77"/>
       <c r="C10" s="76"/>
       <c r="D10" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
+        <v>167</v>
+      </c>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="B11" s="71"/>
+      <c r="B11" s="77"/>
       <c r="C11" s="76"/>
       <c r="D11" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
+        <v>168</v>
+      </c>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
     </row>
     <row r="12" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B12" s="71"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="76"/>
       <c r="D12" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
+        <v>169</v>
+      </c>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
     </row>
     <row r="13" spans="1:10" ht="14.4" customHeight="1">
-      <c r="B13" s="71"/>
-      <c r="C13" s="77" t="s">
-        <v>360</v>
+      <c r="B13" s="77"/>
+      <c r="C13" s="75" t="s">
+        <v>358</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E13" s="90" t="s">
-        <v>146</v>
-      </c>
-      <c r="F13" s="90" cm="1">
+        <v>170</v>
+      </c>
+      <c r="E13" s="74" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" s="74" cm="1">
         <f t="array" ref="F13">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="B14" s="71"/>
-      <c r="C14" s="77"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="75"/>
       <c r="D14" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="77"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="77"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="71"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="13" t="s">
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="77"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="71"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="71"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="E17" s="90"/>
-      <c r="F17" s="90"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="71"/>
+      <c r="B18" s="77"/>
       <c r="C18" s="76">
         <v>1.3</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E18" s="90" t="s">
-        <v>145</v>
-      </c>
-      <c r="F18" s="90" cm="1">
+        <v>175</v>
+      </c>
+      <c r="E18" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="74" cm="1">
         <f t="array" ref="F18">_xlfn.SWITCH(E18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="71"/>
+      <c r="B19" s="77"/>
       <c r="C19" s="76"/>
       <c r="D19" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
+        <v>176</v>
+      </c>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
     </row>
     <row r="20" spans="2:6" ht="28.8" customHeight="1">
-      <c r="B20" s="71"/>
+      <c r="B20" s="77"/>
       <c r="C20" s="76"/>
       <c r="D20" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
+        <v>177</v>
+      </c>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
     </row>
     <row r="21" spans="2:6" ht="28.8" customHeight="1">
-      <c r="B21" s="71"/>
+      <c r="B21" s="77"/>
       <c r="C21" s="76"/>
       <c r="D21" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
+        <v>178</v>
+      </c>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
     </row>
     <row r="22" spans="2:6" ht="28.8" customHeight="1">
-      <c r="B22" s="71"/>
+      <c r="B22" s="77"/>
       <c r="C22" s="76"/>
       <c r="D22" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="77"/>
+      <c r="C23" s="77">
+        <v>1.4</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23" s="71"/>
-      <c r="C23" s="71">
-        <v>1.4</v>
-      </c>
-      <c r="D23" s="13" t="s">
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="13" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="13" t="s">
+    <row r="26" spans="2:6">
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="13" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="13" t="s">
+    <row r="27" spans="2:6" ht="28.8" customHeight="1">
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="13" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="2:6">
-      <c r="B26" s="71"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="13" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" ht="28.8" customHeight="1">
-      <c r="B27" s="71"/>
-      <c r="C27" s="71"/>
-      <c r="D27" s="13" t="s">
-        <v>186</v>
-      </c>
-    </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="71">
+      <c r="B28" s="77">
         <v>2</v>
       </c>
       <c r="C28" s="68">
         <v>2.1</v>
       </c>
       <c r="D28" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="77"/>
+      <c r="C29" s="77">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="71"/>
-      <c r="C29" s="71">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D29" s="13" t="s">
+    <row r="30" spans="2:6">
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="77"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="28.8" customHeight="1">
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="13" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="13" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="13" t="s">
+    <row r="33" spans="2:4">
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="13" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="2:6" ht="28.8" customHeight="1">
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="13" t="s">
+    <row r="34" spans="2:4">
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="13" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="2:4">
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="13" t="s">
+    <row r="35" spans="2:4">
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="13" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="13" t="s">
+    <row r="36" spans="2:4">
+      <c r="B36" s="77"/>
+      <c r="C36" s="77">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D36" s="13" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="13" t="s">
+    <row r="37" spans="2:4">
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="13" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="71"/>
-      <c r="C36" s="71">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D36" s="13" t="s">
+    <row r="38" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B38" s="77"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="13" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="13" t="s">
+    <row r="39" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="13" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B38" s="71"/>
-      <c r="C38" s="71"/>
-      <c r="D38" s="13" t="s">
+    <row r="41" spans="2:4">
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="13" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="39" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B39" s="71"/>
-      <c r="C39" s="71"/>
-      <c r="D39" s="13" t="s">
+    <row r="42" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B42" s="77"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B43" s="77"/>
+      <c r="C43" s="77">
+        <v>2.4</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="77"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="77"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="77"/>
+      <c r="C48" s="77">
+        <v>2.5</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="77"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="77"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="77"/>
+      <c r="C51" s="77"/>
+      <c r="D51" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
+      <c r="D53" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="77"/>
+      <c r="C54" s="77">
+        <v>2.6</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B55" s="77"/>
+      <c r="C55" s="77"/>
+      <c r="D55" s="67" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="77"/>
+      <c r="C57" s="77"/>
+      <c r="D57" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="77">
+        <v>3</v>
+      </c>
+      <c r="C58" s="77">
+        <v>3.1</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="77"/>
+      <c r="C59" s="77"/>
+      <c r="D59" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="77"/>
+      <c r="C60" s="77"/>
+      <c r="D60" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
+      <c r="D62" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="77"/>
+      <c r="C63" s="77"/>
+      <c r="D63" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
+      <c r="D64" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="77"/>
+      <c r="C65" s="77">
+        <v>3.2</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B66" s="77"/>
+      <c r="C66" s="77"/>
+      <c r="D66" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="77"/>
+      <c r="C67" s="77"/>
+      <c r="D67" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" s="77"/>
+      <c r="C68" s="77"/>
+      <c r="D68" s="13" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" s="77"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="77"/>
+      <c r="C70" s="77"/>
+      <c r="D70" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" s="77"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="77"/>
+      <c r="C72" s="77">
+        <v>3.3</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="77"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="13" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="77"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="13" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="77"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="13" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="77"/>
+      <c r="C76" s="77"/>
+      <c r="D76" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B77" s="77"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="13" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" s="77"/>
+      <c r="C78" s="77">
+        <v>3.4</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B79" s="77"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="13" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="B80" s="77"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4">
+      <c r="B81" s="77"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="B82" s="77"/>
+      <c r="C82" s="77"/>
+      <c r="D82" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B83" s="77"/>
+      <c r="C83" s="77"/>
+      <c r="D83" s="13" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4">
+      <c r="B84" s="77"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="13" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="B85" s="77"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B86" s="77"/>
+      <c r="C86" s="77"/>
+      <c r="D86" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" ht="28.8" customHeight="1">
+      <c r="B87" s="77"/>
+      <c r="C87" s="77"/>
+      <c r="D87" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="13" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="13" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B43" s="71"/>
-      <c r="C43" s="71">
-        <v>2.4</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="13" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" s="71"/>
-      <c r="C45" s="71"/>
-      <c r="D45" s="13" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
-      <c r="D47" s="13" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4">
-      <c r="B48" s="71"/>
-      <c r="C48" s="71">
-        <v>2.5</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4">
-      <c r="B49" s="71"/>
-      <c r="C49" s="71"/>
-      <c r="D49" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4">
-      <c r="B50" s="71"/>
-      <c r="C50" s="71"/>
-      <c r="D50" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4">
-      <c r="B51" s="71"/>
-      <c r="C51" s="71"/>
-      <c r="D51" s="13" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B52" s="71"/>
-      <c r="C52" s="71"/>
-      <c r="D52" s="13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B53" s="71"/>
-      <c r="C53" s="71"/>
-      <c r="D53" s="13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" s="71"/>
-      <c r="C54" s="71">
-        <v>2.6</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B55" s="71"/>
-      <c r="C55" s="71"/>
-      <c r="D55" s="67" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B56" s="71"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" s="71"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="B58" s="71">
-        <v>3</v>
-      </c>
-      <c r="C58" s="71">
+    <row r="88" spans="2:4">
+      <c r="B88" s="77"/>
+      <c r="C88" s="77">
+        <v>3.5</v>
+      </c>
+      <c r="D88" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="B89" s="77"/>
+      <c r="C89" s="77"/>
+      <c r="D89" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="77"/>
+      <c r="C90" s="77"/>
+      <c r="D90" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="77"/>
+      <c r="C91" s="77"/>
+      <c r="D91" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" s="77"/>
+      <c r="C92" s="77"/>
+      <c r="D92" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" s="77"/>
+      <c r="C93" s="77"/>
+      <c r="D93" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" s="77"/>
+      <c r="C94" s="77"/>
+      <c r="D94" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" s="77"/>
+      <c r="C95" s="77">
+        <v>3.6</v>
+      </c>
+      <c r="D95" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" s="77"/>
+      <c r="C96" s="77"/>
+      <c r="D96" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" s="77"/>
+      <c r="C97" s="77"/>
+      <c r="D97" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" s="77"/>
+      <c r="C98" s="77"/>
+      <c r="D98" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" s="77"/>
+      <c r="C99" s="77"/>
+      <c r="D99" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" s="77"/>
+      <c r="C100" s="77"/>
+      <c r="D100" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="77"/>
+      <c r="C101" s="77"/>
+      <c r="D101" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" s="77"/>
+      <c r="C102" s="77"/>
+      <c r="D102" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" s="77"/>
+      <c r="C103" s="77"/>
+      <c r="D103" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" s="77"/>
+      <c r="C104" s="77"/>
+      <c r="D104" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" s="77"/>
+      <c r="C105" s="77"/>
+      <c r="D105" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="77"/>
+      <c r="C106" s="77"/>
+      <c r="D106" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" s="77"/>
+      <c r="C107" s="77"/>
+      <c r="D107" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="77"/>
+      <c r="C108" s="77"/>
+      <c r="D108" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" s="77"/>
+      <c r="C109" s="77"/>
+      <c r="D109" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="B110" s="77"/>
+      <c r="C110" s="77"/>
+      <c r="D110" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="B111" s="77"/>
+      <c r="C111" s="77"/>
+      <c r="D111" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="B112" s="77"/>
+      <c r="C112" s="77">
+        <v>3.7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="B113" s="77"/>
+      <c r="C113" s="77"/>
+      <c r="D113" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="77"/>
+      <c r="C114" s="77"/>
+      <c r="D114" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" s="77"/>
+      <c r="C115" s="77"/>
+      <c r="D115" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="77"/>
+      <c r="C116" s="77"/>
+      <c r="D116" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="77"/>
+      <c r="C117" s="77"/>
+      <c r="D117" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="77"/>
+      <c r="C118" s="77">
+        <v>3.8</v>
+      </c>
+      <c r="D118" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="77"/>
+      <c r="C119" s="77"/>
+      <c r="D119" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="B120" s="77"/>
+      <c r="C120" s="77"/>
+      <c r="D120" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" s="77"/>
+      <c r="C121" s="77"/>
+      <c r="D121" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="B122" s="77"/>
+      <c r="C122" s="77"/>
+      <c r="D122" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="B123" s="77"/>
+      <c r="C123" s="77"/>
+      <c r="D123" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="B124" s="77"/>
+      <c r="C124" s="77"/>
+      <c r="D124" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" s="77"/>
+      <c r="C125" s="77"/>
+      <c r="D125" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="B126" s="77"/>
+      <c r="C126" s="77"/>
+      <c r="D126" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="B127" s="77"/>
+      <c r="C127" s="80">
+        <v>3.9</v>
+      </c>
+      <c r="D127" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="77"/>
+      <c r="C128" s="80"/>
+      <c r="D128" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="77"/>
+      <c r="C129" s="80"/>
+      <c r="D129" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="77"/>
+      <c r="C130" s="80"/>
+      <c r="D130" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
+      <c r="B131" s="77"/>
+      <c r="C131" s="80"/>
+      <c r="D131" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
+      <c r="B132" s="77"/>
+      <c r="C132" s="80"/>
+      <c r="D132" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
+      <c r="B133" s="77"/>
+      <c r="C133" s="80"/>
+      <c r="D133" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4">
+      <c r="B134" s="77"/>
+      <c r="C134" s="80"/>
+      <c r="D134" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4">
+      <c r="B135" s="77"/>
+      <c r="C135" s="80"/>
+      <c r="D135" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
+      <c r="B136" s="77"/>
+      <c r="C136" s="80"/>
+      <c r="D136" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
+      <c r="B137" s="77"/>
+      <c r="C137" s="80"/>
+      <c r="D137" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
+      <c r="B138" s="77"/>
+      <c r="C138" s="81">
         <v>3.1</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="B59" s="71"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60" s="71"/>
-      <c r="C60" s="71"/>
-      <c r="D60" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="13" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="B62" s="71"/>
-      <c r="C62" s="71"/>
-      <c r="D62" s="13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="B63" s="71"/>
-      <c r="C63" s="71"/>
-      <c r="D63" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64" s="71"/>
-      <c r="C64" s="71"/>
-      <c r="D64" s="13" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" s="71"/>
-      <c r="C65" s="71">
-        <v>3.2</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B66" s="71"/>
-      <c r="C66" s="71"/>
-      <c r="D66" s="13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4">
-      <c r="B67" s="71"/>
-      <c r="C67" s="71"/>
-      <c r="D67" s="13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4">
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="13" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4">
-      <c r="B69" s="71"/>
-      <c r="C69" s="71"/>
-      <c r="D69" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" s="71"/>
-      <c r="C70" s="71"/>
-      <c r="D70" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" s="71"/>
-      <c r="C71" s="71"/>
-      <c r="D71" s="13" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" s="71"/>
-      <c r="C72" s="71">
-        <v>3.3</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" s="71"/>
-      <c r="C73" s="71"/>
-      <c r="D73" s="13" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" s="71"/>
-      <c r="C74" s="71"/>
-      <c r="D74" s="13" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" s="71"/>
-      <c r="C75" s="71"/>
-      <c r="D75" s="13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76" s="71"/>
-      <c r="C76" s="71"/>
-      <c r="D76" s="13" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B77" s="71"/>
-      <c r="C77" s="71"/>
-      <c r="D77" s="13" t="s">
+      <c r="D138" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="77"/>
+      <c r="C139" s="81"/>
+      <c r="D139" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="77"/>
+      <c r="C140" s="81"/>
+      <c r="D140" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4">
+      <c r="B141" s="77"/>
+      <c r="C141" s="81"/>
+      <c r="D141" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="77"/>
+      <c r="C142" s="81"/>
+      <c r="D142" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="77"/>
+      <c r="C143" s="81"/>
+      <c r="D143" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="77"/>
+      <c r="C144" s="81"/>
+      <c r="D144" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="77"/>
+      <c r="C145" s="81"/>
+      <c r="D145" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="77"/>
+      <c r="C146" s="81"/>
+      <c r="D146" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="77"/>
+      <c r="C147" s="81"/>
+      <c r="D147" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="77"/>
+      <c r="C148" s="77">
+        <v>3.11</v>
+      </c>
+      <c r="D148" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="77"/>
+      <c r="C149" s="77"/>
+      <c r="D149" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="77"/>
+      <c r="C150" s="77"/>
+      <c r="D150" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="77"/>
+      <c r="C151" s="77"/>
+      <c r="D151" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" s="77"/>
+      <c r="C152" s="77"/>
+      <c r="D152" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="77"/>
+      <c r="C153" s="77">
+        <v>3.12</v>
+      </c>
+      <c r="D153" s="69" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="77"/>
+      <c r="C154" s="77"/>
+      <c r="D154" s="69" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="77"/>
+      <c r="C155" s="77"/>
+      <c r="D155" s="69" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="77"/>
+      <c r="C156" s="77"/>
+      <c r="D156" s="69" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="77"/>
+      <c r="C157" s="77"/>
+      <c r="D157" s="69" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="77"/>
+      <c r="C158" s="77"/>
+      <c r="D158" s="69" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="77"/>
+      <c r="C159" s="77"/>
+      <c r="D159" s="69" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="77"/>
+      <c r="C160" s="77"/>
+      <c r="D160" s="69" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="77"/>
+      <c r="C161" s="77"/>
+      <c r="D161" s="69" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="77"/>
+      <c r="C162" s="77"/>
+      <c r="D162" s="69" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="77"/>
+      <c r="C163" s="77"/>
+      <c r="D163" s="69" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="77"/>
+      <c r="C164" s="77"/>
+      <c r="D164" s="69" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="77"/>
+      <c r="C165" s="77"/>
+      <c r="D165" s="69" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="77"/>
+      <c r="C166" s="77">
+        <v>3.13</v>
+      </c>
+      <c r="D166" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="77"/>
+      <c r="C167" s="77"/>
+      <c r="D167" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4">
+      <c r="B168" s="77"/>
+      <c r="C168" s="77"/>
+      <c r="D168" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="77"/>
+      <c r="C169" s="77"/>
+      <c r="D169" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="77"/>
+      <c r="C170" s="77"/>
+      <c r="D170" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="77"/>
+      <c r="C171" s="77"/>
+      <c r="D171" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="77"/>
+      <c r="C172" s="77"/>
+      <c r="D172" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="77"/>
+      <c r="C173" s="77"/>
+      <c r="D173" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="77"/>
+      <c r="C174" s="77"/>
+      <c r="D174" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="77"/>
+      <c r="C175" s="77"/>
+      <c r="D175" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4">
+      <c r="B176" s="77"/>
+      <c r="C176" s="77"/>
+      <c r="D176" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4">
+      <c r="B177" s="77"/>
+      <c r="C177" s="77"/>
+      <c r="D177" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="2:4">
-      <c r="B78" s="71"/>
-      <c r="C78" s="71">
-        <v>3.4</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B79" s="71"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4">
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="13" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4">
-      <c r="B81" s="71"/>
-      <c r="C81" s="71"/>
-      <c r="D81" s="13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4">
-      <c r="B82" s="71"/>
-      <c r="C82" s="71"/>
-      <c r="D82" s="13" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B83" s="71"/>
-      <c r="C83" s="71"/>
-      <c r="D83" s="13" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4">
-      <c r="B84" s="71"/>
-      <c r="C84" s="71"/>
-      <c r="D84" s="13" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4">
-      <c r="B85" s="71"/>
-      <c r="C85" s="71"/>
-      <c r="D85" s="13" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B86" s="71"/>
-      <c r="C86" s="71"/>
-      <c r="D86" s="13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" ht="28.8" customHeight="1">
-      <c r="B87" s="71"/>
-      <c r="C87" s="71"/>
-      <c r="D87" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="B88" s="71"/>
-      <c r="C88" s="71">
-        <v>3.5</v>
-      </c>
-      <c r="D88" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="B89" s="71"/>
-      <c r="C89" s="71"/>
-      <c r="D89" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90" s="71"/>
-      <c r="C90" s="71"/>
-      <c r="D90" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4">
-      <c r="B91" s="71"/>
-      <c r="C91" s="71"/>
-      <c r="D91" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4">
-      <c r="B92" s="71"/>
-      <c r="C92" s="71"/>
-      <c r="D92" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4">
-      <c r="B93" s="71"/>
-      <c r="C93" s="71"/>
-      <c r="D93" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4">
-      <c r="B94" s="71"/>
-      <c r="C94" s="71"/>
-      <c r="D94" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4">
-      <c r="B95" s="71"/>
-      <c r="C95" s="71">
-        <v>3.6</v>
-      </c>
-      <c r="D95" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4">
-      <c r="B96" s="71"/>
-      <c r="C96" s="71"/>
-      <c r="D96" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4">
-      <c r="B97" s="71"/>
-      <c r="C97" s="71"/>
-      <c r="D97" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4">
-      <c r="B98" s="71"/>
-      <c r="C98" s="71"/>
-      <c r="D98" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4">
-      <c r="B99" s="71"/>
-      <c r="C99" s="71"/>
-      <c r="D99" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4">
-      <c r="B100" s="71"/>
-      <c r="C100" s="71"/>
-      <c r="D100" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4">
-      <c r="B101" s="71"/>
-      <c r="C101" s="71"/>
-      <c r="D101" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4">
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4">
-      <c r="B103" s="71"/>
-      <c r="C103" s="71"/>
-      <c r="D103" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4">
-      <c r="B104" s="71"/>
-      <c r="C104" s="71"/>
-      <c r="D104" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4">
-      <c r="B105" s="71"/>
-      <c r="C105" s="71"/>
-      <c r="D105" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4">
-      <c r="B106" s="71"/>
-      <c r="C106" s="71"/>
-      <c r="D106" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4">
-      <c r="B107" s="71"/>
-      <c r="C107" s="71"/>
-      <c r="D107" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4">
-      <c r="B108" s="71"/>
-      <c r="C108" s="71"/>
-      <c r="D108" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4">
-      <c r="B109" s="71"/>
-      <c r="C109" s="71"/>
-      <c r="D109" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4">
-      <c r="B110" s="71"/>
-      <c r="C110" s="71"/>
-      <c r="D110" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4">
-      <c r="B111" s="71"/>
-      <c r="C111" s="71"/>
-      <c r="D111" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4">
-      <c r="B112" s="71"/>
-      <c r="C112" s="71">
-        <v>3.7</v>
-      </c>
-      <c r="D112" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4">
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
-      <c r="D113" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4">
-      <c r="B114" s="71"/>
-      <c r="C114" s="71"/>
-      <c r="D114" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
-      <c r="B115" s="71"/>
-      <c r="C115" s="71"/>
-      <c r="D115" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4">
-      <c r="B116" s="71"/>
-      <c r="C116" s="71"/>
-      <c r="D116" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4">
-      <c r="B117" s="71"/>
-      <c r="C117" s="71"/>
-      <c r="D117" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4">
-      <c r="B118" s="71"/>
-      <c r="C118" s="71">
-        <v>3.8</v>
-      </c>
-      <c r="D118" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4">
-      <c r="B119" s="71"/>
-      <c r="C119" s="71"/>
-      <c r="D119" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4">
-      <c r="B120" s="71"/>
-      <c r="C120" s="71"/>
-      <c r="D120" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4">
-      <c r="B121" s="71"/>
-      <c r="C121" s="71"/>
-      <c r="D121" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4">
-      <c r="B122" s="71"/>
-      <c r="C122" s="71"/>
-      <c r="D122" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4">
-      <c r="B123" s="71"/>
-      <c r="C123" s="71"/>
-      <c r="D123" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4">
-      <c r="B124" s="71"/>
-      <c r="C124" s="71"/>
-      <c r="D124" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4">
-      <c r="B125" s="71"/>
-      <c r="C125" s="71"/>
-      <c r="D125" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4">
-      <c r="B126" s="71"/>
-      <c r="C126" s="71"/>
-      <c r="D126" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4">
-      <c r="B127" s="71"/>
-      <c r="C127" s="74">
-        <v>3.9</v>
-      </c>
-      <c r="D127" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4">
-      <c r="B128" s="71"/>
-      <c r="C128" s="74"/>
-      <c r="D128" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4">
-      <c r="B129" s="71"/>
-      <c r="C129" s="74"/>
-      <c r="D129" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="71"/>
-      <c r="C130" s="74"/>
-      <c r="D130" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="71"/>
-      <c r="C131" s="74"/>
-      <c r="D131" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="71"/>
-      <c r="C132" s="74"/>
-      <c r="D132" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="71"/>
-      <c r="C133" s="74"/>
-      <c r="D133" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="71"/>
-      <c r="C134" s="74"/>
-      <c r="D134" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="135" spans="2:4">
-      <c r="B135" s="71"/>
-      <c r="C135" s="74"/>
-      <c r="D135" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="71"/>
-      <c r="C136" s="74"/>
-      <c r="D136" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="71"/>
-      <c r="C137" s="74"/>
-      <c r="D137" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="71"/>
-      <c r="C138" s="75">
-        <v>3.1</v>
-      </c>
-      <c r="D138" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="71"/>
-      <c r="C139" s="75"/>
-      <c r="D139" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="71"/>
-      <c r="C140" s="75"/>
-      <c r="D140" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="141" spans="2:4">
-      <c r="B141" s="71"/>
-      <c r="C141" s="75"/>
-      <c r="D141" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="71"/>
-      <c r="C142" s="75"/>
-      <c r="D142" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="71"/>
-      <c r="C143" s="75"/>
-      <c r="D143" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="71"/>
-      <c r="C144" s="75"/>
-      <c r="D144" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="71"/>
-      <c r="C145" s="75"/>
-      <c r="D145" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="71"/>
-      <c r="C146" s="75"/>
-      <c r="D146" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="71"/>
-      <c r="C147" s="75"/>
-      <c r="D147" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="71"/>
-      <c r="C148" s="71">
-        <v>3.11</v>
-      </c>
-      <c r="D148" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="71"/>
-      <c r="C149" s="71"/>
-      <c r="D149" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4">
-      <c r="B150" s="71"/>
-      <c r="C150" s="71"/>
-      <c r="D150" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="71"/>
-      <c r="C151" s="71"/>
-      <c r="D151" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="71"/>
-      <c r="C152" s="71"/>
-      <c r="D152" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="71"/>
-      <c r="C153" s="71">
-        <v>3.12</v>
-      </c>
-      <c r="D153" s="69" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="71"/>
-      <c r="C154" s="71"/>
-      <c r="D154" s="69" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="71"/>
-      <c r="C155" s="71"/>
-      <c r="D155" s="69" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="71"/>
-      <c r="C156" s="71"/>
-      <c r="D156" s="69" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="71"/>
-      <c r="C157" s="71"/>
-      <c r="D157" s="69" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4">
-      <c r="B158" s="71"/>
-      <c r="C158" s="71"/>
-      <c r="D158" s="69" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="71"/>
-      <c r="C159" s="71"/>
-      <c r="D159" s="69" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="71"/>
-      <c r="C160" s="71"/>
-      <c r="D160" s="69" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4">
-      <c r="B161" s="71"/>
-      <c r="C161" s="71"/>
-      <c r="D161" s="69" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4">
-      <c r="B162" s="71"/>
-      <c r="C162" s="71"/>
-      <c r="D162" s="69" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4">
-      <c r="B163" s="71"/>
-      <c r="C163" s="71"/>
-      <c r="D163" s="69" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4">
-      <c r="B164" s="71"/>
-      <c r="C164" s="71"/>
-      <c r="D164" s="69" t="s">
+    <row r="178" spans="2:4">
+      <c r="B178" s="77"/>
+      <c r="C178" s="77"/>
+      <c r="D178" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4">
+      <c r="B179" s="77"/>
+      <c r="C179" s="77">
+        <v>3.14</v>
+      </c>
+      <c r="D179" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
-      <c r="B165" s="71"/>
-      <c r="C165" s="71"/>
-      <c r="D165" s="69" t="s">
+    <row r="180" spans="2:4">
+      <c r="B180" s="77"/>
+      <c r="C180" s="77"/>
+      <c r="D180" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="166" spans="2:4">
-      <c r="B166" s="71"/>
-      <c r="C166" s="71">
-        <v>3.13</v>
-      </c>
-      <c r="D166" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4">
-      <c r="B167" s="71"/>
-      <c r="C167" s="71"/>
-      <c r="D167" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4">
-      <c r="B168" s="71"/>
-      <c r="C168" s="71"/>
-      <c r="D168" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4">
-      <c r="B169" s="71"/>
-      <c r="C169" s="71"/>
-      <c r="D169" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4">
-      <c r="B170" s="71"/>
-      <c r="C170" s="71"/>
-      <c r="D170" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4">
-      <c r="B171" s="71"/>
-      <c r="C171" s="71"/>
-      <c r="D171" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4">
-      <c r="B172" s="71"/>
-      <c r="C172" s="71"/>
-      <c r="D172" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4">
-      <c r="B173" s="71"/>
-      <c r="C173" s="71"/>
-      <c r="D173" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4">
-      <c r="B174" s="71"/>
-      <c r="C174" s="71"/>
-      <c r="D174" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4">
-      <c r="B175" s="71"/>
-      <c r="C175" s="71"/>
-      <c r="D175" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4">
-      <c r="B176" s="71"/>
-      <c r="C176" s="71"/>
-      <c r="D176" t="s">
+    <row r="181" spans="2:4">
+      <c r="B181" s="77"/>
+      <c r="C181" s="77"/>
+      <c r="D181" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4">
+      <c r="B182" s="77"/>
+      <c r="C182" s="77"/>
+      <c r="D182" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4">
+      <c r="B183" s="77"/>
+      <c r="C183" s="77"/>
+      <c r="D183" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4">
+      <c r="B184" s="77"/>
+      <c r="C184" s="77"/>
+      <c r="D184" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4">
+      <c r="B185" s="77"/>
+      <c r="C185" s="77"/>
+      <c r="D185" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4">
+      <c r="B186" s="77"/>
+      <c r="C186" s="77"/>
+      <c r="D186" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4">
+      <c r="B187" s="77"/>
+      <c r="C187" s="77"/>
+      <c r="D187" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4">
+      <c r="B188" s="77"/>
+      <c r="C188" s="77"/>
+      <c r="D188" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4">
+      <c r="B189" s="77"/>
+      <c r="C189" s="77"/>
+      <c r="D189" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4">
+      <c r="B190" s="77"/>
+      <c r="C190" s="77"/>
+      <c r="D190" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4">
+      <c r="B191" s="77"/>
+      <c r="C191" s="77">
+        <v>3.15</v>
+      </c>
+      <c r="D191" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4">
+      <c r="B192" s="77"/>
+      <c r="C192" s="77"/>
+      <c r="D192" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4">
+      <c r="B193" s="77"/>
+      <c r="C193" s="77"/>
+      <c r="D193" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4">
+      <c r="B194" s="77"/>
+      <c r="C194" s="77"/>
+      <c r="D194" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4">
+      <c r="B195" s="77"/>
+      <c r="C195" s="77"/>
+      <c r="D195" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4">
+      <c r="B196" s="77"/>
+      <c r="C196" s="77"/>
+      <c r="D196" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4">
+      <c r="B197" s="77"/>
+      <c r="C197" s="77"/>
+      <c r="D197" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4">
+      <c r="B198" s="77"/>
+      <c r="C198" s="77"/>
+      <c r="D198" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4">
+      <c r="B199" s="77"/>
+      <c r="C199" s="77"/>
+      <c r="D199" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4">
+      <c r="B200" s="77"/>
+      <c r="C200" s="77"/>
+      <c r="D200" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4">
+      <c r="B201" s="77"/>
+      <c r="C201" s="77"/>
+      <c r="D201" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4">
+      <c r="B202" s="77"/>
+      <c r="C202" s="77"/>
+      <c r="D202" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4">
+      <c r="B203" s="77"/>
+      <c r="C203" s="77"/>
+      <c r="D203" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4">
+      <c r="B204" s="77"/>
+      <c r="C204" s="77"/>
+      <c r="D204" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4">
+      <c r="B205" s="77"/>
+      <c r="C205" s="77">
+        <v>3.16</v>
+      </c>
+      <c r="D205" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4">
+      <c r="B206" s="77"/>
+      <c r="C206" s="77"/>
+      <c r="D206" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4">
+      <c r="B207" s="77"/>
+      <c r="C207" s="77"/>
+      <c r="D207" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4">
+      <c r="B208" s="77"/>
+      <c r="C208" s="77"/>
+      <c r="D208" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4">
+      <c r="B209" s="77"/>
+      <c r="C209" s="77"/>
+      <c r="D209" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4">
+      <c r="B210" s="77"/>
+      <c r="C210" s="77"/>
+      <c r="D210" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4">
+      <c r="B211" s="77"/>
+      <c r="C211" s="77">
+        <v>3.17</v>
+      </c>
+      <c r="D211" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4">
+      <c r="B212" s="77"/>
+      <c r="C212" s="77"/>
+      <c r="D212" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4">
+      <c r="B213" s="77"/>
+      <c r="C213" s="77"/>
+      <c r="D213" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4">
+      <c r="B214" s="77"/>
+      <c r="C214" s="77"/>
+      <c r="D214" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4">
+      <c r="B215" s="77"/>
+      <c r="C215" s="77"/>
+      <c r="D215" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4">
+      <c r="B216" s="77"/>
+      <c r="C216" s="77"/>
+      <c r="D216" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4">
+      <c r="B217" s="77"/>
+      <c r="C217" s="77">
+        <v>3.18</v>
+      </c>
+      <c r="D217" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4">
+      <c r="B218" s="77"/>
+      <c r="C218" s="77"/>
+      <c r="D218" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4">
+      <c r="B219" s="77"/>
+      <c r="C219" s="77"/>
+      <c r="D219" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4">
+      <c r="B220" s="77"/>
+      <c r="C220" s="77"/>
+      <c r="D220" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4">
+      <c r="B221" s="77"/>
+      <c r="C221" s="77"/>
+      <c r="D221" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4">
+      <c r="B222" s="77"/>
+      <c r="C222" s="77"/>
+      <c r="D222" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4">
+      <c r="B223" s="77"/>
+      <c r="C223" s="77"/>
+      <c r="D223" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4">
+      <c r="B224" s="77"/>
+      <c r="C224" s="77"/>
+      <c r="D224" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="B225" s="77"/>
+      <c r="C225" s="77"/>
+      <c r="D225" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="B226" s="77"/>
+      <c r="C226" s="77"/>
+      <c r="D226" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="B227" s="77"/>
+      <c r="C227" s="77"/>
+      <c r="D227" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="B228" s="77"/>
+      <c r="C228" s="77"/>
+      <c r="D228" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" s="77">
+        <v>4</v>
+      </c>
+      <c r="C229" s="77">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D229" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="B230" s="77"/>
+      <c r="C230" s="77"/>
+      <c r="D230" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231" s="77"/>
+      <c r="C231" s="77"/>
+      <c r="D231" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="B232" s="77"/>
+      <c r="C232" s="77"/>
+      <c r="D232" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" s="77"/>
+      <c r="C233" s="77"/>
+      <c r="D233" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234" s="77"/>
+      <c r="C234" s="77"/>
+      <c r="D234" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235" s="77"/>
+      <c r="C235" s="77"/>
+      <c r="D235" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236" s="77"/>
+      <c r="C236" s="77"/>
+      <c r="D236" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" s="77"/>
+      <c r="C237" s="77"/>
+      <c r="D237" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4">
+      <c r="B238" s="77"/>
+      <c r="C238" s="77">
+        <v>4.2</v>
+      </c>
+      <c r="D238" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="177" spans="2:4">
-      <c r="B177" s="71"/>
-      <c r="C177" s="71"/>
-      <c r="D177" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4">
-      <c r="B178" s="71"/>
-      <c r="C178" s="71"/>
-      <c r="D178" t="s">
+    <row r="239" spans="2:4">
+      <c r="B239" s="77"/>
+      <c r="C239" s="77"/>
+      <c r="D239" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="179" spans="2:4">
-      <c r="B179" s="71"/>
-      <c r="C179" s="71">
-        <v>3.14</v>
-      </c>
-      <c r="D179" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4">
-      <c r="B180" s="71"/>
-      <c r="C180" s="71"/>
-      <c r="D180" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4">
-      <c r="B181" s="71"/>
-      <c r="C181" s="71"/>
-      <c r="D181" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4">
-      <c r="B182" s="71"/>
-      <c r="C182" s="71"/>
-      <c r="D182" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4">
-      <c r="B183" s="71"/>
-      <c r="C183" s="71"/>
-      <c r="D183" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4">
-      <c r="B184" s="71"/>
-      <c r="C184" s="71"/>
-      <c r="D184" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4">
-      <c r="B185" s="71"/>
-      <c r="C185" s="71"/>
-      <c r="D185" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="186" spans="2:4">
-      <c r="B186" s="71"/>
-      <c r="C186" s="71"/>
-      <c r="D186" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="187" spans="2:4">
-      <c r="B187" s="71"/>
-      <c r="C187" s="71"/>
-      <c r="D187" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4">
-      <c r="B188" s="71"/>
-      <c r="C188" s="71"/>
-      <c r="D188" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="189" spans="2:4">
-      <c r="B189" s="71"/>
-      <c r="C189" s="71"/>
-      <c r="D189" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4">
-      <c r="B190" s="71"/>
-      <c r="C190" s="71"/>
-      <c r="D190" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4">
-      <c r="B191" s="71"/>
-      <c r="C191" s="71">
-        <v>3.15</v>
-      </c>
-      <c r="D191" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="192" spans="2:4">
-      <c r="B192" s="71"/>
-      <c r="C192" s="71"/>
-      <c r="D192" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="193" spans="2:4">
-      <c r="B193" s="71"/>
-      <c r="C193" s="71"/>
-      <c r="D193" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="194" spans="2:4">
-      <c r="B194" s="71"/>
-      <c r="C194" s="71"/>
-      <c r="D194" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="195" spans="2:4">
-      <c r="B195" s="71"/>
-      <c r="C195" s="71"/>
-      <c r="D195" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="196" spans="2:4">
-      <c r="B196" s="71"/>
-      <c r="C196" s="71"/>
-      <c r="D196" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="197" spans="2:4">
-      <c r="B197" s="71"/>
-      <c r="C197" s="71"/>
-      <c r="D197" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="198" spans="2:4">
-      <c r="B198" s="71"/>
-      <c r="C198" s="71"/>
-      <c r="D198" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="199" spans="2:4">
-      <c r="B199" s="71"/>
-      <c r="C199" s="71"/>
-      <c r="D199" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="200" spans="2:4">
-      <c r="B200" s="71"/>
-      <c r="C200" s="71"/>
-      <c r="D200" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="201" spans="2:4">
-      <c r="B201" s="71"/>
-      <c r="C201" s="71"/>
-      <c r="D201" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="202" spans="2:4">
-      <c r="B202" s="71"/>
-      <c r="C202" s="71"/>
-      <c r="D202" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="203" spans="2:4">
-      <c r="B203" s="71"/>
-      <c r="C203" s="71"/>
-      <c r="D203" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="204" spans="2:4">
-      <c r="B204" s="71"/>
-      <c r="C204" s="71"/>
-      <c r="D204" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="205" spans="2:4">
-      <c r="B205" s="71"/>
-      <c r="C205" s="71">
-        <v>3.16</v>
-      </c>
-      <c r="D205" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="206" spans="2:4">
-      <c r="B206" s="71"/>
-      <c r="C206" s="71"/>
-      <c r="D206" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="207" spans="2:4">
-      <c r="B207" s="71"/>
-      <c r="C207" s="71"/>
-      <c r="D207" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="208" spans="2:4">
-      <c r="B208" s="71"/>
-      <c r="C208" s="71"/>
-      <c r="D208" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="209" spans="2:4">
-      <c r="B209" s="71"/>
-      <c r="C209" s="71"/>
-      <c r="D209" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="210" spans="2:4">
-      <c r="B210" s="71"/>
-      <c r="C210" s="71"/>
-      <c r="D210" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="211" spans="2:4">
-      <c r="B211" s="71"/>
-      <c r="C211" s="71">
-        <v>3.17</v>
-      </c>
-      <c r="D211" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="212" spans="2:4">
-      <c r="B212" s="71"/>
-      <c r="C212" s="71"/>
-      <c r="D212" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="213" spans="2:4">
-      <c r="B213" s="71"/>
-      <c r="C213" s="71"/>
-      <c r="D213" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="214" spans="2:4">
-      <c r="B214" s="71"/>
-      <c r="C214" s="71"/>
-      <c r="D214" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="215" spans="2:4">
-      <c r="B215" s="71"/>
-      <c r="C215" s="71"/>
-      <c r="D215" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="216" spans="2:4">
-      <c r="B216" s="71"/>
-      <c r="C216" s="71"/>
-      <c r="D216" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="217" spans="2:4">
-      <c r="B217" s="71"/>
-      <c r="C217" s="71">
-        <v>3.18</v>
-      </c>
-      <c r="D217" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="218" spans="2:4">
-      <c r="B218" s="71"/>
-      <c r="C218" s="71"/>
-      <c r="D218" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="219" spans="2:4">
-      <c r="B219" s="71"/>
-      <c r="C219" s="71"/>
-      <c r="D219" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="220" spans="2:4">
-      <c r="B220" s="71"/>
-      <c r="C220" s="71"/>
-      <c r="D220" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="221" spans="2:4">
-      <c r="B221" s="71"/>
-      <c r="C221" s="71"/>
-      <c r="D221" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="222" spans="2:4">
-      <c r="B222" s="71"/>
-      <c r="C222" s="71"/>
-      <c r="D222" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="223" spans="2:4">
-      <c r="B223" s="71"/>
-      <c r="C223" s="71"/>
-      <c r="D223" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="224" spans="2:4">
-      <c r="B224" s="71"/>
-      <c r="C224" s="71"/>
-      <c r="D224" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="225" spans="2:4">
-      <c r="B225" s="71"/>
-      <c r="C225" s="71"/>
-      <c r="D225" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="226" spans="2:4">
-      <c r="B226" s="71"/>
-      <c r="C226" s="71"/>
-      <c r="D226" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="227" spans="2:4">
-      <c r="B227" s="71"/>
-      <c r="C227" s="71"/>
-      <c r="D227" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="228" spans="2:4">
-      <c r="B228" s="71"/>
-      <c r="C228" s="71"/>
-      <c r="D228" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="229" spans="2:4">
-      <c r="B229" s="71">
-        <v>4</v>
-      </c>
-      <c r="C229" s="71">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D229" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="230" spans="2:4">
-      <c r="B230" s="71"/>
-      <c r="C230" s="71"/>
-      <c r="D230" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="231" spans="2:4">
-      <c r="B231" s="71"/>
-      <c r="C231" s="71"/>
-      <c r="D231" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="232" spans="2:4">
-      <c r="B232" s="71"/>
-      <c r="C232" s="71"/>
-      <c r="D232" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="233" spans="2:4">
-      <c r="B233" s="71"/>
-      <c r="C233" s="71"/>
-      <c r="D233" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="234" spans="2:4">
-      <c r="B234" s="71"/>
-      <c r="C234" s="71"/>
-      <c r="D234" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="235" spans="2:4">
-      <c r="B235" s="71"/>
-      <c r="C235" s="71"/>
-      <c r="D235" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="236" spans="2:4">
-      <c r="B236" s="71"/>
-      <c r="C236" s="71"/>
-      <c r="D236" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="237" spans="2:4">
-      <c r="B237" s="71"/>
-      <c r="C237" s="71"/>
-      <c r="D237" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="238" spans="2:4">
-      <c r="B238" s="71"/>
-      <c r="C238" s="71">
-        <v>4.2</v>
-      </c>
-      <c r="D238" t="s">
+    <row r="240" spans="2:4">
+      <c r="B240" s="77"/>
+      <c r="C240" s="77"/>
+      <c r="D240" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="239" spans="2:4">
-      <c r="B239" s="71"/>
-      <c r="C239" s="71"/>
-      <c r="D239" t="s">
+    <row r="241" spans="2:4">
+      <c r="B241" s="77"/>
+      <c r="C241" s="77"/>
+      <c r="D241" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="240" spans="2:4">
-      <c r="B240" s="71"/>
-      <c r="C240" s="71"/>
-      <c r="D240" t="s">
+    <row r="242" spans="2:4">
+      <c r="B242" s="77"/>
+      <c r="C242" s="77"/>
+      <c r="D242" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="241" spans="2:4">
-      <c r="B241" s="71"/>
-      <c r="C241" s="71"/>
-      <c r="D241" t="s">
+    <row r="243" spans="2:4">
+      <c r="B243" s="77"/>
+      <c r="C243" s="77"/>
+      <c r="D243" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="242" spans="2:4">
-      <c r="B242" s="71"/>
-      <c r="C242" s="71"/>
-      <c r="D242" t="s">
+    <row r="244" spans="2:4">
+      <c r="B244" s="77"/>
+      <c r="C244" s="77"/>
+      <c r="D244" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="243" spans="2:4">
-      <c r="B243" s="71"/>
-      <c r="C243" s="71"/>
-      <c r="D243" t="s">
+    <row r="245" spans="2:4">
+      <c r="B245" s="77"/>
+      <c r="C245" s="77"/>
+      <c r="D245" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="244" spans="2:4">
-      <c r="B244" s="71"/>
-      <c r="C244" s="71"/>
-      <c r="D244" t="s">
+    <row r="246" spans="2:4">
+      <c r="B246" s="77"/>
+      <c r="C246" s="77"/>
+      <c r="D246" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="245" spans="2:4">
-      <c r="B245" s="71"/>
-      <c r="C245" s="71"/>
-      <c r="D245" t="s">
+    <row r="247" spans="2:4">
+      <c r="B247" s="77"/>
+      <c r="C247" s="77">
+        <v>4.3</v>
+      </c>
+      <c r="D247" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="246" spans="2:4">
-      <c r="B246" s="71"/>
-      <c r="C246" s="71"/>
-      <c r="D246" t="s">
+    <row r="248" spans="2:4">
+      <c r="B248" s="77"/>
+      <c r="C248" s="77"/>
+      <c r="D248" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="247" spans="2:4">
-      <c r="B247" s="71"/>
-      <c r="C247" s="71">
-        <v>4.3</v>
-      </c>
-      <c r="D247" t="s">
+    <row r="249" spans="2:4">
+      <c r="B249" s="77"/>
+      <c r="C249" s="77"/>
+      <c r="D249" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="248" spans="2:4">
-      <c r="B248" s="71"/>
-      <c r="C248" s="71"/>
-      <c r="D248" t="s">
+    <row r="250" spans="2:4">
+      <c r="B250" s="77"/>
+      <c r="C250" s="77"/>
+      <c r="D250" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="249" spans="2:4">
-      <c r="B249" s="71"/>
-      <c r="C249" s="71"/>
-      <c r="D249" t="s">
+    <row r="251" spans="2:4">
+      <c r="B251" s="77"/>
+      <c r="C251" s="77"/>
+      <c r="D251" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="250" spans="2:4">
-      <c r="B250" s="71"/>
-      <c r="C250" s="71"/>
-      <c r="D250" t="s">
+    <row r="252" spans="2:4">
+      <c r="B252" s="77"/>
+      <c r="C252" s="77"/>
+      <c r="D252" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="251" spans="2:4">
-      <c r="B251" s="71"/>
-      <c r="C251" s="71"/>
-      <c r="D251" t="s">
+    <row r="253" spans="2:4">
+      <c r="B253" s="77"/>
+      <c r="C253" s="77"/>
+      <c r="D253" t="s">
         <v>393</v>
-      </c>
-    </row>
-    <row r="252" spans="2:4">
-      <c r="B252" s="71"/>
-      <c r="C252" s="71"/>
-      <c r="D252" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="253" spans="2:4">
-      <c r="B253" s="71"/>
-      <c r="C253" s="71"/>
-      <c r="D253" t="s">
-        <v>395</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="F3:F12"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="F13:F17"/>
-    <mergeCell ref="E18:E22"/>
-    <mergeCell ref="F18:F22"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="C23:C27"/>
-    <mergeCell ref="E3:E12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C166:C178"/>
-    <mergeCell ref="C179:C190"/>
-    <mergeCell ref="C191:C204"/>
-    <mergeCell ref="C205:C210"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="C58:C64"/>
-    <mergeCell ref="C65:C71"/>
-    <mergeCell ref="C72:C77"/>
-    <mergeCell ref="C78:C87"/>
-    <mergeCell ref="C88:C94"/>
-    <mergeCell ref="C95:C111"/>
-    <mergeCell ref="C112:C117"/>
-    <mergeCell ref="C118:C126"/>
-    <mergeCell ref="C127:C137"/>
-    <mergeCell ref="C138:C147"/>
     <mergeCell ref="C247:C253"/>
     <mergeCell ref="B229:B253"/>
     <mergeCell ref="B58:B228"/>
@@ -6590,6 +7941,31 @@
     <mergeCell ref="C43:C47"/>
     <mergeCell ref="C48:C53"/>
     <mergeCell ref="C3:C12"/>
+    <mergeCell ref="C166:C178"/>
+    <mergeCell ref="C179:C190"/>
+    <mergeCell ref="C191:C204"/>
+    <mergeCell ref="C205:C210"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="C58:C64"/>
+    <mergeCell ref="C65:C71"/>
+    <mergeCell ref="C72:C77"/>
+    <mergeCell ref="C78:C87"/>
+    <mergeCell ref="C88:C94"/>
+    <mergeCell ref="C95:C111"/>
+    <mergeCell ref="C112:C117"/>
+    <mergeCell ref="C118:C126"/>
+    <mergeCell ref="C127:C137"/>
+    <mergeCell ref="C138:C147"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="E3:E12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="F3:F12"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="F13:F17"/>
+    <mergeCell ref="E18:E22"/>
+    <mergeCell ref="F18:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6597,6 +7973,1589 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DC7BB0-6771-4160-B371-AE490E8879B7}">
+  <dimension ref="A1:J181"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71.44140625" style="97" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="100" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+    </row>
+    <row r="2" spans="1:10" s="15" customFormat="1">
+      <c r="A2" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="96" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="59" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="99"/>
+      <c r="B3" s="103">
+        <v>1</v>
+      </c>
+      <c r="C3" s="103">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="98"/>
+      <c r="B4" s="103"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="33" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="98"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="33" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="98"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="98"/>
+      <c r="B7" s="103"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="33" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="98"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="33" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="98"/>
+      <c r="B9" s="103"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="33" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="98"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="33" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="98"/>
+      <c r="B11" s="103"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="33" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="98"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="103">
+        <v>1.2</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="98"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="33" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="98"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="33" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="98"/>
+      <c r="B15" s="103"/>
+      <c r="C15" s="103">
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="98"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="33" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="98"/>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="33" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="98"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103">
+        <v>1.4</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="98"/>
+      <c r="B19" s="103"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="33" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="98"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="33" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="98"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="33" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="98"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="33" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="98"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="98"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="33" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="98"/>
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="33" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="98"/>
+      <c r="B26" s="76">
+        <v>2</v>
+      </c>
+      <c r="C26" s="103">
+        <v>2.1</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="98"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="33" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="99"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="102">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="98"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="33" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="98"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="103">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="98"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="103"/>
+      <c r="D31" s="33" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="98"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="33" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="98"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="33" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="98"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="103"/>
+      <c r="D34" s="33" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="98"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="33" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="98"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="33" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="98"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="103">
+        <v>2.4</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="98"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="33" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="98"/>
+      <c r="B39" s="76"/>
+      <c r="C39" s="103"/>
+      <c r="D39" s="33" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="98"/>
+      <c r="B40" s="76"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="98"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="103"/>
+      <c r="D41" s="33" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="98"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="33" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="98"/>
+      <c r="B43" s="76"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="33" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="98"/>
+      <c r="B44" s="76"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="33" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="98"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="103">
+        <v>2.5</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="98"/>
+      <c r="B46" s="76"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="33" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="98"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="103"/>
+      <c r="D47" s="33" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="98"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="98"/>
+      <c r="B49" s="76"/>
+      <c r="C49" s="103"/>
+      <c r="D49" s="33" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="98"/>
+      <c r="B50" s="76"/>
+      <c r="C50" s="103">
+        <v>2.7</v>
+      </c>
+      <c r="D50" s="33" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="98"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="103"/>
+      <c r="D51" s="33" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="98"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="103"/>
+      <c r="D52" s="33" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="98"/>
+      <c r="B53" s="76"/>
+      <c r="C53" s="103"/>
+      <c r="D53" s="33" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="98"/>
+      <c r="B54" s="76"/>
+      <c r="C54" s="103"/>
+      <c r="D54" s="33" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="98"/>
+      <c r="B55" s="76"/>
+      <c r="C55" s="103"/>
+      <c r="D55" s="33" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="98"/>
+      <c r="B56" s="76"/>
+      <c r="C56" s="103"/>
+      <c r="D56" s="33" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="98"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="103"/>
+      <c r="D57" s="33" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="98"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="103"/>
+      <c r="D58" s="33" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="99"/>
+      <c r="B59" s="103">
+        <v>3</v>
+      </c>
+      <c r="C59" s="103">
+        <v>3.1</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="98"/>
+      <c r="B60" s="103"/>
+      <c r="C60" s="103"/>
+      <c r="D60" s="33" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="98"/>
+      <c r="B61" s="103"/>
+      <c r="C61" s="103"/>
+      <c r="D61" s="33" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="98"/>
+      <c r="B62" s="103"/>
+      <c r="C62" s="103"/>
+      <c r="D62" s="33" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="98"/>
+      <c r="B63" s="103"/>
+      <c r="C63" s="103"/>
+      <c r="D63" s="33" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="98"/>
+      <c r="B64" s="103"/>
+      <c r="C64" s="103"/>
+      <c r="D64" s="33" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="98"/>
+      <c r="B65" s="103"/>
+      <c r="C65" s="103">
+        <v>3.2</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="98"/>
+      <c r="B66" s="103"/>
+      <c r="C66" s="103"/>
+      <c r="D66" s="33" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="98"/>
+      <c r="B67" s="103"/>
+      <c r="C67" s="103"/>
+      <c r="D67" s="33" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="98"/>
+      <c r="B68" s="103"/>
+      <c r="C68" s="103"/>
+      <c r="D68" s="33" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="98"/>
+      <c r="B69" s="103"/>
+      <c r="C69" s="103"/>
+      <c r="D69" s="33" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="98"/>
+      <c r="B70" s="103"/>
+      <c r="C70" s="103"/>
+      <c r="D70" s="33" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="98"/>
+      <c r="B71" s="103"/>
+      <c r="C71" s="103"/>
+      <c r="D71" s="33" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="98"/>
+      <c r="B72" s="103"/>
+      <c r="C72" s="103"/>
+      <c r="D72" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="98"/>
+      <c r="B73" s="103"/>
+      <c r="C73" s="103"/>
+      <c r="D73" s="33" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="98"/>
+      <c r="B74" s="103"/>
+      <c r="C74" s="103"/>
+      <c r="D74" s="33" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="98"/>
+      <c r="B75" s="103"/>
+      <c r="C75" s="103"/>
+      <c r="D75" s="33" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="98"/>
+      <c r="B76" s="103"/>
+      <c r="C76" s="103"/>
+      <c r="D76" s="33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="98"/>
+      <c r="B77" s="103"/>
+      <c r="C77" s="103">
+        <v>3.3</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="98"/>
+      <c r="B78" s="103"/>
+      <c r="C78" s="103"/>
+      <c r="D78" s="33" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="98"/>
+      <c r="B79" s="103"/>
+      <c r="C79" s="103"/>
+      <c r="D79" s="33" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="98"/>
+      <c r="B80" s="103"/>
+      <c r="C80" s="103"/>
+      <c r="D80" s="33" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="98"/>
+      <c r="B81" s="103"/>
+      <c r="C81" s="103"/>
+      <c r="D81" s="33" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="98"/>
+      <c r="B82" s="103"/>
+      <c r="C82" s="103"/>
+      <c r="D82" s="33" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="98"/>
+      <c r="B83" s="103"/>
+      <c r="C83" s="103"/>
+      <c r="D83" s="33" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="98"/>
+      <c r="B84" s="103"/>
+      <c r="C84" s="103"/>
+      <c r="D84" s="33" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="98"/>
+      <c r="B85" s="103"/>
+      <c r="C85" s="103"/>
+      <c r="D85" s="33" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="98"/>
+      <c r="B86" s="103"/>
+      <c r="C86" s="103"/>
+      <c r="D86" s="33" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="98"/>
+      <c r="B87" s="103"/>
+      <c r="C87" s="103"/>
+      <c r="D87" s="33" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="98"/>
+      <c r="B88" s="103"/>
+      <c r="C88" s="103">
+        <v>3.4</v>
+      </c>
+      <c r="D88" s="66" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="98"/>
+      <c r="B89" s="103"/>
+      <c r="C89" s="103"/>
+      <c r="D89" s="33" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="98"/>
+      <c r="B90" s="103"/>
+      <c r="C90" s="103"/>
+      <c r="D90" s="33" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="98"/>
+      <c r="B91" s="103"/>
+      <c r="C91" s="103"/>
+      <c r="D91" s="33" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="98"/>
+      <c r="B92" s="103"/>
+      <c r="C92" s="103"/>
+      <c r="D92" s="33" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="98"/>
+      <c r="B93" s="103"/>
+      <c r="C93" s="103"/>
+      <c r="D93" s="33" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="98"/>
+      <c r="B94" s="103"/>
+      <c r="C94" s="103"/>
+      <c r="D94" s="33" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="98"/>
+      <c r="B95" s="103"/>
+      <c r="C95" s="103"/>
+      <c r="D95" s="33" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="98"/>
+      <c r="B96" s="103"/>
+      <c r="C96" s="103"/>
+      <c r="D96" s="33" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="98"/>
+      <c r="B97" s="103"/>
+      <c r="C97" s="103"/>
+      <c r="D97" s="33" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="98"/>
+      <c r="B98" s="103"/>
+      <c r="C98" s="103"/>
+      <c r="D98" s="33" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="98"/>
+      <c r="B99" s="103"/>
+      <c r="C99" s="103"/>
+      <c r="D99" s="33" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="98"/>
+      <c r="B100" s="103"/>
+      <c r="C100" s="103"/>
+      <c r="D100" s="33" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="98"/>
+      <c r="B101" s="103"/>
+      <c r="C101" s="103">
+        <v>3.5</v>
+      </c>
+      <c r="D101" s="62" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="98"/>
+      <c r="B102" s="103"/>
+      <c r="C102" s="103"/>
+      <c r="D102" s="33" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="98"/>
+      <c r="B103" s="103"/>
+      <c r="C103" s="103"/>
+      <c r="D103" s="33" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="98"/>
+      <c r="B104" s="103"/>
+      <c r="C104" s="103"/>
+      <c r="D104" s="33" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="98"/>
+      <c r="B105" s="103"/>
+      <c r="C105" s="103"/>
+      <c r="D105" s="33" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="98"/>
+      <c r="B106" s="103"/>
+      <c r="C106" s="103"/>
+      <c r="D106" s="33" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="98"/>
+      <c r="B107" s="103"/>
+      <c r="C107" s="103"/>
+      <c r="D107" s="33" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="98"/>
+      <c r="B108" s="103"/>
+      <c r="C108" s="103"/>
+      <c r="D108" s="33" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="98"/>
+      <c r="B109" s="103"/>
+      <c r="C109" s="103"/>
+      <c r="D109" s="33" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="98"/>
+      <c r="B110" s="103"/>
+      <c r="C110" s="103">
+        <v>3.6</v>
+      </c>
+      <c r="D110" s="33" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="98"/>
+      <c r="B111" s="103"/>
+      <c r="C111" s="103"/>
+      <c r="D111" s="33" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="98"/>
+      <c r="B112" s="103"/>
+      <c r="C112" s="103"/>
+      <c r="D112" s="33" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="98"/>
+      <c r="B113" s="103"/>
+      <c r="C113" s="103"/>
+      <c r="D113" s="33" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="98"/>
+      <c r="B114" s="103"/>
+      <c r="C114" s="103"/>
+      <c r="D114" s="33" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="98"/>
+      <c r="B115" s="103"/>
+      <c r="C115" s="103"/>
+      <c r="D115" s="33" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="98"/>
+      <c r="B116" s="103"/>
+      <c r="C116" s="103">
+        <v>3.7</v>
+      </c>
+      <c r="D116" s="33" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="98"/>
+      <c r="B117" s="103"/>
+      <c r="C117" s="103"/>
+      <c r="D117" s="33" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="98"/>
+      <c r="B118" s="103"/>
+      <c r="C118" s="103"/>
+      <c r="D118" s="33" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="98"/>
+      <c r="B119" s="103"/>
+      <c r="C119" s="103"/>
+      <c r="D119" s="33" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="98"/>
+      <c r="B120" s="103"/>
+      <c r="C120" s="103"/>
+      <c r="D120" s="33" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="98"/>
+      <c r="B121" s="103"/>
+      <c r="C121" s="103"/>
+      <c r="D121" s="33" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="98"/>
+      <c r="B122" s="103"/>
+      <c r="C122" s="103"/>
+      <c r="D122" s="33" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="98"/>
+      <c r="B123" s="103"/>
+      <c r="C123" s="103"/>
+      <c r="D123" s="33" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="98"/>
+      <c r="B124" s="103"/>
+      <c r="C124" s="103"/>
+      <c r="D124" s="33" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="98"/>
+      <c r="B125" s="103"/>
+      <c r="C125" s="103"/>
+      <c r="D125" s="33" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="98"/>
+      <c r="B126" s="103"/>
+      <c r="C126" s="103"/>
+      <c r="D126" s="33" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="98"/>
+      <c r="B127" s="103"/>
+      <c r="C127" s="103">
+        <v>3.8</v>
+      </c>
+      <c r="D127" s="33" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="98"/>
+      <c r="B128" s="103"/>
+      <c r="C128" s="103"/>
+      <c r="D128" s="33" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="98"/>
+      <c r="B129" s="103"/>
+      <c r="C129" s="103"/>
+      <c r="D129" s="33" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="98"/>
+      <c r="B130" s="103"/>
+      <c r="C130" s="103"/>
+      <c r="D130" s="33" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="98"/>
+      <c r="B131" s="103"/>
+      <c r="C131" s="103"/>
+      <c r="D131" s="33" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="98"/>
+      <c r="B132" s="103"/>
+      <c r="C132" s="103"/>
+      <c r="D132" s="33" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="98"/>
+      <c r="B133" s="103"/>
+      <c r="C133" s="103"/>
+      <c r="D133" s="33" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="98"/>
+      <c r="B134" s="103"/>
+      <c r="C134" s="103"/>
+      <c r="D134" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="98"/>
+      <c r="B135" s="103"/>
+      <c r="C135" s="103"/>
+      <c r="D135" s="33" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="98"/>
+      <c r="B136" s="103"/>
+      <c r="C136" s="103"/>
+      <c r="D136" s="33" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="98"/>
+      <c r="B137" s="103"/>
+      <c r="C137" s="103">
+        <v>3.9</v>
+      </c>
+      <c r="D137" s="33" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="98"/>
+      <c r="B138" s="103"/>
+      <c r="C138" s="103"/>
+      <c r="D138" s="33" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="98"/>
+      <c r="B139" s="103"/>
+      <c r="C139" s="103"/>
+      <c r="D139" s="33" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="98"/>
+      <c r="B140" s="103"/>
+      <c r="C140" s="103"/>
+      <c r="D140" s="33" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="98"/>
+      <c r="B141" s="103"/>
+      <c r="C141" s="103"/>
+      <c r="D141" s="33" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="98"/>
+      <c r="B142" s="103"/>
+      <c r="C142" s="104">
+        <v>3.1</v>
+      </c>
+      <c r="D142" s="33" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="98"/>
+      <c r="B143" s="103"/>
+      <c r="C143" s="104"/>
+      <c r="D143" s="33" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="98"/>
+      <c r="B144" s="103"/>
+      <c r="C144" s="104"/>
+      <c r="D144" s="33" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="98"/>
+      <c r="B145" s="103"/>
+      <c r="C145" s="104"/>
+      <c r="D145" s="33" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="98"/>
+      <c r="B146" s="103"/>
+      <c r="C146" s="104"/>
+      <c r="D146" s="33" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="98"/>
+      <c r="B147" s="103"/>
+      <c r="C147" s="104"/>
+      <c r="D147" s="33" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="98"/>
+      <c r="B148" s="103"/>
+      <c r="C148" s="104"/>
+      <c r="D148" s="33" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="98"/>
+      <c r="B149" s="103"/>
+      <c r="C149" s="104"/>
+      <c r="D149" s="33" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="98"/>
+      <c r="B150" s="103"/>
+      <c r="C150" s="104"/>
+      <c r="D150" s="33" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="98"/>
+      <c r="B151" s="103"/>
+      <c r="C151" s="104"/>
+      <c r="D151" s="33" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="98"/>
+      <c r="B152" s="103"/>
+      <c r="C152" s="104"/>
+      <c r="D152" s="33" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="98"/>
+      <c r="B153" s="103"/>
+      <c r="C153" s="104"/>
+      <c r="D153" s="33" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="98"/>
+      <c r="B154" s="103"/>
+      <c r="C154" s="104"/>
+      <c r="D154" s="33" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="98"/>
+      <c r="B155" s="103"/>
+      <c r="C155" s="104"/>
+      <c r="D155" s="33" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="98"/>
+      <c r="B156" s="103"/>
+      <c r="C156" s="104"/>
+      <c r="D156" s="33" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="99"/>
+      <c r="B157" s="103">
+        <v>4</v>
+      </c>
+      <c r="C157" s="103">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D157" s="33" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="98"/>
+      <c r="B158" s="103"/>
+      <c r="C158" s="103"/>
+      <c r="D158" s="33" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="98"/>
+      <c r="B159" s="103"/>
+      <c r="C159" s="103"/>
+      <c r="D159" s="33" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="98"/>
+      <c r="B160" s="103"/>
+      <c r="C160" s="103"/>
+      <c r="D160" s="33" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="98"/>
+      <c r="B161" s="103"/>
+      <c r="C161" s="103">
+        <v>4.2</v>
+      </c>
+      <c r="D161" s="33" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="98"/>
+      <c r="B162" s="103"/>
+      <c r="C162" s="103"/>
+      <c r="D162" s="33" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="98"/>
+      <c r="B163" s="103"/>
+      <c r="C163" s="103"/>
+      <c r="D163" s="33" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="98"/>
+      <c r="B164" s="103"/>
+      <c r="C164" s="103"/>
+      <c r="D164" s="33" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="98"/>
+      <c r="B165" s="103"/>
+      <c r="C165" s="103"/>
+      <c r="D165" s="33" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="98"/>
+      <c r="B166" s="103"/>
+      <c r="C166" s="103"/>
+      <c r="D166" s="33" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="98"/>
+      <c r="B167" s="103"/>
+      <c r="C167" s="103"/>
+      <c r="D167" s="33" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="98"/>
+      <c r="B168" s="103"/>
+      <c r="C168" s="103">
+        <v>4.3</v>
+      </c>
+      <c r="D168" s="33" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="98"/>
+      <c r="B169" s="103"/>
+      <c r="C169" s="103"/>
+      <c r="D169" s="33" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="98"/>
+      <c r="B170" s="103"/>
+      <c r="C170" s="103"/>
+      <c r="D170" s="33" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="98"/>
+      <c r="B171" s="103"/>
+      <c r="C171" s="103"/>
+      <c r="D171" s="33" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="98"/>
+      <c r="B172" s="103"/>
+      <c r="C172" s="103"/>
+      <c r="D172" s="33" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="98"/>
+      <c r="B173" s="103"/>
+      <c r="C173" s="103"/>
+      <c r="D173" s="33" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="98"/>
+      <c r="B174" s="103"/>
+      <c r="C174" s="103">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D174" s="33" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="98"/>
+      <c r="B175" s="103"/>
+      <c r="C175" s="103"/>
+      <c r="D175" s="33" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="98"/>
+      <c r="B176" s="103"/>
+      <c r="C176" s="103"/>
+      <c r="D176" s="33" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="98"/>
+      <c r="B177" s="103"/>
+      <c r="C177" s="103"/>
+      <c r="D177" s="33" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="98"/>
+      <c r="B178" s="103"/>
+      <c r="C178" s="103"/>
+      <c r="D178" s="33" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="98"/>
+      <c r="B179" s="103"/>
+      <c r="C179" s="103"/>
+      <c r="D179" s="33" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="98"/>
+      <c r="B180" s="103"/>
+      <c r="C180" s="103"/>
+      <c r="D180" s="33" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="98"/>
+      <c r="B181" s="103"/>
+      <c r="C181" s="103"/>
+      <c r="D181" s="33" t="s">
+        <v>421</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="C168:C173"/>
+    <mergeCell ref="C174:C181"/>
+    <mergeCell ref="B3:B25"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="B59:B156"/>
+    <mergeCell ref="B157:B181"/>
+    <mergeCell ref="C116:C126"/>
+    <mergeCell ref="C127:C136"/>
+    <mergeCell ref="C137:C141"/>
+    <mergeCell ref="C142:C156"/>
+    <mergeCell ref="C157:C160"/>
+    <mergeCell ref="C161:C167"/>
+    <mergeCell ref="C59:C64"/>
+    <mergeCell ref="C65:C76"/>
+    <mergeCell ref="C77:C87"/>
+    <mergeCell ref="C88:C100"/>
+    <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C36"/>
+    <mergeCell ref="C37:C44"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="C26:C27"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D13B384-1725-40B5-B0F7-A3A77A0F68B1}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6611,11 +9570,11 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="59"/>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="89" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
       <c r="E1" s="59"/>
       <c r="F1" s="59"/>
     </row>
@@ -6624,7 +9583,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C2" s="53" t="s">
         <v>130</v>
@@ -6640,7 +9599,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="100.8">
-      <c r="A3" s="87">
+      <c r="A3" s="71">
         <v>1</v>
       </c>
       <c r="B3" s="62" t="s">
@@ -6653,58 +9612,58 @@
         <v>135</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="158.4">
-      <c r="A4" s="66">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="91" customFormat="1" ht="302.39999999999998">
+      <c r="A4" s="92">
         <v>2</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>156</v>
+      <c r="C4" s="94" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" s="95" t="s">
+        <v>416</v>
+      </c>
+      <c r="E4" s="94" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="13" customFormat="1" ht="294" customHeight="1">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="88" t="s">
+      <c r="B5" s="72" t="s">
         <v>132</v>
       </c>
       <c r="C5" s="57" t="s">
         <v>141</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="86.4">
       <c r="A6" s="66">
         <v>4</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="73" t="s">
         <v>132</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6739,43 +9698,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF11110B-B1A6-47E4-BCEC-C2B4CA62D5BE}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="86" t="s">
-        <v>151</v>
-      </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="A1" s="90" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="90"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="63" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="C2" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="D2" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="E2" s="63" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="F2" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="63" t="s">
+      <c r="G2" s="63" t="s">
         <v>149</v>
-      </c>
-      <c r="G2" s="63" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:7">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD39C3B-4F9D-47AE-93EB-5D0C8D9CDD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709AE51C-8799-4246-B57B-06429302E847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
     <sheet name="Sprint Backlog" sheetId="8" r:id="rId2"/>
-    <sheet name="Burndown Chart" sheetId="9" r:id="rId3"/>
-    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId4"/>
+    <sheet name="Updated Sprint" sheetId="10" r:id="rId3"/>
+    <sheet name="Burndown Chart" sheetId="9" r:id="rId4"/>
+    <sheet name="T Shirt sizing rules" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
@@ -664,8 +665,44 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{4C8D1B9E-A5AC-43BE-8365-C18029D3B009}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+TBD
+WiP
+Done</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -687,7 +724,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="258">
   <si>
     <t>Work Item</t>
   </si>
@@ -1031,9 +1068,6 @@
 and press on submit button</t>
   </si>
   <si>
-    <t xml:space="preserve">I can have my skin image analysed for visible skin concerns and proceed to the questionnaire to provide additional information about my skin. </t>
-  </si>
-  <si>
     <t>Test User Story 1 acceptance criteria</t>
   </si>
   <si>
@@ -1757,13 +1791,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">1. The user must only be allowed to proceed if the uploaded image passes all image-quality checks for blurriness, lighting, and resolution.
-2. Once the image passes the quality checks, the image must be submitted to the Visual AI component for skin-concern analysis.
-3. The image-analysis results should be retained and passed to the concern fusion stage so that they can later be combined with the questionnaire results.
-4. After successful Visual AI analysis, the user must be redirected to the skin questionnaire.
-</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Store accepted image in </t>
     </r>
@@ -1801,9 +1828,6 @@
     <t>Story Points Done</t>
   </si>
   <si>
-    <t>Total Story Points</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -1829,6 +1853,331 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I can have my skin image analysed for visible skin concerns , be redirected to a questionnaire to give a complete profile of my skin, and finally view my reccomendations page with the following fields:
+1. Hello "user_full_name" !
+2. Skin analysis results: Primary Concerns:
+those detected through the image.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The user must only be allowed to proceed if the uploaded image passes all image-quality checks for blurriness, lighting, and resolution.
+2. Once the image passes the quality checks, the image must be submitted to the Visual AI component for skin-concern analysis.
+3. After successful Visual AI analysis, the user must be redirected to the skin questionnaire.
+4. Detected skin concerns should be from the series: 
+SC0001-SC0019 &amp; SC1001-SC1009
+5. If no skin concern is detected(perfectly fit skin) then Skin analysis results should show the following message:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"Your skin looks perfect!"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6. If the image contains one or multiple particular skin concerns then, all of those should be shown in the Skin analysis results: Primary Concerns.
+7. No other skins concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images and questionnaire.</t>
+    </r>
+  </si>
+  <si>
+    <t>Receive image from Shopify widget
+Validate image file type
+Validate image can be decoded/read
+Validate image resolution
+Calculate image sharpness
+Calculate image brightness/lighting
+Define/configure blur rejection threshold
+Define/configure low-light rejection threshold
+Define/configure minimum resolution threshold</t>
+  </si>
+  <si>
+    <t>Combine all image-quality checks
+Reject image if any required quality check fails
+Accept image only if all required checks pass</t>
+  </si>
+  <si>
+    <t>Return image-validation result to frontend
+Display "Your image is not valid. Take another image with better quality"
+Redirect user back to selfie capture</t>
+  </si>
+  <si>
+    <t>Test invalid file type
+Test unreadable image
+Test low-resolution image
+Test blurry image
+Test low-light image
+Test combinations of quality failures
+Test valid image
+Test User Story 1 acceptance criteria</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store accepted image in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">skin_image
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Associate image with current </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">customer_session
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Initiate asynchronous Visual AI image analysis
+Redirect user to questionnaire </t>
+    </r>
+  </si>
+  <si>
+    <t>Define Visual AI response JSON schema based on image_detection.json
+Define supported image-detectable concern IDs: SC0001–SC0019, SC1001–SC1009</t>
+  </si>
+  <si>
+    <t>Define Visual AI system prompt
+Define image-analysis instructions
+Define skin-concern detection rules
+Restrict output to supported concern IDs
+Define no-concern behaviour
+Require AI explanation for detected concerns
+Require JSON-only response</t>
+  </si>
+  <si>
+    <t>Send accepted image to Visual AI
+Validate Visual AI response against JSON schema
+Validate returned concern IDs
+Handle duplicate concern IDs
+Handle unsupported concern IDs
+Handle empty/no-concern response
+Handle malformed AI response
+Handle AI/API failure</t>
+  </si>
+  <si>
+    <t>Store Visual AI result in session_skin_concern_detection
+Store detected concern IDs
+Store AI-generated explanations
+Store raw detection JSON</t>
+  </si>
+  <si>
+    <t>Build recommendation response containing user full name
+		Include image-detected primary skin concerns
+		Display "Your skin looks perfect!" when no concern is detected
+		Return recommendation response to Shopify widget
+		Display user name
+		Display primary skin concerns</t>
+  </si>
+  <si>
+    <t>Test Visual AI response validation
+		Test supported concern IDs
+		Test unsupported concern IDs
+		Test duplicate concern handling
+		Test multiple detected concerns
+		Test no visible concern
+		Test malformed AI response
+		Test AI/API failure
+		Test asynchronous image analysis flow
+		Test image-based recommendation response
+		Test User Story 2 acceptance criteria</t>
+  </si>
+  <si>
+    <t>Total Sprint Story Points</t>
+  </si>
+  <si>
+    <t>Display questionnaire to user
+Collect questionnaire answers
+Validate required questionnaire fields
+Store questionnaire answers in questionnaire_response
+Associate questionnaire response with current customer_session
+Submit questionnaire for LLM analysis</t>
+  </si>
+  <si>
+    <t>Define questionnaire-analysis LLM prompt
+Pass questionnaire JSON to LLM
+Define concern extraction rules
+Define skin-type extraction
+Define sensitivity extraction
+Define questionnaire-only concern handling
+Validate LLM response
+Handle malformed LLM response
+Handle LLM/API failure
+Store questionnaire detection result in session_skin_concern_detection
+Store LLM-generated explanations
+Store raw detection JSON</t>
+  </si>
+  <si>
+    <t>Retrieve image-based detection results
+Retrieve questionnaire-based detection results
+Match results using skin_concern_id
+Calculate image_skin_concern_exists OR questionnaire_skin_concern_exists
+Combine image and questionnaire explanations
+Store combined result in session_skin_concern
+Handle concerns detected only from image
+Handle concerns detected only from questionnaire
+Handle concerns detected by both
+Handle no detected concerns
+Validate final combined concern set</t>
+  </si>
+  <si>
+    <t>Retrieve combined skin concerns
+Retrieve relevant concern_benefit mappings
+Retrieve active_benefit_score data
+Calculate/rank active candidates
+Retrieve applicable bases using questionnaire/session information
+Apply age suitability
+Apply skin-type suitability
+Apply climate/location considerations
+Apply acne-suitability requirements
+Apply questionnaire preferences
+Check base-active compatibility
+Produce candidate bases
+Produce candidate actives</t>
+  </si>
+  <si>
+    <t>Pass candidate information and relevant RAG information to LLM
+Generate recommended base
+Generate recommended active ingredients
+Generate explanation for selected base
+Generate explanation for selected actives
+Ensure selected actives address detected concerns
+Ensure selected actives are compatible with selected base
+Generate formulation information
+Validate recommendation output</t>
+  </si>
+  <si>
+    <t>Create recommendation_run
+Store selected base in recommendation_base
+Store selected actives in recommendation_active
+Store recommendation explanations
+Store recommendation scores/ranks where applicable
+Store final formatted response in recommendation_output</t>
+  </si>
+  <si>
+    <t>Build final response containing user full name
+Include combined primary skin concerns
+Include skin type
+Include sensitivity level
+Include recommended base
+Include recommended active ingredients
+Include active percentages/quantities
+Include formulation weight
+Include formulation explanation
+Include formulation/recommendation ID
+Return recommendation response to Shopify widget</t>
+  </si>
+  <si>
+    <t>Display user name
+Display primary skin concerns
+Display "Your skin looks perfect!" when no concern is detected
+Display skin type
+Display sensitivity level
+Display recommended base
+Display active ingredients
+Display active percentages
+Display formulation explanation
+Display formulation information</t>
+  </si>
+  <si>
+    <t>Handle no-compatible-recommendation case
+Handle LLM failure
+Handle database failure
+Handle invalid recommendation/formulation
+Return appropriate frontend error response</t>
+  </si>
+  <si>
+    <t>Test questionnaire submission
+Test questionnaire LLM analysis
+Test concern fusion
+Test image/questionnaire OR logic
+Test candidate generation
+Test base selection
+Test active selection
+Test base-active compatibility
+Test formulation validation
+Test 100 g formulation requirement
+Test recommendation persistence
+Test final recommendation response
+Test no-concern scenario
+Test recommendation error handling
+Test User Story 3 acceptance criteria</t>
+  </si>
+  <si>
+    <t>Identify required Shopify cart/API capability
+Identify Shopify product/variant representing the formulation
+Define formulation metadata required by Shopify cart
+Create/test Shopify product or variant</t>
+  </si>
+  <si>
+    <t>Receive formulation ID from frontend
+Retrieve saved formulation
+Verify formulation belongs to the logged-in customer/session
+Verify formulation is valid
+Add recommended formulation/product to Shopify cart
+Attach required formulation metadata
+Return cart response</t>
+  </si>
+  <si>
+    <t>Implement Add to Cart button
+Disable button while request is processing
+Call Add to Cart API
+Display successful cart-addition state
+Handle Add to Cart failure
+Prevent duplicate submissions</t>
+  </si>
+  <si>
+    <t>Test formulation ID validation
+Test customer/formulation ownership
+Test Shopify cart item creation
+Test formulation metadata
+Test successful Add to Cart
+Test Add to Cart failure
+Test duplicate submission prevention
+Test User Story 4 acceptance criteria</t>
   </si>
 </sst>
 </file>
@@ -1908,7 +2257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1939,8 +2288,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1963,11 +2318,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2030,11 +2431,23 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2043,26 +2456,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2159,10 +2580,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Burndown Chart'!$B$2:$B$10</c:f>
+              <c:f>'Burndown Chart'!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46265</c:v>
                 </c:pt>
@@ -2195,36 +2616,36 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Burndown Chart'!$C$2:$C$10</c:f>
+              <c:f>'Burndown Chart'!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2232,7 +2653,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7C1A-409D-AABE-FDA2C642585F}"/>
+              <c16:uniqueId val="{00000000-007D-47A5-8A1B-3F2D0F713771}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2264,10 +2685,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Burndown Chart'!$B$2:$B$10</c:f>
+              <c:f>'Burndown Chart'!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>46265</c:v>
                 </c:pt>
@@ -2300,33 +2721,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Burndown Chart'!$D$2:$D$10</c:f>
+              <c:f>'Burndown Chart'!$D$2:$D$11</c:f>
               <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.5</c:v>
+                  <c:v>33.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45</c:v>
+                  <c:v>28.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.5</c:v>
+                  <c:v>23.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>22.5</c:v>
+                  <c:v>14.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.5</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -2337,7 +2758,112 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7C1A-409D-AABE-FDA2C642585F}"/>
+              <c16:uniqueId val="{00000001-007D-47A5-8A1B-3F2D0F713771}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Burndown Chart'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Story Points Done</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Burndown Chart'!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46275</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Burndown Chart'!$E$2:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-007D-47A5-8A1B-3F2D0F713771}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2350,11 +2876,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1750665967"/>
-        <c:axId val="498407599"/>
+        <c:axId val="1354025151"/>
+        <c:axId val="930835984"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1750665967"/>
+        <c:axId val="1354025151"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2397,7 +2923,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="498407599"/>
+        <c:crossAx val="930835984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -2405,7 +2931,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="498407599"/>
+        <c:axId val="930835984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2456,7 +2982,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1750665967"/>
+        <c:crossAx val="1354025151"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3103,23 +3629,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>525780</xdr:rowOff>
+      <xdr:rowOff>716280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>365760</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{368878C4-32C9-AB53-5A7A-E52A81DEFEC7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{114FF3BD-8CD1-F1A6-71A7-8072407EE36D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3448,11 +3974,11 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -3493,7 +4019,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="172.8">
+    <row r="4" spans="1:6" ht="279" customHeight="1">
       <c r="A4" s="15">
         <v>2</v>
       </c>
@@ -3504,10 +4030,10 @@
         <v>55</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>230</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" ht="294" customHeight="1">
@@ -3572,7 +4098,8 @@
     <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3591,18 +4118,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -3637,1190 +4164,1190 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="32">
+      <c r="A3" s="36">
         <v>1</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="30">
         <v>1</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="30">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="30" cm="1">
+      <c r="F3" s="34" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
+        <v>61</v>
+      </c>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="32"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="32"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
+      <c r="A6" s="36"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="36"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="32"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="36"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="32"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="36"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="32"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="36"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="32"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="36"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30">
+        <v>1.2</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="32"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33">
-        <v>1.2</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="30" cm="1">
+      <c r="F12" s="34" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="36"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="32"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="36"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30">
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33">
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="34"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="36"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="36"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="36"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30">
+        <v>1.4</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="34"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="36"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="36"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="36"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="36"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="36"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="36"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="36"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="36"/>
+      <c r="B26" s="37">
+        <v>2</v>
+      </c>
+      <c r="C26" s="30">
+        <v>2.1</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E26" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="30"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="32"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33">
-        <v>1.4</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="30" t="s">
+      <c r="F26" s="34"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="36"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="35"/>
+      <c r="F27" s="34"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="36"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E28" s="35"/>
+      <c r="F28" s="34"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="36"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="32">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="34"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="36"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="36"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="30">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="36"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="36"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="36"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="36"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="36"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="36"/>
+      <c r="B37" s="37"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="36"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="30">
+        <v>2.4</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="30"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="32"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="32"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="32"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="32"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="32"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="32"/>
-      <c r="B26" s="34">
-        <v>2</v>
-      </c>
-      <c r="C26" s="33">
-        <v>2.1</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="30"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="32"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="30"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="32"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="30"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="32"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="36">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="30"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="32"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="32"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="33">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="32"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="32"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="32"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="32"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="32"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="32"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="32"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="33">
-        <v>2.4</v>
-      </c>
-      <c r="D38" s="7" t="s">
+      <c r="F38" s="34"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="36"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E38" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" s="30"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="32"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="7" t="s">
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="36"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="32"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="32"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="33"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="32"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="33"/>
+      <c r="A42" s="36"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="30"/>
       <c r="D42" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="36"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="32"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="7" t="s">
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="36"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="32"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="7" t="s">
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="36"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="32"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="7" t="s">
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="36"/>
+      <c r="B46" s="37"/>
+      <c r="C46" s="30">
+        <v>2.5</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="34"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="36"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="32"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="33">
-        <v>2.5</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="E46" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46" s="30"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="32"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="7" t="s">
+      <c r="E47" s="35"/>
+      <c r="F47" s="34"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="36"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E47" s="31"/>
-      <c r="F47" s="30"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="32"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="7" t="s">
+      <c r="E48" s="35"/>
+      <c r="F48" s="34"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="36"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E48" s="31"/>
-      <c r="F48" s="30"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="32"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="7" t="s">
+      <c r="E49" s="35"/>
+      <c r="F49" s="34"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="36"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="30">
+        <v>2.7</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E49" s="31"/>
-      <c r="F49" s="30"/>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="32"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="33">
-        <v>2.7</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="E50" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="34"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="36"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E50" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F50" s="30"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="32"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="7" t="s">
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="36"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="32"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="7" t="s">
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="36"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="32"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="7" t="s">
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="36"/>
+      <c r="B54" s="37"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="32"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="7" t="s">
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="36"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="32"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="7" t="s">
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="36"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="32"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="7" t="s">
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="36"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="32"/>
-      <c r="B57" s="34"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="32"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="33"/>
+      <c r="A58" s="36"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="33">
+      <c r="B59" s="30">
         <v>3</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="30">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
       <c r="D60" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="33"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
       <c r="D61" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="33"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
       <c r="D62" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="33"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
       <c r="D63" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
       <c r="D64" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="33"/>
-      <c r="C65" s="33">
+      <c r="B65" s="30"/>
+      <c r="C65" s="30">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="33"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
       <c r="D66" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="33"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
       <c r="D68" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="33"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
       <c r="D69" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="33"/>
-      <c r="C70" s="33"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
       <c r="D70" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
       <c r="D71" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="33"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="33"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
       <c r="D73" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="33"/>
-      <c r="C74" s="33"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
       <c r="D74" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="33"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
       <c r="D75" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="33"/>
-      <c r="C76" s="33"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
       <c r="D76" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="33"/>
-      <c r="C77" s="33">
+      <c r="B77" s="30"/>
+      <c r="C77" s="30">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="33"/>
-      <c r="C78" s="33"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
       <c r="D78" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="33"/>
-      <c r="C79" s="33"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
       <c r="D79" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="33"/>
-      <c r="C80" s="33"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
       <c r="D80" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="33"/>
-      <c r="C81" s="33"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="30"/>
       <c r="D81" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="33"/>
-      <c r="C82" s="33"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
       <c r="D82" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="33"/>
-      <c r="C83" s="33"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
       <c r="D83" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="33"/>
-      <c r="C84" s="33"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
       <c r="D84" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="33"/>
-      <c r="C85" s="33"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
       <c r="D85" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="33"/>
-      <c r="C86" s="33"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
       <c r="D86" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="33"/>
-      <c r="C87" s="33"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
       <c r="D87" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="33"/>
-      <c r="C88" s="33">
+      <c r="B88" s="30"/>
+      <c r="C88" s="30">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="33"/>
-      <c r="C89" s="33"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
       <c r="D89" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="33"/>
-      <c r="C90" s="33"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
       <c r="D90" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="33"/>
-      <c r="C91" s="33"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
       <c r="D91" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="33"/>
-      <c r="C92" s="33"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
       <c r="D92" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="33"/>
-      <c r="C93" s="33"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
       <c r="D93" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="33"/>
-      <c r="C94" s="33"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
       <c r="D94" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="33"/>
-      <c r="C95" s="33"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
       <c r="D95" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="33"/>
-      <c r="C96" s="33"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
       <c r="D96" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="33"/>
-      <c r="C97" s="33"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
       <c r="D97" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="33"/>
-      <c r="C98" s="33"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
       <c r="D98" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="33"/>
-      <c r="C99" s="33"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
       <c r="D99" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="33"/>
-      <c r="C100" s="33"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
       <c r="D100" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="33"/>
-      <c r="C101" s="33">
+      <c r="B101" s="30"/>
+      <c r="C101" s="30">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="33"/>
-      <c r="C102" s="33"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30"/>
       <c r="D102" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="33"/>
-      <c r="C103" s="33"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
       <c r="D103" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="33"/>
-      <c r="C104" s="33"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
       <c r="D104" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="33"/>
-      <c r="C105" s="33"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
       <c r="D105" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="33"/>
-      <c r="C106" s="33"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="30"/>
       <c r="D106" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="33"/>
-      <c r="C107" s="33"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
       <c r="D107" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="33"/>
-      <c r="C108" s="33"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30"/>
       <c r="D108" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="33"/>
-      <c r="C109" s="33"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="30"/>
       <c r="D109" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="33"/>
-      <c r="C110" s="33">
+      <c r="B110" s="30"/>
+      <c r="C110" s="30">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="33"/>
-      <c r="C111" s="33"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="30"/>
       <c r="D111" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="33"/>
-      <c r="C112" s="33"/>
+      <c r="B112" s="30"/>
+      <c r="C112" s="30"/>
       <c r="D112" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="33"/>
-      <c r="C113" s="33"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
       <c r="D113" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="33"/>
-      <c r="C114" s="33"/>
+      <c r="B114" s="30"/>
+      <c r="C114" s="30"/>
       <c r="D114" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="33"/>
-      <c r="C115" s="33"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="30"/>
       <c r="D115" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="33"/>
-      <c r="C116" s="33">
+      <c r="B116" s="30"/>
+      <c r="C116" s="30">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="33"/>
-      <c r="C117" s="33"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="30"/>
       <c r="D117" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="33"/>
-      <c r="C118" s="33"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="30"/>
       <c r="D118" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="33"/>
-      <c r="C119" s="33"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
       <c r="D119" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="33"/>
-      <c r="C120" s="33"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="30"/>
       <c r="D120" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="33"/>
-      <c r="C121" s="33"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="30"/>
       <c r="D121" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="33"/>
-      <c r="C122" s="33"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="30"/>
       <c r="D122" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="33"/>
-      <c r="C123" s="33"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="30"/>
       <c r="D123" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="33"/>
-      <c r="C124" s="33"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="30"/>
       <c r="D124" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="33"/>
-      <c r="C125" s="33"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
       <c r="D125" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="33"/>
-      <c r="C126" s="33"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="30"/>
       <c r="D126" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="33"/>
-      <c r="C127" s="33">
+      <c r="B127" s="30"/>
+      <c r="C127" s="30">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -4829,338 +5356,338 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="33"/>
-      <c r="C128" s="33"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="30"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="33"/>
-      <c r="C129" s="33"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="30"/>
       <c r="D129" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="33"/>
-      <c r="C130" s="33"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="30"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="33"/>
-      <c r="C131" s="33"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="33"/>
-      <c r="C132" s="33"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="30"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="33"/>
-      <c r="C133" s="33"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="30"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="33"/>
-      <c r="C134" s="33"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="30"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="33"/>
-      <c r="C135" s="33"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="30"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="33"/>
-      <c r="C136" s="33"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="30"/>
       <c r="D136" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="33"/>
-      <c r="C137" s="33">
+      <c r="B137" s="30"/>
+      <c r="C137" s="30">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="33"/>
-      <c r="C138" s="33"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="30"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="33"/>
-      <c r="C139" s="33"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="30"/>
       <c r="D139" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="33"/>
-      <c r="C140" s="33"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="30"/>
       <c r="D140" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="33"/>
-      <c r="C141" s="33"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="30"/>
       <c r="D141" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="33"/>
-      <c r="C142" s="37">
+      <c r="B142" s="30"/>
+      <c r="C142" s="31">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="33"/>
-      <c r="C143" s="37"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="31"/>
       <c r="D143" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="33"/>
-      <c r="C144" s="37"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="31"/>
       <c r="D144" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="33"/>
-      <c r="C145" s="37"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="31"/>
       <c r="D145" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="33"/>
-      <c r="C146" s="37"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="31"/>
       <c r="D146" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="33"/>
-      <c r="C147" s="37"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="31"/>
       <c r="D147" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="33"/>
-      <c r="C148" s="37"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="31"/>
       <c r="D148" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="33"/>
-      <c r="C149" s="37"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="31"/>
       <c r="D149" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="33"/>
-      <c r="C150" s="37"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="31"/>
       <c r="D150" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="33"/>
-      <c r="C151" s="37"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="31"/>
       <c r="D151" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="33"/>
-      <c r="C152" s="37"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="31"/>
       <c r="D152" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="33"/>
-      <c r="C153" s="37"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="31"/>
       <c r="D153" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="33"/>
-      <c r="C154" s="37"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="31"/>
       <c r="D154" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="33"/>
-      <c r="C155" s="37"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="31"/>
       <c r="D155" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="33"/>
-      <c r="C156" s="37"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="31"/>
       <c r="D156" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="33">
+      <c r="B157" s="30">
         <v>4</v>
       </c>
-      <c r="C157" s="33">
+      <c r="C157" s="30">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="33"/>
-      <c r="C158" s="33"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="30"/>
       <c r="D158" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="33"/>
-      <c r="C159" s="33"/>
+      <c r="B159" s="30"/>
+      <c r="C159" s="30"/>
       <c r="D159" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="33"/>
-      <c r="C160" s="33"/>
+      <c r="B160" s="30"/>
+      <c r="C160" s="30"/>
       <c r="D160" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="33"/>
-      <c r="C161" s="33">
+      <c r="B161" s="30"/>
+      <c r="C161" s="30">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="33"/>
-      <c r="C162" s="33"/>
+      <c r="B162" s="30"/>
+      <c r="C162" s="30"/>
       <c r="D162" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="33"/>
-      <c r="C163" s="33"/>
+      <c r="B163" s="30"/>
+      <c r="C163" s="30"/>
       <c r="D163" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="33"/>
-      <c r="C164" s="33"/>
+      <c r="B164" s="30"/>
+      <c r="C164" s="30"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="33"/>
-      <c r="C165" s="33"/>
+      <c r="B165" s="30"/>
+      <c r="C165" s="30"/>
       <c r="D165" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="33"/>
-      <c r="C166" s="33"/>
+      <c r="B166" s="30"/>
+      <c r="C166" s="30"/>
       <c r="D166" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="33"/>
-      <c r="C167" s="33"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="33"/>
-      <c r="C168" s="33">
+      <c r="B168" s="30"/>
+      <c r="C168" s="30">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -5169,113 +5696,148 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="33"/>
-      <c r="C169" s="33"/>
+      <c r="B169" s="30"/>
+      <c r="C169" s="30"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="33"/>
-      <c r="C170" s="33"/>
+      <c r="B170" s="30"/>
+      <c r="C170" s="30"/>
       <c r="D170" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="33"/>
-      <c r="C171" s="33"/>
+      <c r="B171" s="30"/>
+      <c r="C171" s="30"/>
       <c r="D171" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="33"/>
-      <c r="C172" s="33"/>
+      <c r="B172" s="30"/>
+      <c r="C172" s="30"/>
       <c r="D172" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="33"/>
-      <c r="C173" s="33"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="33"/>
-      <c r="C174" s="33">
+      <c r="B174" s="30"/>
+      <c r="C174" s="30">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="33"/>
-      <c r="C175" s="33"/>
+      <c r="B175" s="30"/>
+      <c r="C175" s="30"/>
       <c r="D175" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="33"/>
-      <c r="C176" s="33"/>
+      <c r="B176" s="30"/>
+      <c r="C176" s="30"/>
       <c r="D176" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="33"/>
-      <c r="C177" s="33"/>
+      <c r="B177" s="30"/>
+      <c r="C177" s="30"/>
       <c r="D177" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="33"/>
-      <c r="C178" s="33"/>
+      <c r="B178" s="30"/>
+      <c r="C178" s="30"/>
       <c r="D178" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="33"/>
-      <c r="C179" s="33"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
       <c r="D179" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="33"/>
-      <c r="C180" s="33"/>
+      <c r="B180" s="30"/>
+      <c r="C180" s="30"/>
       <c r="D180" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="33"/>
-      <c r="C181" s="33"/>
+      <c r="B181" s="30"/>
+      <c r="C181" s="30"/>
       <c r="D181" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{F0DC7BB0-6771-4160-B371-AE490E8879B7}"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -5292,276 +5854,646 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AFAF48-8618-45CD-B1C5-CEC08E5846C2}">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" s="4" customFormat="1">
+      <c r="A2" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="129.6">
+      <c r="A3" s="43">
+        <v>1</v>
+      </c>
+      <c r="B3" s="43">
+        <v>1</v>
+      </c>
+      <c r="C3" s="15">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" cm="1">
+        <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.2">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" cm="1">
+        <f t="array" ref="F4">_xlfn.SWITCH(E4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.2">
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" cm="1">
+        <f t="array" ref="F5">_xlfn.SWITCH(E5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="115.2">
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="15">
+        <v>1.4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" cm="1">
+        <f t="array" ref="F6">_xlfn.SWITCH(E6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57.6">
+      <c r="A7" s="43"/>
+      <c r="B7" s="43">
+        <v>2</v>
+      </c>
+      <c r="C7" s="15">
+        <v>2.1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">_xlfn.SWITCH(E7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="43.2">
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="15">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" cm="1">
+        <f t="array" ref="F8">_xlfn.SWITCH(E8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="100.8">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="15">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" cm="1">
+        <f t="array" ref="F9">_xlfn.SWITCH(E9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="115.2">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="15">
+        <v>2.4</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" cm="1">
+        <f t="array" ref="F10">_xlfn.SWITCH(E10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" cm="1">
+        <f t="array" ref="F11">_xlfn.SWITCH(E11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="86.4">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="15">
+        <v>2.6</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" cm="1">
+        <f t="array" ref="F12">_xlfn.SWITCH(E12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="158.4">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="15">
+        <v>2.7</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" cm="1">
+        <f t="array" ref="F13">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="44"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39">
+        <f>SUM(F3:F13)</f>
+        <v>38</v>
+      </c>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="41"/>
+    </row>
+    <row r="15" spans="1:10" ht="86.4">
+      <c r="A15" s="45">
+        <v>2</v>
+      </c>
+      <c r="B15" s="45">
+        <v>3</v>
+      </c>
+      <c r="C15" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="172.8">
+      <c r="A16" s="43"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="172.8">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="15">
+        <v>3.3</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="187.2">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="15">
+        <v>3.4</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="129.6">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="86.4">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="158.4">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="15">
+        <v>3.7</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="144">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="15">
+        <v>3.8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="72">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="15">
+        <v>3.9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="216">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="47">
+        <v>3.1</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="57.6">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43">
+        <v>4</v>
+      </c>
+      <c r="C25" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="100.8">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="86.4">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="115.2">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="A3:A13"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="B15:B24"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A15:A28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA087AEC-DE6A-4BD3-B656-5E86DF79D39A}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="10.77734375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43.2">
+    <row r="1" spans="1:5" ht="57.6">
       <c r="A1" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="D1" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="E1" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="25" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B2" s="26">
         <v>46265</v>
       </c>
       <c r="C2" s="27">
-        <f>F2-SUM(E$2:E2)</f>
-        <v>60</v>
-      </c>
-      <c r="D2" s="28">
-        <f t="shared" ref="D2:D10" si="0">F2*(1-(A2-1)/8)</f>
-        <v>60</v>
-      </c>
-      <c r="E2" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E2)</f>
+        <v>38</v>
+      </c>
+      <c r="D2" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A2-1)/8)</f>
+        <v>38</v>
+      </c>
+      <c r="E2" s="28">
         <v>0</v>
       </c>
-      <c r="F2" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="25" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B3" s="26">
         <v>46266</v>
       </c>
       <c r="C3" s="27">
-        <f>F3-SUM(E$2:E3)</f>
-        <v>60</v>
-      </c>
-      <c r="D3" s="28">
-        <f t="shared" si="0"/>
-        <v>52.5</v>
-      </c>
-      <c r="E3" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E3)</f>
+        <v>38</v>
+      </c>
+      <c r="D3" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A3-1)/8)</f>
+        <v>33.25</v>
+      </c>
+      <c r="E3" s="28">
         <v>0</v>
       </c>
-      <c r="F3" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="25" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B4" s="26">
         <v>46267</v>
       </c>
       <c r="C4" s="27">
-        <f>F4-SUM(E$2:E4)</f>
-        <v>60</v>
-      </c>
-      <c r="D4" s="28">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="E4" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E4)</f>
+        <v>38</v>
+      </c>
+      <c r="D4" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A4-1)/8)</f>
+        <v>28.5</v>
+      </c>
+      <c r="E4" s="28">
         <v>0</v>
       </c>
-      <c r="F4" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="25" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B5" s="26">
         <v>46268</v>
       </c>
       <c r="C5" s="27">
-        <f>F5-SUM(E$2:E5)</f>
-        <v>60</v>
-      </c>
-      <c r="D5" s="28">
-        <f t="shared" si="0"/>
-        <v>37.5</v>
-      </c>
-      <c r="E5" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E5)</f>
+        <v>38</v>
+      </c>
+      <c r="D5" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A5-1)/8)</f>
+        <v>23.75</v>
+      </c>
+      <c r="E5" s="28">
         <v>0</v>
       </c>
-      <c r="F5" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="25" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B6" s="26">
         <v>46269</v>
       </c>
       <c r="C6" s="27">
-        <f>F6-SUM(E$2:E6)</f>
-        <v>60</v>
-      </c>
-      <c r="D6" s="28">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="E6" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E6)</f>
+        <v>38</v>
+      </c>
+      <c r="D6" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A6-1)/8)</f>
+        <v>19</v>
+      </c>
+      <c r="E6" s="28">
         <v>0</v>
       </c>
-      <c r="F6" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="25" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B7" s="26">
         <v>46272</v>
       </c>
       <c r="C7" s="27">
-        <f>F7-SUM(E$2:E7)</f>
-        <v>60</v>
-      </c>
-      <c r="D7" s="28">
-        <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-      <c r="E7" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E7)</f>
+        <v>38</v>
+      </c>
+      <c r="D7" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A7-1)/8)</f>
+        <v>14.25</v>
+      </c>
+      <c r="E7" s="28">
         <v>0</v>
       </c>
-      <c r="F7" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="25" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B8" s="26">
         <v>46273</v>
       </c>
       <c r="C8" s="27">
-        <f>F8-SUM(E$2:E8)</f>
-        <v>60</v>
-      </c>
-      <c r="D8" s="28">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E8" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E8)</f>
+        <v>38</v>
+      </c>
+      <c r="D8" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A8-1)/8)</f>
+        <v>9.5</v>
+      </c>
+      <c r="E8" s="28">
         <v>0</v>
       </c>
-      <c r="F8" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B9" s="26">
         <v>46274</v>
       </c>
       <c r="C9" s="27">
-        <f>F9-SUM(E$2:E9)</f>
-        <v>60</v>
-      </c>
-      <c r="D9" s="28">
-        <f t="shared" si="0"/>
-        <v>7.5</v>
-      </c>
-      <c r="E9" s="29">
+        <f>('Updated Sprint'!F14)-SUM(E$2:E9)</f>
+        <v>38</v>
+      </c>
+      <c r="D9" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A9-1)/8)</f>
+        <v>4.75</v>
+      </c>
+      <c r="E9" s="28">
         <v>0</v>
       </c>
-      <c r="F9" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="25" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B10" s="26">
         <v>46275</v>
       </c>
       <c r="C10" s="27">
-        <f>F10-SUM(E$2:E10)</f>
-        <v>60</v>
-      </c>
-      <c r="D10" s="28">
-        <f t="shared" si="0"/>
+        <f>('Updated Sprint'!F14)-SUM(E$2:E10)</f>
+        <v>38</v>
+      </c>
+      <c r="D10" s="12">
+        <f>('Updated Sprint'!F14)*(1-(A10-1)/8)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="28">
         <v>0</v>
       </c>
-      <c r="F10" s="29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:5">
       <c r="B11" s="5"/>
     </row>
   </sheetData>
@@ -5571,21 +6503,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF11110B-B1A6-47E4-BCEC-C2B4CA62D5BE}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709AE51C-8799-4246-B57B-06429302E847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5226C896-19F0-4C3B-84F0-AF4AC9EE4895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -702,7 +702,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -724,7 +724,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="265">
   <si>
     <t>Work Item</t>
   </si>
@@ -1997,12 +1997,6 @@
 Handle empty/no-concern response
 Handle malformed AI response
 Handle AI/API failure</t>
-  </si>
-  <si>
-    <t>Store Visual AI result in session_skin_concern_detection
-Store detected concern IDs
-Store AI-generated explanations
-Store raw detection JSON</t>
   </si>
   <si>
     <t>Build recommendation response containing user full name
@@ -2178,6 +2172,33 @@
 Test Add to Cart failure
 Test duplicate submission prevention
 Test User Story 4 acceptance criteria</t>
+  </si>
+  <si>
+    <t>Vidit</t>
+  </si>
+  <si>
+    <t>Azad</t>
+  </si>
+  <si>
+    <t>Rajanya</t>
+  </si>
+  <si>
+    <t>Everyone</t>
+  </si>
+  <si>
+    <t>Sayan</t>
+  </si>
+  <si>
+    <t>Store Visual AI result in session_skin_concern_detection db table
+Store detected concern IDs column 
+Store AI-generated explanations column against concern IDs
+Store raw detection JSON against concern IDs</t>
+  </si>
+  <si>
+    <t>Azad, Sayan</t>
+  </si>
+  <si>
+    <t>Priority</t>
   </si>
 </sst>
 </file>
@@ -2257,7 +2278,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2291,6 +2312,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2368,7 +2395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2434,19 +2461,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2456,35 +2497,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2621,31 +2657,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2726,28 +2762,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>38</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33.25</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.5</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.75</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>14.25</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.5</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.75</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -3974,11 +4010,11 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4118,18 +4154,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4164,632 +4200,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="36">
+      <c r="A3" s="42">
         <v>1</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="43">
         <v>1</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="43">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="34" cm="1">
+      <c r="F3" s="40" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="36"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
       <c r="D4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="36"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
+      <c r="A5" s="42"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="36"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="36"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
       <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="36"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
       <c r="D8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="36"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
+      <c r="A9" s="42"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="36"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="42"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
       <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="36"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
       <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="36"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30">
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="34" cm="1">
+      <c r="F12" s="40" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="36"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
       <c r="D13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="36"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="A14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
       <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="36"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30">
+      <c r="A15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="34"/>
+      <c r="F15" s="40"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="36"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
       <c r="D16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="36"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
       <c r="D17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="36"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30">
+      <c r="A18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="34"/>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="36"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="36"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
       <c r="D20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="36"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
       <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="36"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
       <c r="D22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="36"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
       <c r="D23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="36"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
       <c r="D24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="36"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
       <c r="D25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="36"/>
-      <c r="B26" s="37">
+      <c r="A26" s="42"/>
+      <c r="B26" s="44">
         <v>2</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="43">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="34"/>
+      <c r="F26" s="40"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="36"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="30"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="43"/>
       <c r="D27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="34"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="36"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="30"/>
+      <c r="A28" s="42"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="43"/>
       <c r="D28" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="34"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="40"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="36"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="32">
+      <c r="A29" s="42"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="34" t="s">
+      <c r="E29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="34"/>
+      <c r="F29" s="40"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="36"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="32"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45"/>
       <c r="D30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="36"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="30">
+      <c r="A31" s="42"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="43">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34" t="s">
+      <c r="F31" s="40"/>
+      <c r="G31" s="40" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="36"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="30"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="43"/>
       <c r="D32" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="36"/>
-      <c r="B33" s="37"/>
-      <c r="C33" s="30"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="43"/>
       <c r="D33" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="36"/>
-      <c r="B34" s="37"/>
-      <c r="C34" s="30"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="43"/>
       <c r="D34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="36"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="30"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="43"/>
       <c r="D35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="36"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="30"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="43"/>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="36"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="30"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="43"/>
       <c r="D37" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="36"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="30">
+      <c r="A38" s="42"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="43">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="34" t="s">
+      <c r="E38" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="34"/>
+      <c r="F38" s="40"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="36"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="30"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="43"/>
       <c r="D39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="36"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="30"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="43"/>
       <c r="D40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="36"/>
-      <c r="B41" s="37"/>
-      <c r="C41" s="30"/>
+      <c r="A41" s="42"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="43"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="36"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="30"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="43"/>
       <c r="D42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="36"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="30"/>
+      <c r="A43" s="42"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="43"/>
       <c r="D43" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="36"/>
-      <c r="B44" s="37"/>
-      <c r="C44" s="30"/>
+      <c r="A44" s="42"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="43"/>
       <c r="D44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="36"/>
-      <c r="B45" s="37"/>
-      <c r="C45" s="30"/>
+      <c r="A45" s="42"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="43"/>
       <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="36"/>
-      <c r="B46" s="37"/>
-      <c r="C46" s="30">
+      <c r="A46" s="42"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="43">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="35" t="s">
+      <c r="E46" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="34"/>
+      <c r="F46" s="40"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="36"/>
-      <c r="B47" s="37"/>
-      <c r="C47" s="30"/>
+      <c r="A47" s="42"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="43"/>
       <c r="D47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="34"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="40"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="36"/>
-      <c r="B48" s="37"/>
-      <c r="C48" s="30"/>
+      <c r="A48" s="42"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="43"/>
       <c r="D48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="35"/>
-      <c r="F48" s="34"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="40"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="36"/>
-      <c r="B49" s="37"/>
-      <c r="C49" s="30"/>
+      <c r="A49" s="42"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="43"/>
       <c r="D49" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E49" s="35"/>
-      <c r="F49" s="34"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="40"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="36"/>
-      <c r="B50" s="37"/>
-      <c r="C50" s="30">
+      <c r="A50" s="42"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="43">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="34" t="s">
+      <c r="E50" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="34"/>
+      <c r="F50" s="40"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="36"/>
-      <c r="B51" s="37"/>
-      <c r="C51" s="30"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="43"/>
       <c r="D51" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="36"/>
-      <c r="B52" s="37"/>
-      <c r="C52" s="30"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="43"/>
       <c r="D52" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="36"/>
-      <c r="B53" s="37"/>
-      <c r="C53" s="30"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="43"/>
       <c r="D53" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="36"/>
-      <c r="B54" s="37"/>
-      <c r="C54" s="30"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="43"/>
       <c r="D54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="36"/>
-      <c r="B55" s="37"/>
-      <c r="C55" s="30"/>
+      <c r="A55" s="42"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="43"/>
       <c r="D55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="36"/>
-      <c r="B56" s="37"/>
-      <c r="C56" s="30"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="43"/>
       <c r="D56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="36"/>
-      <c r="B57" s="37"/>
-      <c r="C57" s="30"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="43"/>
       <c r="D57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="36"/>
-      <c r="B58" s="37"/>
-      <c r="C58" s="30"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="43"/>
       <c r="D58" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="30">
+      <c r="B59" s="43">
         <v>3</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C59" s="43">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -4798,48 +4834,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="43"/>
       <c r="D60" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="43"/>
       <c r="D61" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
+      <c r="B62" s="43"/>
+      <c r="C62" s="43"/>
       <c r="D62" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
       <c r="D63" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
+      <c r="B64" s="43"/>
+      <c r="C64" s="43"/>
       <c r="D64" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30">
+      <c r="B65" s="43"/>
+      <c r="C65" s="43">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -4848,96 +4884,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="43"/>
       <c r="D66" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="43"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="30"/>
-      <c r="C68" s="30"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="43"/>
       <c r="D68" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43"/>
       <c r="D69" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43"/>
       <c r="D70" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="30"/>
+      <c r="B71" s="43"/>
+      <c r="C71" s="43"/>
       <c r="D71" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
+      <c r="B72" s="43"/>
+      <c r="C72" s="43"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="30"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="43"/>
       <c r="D73" s="7" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="43"/>
       <c r="D74" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="43"/>
       <c r="D75" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="30"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="43"/>
       <c r="D76" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="30"/>
-      <c r="C77" s="30">
+      <c r="B77" s="43"/>
+      <c r="C77" s="43">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -4946,88 +4982,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="43"/>
       <c r="D78" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="43"/>
       <c r="D79" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="30"/>
-      <c r="C80" s="30"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="43"/>
       <c r="D80" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="30"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="43"/>
       <c r="D81" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="43"/>
       <c r="D82" s="7" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="30"/>
-      <c r="C83" s="30"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="43"/>
       <c r="D83" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="43"/>
       <c r="D84" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
+      <c r="B85" s="43"/>
+      <c r="C85" s="43"/>
       <c r="D85" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
+      <c r="B86" s="43"/>
+      <c r="C86" s="43"/>
       <c r="D86" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="43"/>
       <c r="D87" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="30"/>
-      <c r="C88" s="30">
+      <c r="B88" s="43"/>
+      <c r="C88" s="43">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5036,104 +5072,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="30"/>
-      <c r="C89" s="30"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="43"/>
       <c r="D89" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="30"/>
-      <c r="C90" s="30"/>
+      <c r="B90" s="43"/>
+      <c r="C90" s="43"/>
       <c r="D90" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
+      <c r="B91" s="43"/>
+      <c r="C91" s="43"/>
       <c r="D91" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="30"/>
+      <c r="B92" s="43"/>
+      <c r="C92" s="43"/>
       <c r="D92" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="30"/>
-      <c r="C93" s="30"/>
+      <c r="B93" s="43"/>
+      <c r="C93" s="43"/>
       <c r="D93" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="30"/>
-      <c r="C94" s="30"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="43"/>
       <c r="D94" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="30"/>
-      <c r="C95" s="30"/>
+      <c r="B95" s="43"/>
+      <c r="C95" s="43"/>
       <c r="D95" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="30"/>
+      <c r="B96" s="43"/>
+      <c r="C96" s="43"/>
       <c r="D96" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="30"/>
-      <c r="C97" s="30"/>
+      <c r="B97" s="43"/>
+      <c r="C97" s="43"/>
       <c r="D97" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="30"/>
-      <c r="C98" s="30"/>
+      <c r="B98" s="43"/>
+      <c r="C98" s="43"/>
       <c r="D98" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
+      <c r="B99" s="43"/>
+      <c r="C99" s="43"/>
       <c r="D99" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
+      <c r="B100" s="43"/>
+      <c r="C100" s="43"/>
       <c r="D100" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="30"/>
-      <c r="C101" s="30">
+      <c r="B101" s="43"/>
+      <c r="C101" s="43">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5142,72 +5178,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="30"/>
-      <c r="C102" s="30"/>
+      <c r="B102" s="43"/>
+      <c r="C102" s="43"/>
       <c r="D102" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
+      <c r="B103" s="43"/>
+      <c r="C103" s="43"/>
       <c r="D103" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="30"/>
-      <c r="C104" s="30"/>
+      <c r="B104" s="43"/>
+      <c r="C104" s="43"/>
       <c r="D104" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="30"/>
+      <c r="B105" s="43"/>
+      <c r="C105" s="43"/>
       <c r="D105" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="30"/>
-      <c r="C106" s="30"/>
+      <c r="B106" s="43"/>
+      <c r="C106" s="43"/>
       <c r="D106" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="30"/>
-      <c r="C107" s="30"/>
+      <c r="B107" s="43"/>
+      <c r="C107" s="43"/>
       <c r="D107" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="30"/>
-      <c r="C108" s="30"/>
+      <c r="B108" s="43"/>
+      <c r="C108" s="43"/>
       <c r="D108" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="30"/>
+      <c r="B109" s="43"/>
+      <c r="C109" s="43"/>
       <c r="D109" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="30"/>
-      <c r="C110" s="30">
+      <c r="B110" s="43"/>
+      <c r="C110" s="43">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5216,48 +5252,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="30"/>
-      <c r="C111" s="30"/>
+      <c r="B111" s="43"/>
+      <c r="C111" s="43"/>
       <c r="D111" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="30"/>
-      <c r="C112" s="30"/>
+      <c r="B112" s="43"/>
+      <c r="C112" s="43"/>
       <c r="D112" s="7" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="30"/>
-      <c r="C113" s="30"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="43"/>
       <c r="D113" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="30"/>
-      <c r="C114" s="30"/>
+      <c r="B114" s="43"/>
+      <c r="C114" s="43"/>
       <c r="D114" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="30"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="43"/>
       <c r="D115" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="30">
+      <c r="B116" s="43"/>
+      <c r="C116" s="43">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5266,88 +5302,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="30"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="43"/>
       <c r="D117" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="30"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="43"/>
       <c r="D118" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="30"/>
+      <c r="B119" s="43"/>
+      <c r="C119" s="43"/>
       <c r="D119" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="30"/>
+      <c r="B120" s="43"/>
+      <c r="C120" s="43"/>
       <c r="D120" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="30"/>
+      <c r="B121" s="43"/>
+      <c r="C121" s="43"/>
       <c r="D121" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="30"/>
+      <c r="B122" s="43"/>
+      <c r="C122" s="43"/>
       <c r="D122" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="30"/>
+      <c r="B123" s="43"/>
+      <c r="C123" s="43"/>
       <c r="D123" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="30"/>
+      <c r="B124" s="43"/>
+      <c r="C124" s="43"/>
       <c r="D124" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="30"/>
+      <c r="B125" s="43"/>
+      <c r="C125" s="43"/>
       <c r="D125" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="30"/>
+      <c r="B126" s="43"/>
+      <c r="C126" s="43"/>
       <c r="D126" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="30">
+      <c r="B127" s="43"/>
+      <c r="C127" s="43">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5356,80 +5392,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="30"/>
+      <c r="B128" s="43"/>
+      <c r="C128" s="43"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="30"/>
+      <c r="B129" s="43"/>
+      <c r="C129" s="43"/>
       <c r="D129" s="7" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="30"/>
+      <c r="B130" s="43"/>
+      <c r="C130" s="43"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="30"/>
+      <c r="B131" s="43"/>
+      <c r="C131" s="43"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="30"/>
+      <c r="B132" s="43"/>
+      <c r="C132" s="43"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="30"/>
-      <c r="C133" s="30"/>
+      <c r="B133" s="43"/>
+      <c r="C133" s="43"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="30"/>
+      <c r="B134" s="43"/>
+      <c r="C134" s="43"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="30"/>
+      <c r="B135" s="43"/>
+      <c r="C135" s="43"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="30"/>
+      <c r="B136" s="43"/>
+      <c r="C136" s="43"/>
       <c r="D136" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="30"/>
-      <c r="C137" s="30">
+      <c r="B137" s="43"/>
+      <c r="C137" s="43">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5438,40 +5474,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="30"/>
+      <c r="B138" s="43"/>
+      <c r="C138" s="43"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="30"/>
+      <c r="B139" s="43"/>
+      <c r="C139" s="43"/>
       <c r="D139" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="30"/>
+      <c r="B140" s="43"/>
+      <c r="C140" s="43"/>
       <c r="D140" s="7" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="30"/>
+      <c r="B141" s="43"/>
+      <c r="C141" s="43"/>
       <c r="D141" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="31">
+      <c r="B142" s="43"/>
+      <c r="C142" s="46">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5480,122 +5516,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="31"/>
+      <c r="B143" s="43"/>
+      <c r="C143" s="46"/>
       <c r="D143" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="30"/>
-      <c r="C144" s="31"/>
+      <c r="B144" s="43"/>
+      <c r="C144" s="46"/>
       <c r="D144" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="30"/>
-      <c r="C145" s="31"/>
+      <c r="B145" s="43"/>
+      <c r="C145" s="46"/>
       <c r="D145" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="30"/>
-      <c r="C146" s="31"/>
+      <c r="B146" s="43"/>
+      <c r="C146" s="46"/>
       <c r="D146" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="30"/>
-      <c r="C147" s="31"/>
+      <c r="B147" s="43"/>
+      <c r="C147" s="46"/>
       <c r="D147" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="30"/>
-      <c r="C148" s="31"/>
+      <c r="B148" s="43"/>
+      <c r="C148" s="46"/>
       <c r="D148" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="31"/>
+      <c r="B149" s="43"/>
+      <c r="C149" s="46"/>
       <c r="D149" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="31"/>
+      <c r="B150" s="43"/>
+      <c r="C150" s="46"/>
       <c r="D150" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="30"/>
-      <c r="C151" s="31"/>
+      <c r="B151" s="43"/>
+      <c r="C151" s="46"/>
       <c r="D151" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="30"/>
-      <c r="C152" s="31"/>
+      <c r="B152" s="43"/>
+      <c r="C152" s="46"/>
       <c r="D152" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="31"/>
+      <c r="B153" s="43"/>
+      <c r="C153" s="46"/>
       <c r="D153" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="31"/>
+      <c r="B154" s="43"/>
+      <c r="C154" s="46"/>
       <c r="D154" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="31"/>
+      <c r="B155" s="43"/>
+      <c r="C155" s="46"/>
       <c r="D155" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="31"/>
+      <c r="B156" s="43"/>
+      <c r="C156" s="46"/>
       <c r="D156" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="30">
+      <c r="B157" s="43">
         <v>4</v>
       </c>
-      <c r="C157" s="30">
+      <c r="C157" s="43">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -5604,32 +5640,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="30"/>
+      <c r="B158" s="43"/>
+      <c r="C158" s="43"/>
       <c r="D158" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="30"/>
-      <c r="C159" s="30"/>
+      <c r="B159" s="43"/>
+      <c r="C159" s="43"/>
       <c r="D159" s="7" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="30"/>
-      <c r="C160" s="30"/>
+      <c r="B160" s="43"/>
+      <c r="C160" s="43"/>
       <c r="D160" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="30"/>
-      <c r="C161" s="30">
+      <c r="B161" s="43"/>
+      <c r="C161" s="43">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -5638,56 +5674,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="30"/>
-      <c r="C162" s="30"/>
+      <c r="B162" s="43"/>
+      <c r="C162" s="43"/>
       <c r="D162" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="30"/>
-      <c r="C163" s="30"/>
+      <c r="B163" s="43"/>
+      <c r="C163" s="43"/>
       <c r="D163" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="30"/>
-      <c r="C164" s="30"/>
+      <c r="B164" s="43"/>
+      <c r="C164" s="43"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="30"/>
-      <c r="C165" s="30"/>
+      <c r="B165" s="43"/>
+      <c r="C165" s="43"/>
       <c r="D165" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="30"/>
-      <c r="C166" s="30"/>
+      <c r="B166" s="43"/>
+      <c r="C166" s="43"/>
       <c r="D166" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="30"/>
-      <c r="C167" s="30"/>
+      <c r="B167" s="43"/>
+      <c r="C167" s="43"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="30"/>
-      <c r="C168" s="30">
+      <c r="B168" s="43"/>
+      <c r="C168" s="43">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -5696,48 +5732,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="30"/>
-      <c r="C169" s="30"/>
+      <c r="B169" s="43"/>
+      <c r="C169" s="43"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="30"/>
-      <c r="C170" s="30"/>
+      <c r="B170" s="43"/>
+      <c r="C170" s="43"/>
       <c r="D170" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="30"/>
-      <c r="C171" s="30"/>
+      <c r="B171" s="43"/>
+      <c r="C171" s="43"/>
       <c r="D171" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="30"/>
-      <c r="C172" s="30"/>
+      <c r="B172" s="43"/>
+      <c r="C172" s="43"/>
       <c r="D172" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="30"/>
-      <c r="C173" s="30"/>
+      <c r="B173" s="43"/>
+      <c r="C173" s="43"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="30"/>
-      <c r="C174" s="30">
+      <c r="B174" s="43"/>
+      <c r="C174" s="43">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -5746,56 +5782,56 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="30"/>
-      <c r="C175" s="30"/>
+      <c r="B175" s="43"/>
+      <c r="C175" s="43"/>
       <c r="D175" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="30"/>
-      <c r="C176" s="30"/>
+      <c r="B176" s="43"/>
+      <c r="C176" s="43"/>
       <c r="D176" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="30"/>
-      <c r="C177" s="30"/>
+      <c r="B177" s="43"/>
+      <c r="C177" s="43"/>
       <c r="D177" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="30"/>
-      <c r="C178" s="30"/>
+      <c r="B178" s="43"/>
+      <c r="C178" s="43"/>
       <c r="D178" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="30"/>
-      <c r="C179" s="30"/>
+      <c r="B179" s="43"/>
+      <c r="C179" s="43"/>
       <c r="D179" s="7" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="30"/>
-      <c r="C180" s="30"/>
+      <c r="B180" s="43"/>
+      <c r="C180" s="43"/>
       <c r="D180" s="7" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="30"/>
-      <c r="C181" s="30"/>
+      <c r="B181" s="43"/>
+      <c r="C181" s="43"/>
       <c r="D181" s="7" t="s">
         <v>59</v>
       </c>
@@ -5803,41 +5839,6 @@
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{F0DC7BB0-6771-4160-B371-AE490E8879B7}"/>
   <mergeCells count="51">
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -5854,6 +5855,41 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5863,7 +5899,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AFAF48-8618-45CD-B1C5-CEC08E5846C2}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
@@ -5872,30 +5908,31 @@
     <col min="4" max="4" width="60.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-    </row>
-    <row r="2" spans="1:10" s="4" customFormat="1">
-      <c r="A2" s="42" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1">
+      <c r="A2" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="32" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
@@ -5919,12 +5956,16 @@
       <c r="J2" s="10" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="129.6">
-      <c r="A3" s="43">
+      <c r="K2" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="L2" s="52"/>
+    </row>
+    <row r="3" spans="1:12" ht="129.6">
+      <c r="A3" s="37">
         <v>1</v>
       </c>
-      <c r="B3" s="43">
+      <c r="B3" s="37">
         <v>1</v>
       </c>
       <c r="C3" s="15">
@@ -5934,16 +5975,19 @@
         <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.2">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="43.2">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
@@ -5957,10 +6001,13 @@
         <f t="array" ref="F4">_xlfn.SWITCH(E4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.2">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
+      <c r="G4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2">
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -5974,27 +6021,36 @@
         <f t="array" ref="F5">_xlfn.SWITCH(E5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="115.2">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="15">
+      <c r="G5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="115.2">
+      <c r="A6" s="37"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="48">
         <v>1.4</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="F6" cm="1">
+      <c r="F6" s="50" cm="1">
         <f t="array" ref="F6">_xlfn.SWITCH(E6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="57.6">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43">
+      <c r="G6" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+    </row>
+    <row r="7" spans="1:12" ht="57.6">
+      <c r="A7" s="37"/>
+      <c r="B7" s="37">
         <v>2</v>
       </c>
       <c r="C7" s="15">
@@ -6010,10 +6066,13 @@
         <f t="array" ref="F7">_xlfn.SWITCH(E7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="43.2">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
+      <c r="G7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="43.2">
+      <c r="A8" s="37"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
@@ -6027,10 +6086,13 @@
         <f t="array" ref="F8">_xlfn.SWITCH(E8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="100.8">
-      <c r="A9" s="43"/>
-      <c r="B9" s="43"/>
+      <c r="G8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="100.8">
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
@@ -6048,9 +6110,9 @@
         <v>214</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="115.2">
-      <c r="A10" s="43"/>
-      <c r="B10" s="43"/>
+    <row r="10" spans="1:12" ht="115.2">
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
@@ -6064,15 +6126,18 @@
         <f t="array" ref="F10">_xlfn.SWITCH(E10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="57.6">
-      <c r="A11" s="43"/>
-      <c r="B11" s="43"/>
+      <c r="G10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="57.6">
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -6081,15 +6146,18 @@
         <f t="array" ref="F11">_xlfn.SWITCH(E11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="86.4">
-      <c r="A12" s="43"/>
-      <c r="B12" s="43"/>
+      <c r="G11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="86.4">
+      <c r="A12" s="37"/>
+      <c r="B12" s="37"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -6098,196 +6166,205 @@
         <f t="array" ref="F12">_xlfn.SWITCH(E12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="158.4">
-      <c r="A13" s="43"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="15">
+      <c r="G12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="158.4">
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="48">
         <v>2.7</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="F13" cm="1">
+      <c r="F13" s="50" cm="1">
         <f t="array" ref="F13">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="44"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39">
+      <c r="G13" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="33"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29">
         <f>SUM(F3:F13)</f>
-        <v>38</v>
-      </c>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="41"/>
-    </row>
-    <row r="15" spans="1:10" ht="86.4">
-      <c r="A15" s="45">
+        <v>40</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="31"/>
+    </row>
+    <row r="15" spans="1:12" ht="86.4">
+      <c r="A15" s="38">
         <v>2</v>
       </c>
-      <c r="B15" s="45">
+      <c r="B15" s="38">
         <v>3</v>
       </c>
       <c r="C15" s="15">
         <v>3.1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="172.8">
-      <c r="A16" s="43"/>
-      <c r="B16" s="43"/>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="172.8">
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
       <c r="C16" s="15">
         <v>3.2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="172.8">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="15">
         <v>3.3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="187.2">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
       <c r="C18" s="15">
         <v>3.4</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="129.6">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="15">
         <v>3.5</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="86.4">
-      <c r="A20" s="43"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="37"/>
       <c r="C20" s="15">
         <v>3.6</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="158.4">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
       <c r="C21" s="15">
         <v>3.7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="144">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="15">
         <v>3.8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="72">
-      <c r="A23" s="43"/>
-      <c r="B23" s="43"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="37"/>
       <c r="C23" s="15">
         <v>3.9</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="216">
+      <c r="A24" s="37"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="35">
+        <v>3.1</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="216">
-      <c r="A24" s="43"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="47">
-        <v>3.1</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
     <row r="25" spans="1:4" ht="57.6">
-      <c r="A25" s="43"/>
-      <c r="B25" s="43">
+      <c r="A25" s="37"/>
+      <c r="B25" s="37">
         <v>4</v>
       </c>
       <c r="C25" s="15">
         <v>4.0999999999999996</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="100.8">
-      <c r="A26" s="43"/>
-      <c r="B26" s="43"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
       <c r="C26" s="15">
         <v>4.2</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="86.4">
-      <c r="A27" s="43"/>
-      <c r="B27" s="43"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="15">
         <v>4.3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="115.2">
-      <c r="A28" s="43"/>
-      <c r="B28" s="43"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="37"/>
       <c r="C28" s="15">
         <v>4.4000000000000004</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="A15:A28"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B13"/>
     <mergeCell ref="B15:B24"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A15:A28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6331,11 +6408,11 @@
       </c>
       <c r="C2" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E2)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" s="12">
         <f>('Updated Sprint'!F14)*(1-(A2-1)/8)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E2" s="28">
         <v>0</v>
@@ -6350,11 +6427,11 @@
       </c>
       <c r="C3" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E3)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" s="12">
         <f>('Updated Sprint'!F14)*(1-(A3-1)/8)</f>
-        <v>33.25</v>
+        <v>35</v>
       </c>
       <c r="E3" s="28">
         <v>0</v>
@@ -6369,11 +6446,11 @@
       </c>
       <c r="C4" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E4)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" s="12">
         <f>('Updated Sprint'!F14)*(1-(A4-1)/8)</f>
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="E4" s="28">
         <v>0</v>
@@ -6388,11 +6465,11 @@
       </c>
       <c r="C5" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E5)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" s="12">
         <f>('Updated Sprint'!F14)*(1-(A5-1)/8)</f>
-        <v>23.75</v>
+        <v>25</v>
       </c>
       <c r="E5" s="28">
         <v>0</v>
@@ -6407,11 +6484,11 @@
       </c>
       <c r="C6" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E6)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="12">
         <f>('Updated Sprint'!F14)*(1-(A6-1)/8)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="28">
         <v>0</v>
@@ -6426,11 +6503,11 @@
       </c>
       <c r="C7" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E7)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="12">
         <f>('Updated Sprint'!F14)*(1-(A7-1)/8)</f>
-        <v>14.25</v>
+        <v>15</v>
       </c>
       <c r="E7" s="28">
         <v>0</v>
@@ -6445,11 +6522,11 @@
       </c>
       <c r="C8" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E8)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" s="12">
         <f>('Updated Sprint'!F14)*(1-(A8-1)/8)</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="E8" s="28">
         <v>0</v>
@@ -6464,11 +6541,11 @@
       </c>
       <c r="C9" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E9)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="12">
         <f>('Updated Sprint'!F14)*(1-(A9-1)/8)</f>
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="E9" s="28">
         <v>0</v>
@@ -6483,7 +6560,7 @@
       </c>
       <c r="C10" s="27">
         <f>('Updated Sprint'!F14)-SUM(E$2:E10)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="12">
         <f>('Updated Sprint'!F14)*(1-(A10-1)/8)</f>
@@ -6509,15 +6586,15 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5226C896-19F0-4C3B-84F0-AF4AC9EE4895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAF31A5-BF80-4725-89FF-AEFF58B89D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -724,7 +724,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="266">
   <si>
     <t>Work Item</t>
   </si>
@@ -1895,22 +1895,6 @@
     </r>
   </si>
   <si>
-    <t>Receive image from Shopify widget
-Validate image file type
-Validate image can be decoded/read
-Validate image resolution
-Calculate image sharpness
-Calculate image brightness/lighting
-Define/configure blur rejection threshold
-Define/configure low-light rejection threshold
-Define/configure minimum resolution threshold</t>
-  </si>
-  <si>
-    <t>Combine all image-quality checks
-Reject image if any required quality check fails
-Accept image only if all required checks pass</t>
-  </si>
-  <si>
     <t>Return image-validation result to frontend
 Display "Your image is not valid. Take another image with better quality"
 Redirect user back to selfie capture</t>
@@ -1924,87 +1908,6 @@
 Test combinations of quality failures
 Test valid image
 Test User Story 1 acceptance criteria</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Store accepted image in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">skin_image
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Associate image with current </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">customer_session
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Initiate asynchronous Visual AI image analysis
-Redirect user to questionnaire </t>
-    </r>
-  </si>
-  <si>
-    <t>Define Visual AI response JSON schema based on image_detection.json
-Define supported image-detectable concern IDs: SC0001–SC0019, SC1001–SC1009</t>
-  </si>
-  <si>
-    <t>Define Visual AI system prompt
-Define image-analysis instructions
-Define skin-concern detection rules
-Restrict output to supported concern IDs
-Define no-concern behaviour
-Require AI explanation for detected concerns
-Require JSON-only response</t>
-  </si>
-  <si>
-    <t>Send accepted image to Visual AI
-Validate Visual AI response against JSON schema
-Validate returned concern IDs
-Handle duplicate concern IDs
-Handle unsupported concern IDs
-Handle empty/no-concern response
-Handle malformed AI response
-Handle AI/API failure</t>
-  </si>
-  <si>
-    <t>Build recommendation response containing user full name
-		Include image-detected primary skin concerns
-		Display "Your skin looks perfect!" when no concern is detected
-		Return recommendation response to Shopify widget
-		Display user name
-		Display primary skin concerns</t>
   </si>
   <si>
     <t>Test Visual AI response validation
@@ -2189,16 +2092,481 @@
     <t>Sayan</t>
   </si>
   <si>
-    <t>Store Visual AI result in session_skin_concern_detection db table
-Store detected concern IDs column 
-Store AI-generated explanations column against concern IDs
-Store raw detection JSON against concern IDs</t>
-  </si>
-  <si>
     <t>Azad, Sayan</t>
   </si>
   <si>
     <t>Priority</t>
+  </si>
+  <si>
+    <t>Receive image from Shopify widget and pass it to the image-validation service
+Validate uploaded image filetype before image processing 
+Validate uploaded image can be decoded/read
+Validate image resolution against the configured minimum resolution.
+Calculate image sharpness score.
+Calculate image brightness/lighting score.
+Define/configure blur rejection threshold
+Define/configure low-light rejection threshold
+Define/configure minimum resolution threshold</t>
+  </si>
+  <si>
+    <t>Combine all image-quality checks into one image-validation API call - POST /image-validation
+Reject image when any required quality check fails. 
+Accept image only when all required quality checks pass.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store accepted image in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">skin_image </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>database table.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Associate the stored image with the current </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customer_session</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> database record using the session identifier.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Trigger the asynchronous Visual AI image analysis process for the accepted image
+Redirect user to static questionnaire page immediately after image validation succeeds. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define Visual AI response JSON schema using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">image_detection.json </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">as the schema definition.
+Define the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">skin_concern_id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">field in the Visual AI response.
+Restrict </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skin_concern_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> values to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SC0001–SC0019, SC1001–SC1009.</t>
+    </r>
+  </si>
+  <si>
+    <t>Define Visual AI system prompt
+Define image-analysis instructions
+Define skin-concern detection rules
+Restrict output to supported concern IDs
+Define no-concern behaviour
+Require AI explanation for every detected concerns
+Require JSON-only response</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Send accepted image to Visual AI API for image analysis
+Validate Visual AI response against Visual AI response JSON schema
+Validate every returned </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skin_concern_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> against the supported concern-ID list. 
+Handle duplicate concern IDs before storing the results
+Handle unsupported concern IDs 
+Handle empty/no-concern response
+Handle malformed AI response
+Handle AI/API failure</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Store the validated Visual AI result in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>session_skin_concern_detection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> database table
+Store the detected </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skin_concern_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> value in the concern-ID column of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>session_skin_concern_detection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+Store AI-generated explanations in the explanation column against the corresponding </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skin_concern_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+Store raw Visual AI response JSON in the raw-detection-JSON column
+Associate each detection record with the current </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customer_session</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create the image analysis reccomendation response JSON.
+Populate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">user_full_name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from the logged-in customer's user record.
+Populate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Primary Concerns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">using only validated </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skin_concern_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> values stored from the Visual AI analysis.
+Return "Your skin looks perfect!" when the validated image concern list is empty. 
+Return the reccomendation response JSON to the Shopify widget frontend.
+Display </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user_full_name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on the reccomendation page.
+Display image-detected </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Primary Concerns </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">on the reccomendation page. </t>
+    </r>
+  </si>
+  <si>
+    <t>Generate 10–20 GenAI test images covering different skin tones, ages, and visible skin concerns
+	Test redness detection across different skin tones
+	Test redness detection on a person with black skin
+	Test visible skin concerns on a person below 50
+	Test multiple visible skin concerns in a single image
+	Test an image containing no visible skin concern
+	Compare Visual AI returned skin_concern_id values against expected test results
+	Verify unsupported concern IDs are not persisted in the session_skin_concern_detection database table</t>
   </si>
 </sst>
 </file>
@@ -2278,7 +2646,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2318,6 +2686,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2395,7 +2769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2478,14 +2852,23 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2512,15 +2895,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2657,31 +3038,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2762,28 +3143,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>40</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>35</c:v>
+                  <c:v>39.375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30</c:v>
+                  <c:v>33.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25</c:v>
+                  <c:v>28.125</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20</c:v>
+                  <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>15</c:v>
+                  <c:v>16.875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10</c:v>
+                  <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5</c:v>
+                  <c:v>5.625</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4010,11 +4391,11 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4154,18 +4535,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4200,632 +4581,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="42">
+      <c r="A3" s="47">
         <v>1</v>
       </c>
-      <c r="B3" s="43">
+      <c r="B3" s="48">
         <v>1</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="48">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="40" cm="1">
+      <c r="F3" s="45" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="42"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="42"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="42"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
+      <c r="A7" s="47"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="42"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
       <c r="D8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="42"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="42"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="42"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="42"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43">
+      <c r="A12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="40" cm="1">
+      <c r="F12" s="45" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="42"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="42"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="40" t="s">
+      <c r="E15" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="40"/>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="42"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="42"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43">
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="40"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="42"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="42"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="42"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
       <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="42"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="42"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
       <c r="D24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
       <c r="D25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="42"/>
-      <c r="B26" s="44">
+      <c r="A26" s="47"/>
+      <c r="B26" s="49">
         <v>2</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="48">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E26" s="41" t="s">
+      <c r="E26" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="40"/>
+      <c r="F26" s="45"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="42"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="43"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="48"/>
       <c r="D27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="40"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="45"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="42"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="43"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="41"/>
-      <c r="F28" s="40"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="45"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="42"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="45">
+      <c r="A29" s="47"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="40" t="s">
+      <c r="E29" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="40"/>
+      <c r="F29" s="45"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="42"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="45"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="42"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="43">
+      <c r="A31" s="47"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="48">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="E31" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40" t="s">
+      <c r="F31" s="45"/>
+      <c r="G31" s="45" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="42"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="43"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="48"/>
       <c r="D32" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="40"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="42"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="43"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="48"/>
       <c r="D33" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="42"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="43"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="42"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="43"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="48"/>
       <c r="D35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="42"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="43"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="48"/>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="42"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="43"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="48"/>
       <c r="D37" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="42"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="43">
+      <c r="A38" s="47"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="48">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="40"/>
+      <c r="F38" s="45"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="42"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="43"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="48"/>
       <c r="D39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="42"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="43"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="48"/>
       <c r="D40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="42"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="43"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="48"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="42"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="43"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="42"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="43"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="48"/>
       <c r="D43" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="42"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="43"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="48"/>
       <c r="D44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="42"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="43"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="48"/>
       <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="40"/>
-      <c r="F45" s="40"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="42"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="43">
+      <c r="A46" s="47"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="48">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="41" t="s">
+      <c r="E46" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="40"/>
+      <c r="F46" s="45"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="42"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="43"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="48"/>
       <c r="D47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="41"/>
-      <c r="F47" s="40"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="45"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="42"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="43"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="48"/>
       <c r="D48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="41"/>
-      <c r="F48" s="40"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="45"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="42"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="43"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="48"/>
       <c r="D49" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E49" s="41"/>
-      <c r="F49" s="40"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="45"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="42"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="43">
+      <c r="A50" s="47"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="48">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="40" t="s">
+      <c r="E50" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="40"/>
+      <c r="F50" s="45"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="42"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="43"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="48"/>
       <c r="D51" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="42"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="43"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="48"/>
       <c r="D52" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="42"/>
-      <c r="B53" s="44"/>
-      <c r="C53" s="43"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="48"/>
       <c r="D53" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="42"/>
-      <c r="B54" s="44"/>
-      <c r="C54" s="43"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="48"/>
       <c r="D54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="42"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="43"/>
+      <c r="A55" s="47"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="48"/>
       <c r="D55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="42"/>
-      <c r="B56" s="44"/>
-      <c r="C56" s="43"/>
+      <c r="A56" s="47"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="48"/>
       <c r="D56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="42"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="43"/>
+      <c r="A57" s="47"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="48"/>
       <c r="D57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="42"/>
-      <c r="B58" s="44"/>
-      <c r="C58" s="43"/>
+      <c r="A58" s="47"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="48"/>
       <c r="D58" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="43">
+      <c r="B59" s="48">
         <v>3</v>
       </c>
-      <c r="C59" s="43">
+      <c r="C59" s="48">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -4834,48 +5215,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="43"/>
-      <c r="C60" s="43"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="48"/>
       <c r="D60" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="43"/>
+      <c r="B61" s="48"/>
+      <c r="C61" s="48"/>
       <c r="D61" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="43"/>
-      <c r="C62" s="43"/>
+      <c r="B62" s="48"/>
+      <c r="C62" s="48"/>
       <c r="D62" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
+      <c r="B63" s="48"/>
+      <c r="C63" s="48"/>
       <c r="D63" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="43"/>
-      <c r="C64" s="43"/>
+      <c r="B64" s="48"/>
+      <c r="C64" s="48"/>
       <c r="D64" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="43">
+      <c r="B65" s="48"/>
+      <c r="C65" s="48">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -4884,96 +5265,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="43"/>
+      <c r="B66" s="48"/>
+      <c r="C66" s="48"/>
       <c r="D66" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="43"/>
+      <c r="B67" s="48"/>
+      <c r="C67" s="48"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="43"/>
-      <c r="C68" s="43"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
       <c r="D68" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="43"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
       <c r="D69" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="43"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
       <c r="D70" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="43"/>
-      <c r="C71" s="43"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
       <c r="D71" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="43"/>
-      <c r="C72" s="43"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="43"/>
-      <c r="C73" s="43"/>
+      <c r="B73" s="48"/>
+      <c r="C73" s="48"/>
       <c r="D73" s="7" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="43"/>
-      <c r="C74" s="43"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
       <c r="D74" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="43"/>
-      <c r="C75" s="43"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
       <c r="D75" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="43"/>
-      <c r="C76" s="43"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
       <c r="D76" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="43"/>
-      <c r="C77" s="43">
+      <c r="B77" s="48"/>
+      <c r="C77" s="48">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -4982,88 +5363,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="43"/>
-      <c r="C78" s="43"/>
+      <c r="B78" s="48"/>
+      <c r="C78" s="48"/>
       <c r="D78" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="43"/>
-      <c r="C79" s="43"/>
+      <c r="B79" s="48"/>
+      <c r="C79" s="48"/>
       <c r="D79" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="43"/>
-      <c r="C80" s="43"/>
+      <c r="B80" s="48"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="43"/>
-      <c r="C81" s="43"/>
+      <c r="B81" s="48"/>
+      <c r="C81" s="48"/>
       <c r="D81" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="43"/>
-      <c r="C82" s="43"/>
+      <c r="B82" s="48"/>
+      <c r="C82" s="48"/>
       <c r="D82" s="7" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="43"/>
-      <c r="C83" s="43"/>
+      <c r="B83" s="48"/>
+      <c r="C83" s="48"/>
       <c r="D83" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="43"/>
-      <c r="C84" s="43"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="48"/>
       <c r="D84" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="43"/>
-      <c r="C85" s="43"/>
+      <c r="B85" s="48"/>
+      <c r="C85" s="48"/>
       <c r="D85" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="43"/>
-      <c r="C86" s="43"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
       <c r="D86" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="43"/>
-      <c r="C87" s="43"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
       <c r="D87" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="43"/>
-      <c r="C88" s="43">
+      <c r="B88" s="48"/>
+      <c r="C88" s="48">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5072,104 +5453,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="43"/>
-      <c r="C89" s="43"/>
+      <c r="B89" s="48"/>
+      <c r="C89" s="48"/>
       <c r="D89" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="43"/>
-      <c r="C90" s="43"/>
+      <c r="B90" s="48"/>
+      <c r="C90" s="48"/>
       <c r="D90" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="43"/>
-      <c r="C91" s="43"/>
+      <c r="B91" s="48"/>
+      <c r="C91" s="48"/>
       <c r="D91" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="43"/>
-      <c r="C92" s="43"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="48"/>
       <c r="D92" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="43"/>
-      <c r="C93" s="43"/>
+      <c r="B93" s="48"/>
+      <c r="C93" s="48"/>
       <c r="D93" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="43"/>
-      <c r="C94" s="43"/>
+      <c r="B94" s="48"/>
+      <c r="C94" s="48"/>
       <c r="D94" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="43"/>
-      <c r="C95" s="43"/>
+      <c r="B95" s="48"/>
+      <c r="C95" s="48"/>
       <c r="D95" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="43"/>
-      <c r="C96" s="43"/>
+      <c r="B96" s="48"/>
+      <c r="C96" s="48"/>
       <c r="D96" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="43"/>
-      <c r="C97" s="43"/>
+      <c r="B97" s="48"/>
+      <c r="C97" s="48"/>
       <c r="D97" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="43"/>
-      <c r="C98" s="43"/>
+      <c r="B98" s="48"/>
+      <c r="C98" s="48"/>
       <c r="D98" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="43"/>
-      <c r="C99" s="43"/>
+      <c r="B99" s="48"/>
+      <c r="C99" s="48"/>
       <c r="D99" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="43"/>
-      <c r="C100" s="43"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="48"/>
       <c r="D100" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="43"/>
-      <c r="C101" s="43">
+      <c r="B101" s="48"/>
+      <c r="C101" s="48">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5178,72 +5559,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="43"/>
-      <c r="C102" s="43"/>
+      <c r="B102" s="48"/>
+      <c r="C102" s="48"/>
       <c r="D102" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="43"/>
-      <c r="C103" s="43"/>
+      <c r="B103" s="48"/>
+      <c r="C103" s="48"/>
       <c r="D103" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="43"/>
-      <c r="C104" s="43"/>
+      <c r="B104" s="48"/>
+      <c r="C104" s="48"/>
       <c r="D104" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="43"/>
-      <c r="C105" s="43"/>
+      <c r="B105" s="48"/>
+      <c r="C105" s="48"/>
       <c r="D105" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="43"/>
-      <c r="C106" s="43"/>
+      <c r="B106" s="48"/>
+      <c r="C106" s="48"/>
       <c r="D106" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="43"/>
-      <c r="C107" s="43"/>
+      <c r="B107" s="48"/>
+      <c r="C107" s="48"/>
       <c r="D107" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="43"/>
-      <c r="C108" s="43"/>
+      <c r="B108" s="48"/>
+      <c r="C108" s="48"/>
       <c r="D108" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="43"/>
-      <c r="C109" s="43"/>
+      <c r="B109" s="48"/>
+      <c r="C109" s="48"/>
       <c r="D109" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="43"/>
-      <c r="C110" s="43">
+      <c r="B110" s="48"/>
+      <c r="C110" s="48">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5252,48 +5633,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="43"/>
-      <c r="C111" s="43"/>
+      <c r="B111" s="48"/>
+      <c r="C111" s="48"/>
       <c r="D111" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="43"/>
-      <c r="C112" s="43"/>
+      <c r="B112" s="48"/>
+      <c r="C112" s="48"/>
       <c r="D112" s="7" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="43"/>
-      <c r="C113" s="43"/>
+      <c r="B113" s="48"/>
+      <c r="C113" s="48"/>
       <c r="D113" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="43"/>
-      <c r="C114" s="43"/>
+      <c r="B114" s="48"/>
+      <c r="C114" s="48"/>
       <c r="D114" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="43"/>
-      <c r="C115" s="43"/>
+      <c r="B115" s="48"/>
+      <c r="C115" s="48"/>
       <c r="D115" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="43"/>
-      <c r="C116" s="43">
+      <c r="B116" s="48"/>
+      <c r="C116" s="48">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5302,88 +5683,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="43"/>
-      <c r="C117" s="43"/>
+      <c r="B117" s="48"/>
+      <c r="C117" s="48"/>
       <c r="D117" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="43"/>
-      <c r="C118" s="43"/>
+      <c r="B118" s="48"/>
+      <c r="C118" s="48"/>
       <c r="D118" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="43"/>
-      <c r="C119" s="43"/>
+      <c r="B119" s="48"/>
+      <c r="C119" s="48"/>
       <c r="D119" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="43"/>
-      <c r="C120" s="43"/>
+      <c r="B120" s="48"/>
+      <c r="C120" s="48"/>
       <c r="D120" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="43"/>
-      <c r="C121" s="43"/>
+      <c r="B121" s="48"/>
+      <c r="C121" s="48"/>
       <c r="D121" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="43"/>
-      <c r="C122" s="43"/>
+      <c r="B122" s="48"/>
+      <c r="C122" s="48"/>
       <c r="D122" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="43"/>
-      <c r="C123" s="43"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="48"/>
       <c r="D123" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="43"/>
-      <c r="C124" s="43"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="48"/>
       <c r="D124" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="43"/>
-      <c r="C125" s="43"/>
+      <c r="B125" s="48"/>
+      <c r="C125" s="48"/>
       <c r="D125" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="43"/>
-      <c r="C126" s="43"/>
+      <c r="B126" s="48"/>
+      <c r="C126" s="48"/>
       <c r="D126" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="43"/>
-      <c r="C127" s="43">
+      <c r="B127" s="48"/>
+      <c r="C127" s="48">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5392,80 +5773,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="43"/>
-      <c r="C128" s="43"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="48"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="43"/>
-      <c r="C129" s="43"/>
+      <c r="B129" s="48"/>
+      <c r="C129" s="48"/>
       <c r="D129" s="7" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="43"/>
-      <c r="C130" s="43"/>
+      <c r="B130" s="48"/>
+      <c r="C130" s="48"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="43"/>
-      <c r="C131" s="43"/>
+      <c r="B131" s="48"/>
+      <c r="C131" s="48"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="43"/>
-      <c r="C132" s="43"/>
+      <c r="B132" s="48"/>
+      <c r="C132" s="48"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="43"/>
-      <c r="C133" s="43"/>
+      <c r="B133" s="48"/>
+      <c r="C133" s="48"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="43"/>
-      <c r="C134" s="43"/>
+      <c r="B134" s="48"/>
+      <c r="C134" s="48"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="43"/>
-      <c r="C135" s="43"/>
+      <c r="B135" s="48"/>
+      <c r="C135" s="48"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="43"/>
-      <c r="C136" s="43"/>
+      <c r="B136" s="48"/>
+      <c r="C136" s="48"/>
       <c r="D136" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="43"/>
-      <c r="C137" s="43">
+      <c r="B137" s="48"/>
+      <c r="C137" s="48">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5474,40 +5855,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="43"/>
-      <c r="C138" s="43"/>
+      <c r="B138" s="48"/>
+      <c r="C138" s="48"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="43"/>
-      <c r="C139" s="43"/>
+      <c r="B139" s="48"/>
+      <c r="C139" s="48"/>
       <c r="D139" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="43"/>
-      <c r="C140" s="43"/>
+      <c r="B140" s="48"/>
+      <c r="C140" s="48"/>
       <c r="D140" s="7" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="43"/>
-      <c r="C141" s="43"/>
+      <c r="B141" s="48"/>
+      <c r="C141" s="48"/>
       <c r="D141" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="43"/>
-      <c r="C142" s="46">
+      <c r="B142" s="48"/>
+      <c r="C142" s="51">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5516,122 +5897,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="43"/>
-      <c r="C143" s="46"/>
+      <c r="B143" s="48"/>
+      <c r="C143" s="51"/>
       <c r="D143" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="43"/>
-      <c r="C144" s="46"/>
+      <c r="B144" s="48"/>
+      <c r="C144" s="51"/>
       <c r="D144" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="43"/>
-      <c r="C145" s="46"/>
+      <c r="B145" s="48"/>
+      <c r="C145" s="51"/>
       <c r="D145" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="43"/>
-      <c r="C146" s="46"/>
+      <c r="B146" s="48"/>
+      <c r="C146" s="51"/>
       <c r="D146" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="43"/>
-      <c r="C147" s="46"/>
+      <c r="B147" s="48"/>
+      <c r="C147" s="51"/>
       <c r="D147" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="43"/>
-      <c r="C148" s="46"/>
+      <c r="B148" s="48"/>
+      <c r="C148" s="51"/>
       <c r="D148" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="43"/>
-      <c r="C149" s="46"/>
+      <c r="B149" s="48"/>
+      <c r="C149" s="51"/>
       <c r="D149" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="43"/>
-      <c r="C150" s="46"/>
+      <c r="B150" s="48"/>
+      <c r="C150" s="51"/>
       <c r="D150" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="43"/>
-      <c r="C151" s="46"/>
+      <c r="B151" s="48"/>
+      <c r="C151" s="51"/>
       <c r="D151" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="43"/>
-      <c r="C152" s="46"/>
+      <c r="B152" s="48"/>
+      <c r="C152" s="51"/>
       <c r="D152" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="43"/>
-      <c r="C153" s="46"/>
+      <c r="B153" s="48"/>
+      <c r="C153" s="51"/>
       <c r="D153" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="43"/>
-      <c r="C154" s="46"/>
+      <c r="B154" s="48"/>
+      <c r="C154" s="51"/>
       <c r="D154" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="43"/>
-      <c r="C155" s="46"/>
+      <c r="B155" s="48"/>
+      <c r="C155" s="51"/>
       <c r="D155" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="43"/>
-      <c r="C156" s="46"/>
+      <c r="B156" s="48"/>
+      <c r="C156" s="51"/>
       <c r="D156" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="43">
+      <c r="B157" s="48">
         <v>4</v>
       </c>
-      <c r="C157" s="43">
+      <c r="C157" s="48">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -5640,32 +6021,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="43"/>
-      <c r="C158" s="43"/>
+      <c r="B158" s="48"/>
+      <c r="C158" s="48"/>
       <c r="D158" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="43"/>
-      <c r="C159" s="43"/>
+      <c r="B159" s="48"/>
+      <c r="C159" s="48"/>
       <c r="D159" s="7" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="43"/>
-      <c r="C160" s="43"/>
+      <c r="B160" s="48"/>
+      <c r="C160" s="48"/>
       <c r="D160" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="43"/>
-      <c r="C161" s="43">
+      <c r="B161" s="48"/>
+      <c r="C161" s="48">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -5674,56 +6055,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="43"/>
-      <c r="C162" s="43"/>
+      <c r="B162" s="48"/>
+      <c r="C162" s="48"/>
       <c r="D162" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="43"/>
-      <c r="C163" s="43"/>
+      <c r="B163" s="48"/>
+      <c r="C163" s="48"/>
       <c r="D163" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="43"/>
-      <c r="C164" s="43"/>
+      <c r="B164" s="48"/>
+      <c r="C164" s="48"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="43"/>
-      <c r="C165" s="43"/>
+      <c r="B165" s="48"/>
+      <c r="C165" s="48"/>
       <c r="D165" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="43"/>
-      <c r="C166" s="43"/>
+      <c r="B166" s="48"/>
+      <c r="C166" s="48"/>
       <c r="D166" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="43"/>
-      <c r="C167" s="43"/>
+      <c r="B167" s="48"/>
+      <c r="C167" s="48"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="43"/>
-      <c r="C168" s="43">
+      <c r="B168" s="48"/>
+      <c r="C168" s="48">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -5732,48 +6113,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="43"/>
-      <c r="C169" s="43"/>
+      <c r="B169" s="48"/>
+      <c r="C169" s="48"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="43"/>
-      <c r="C170" s="43"/>
+      <c r="B170" s="48"/>
+      <c r="C170" s="48"/>
       <c r="D170" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="43"/>
-      <c r="C171" s="43"/>
+      <c r="B171" s="48"/>
+      <c r="C171" s="48"/>
       <c r="D171" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="43"/>
-      <c r="C172" s="43"/>
+      <c r="B172" s="48"/>
+      <c r="C172" s="48"/>
       <c r="D172" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="43"/>
-      <c r="C173" s="43"/>
+      <c r="B173" s="48"/>
+      <c r="C173" s="48"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="43"/>
-      <c r="C174" s="43">
+      <c r="B174" s="48"/>
+      <c r="C174" s="48">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -5782,56 +6163,56 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="43"/>
-      <c r="C175" s="43"/>
+      <c r="B175" s="48"/>
+      <c r="C175" s="48"/>
       <c r="D175" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="43"/>
-      <c r="C176" s="43"/>
+      <c r="B176" s="48"/>
+      <c r="C176" s="48"/>
       <c r="D176" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="43"/>
-      <c r="C177" s="43"/>
+      <c r="B177" s="48"/>
+      <c r="C177" s="48"/>
       <c r="D177" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="43"/>
-      <c r="C178" s="43"/>
+      <c r="B178" s="48"/>
+      <c r="C178" s="48"/>
       <c r="D178" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="43"/>
-      <c r="C179" s="43"/>
+      <c r="B179" s="48"/>
+      <c r="C179" s="48"/>
       <c r="D179" s="7" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="43"/>
-      <c r="C180" s="43"/>
+      <c r="B180" s="48"/>
+      <c r="C180" s="48"/>
       <c r="D180" s="7" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="43"/>
-      <c r="C181" s="43"/>
+      <c r="B181" s="48"/>
+      <c r="C181" s="48"/>
       <c r="D181" s="7" t="s">
         <v>59</v>
       </c>
@@ -5899,31 +6280,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AFAF48-8618-45CD-B1C5-CEC08E5846C2}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
     <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -5956,23 +6337,23 @@
       <c r="J2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="L2" s="52"/>
+      <c r="K2" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:12" ht="129.6">
-      <c r="A3" s="37">
+      <c r="A3" s="41">
         <v>1</v>
       </c>
-      <c r="B3" s="37">
+      <c r="B3" s="41">
         <v>1</v>
       </c>
       <c r="C3" s="15">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -5982,17 +6363,17 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="43.2">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="57.6">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -6002,17 +6383,17 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="43.2">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -6022,42 +6403,42 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="115.2">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="48">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="36">
         <v>1.4</v>
       </c>
-      <c r="D6" s="49" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="50" t="s">
+      <c r="D6" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="50" cm="1">
+      <c r="F6" s="38" cm="1">
         <f t="array" ref="F6">_xlfn.SWITCH(E6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="G6" s="50" t="s">
-        <v>260</v>
-      </c>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-    </row>
-    <row r="7" spans="1:12" ht="57.6">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37">
+      <c r="G6" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+    </row>
+    <row r="7" spans="1:12" ht="86.4">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41">
         <v>2</v>
       </c>
       <c r="C7" s="15">
         <v>2.1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -6067,17 +6448,17 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="43.2">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="57.6">
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -6087,17 +6468,17 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="100.8">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -6111,13 +6492,13 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="115.2">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -6127,17 +6508,17 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="57.6">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="100.8">
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -6147,17 +6528,17 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="86.4">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="115.2">
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -6167,207 +6548,229 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="158.4">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="48">
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="36">
         <v>2.7</v>
       </c>
-      <c r="D13" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="E13" s="50" t="s">
+      <c r="D13" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="50" cm="1">
+      <c r="F13" s="38" cm="1">
         <f t="array" ref="F13">_xlfn.SWITCH(E13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="G13" s="50" t="s">
-        <v>260</v>
-      </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="30" t="s">
+      <c r="G13" s="38" t="s">
+        <v>253</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+    </row>
+    <row r="14" spans="1:12" ht="144">
+      <c r="C14" s="53">
+        <v>2.8</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="55" cm="1">
+        <f t="array" ref="F14">_xlfn.SWITCH(E14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="G14" s="55" t="s">
+        <v>253</v>
+      </c>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29">
+        <f>SUM(F3:F14)</f>
+        <v>45</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="31"/>
+    </row>
+    <row r="16" spans="1:12" ht="86.4">
+      <c r="A16" s="42">
+        <v>2</v>
+      </c>
+      <c r="B16" s="42">
+        <v>3</v>
+      </c>
+      <c r="C16" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="172.8">
+      <c r="A17" s="41"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="172.8">
+      <c r="A18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="15">
+        <v>3.3</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="187.2">
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="15">
+        <v>3.4</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="129.6">
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="86.4">
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="158.4">
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="15">
+        <v>3.7</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29">
-        <f>SUM(F3:F13)</f>
-        <v>40</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="31"/>
-    </row>
-    <row r="15" spans="1:12" ht="86.4">
-      <c r="A15" s="38">
-        <v>2</v>
-      </c>
-      <c r="B15" s="38">
-        <v>3</v>
-      </c>
-      <c r="C15" s="15">
+    </row>
+    <row r="23" spans="1:4" ht="144">
+      <c r="A23" s="41"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="15">
+        <v>3.8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="72">
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="15">
+        <v>3.9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="216">
+      <c r="A25" s="41"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="35">
         <v>3.1</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="172.8">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="15">
-        <v>3.2</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="172.8">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="15">
-        <v>3.3</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="187.2">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="15">
-        <v>3.4</v>
-      </c>
-      <c r="D18" s="2" t="s">
+    <row r="26" spans="1:4" ht="57.6">
+      <c r="A26" s="41"/>
+      <c r="B26" s="41">
+        <v>4</v>
+      </c>
+      <c r="C26" s="15">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="129.6">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="15">
-        <v>3.5</v>
-      </c>
-      <c r="D19" s="2" t="s">
+    <row r="27" spans="1:4" ht="100.8">
+      <c r="A27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="86.4">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="15">
-        <v>3.6</v>
-      </c>
-      <c r="D20" s="2" t="s">
+    <row r="28" spans="1:4" ht="86.4">
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="158.4">
-      <c r="A21" s="37"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="15">
-        <v>3.7</v>
-      </c>
-      <c r="D21" s="2" t="s">
+    <row r="29" spans="1:4" ht="115.2">
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="15">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="144">
-      <c r="A22" s="37"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="15">
-        <v>3.8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="72">
-      <c r="A23" s="37"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="15">
-        <v>3.9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="216">
-      <c r="A24" s="37"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="35">
-        <v>3.1</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="57.6">
-      <c r="A25" s="37"/>
-      <c r="B25" s="37">
-        <v>4</v>
-      </c>
-      <c r="C25" s="15">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="100.8">
-      <c r="A26" s="37"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="86.4">
-      <c r="A27" s="37"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="15">
-        <v>4.3</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="115.2">
-      <c r="A28" s="37"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="15">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="A15:A28"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A16:A29"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B13"/>
-    <mergeCell ref="B15:B24"/>
+    <mergeCell ref="B16:B25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6407,12 +6810,12 @@
         <v>46265</v>
       </c>
       <c r="C2" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E2)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E2)</f>
+        <v>45</v>
       </c>
       <c r="D2" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A2-1)/8)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)*(1-(A2-1)/8)</f>
+        <v>45</v>
       </c>
       <c r="E2" s="28">
         <v>0</v>
@@ -6426,12 +6829,12 @@
         <v>46266</v>
       </c>
       <c r="C3" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E3)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E3)</f>
+        <v>45</v>
       </c>
       <c r="D3" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A3-1)/8)</f>
-        <v>35</v>
+        <f>('Updated Sprint'!F15)*(1-(A3-1)/8)</f>
+        <v>39.375</v>
       </c>
       <c r="E3" s="28">
         <v>0</v>
@@ -6445,12 +6848,12 @@
         <v>46267</v>
       </c>
       <c r="C4" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E4)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E4)</f>
+        <v>45</v>
       </c>
       <c r="D4" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A4-1)/8)</f>
-        <v>30</v>
+        <f>('Updated Sprint'!F15)*(1-(A4-1)/8)</f>
+        <v>33.75</v>
       </c>
       <c r="E4" s="28">
         <v>0</v>
@@ -6464,12 +6867,12 @@
         <v>46268</v>
       </c>
       <c r="C5" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E5)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E5)</f>
+        <v>45</v>
       </c>
       <c r="D5" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A5-1)/8)</f>
-        <v>25</v>
+        <f>('Updated Sprint'!F15)*(1-(A5-1)/8)</f>
+        <v>28.125</v>
       </c>
       <c r="E5" s="28">
         <v>0</v>
@@ -6483,12 +6886,12 @@
         <v>46269</v>
       </c>
       <c r="C6" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E6)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E6)</f>
+        <v>45</v>
       </c>
       <c r="D6" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A6-1)/8)</f>
-        <v>20</v>
+        <f>('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
+        <v>22.5</v>
       </c>
       <c r="E6" s="28">
         <v>0</v>
@@ -6502,12 +6905,12 @@
         <v>46272</v>
       </c>
       <c r="C7" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E7)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E7)</f>
+        <v>45</v>
       </c>
       <c r="D7" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A7-1)/8)</f>
-        <v>15</v>
+        <f>('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
+        <v>16.875</v>
       </c>
       <c r="E7" s="28">
         <v>0</v>
@@ -6521,12 +6924,12 @@
         <v>46273</v>
       </c>
       <c r="C8" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E8)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E8)</f>
+        <v>45</v>
       </c>
       <c r="D8" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A8-1)/8)</f>
-        <v>10</v>
+        <f>('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
+        <v>11.25</v>
       </c>
       <c r="E8" s="28">
         <v>0</v>
@@ -6540,12 +6943,12 @@
         <v>46274</v>
       </c>
       <c r="C9" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E9)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E9)</f>
+        <v>45</v>
       </c>
       <c r="D9" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A9-1)/8)</f>
-        <v>5</v>
+        <f>('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
+        <v>5.625</v>
       </c>
       <c r="E9" s="28">
         <v>0</v>
@@ -6559,11 +6962,11 @@
         <v>46275</v>
       </c>
       <c r="C10" s="27">
-        <f>('Updated Sprint'!F14)-SUM(E$2:E10)</f>
-        <v>40</v>
+        <f>('Updated Sprint'!F15)-SUM(E$2:E10)</f>
+        <v>45</v>
       </c>
       <c r="D10" s="12">
-        <f>('Updated Sprint'!F14)*(1-(A10-1)/8)</f>
+        <f>('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
         <v>0</v>
       </c>
       <c r="E10" s="28">
@@ -6586,15 +6989,15 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAF31A5-BF80-4725-89FF-AEFF58B89D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C90FACC-3880-453D-920A-227FB67A67F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -724,7 +724,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="269">
   <si>
     <t>Work Item</t>
   </si>
@@ -2567,6 +2567,15 @@
 	Test an image containing no visible skin concern
 	Compare Visual AI returned skin_concern_id values against expected test results
 	Verify unsupported concern IDs are not persisted in the session_skin_concern_detection database table</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>WiP</t>
+  </si>
+  <si>
+    <t>TBD</t>
   </si>
 </sst>
 </file>
@@ -2861,6 +2870,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2873,6 +2889,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2880,28 +2905,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3038,31 +3047,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>45</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3248,7 +3257,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4391,11 +4400,11 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4535,18 +4544,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4581,7 +4590,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="47">
+      <c r="A3" s="53">
         <v>1</v>
       </c>
       <c r="B3" s="48">
@@ -4593,96 +4602,96 @@
       <c r="D3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="45" cm="1">
+      <c r="F3" s="51" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="47"/>
+      <c r="A4" s="53"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="47"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="47"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="47"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="47"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
       <c r="D8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="47"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="48"/>
       <c r="C9" s="48"/>
       <c r="D9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="47"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="48"/>
       <c r="C10" s="48"/>
       <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="47"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="47"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48">
         <v>1.2</v>
@@ -4690,36 +4699,36 @@
       <c r="D12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="45" cm="1">
+      <c r="F12" s="51" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="47"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
       <c r="D13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="47"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
       <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="47"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="48"/>
       <c r="C15" s="48">
         <v>1.3</v>
@@ -4727,33 +4736,33 @@
       <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="45"/>
+      <c r="F15" s="51"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="47"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
       <c r="D16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="47"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="47"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48">
         <v>1.4</v>
@@ -4761,84 +4770,84 @@
       <c r="D18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="45" t="s">
+      <c r="E18" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="45"/>
+      <c r="F18" s="51"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="47"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="47"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
       <c r="D20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="47"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
       <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="47"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
       <c r="D22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="47"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
       <c r="D23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="47"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
       <c r="D24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="47"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
       <c r="D25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="47"/>
-      <c r="B26" s="49">
+      <c r="A26" s="53"/>
+      <c r="B26" s="54">
         <v>2</v>
       </c>
       <c r="C26" s="48">
@@ -4847,359 +4856,359 @@
       <c r="D26" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="45"/>
+      <c r="F26" s="51"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="47"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="48"/>
       <c r="D27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="45"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="51"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="47"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="48"/>
       <c r="D28" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="45"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="47"/>
-      <c r="B29" s="49"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="50">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="45"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="47"/>
-      <c r="B30" s="49"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="54"/>
       <c r="C30" s="50"/>
       <c r="D30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="47"/>
-      <c r="B31" s="49"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="48">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="45" t="s">
+      <c r="E31" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45" t="s">
+      <c r="F31" s="51"/>
+      <c r="G31" s="51" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="47"/>
-      <c r="B32" s="49"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="54"/>
       <c r="C32" s="48"/>
       <c r="D32" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="47"/>
-      <c r="B33" s="49"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="54"/>
       <c r="C33" s="48"/>
       <c r="D33" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="47"/>
-      <c r="B34" s="49"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="48"/>
       <c r="D34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="47"/>
-      <c r="B35" s="49"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="54"/>
       <c r="C35" s="48"/>
       <c r="D35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="47"/>
-      <c r="B36" s="49"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="54"/>
       <c r="C36" s="48"/>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="47"/>
-      <c r="B37" s="49"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="48"/>
       <c r="D37" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="47"/>
-      <c r="B38" s="49"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="54"/>
       <c r="C38" s="48">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="45"/>
+      <c r="F38" s="51"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="47"/>
-      <c r="B39" s="49"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="54"/>
       <c r="C39" s="48"/>
       <c r="D39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="47"/>
-      <c r="B40" s="49"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="54"/>
       <c r="C40" s="48"/>
       <c r="D40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="47"/>
-      <c r="B41" s="49"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="54"/>
       <c r="C41" s="48"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="47"/>
-      <c r="B42" s="49"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="54"/>
       <c r="C42" s="48"/>
       <c r="D42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="47"/>
-      <c r="B43" s="49"/>
+      <c r="A43" s="53"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="48"/>
       <c r="D43" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="47"/>
-      <c r="B44" s="49"/>
+      <c r="A44" s="53"/>
+      <c r="B44" s="54"/>
       <c r="C44" s="48"/>
       <c r="D44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="47"/>
-      <c r="B45" s="49"/>
+      <c r="A45" s="53"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="48"/>
       <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="47"/>
-      <c r="B46" s="49"/>
+      <c r="A46" s="53"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="48">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="46" t="s">
+      <c r="E46" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="45"/>
+      <c r="F46" s="51"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="47"/>
-      <c r="B47" s="49"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="48"/>
       <c r="D47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="45"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="51"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="47"/>
-      <c r="B48" s="49"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="54"/>
       <c r="C48" s="48"/>
       <c r="D48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="46"/>
-      <c r="F48" s="45"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="51"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="47"/>
-      <c r="B49" s="49"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="54"/>
       <c r="C49" s="48"/>
       <c r="D49" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="45"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="51"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="47"/>
-      <c r="B50" s="49"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="54"/>
       <c r="C50" s="48">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="45"/>
+      <c r="F50" s="51"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="47"/>
-      <c r="B51" s="49"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="48"/>
       <c r="D51" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="47"/>
-      <c r="B52" s="49"/>
+      <c r="A52" s="53"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="48"/>
       <c r="D52" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="47"/>
-      <c r="B53" s="49"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="48"/>
       <c r="D53" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="47"/>
-      <c r="B54" s="49"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="54"/>
       <c r="C54" s="48"/>
       <c r="D54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="45"/>
-      <c r="F54" s="45"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="51"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="47"/>
-      <c r="B55" s="49"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="54"/>
       <c r="C55" s="48"/>
       <c r="D55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="47"/>
-      <c r="B56" s="49"/>
+      <c r="A56" s="53"/>
+      <c r="B56" s="54"/>
       <c r="C56" s="48"/>
       <c r="D56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="47"/>
-      <c r="B57" s="49"/>
+      <c r="A57" s="53"/>
+      <c r="B57" s="54"/>
       <c r="C57" s="48"/>
       <c r="D57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="47"/>
-      <c r="B58" s="49"/>
+      <c r="A58" s="53"/>
+      <c r="B58" s="54"/>
       <c r="C58" s="48"/>
       <c r="D58" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="51"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
@@ -5888,7 +5897,7 @@
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
       <c r="B142" s="48"/>
-      <c r="C142" s="51">
+      <c r="C142" s="49">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5898,7 +5907,7 @@
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
       <c r="B143" s="48"/>
-      <c r="C143" s="51"/>
+      <c r="C143" s="49"/>
       <c r="D143" s="7" t="s">
         <v>170</v>
       </c>
@@ -5906,7 +5915,7 @@
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
       <c r="B144" s="48"/>
-      <c r="C144" s="51"/>
+      <c r="C144" s="49"/>
       <c r="D144" s="7" t="s">
         <v>171</v>
       </c>
@@ -5914,7 +5923,7 @@
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
       <c r="B145" s="48"/>
-      <c r="C145" s="51"/>
+      <c r="C145" s="49"/>
       <c r="D145" s="7" t="s">
         <v>172</v>
       </c>
@@ -5922,7 +5931,7 @@
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
       <c r="B146" s="48"/>
-      <c r="C146" s="51"/>
+      <c r="C146" s="49"/>
       <c r="D146" s="7" t="s">
         <v>173</v>
       </c>
@@ -5930,7 +5939,7 @@
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
       <c r="B147" s="48"/>
-      <c r="C147" s="51"/>
+      <c r="C147" s="49"/>
       <c r="D147" s="7" t="s">
         <v>174</v>
       </c>
@@ -5938,7 +5947,7 @@
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
       <c r="B148" s="48"/>
-      <c r="C148" s="51"/>
+      <c r="C148" s="49"/>
       <c r="D148" s="7" t="s">
         <v>175</v>
       </c>
@@ -5946,7 +5955,7 @@
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
       <c r="B149" s="48"/>
-      <c r="C149" s="51"/>
+      <c r="C149" s="49"/>
       <c r="D149" s="7" t="s">
         <v>176</v>
       </c>
@@ -5954,7 +5963,7 @@
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
       <c r="B150" s="48"/>
-      <c r="C150" s="51"/>
+      <c r="C150" s="49"/>
       <c r="D150" s="7" t="s">
         <v>177</v>
       </c>
@@ -5962,7 +5971,7 @@
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
       <c r="B151" s="48"/>
-      <c r="C151" s="51"/>
+      <c r="C151" s="49"/>
       <c r="D151" s="7" t="s">
         <v>178</v>
       </c>
@@ -5970,7 +5979,7 @@
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
       <c r="B152" s="48"/>
-      <c r="C152" s="51"/>
+      <c r="C152" s="49"/>
       <c r="D152" s="7" t="s">
         <v>179</v>
       </c>
@@ -5978,7 +5987,7 @@
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
       <c r="B153" s="48"/>
-      <c r="C153" s="51"/>
+      <c r="C153" s="49"/>
       <c r="D153" s="7" t="s">
         <v>180</v>
       </c>
@@ -5986,7 +5995,7 @@
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
       <c r="B154" s="48"/>
-      <c r="C154" s="51"/>
+      <c r="C154" s="49"/>
       <c r="D154" s="7" t="s">
         <v>181</v>
       </c>
@@ -5994,7 +6003,7 @@
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
       <c r="B155" s="48"/>
-      <c r="C155" s="51"/>
+      <c r="C155" s="49"/>
       <c r="D155" s="7" t="s">
         <v>182</v>
       </c>
@@ -6002,7 +6011,7 @@
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
       <c r="B156" s="48"/>
-      <c r="C156" s="51"/>
+      <c r="C156" s="49"/>
       <c r="D156" s="7" t="s">
         <v>58</v>
       </c>
@@ -6220,6 +6229,41 @@
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{F0DC7BB0-6771-4160-B371-AE490E8879B7}"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6236,41 +6280,6 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6293,18 +6302,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -6343,10 +6352,10 @@
       <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:12" ht="129.6">
-      <c r="A3" s="41">
+      <c r="A3" s="44">
         <v>1</v>
       </c>
-      <c r="B3" s="41">
+      <c r="B3" s="44">
         <v>1</v>
       </c>
       <c r="C3" s="15">
@@ -6365,10 +6374,13 @@
       <c r="G3" t="s">
         <v>250</v>
       </c>
+      <c r="H3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="57.6">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
@@ -6385,10 +6397,13 @@
       <c r="G4" t="s">
         <v>250</v>
       </c>
+      <c r="H4" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="43.2">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -6405,10 +6420,13 @@
       <c r="G5" t="s">
         <v>251</v>
       </c>
+      <c r="H5" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="115.2">
-      <c r="A6" s="41"/>
-      <c r="B6" s="41"/>
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -6425,13 +6443,15 @@
       <c r="G6" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H6" s="38"/>
+      <c r="H6" s="38" t="s">
+        <v>268</v>
+      </c>
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
     </row>
-    <row r="7" spans="1:12" ht="86.4">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41">
+    <row r="7" spans="1:12" ht="72">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44">
         <v>2</v>
       </c>
       <c r="C7" s="15">
@@ -6450,10 +6470,13 @@
       <c r="G7" t="s">
         <v>252</v>
       </c>
+      <c r="H7" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="57.6">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
@@ -6470,10 +6493,13 @@
       <c r="G8" t="s">
         <v>252</v>
       </c>
+      <c r="H8" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="100.8">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
@@ -6490,10 +6516,13 @@
       <c r="G9" t="s">
         <v>214</v>
       </c>
+      <c r="H9" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="10" spans="1:12" ht="115.2">
-      <c r="A10" s="41"/>
-      <c r="B10" s="41"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
@@ -6510,10 +6539,13 @@
       <c r="G10" t="s">
         <v>254</v>
       </c>
+      <c r="H10" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="100.8">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
@@ -6530,10 +6562,13 @@
       <c r="G11" t="s">
         <v>252</v>
       </c>
+      <c r="H11" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="115.2">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
@@ -6550,10 +6585,13 @@
       <c r="G12" t="s">
         <v>255</v>
       </c>
+      <c r="H12" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="158.4">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -6570,30 +6608,34 @@
       <c r="G13" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="H13" s="38"/>
+      <c r="H13" s="38" t="s">
+        <v>268</v>
+      </c>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
     </row>
     <row r="14" spans="1:12" ht="144">
-      <c r="C14" s="53">
+      <c r="C14" s="41">
         <v>2.8</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="42" t="s">
         <v>265</v>
       </c>
-      <c r="E14" s="55" t="s">
+      <c r="E14" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="55" cm="1">
+      <c r="F14" s="43" cm="1">
         <f t="array" ref="F14">_xlfn.SWITCH(E14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="G14" s="55" t="s">
+      <c r="G14" s="43" t="s">
         <v>253</v>
       </c>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
+      <c r="H14" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="33"/>
@@ -6613,10 +6655,10 @@
       <c r="J15" s="31"/>
     </row>
     <row r="16" spans="1:12" ht="86.4">
-      <c r="A16" s="42">
+      <c r="A16" s="45">
         <v>2</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="45">
         <v>3</v>
       </c>
       <c r="C16" s="15">
@@ -6627,8 +6669,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="172.8">
-      <c r="A17" s="41"/>
-      <c r="B17" s="41"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="15">
         <v>3.2</v>
       </c>
@@ -6636,9 +6678,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="172.8">
-      <c r="A18" s="41"/>
-      <c r="B18" s="41"/>
+    <row r="18" spans="1:4" ht="158.4">
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
       <c r="C18" s="15">
         <v>3.3</v>
       </c>
@@ -6647,8 +6689,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="187.2">
-      <c r="A19" s="41"/>
-      <c r="B19" s="41"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
       <c r="C19" s="15">
         <v>3.4</v>
       </c>
@@ -6657,8 +6699,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="129.6">
-      <c r="A20" s="41"/>
-      <c r="B20" s="41"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="15">
         <v>3.5</v>
       </c>
@@ -6667,8 +6709,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="86.4">
-      <c r="A21" s="41"/>
-      <c r="B21" s="41"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
       <c r="C21" s="15">
         <v>3.6</v>
       </c>
@@ -6677,8 +6719,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="158.4">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
       <c r="C22" s="15">
         <v>3.7</v>
       </c>
@@ -6687,8 +6729,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" ht="144">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="15">
         <v>3.8</v>
       </c>
@@ -6697,8 +6739,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="72">
-      <c r="A24" s="41"/>
-      <c r="B24" s="41"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
       <c r="C24" s="15">
         <v>3.9</v>
       </c>
@@ -6707,8 +6749,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="216">
-      <c r="A25" s="41"/>
-      <c r="B25" s="41"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
       <c r="C25" s="35">
         <v>3.1</v>
       </c>
@@ -6717,8 +6759,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="57.6">
-      <c r="A26" s="41"/>
-      <c r="B26" s="41">
+      <c r="A26" s="44"/>
+      <c r="B26" s="44">
         <v>4</v>
       </c>
       <c r="C26" s="15">
@@ -6729,8 +6771,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="100.8">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="15">
         <v>4.2</v>
       </c>
@@ -6739,8 +6781,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="86.4">
-      <c r="A28" s="41"/>
-      <c r="B28" s="41"/>
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
       <c r="C28" s="15">
         <v>4.3</v>
       </c>
@@ -6749,8 +6791,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="115.2">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
       <c r="C29" s="15">
         <v>4.4000000000000004</v>
       </c>
@@ -6811,14 +6853,14 @@
       </c>
       <c r="C2" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E2)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" s="12">
         <f>('Updated Sprint'!F15)*(1-(A2-1)/8)</f>
         <v>45</v>
       </c>
       <c r="E2" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6830,7 +6872,7 @@
       </c>
       <c r="C3" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E3)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="12">
         <f>('Updated Sprint'!F15)*(1-(A3-1)/8)</f>
@@ -6849,7 +6891,7 @@
       </c>
       <c r="C4" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E4)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="12">
         <f>('Updated Sprint'!F15)*(1-(A4-1)/8)</f>
@@ -6868,7 +6910,7 @@
       </c>
       <c r="C5" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E5)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="12">
         <f>('Updated Sprint'!F15)*(1-(A5-1)/8)</f>
@@ -6887,7 +6929,7 @@
       </c>
       <c r="C6" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E6)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="12">
         <f>('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
@@ -6906,7 +6948,7 @@
       </c>
       <c r="C7" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E7)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="12">
         <f>('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
@@ -6925,7 +6967,7 @@
       </c>
       <c r="C8" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E8)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8" s="12">
         <f>('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
@@ -6944,7 +6986,7 @@
       </c>
       <c r="C9" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E9)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="12">
         <f>('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
@@ -6963,7 +7005,7 @@
       </c>
       <c r="C10" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E10)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" s="12">
         <f>('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
@@ -6989,15 +7031,15 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="12" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C90FACC-3880-453D-920A-227FB67A67F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
@@ -17,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,17 +34,26 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>tc={233094A3-3D2A-436A-904F-A8273DA397F5}</author>
+    <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{233094A3-3D2A-436A-904F-A8273DA397F5}">
+    <comment ref="E5" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Should all skin concerns be listed when we are only addressing top n.</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -53,12 +61,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{A6123E30-2FFB-4B36-8675-D2A1F49CF554}">
+    <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{3BEE7270-9E5D-4C3B-88E0-91F05B9BD669}">
+    <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -108,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{D5A9F85E-92E8-4B8A-B751-650E1FE2569F}">
+    <comment ref="C12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -132,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{EFBBA07C-E254-4781-9933-E074E562E094}">
+    <comment ref="C15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -156,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{08C2F3F8-DE97-42AE-B963-708E64840735}">
+    <comment ref="C18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -180,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{98BE6294-CAA3-4259-A595-9BA237237285}">
+    <comment ref="C26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -205,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{140A5E96-154A-4162-A239-1DBD3E41810C}">
+    <comment ref="C29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -229,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{E3A3B5A0-0F07-42D5-9D6D-8B8281899F6E}">
+    <comment ref="C31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -253,7 +261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{FDDD7F68-C10A-4FC9-9764-CDD59417EB55}">
+    <comment ref="C38" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -277,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0" shapeId="0" xr:uid="{51C480C2-E212-4A32-86A1-5F704BCFF728}">
+    <comment ref="C46" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -301,7 +309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{52553FD1-E265-4535-9DD2-2EA05E499E51}">
+    <comment ref="C50" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -325,7 +333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C59" authorId="0" shapeId="0" xr:uid="{E4589DAE-73CB-47AB-AD0F-AB8AF18DDD65}">
+    <comment ref="C59" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -349,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{D05C5BAE-0CC4-4ED2-88B6-98BF1ED2B235}">
+    <comment ref="C65" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -373,7 +381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{8C37B025-1BDA-457E-ADB8-C6B979CBD1B1}">
+    <comment ref="C77" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -397,7 +405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0" xr:uid="{D1A59F32-F52A-4554-9D45-7BAAF46B83A7}">
+    <comment ref="C88" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -421,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0" xr:uid="{29757E96-410A-48C6-A86D-C6221515FA91}">
+    <comment ref="C101" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -445,7 +453,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0" xr:uid="{C9E3522F-95B1-4BD8-BE53-4B604FDEA74C}">
+    <comment ref="C110" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -469,7 +477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0" xr:uid="{87018544-F456-4F26-A7A5-F72A08475131}">
+    <comment ref="C116" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -493,7 +501,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0" xr:uid="{EC2B78D7-751C-44BB-9D07-F55A82442F1A}">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -517,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0" xr:uid="{99C81342-5268-4323-82B8-DCB2C87D9E02}">
+    <comment ref="C137" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -541,7 +549,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{73BA3055-4675-4813-88D0-50B14C092AF1}">
+    <comment ref="C142" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -565,7 +573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{706E98C8-4B35-46F2-B926-68F27F8F78A4}">
+    <comment ref="C157" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -589,7 +597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{A79A220B-8C29-48AD-9825-8780EE217E6A}">
+    <comment ref="C161" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -613,7 +621,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{C4E0F00C-6245-4423-9EA8-8A42808307DE}">
+    <comment ref="C168" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -637,7 +645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{D8702894-1958-4EC2-ACC6-FDE92A697344}">
+    <comment ref="C174" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -666,12 +674,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{4C8D1B9E-A5AC-43BE-8365-C18029D3B009}">
+    <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -702,14 +710,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2581,7 +2589,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -2877,26 +2885,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2905,8 +2895,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2943,6 +2951,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3053,25 +3062,25 @@
                   <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3263,7 +3272,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3422,6 +3431,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4093,9 +4103,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4133,9 +4143,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4170,7 +4180,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4205,7 +4215,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4386,25 +4396,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D13B384-1725-40B5-B0F7-A3A77A0F68B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="35.77734375" customWidth="1"/>
-    <col min="5" max="5" width="51.109375" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="51.140625" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4428,7 +4438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="100.8">
+    <row r="3" spans="1:6" ht="105">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -4479,7 +4489,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="86.4">
+    <row r="6" spans="1:6" ht="90">
       <c r="A6" s="15">
         <v>4</v>
       </c>
@@ -4530,32 +4540,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0DC7BB0-6771-4160-B371-AE490E8879B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J181"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4590,7 +4600,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="53">
+      <c r="A3" s="47">
         <v>1</v>
       </c>
       <c r="B3" s="48">
@@ -4602,96 +4612,96 @@
       <c r="D3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="51" cm="1">
+      <c r="F3" s="45" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="53"/>
+      <c r="A4" s="47"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="53"/>
+      <c r="A5" s="47"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="53"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="53"/>
+      <c r="A7" s="47"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="53"/>
+      <c r="A8" s="47"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
       <c r="D8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="53"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="48"/>
       <c r="C9" s="48"/>
       <c r="D9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="53"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="48"/>
       <c r="C10" s="48"/>
       <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="53"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="53"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48">
         <v>1.2</v>
@@ -4699,36 +4709,36 @@
       <c r="D12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="51" cm="1">
+      <c r="F12" s="45" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="53"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
       <c r="D13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="53"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
       <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="53"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="48"/>
       <c r="C15" s="48">
         <v>1.3</v>
@@ -4736,33 +4746,33 @@
       <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="51"/>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="53"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
       <c r="D16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="53"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="53"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48">
         <v>1.4</v>
@@ -4770,84 +4780,84 @@
       <c r="D18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="51"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="53"/>
+      <c r="A19" s="47"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="53"/>
+      <c r="A20" s="47"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
       <c r="D20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="53"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
       <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="53"/>
+      <c r="A22" s="47"/>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
       <c r="D22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="53"/>
+      <c r="A23" s="47"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
       <c r="D23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="53"/>
+      <c r="A24" s="47"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
       <c r="D24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="53"/>
+      <c r="A25" s="47"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
       <c r="D25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="53"/>
-      <c r="B26" s="54">
+      <c r="A26" s="47"/>
+      <c r="B26" s="49">
         <v>2</v>
       </c>
       <c r="C26" s="48">
@@ -4856,359 +4866,359 @@
       <c r="D26" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="51"/>
+      <c r="F26" s="45"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
+      <c r="A27" s="47"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="48"/>
       <c r="D27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="51"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="45"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="53"/>
-      <c r="B28" s="54"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="49"/>
       <c r="C28" s="48"/>
       <c r="D28" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="52"/>
-      <c r="F28" s="51"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="45"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="53"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="50">
+      <c r="A29" s="47"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="51">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="51"/>
+      <c r="F29" s="45"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="53"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="50"/>
+      <c r="A30" s="47"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="51"/>
       <c r="D30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="53"/>
-      <c r="B31" s="54"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="48">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51" t="s">
+      <c r="F31" s="45"/>
+      <c r="G31" s="45" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="53"/>
-      <c r="B32" s="54"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="49"/>
       <c r="C32" s="48"/>
       <c r="D32" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="53"/>
-      <c r="B33" s="54"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="49"/>
       <c r="C33" s="48"/>
       <c r="D33" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="53"/>
-      <c r="B34" s="54"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="49"/>
       <c r="C34" s="48"/>
       <c r="D34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="49"/>
       <c r="C35" s="48"/>
       <c r="D35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="53"/>
-      <c r="B36" s="54"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="49"/>
       <c r="C36" s="48"/>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="53"/>
-      <c r="B37" s="54"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="49"/>
       <c r="C37" s="48"/>
       <c r="D37" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="53"/>
-      <c r="B38" s="54"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="49"/>
       <c r="C38" s="48">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="51" t="s">
+      <c r="E38" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="51"/>
+      <c r="F38" s="45"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="53"/>
-      <c r="B39" s="54"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="49"/>
       <c r="C39" s="48"/>
       <c r="D39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="53"/>
-      <c r="B40" s="54"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="49"/>
       <c r="C40" s="48"/>
       <c r="D40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="53"/>
-      <c r="B41" s="54"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="49"/>
       <c r="C41" s="48"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="53"/>
-      <c r="B42" s="54"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="49"/>
       <c r="C42" s="48"/>
       <c r="D42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="53"/>
-      <c r="B43" s="54"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="49"/>
       <c r="C43" s="48"/>
       <c r="D43" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="53"/>
-      <c r="B44" s="54"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="49"/>
       <c r="C44" s="48"/>
       <c r="D44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="53"/>
-      <c r="B45" s="54"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="49"/>
       <c r="C45" s="48"/>
       <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="53"/>
-      <c r="B46" s="54"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="49"/>
       <c r="C46" s="48">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="52" t="s">
+      <c r="E46" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="51"/>
+      <c r="F46" s="45"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="53"/>
-      <c r="B47" s="54"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="49"/>
       <c r="C47" s="48"/>
       <c r="D47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="52"/>
-      <c r="F47" s="51"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="45"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="53"/>
-      <c r="B48" s="54"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="49"/>
       <c r="C48" s="48"/>
       <c r="D48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="52"/>
-      <c r="F48" s="51"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="45"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="53"/>
-      <c r="B49" s="54"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="49"/>
       <c r="C49" s="48"/>
       <c r="D49" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E49" s="52"/>
-      <c r="F49" s="51"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="45"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="53"/>
-      <c r="B50" s="54"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="49"/>
       <c r="C50" s="48">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="51" t="s">
+      <c r="E50" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="51"/>
+      <c r="F50" s="45"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="53"/>
-      <c r="B51" s="54"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="49"/>
       <c r="C51" s="48"/>
       <c r="D51" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="53"/>
-      <c r="B52" s="54"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="49"/>
       <c r="C52" s="48"/>
       <c r="D52" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="53"/>
-      <c r="B53" s="54"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="49"/>
       <c r="C53" s="48"/>
       <c r="D53" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="53"/>
-      <c r="B54" s="54"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="49"/>
       <c r="C54" s="48"/>
       <c r="D54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="53"/>
-      <c r="B55" s="54"/>
+      <c r="A55" s="47"/>
+      <c r="B55" s="49"/>
       <c r="C55" s="48"/>
       <c r="D55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="53"/>
-      <c r="B56" s="54"/>
+      <c r="A56" s="47"/>
+      <c r="B56" s="49"/>
       <c r="C56" s="48"/>
       <c r="D56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E56" s="51"/>
-      <c r="F56" s="51"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="53"/>
-      <c r="B57" s="54"/>
+      <c r="A57" s="47"/>
+      <c r="B57" s="49"/>
       <c r="C57" s="48"/>
       <c r="D57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="53"/>
-      <c r="B58" s="54"/>
+      <c r="A58" s="47"/>
+      <c r="B58" s="49"/>
       <c r="C58" s="48"/>
       <c r="D58" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="51"/>
-      <c r="F58" s="51"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
@@ -5897,7 +5907,7 @@
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
       <c r="B142" s="48"/>
-      <c r="C142" s="49">
+      <c r="C142" s="52">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5907,7 +5917,7 @@
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
       <c r="B143" s="48"/>
-      <c r="C143" s="49"/>
+      <c r="C143" s="52"/>
       <c r="D143" s="7" t="s">
         <v>170</v>
       </c>
@@ -5915,7 +5925,7 @@
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
       <c r="B144" s="48"/>
-      <c r="C144" s="49"/>
+      <c r="C144" s="52"/>
       <c r="D144" s="7" t="s">
         <v>171</v>
       </c>
@@ -5923,7 +5933,7 @@
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
       <c r="B145" s="48"/>
-      <c r="C145" s="49"/>
+      <c r="C145" s="52"/>
       <c r="D145" s="7" t="s">
         <v>172</v>
       </c>
@@ -5931,7 +5941,7 @@
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
       <c r="B146" s="48"/>
-      <c r="C146" s="49"/>
+      <c r="C146" s="52"/>
       <c r="D146" s="7" t="s">
         <v>173</v>
       </c>
@@ -5939,7 +5949,7 @@
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
       <c r="B147" s="48"/>
-      <c r="C147" s="49"/>
+      <c r="C147" s="52"/>
       <c r="D147" s="7" t="s">
         <v>174</v>
       </c>
@@ -5947,7 +5957,7 @@
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
       <c r="B148" s="48"/>
-      <c r="C148" s="49"/>
+      <c r="C148" s="52"/>
       <c r="D148" s="7" t="s">
         <v>175</v>
       </c>
@@ -5955,7 +5965,7 @@
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
       <c r="B149" s="48"/>
-      <c r="C149" s="49"/>
+      <c r="C149" s="52"/>
       <c r="D149" s="7" t="s">
         <v>176</v>
       </c>
@@ -5963,7 +5973,7 @@
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
       <c r="B150" s="48"/>
-      <c r="C150" s="49"/>
+      <c r="C150" s="52"/>
       <c r="D150" s="7" t="s">
         <v>177</v>
       </c>
@@ -5971,7 +5981,7 @@
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
       <c r="B151" s="48"/>
-      <c r="C151" s="49"/>
+      <c r="C151" s="52"/>
       <c r="D151" s="7" t="s">
         <v>178</v>
       </c>
@@ -5979,7 +5989,7 @@
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
       <c r="B152" s="48"/>
-      <c r="C152" s="49"/>
+      <c r="C152" s="52"/>
       <c r="D152" s="7" t="s">
         <v>179</v>
       </c>
@@ -5987,7 +5997,7 @@
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
       <c r="B153" s="48"/>
-      <c r="C153" s="49"/>
+      <c r="C153" s="52"/>
       <c r="D153" s="7" t="s">
         <v>180</v>
       </c>
@@ -5995,7 +6005,7 @@
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
       <c r="B154" s="48"/>
-      <c r="C154" s="49"/>
+      <c r="C154" s="52"/>
       <c r="D154" s="7" t="s">
         <v>181</v>
       </c>
@@ -6003,7 +6013,7 @@
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
       <c r="B155" s="48"/>
-      <c r="C155" s="49"/>
+      <c r="C155" s="52"/>
       <c r="D155" s="7" t="s">
         <v>182</v>
       </c>
@@ -6011,7 +6021,7 @@
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
       <c r="B156" s="48"/>
-      <c r="C156" s="49"/>
+      <c r="C156" s="52"/>
       <c r="D156" s="7" t="s">
         <v>58</v>
       </c>
@@ -6227,43 +6237,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J181" xr:uid="{F0DC7BB0-6771-4160-B371-AE490E8879B7}"/>
+  <autoFilter ref="A2:J181"/>
   <mergeCells count="51">
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6280,6 +6255,41 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6288,32 +6298,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AFAF48-8618-45CD-B1C5-CEC08E5846C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -6351,11 +6361,11 @@
       </c>
       <c r="L2" s="40"/>
     </row>
-    <row r="3" spans="1:12" ht="129.6">
-      <c r="A3" s="44">
+    <row r="3" spans="1:12" ht="135">
+      <c r="A3" s="53">
         <v>1</v>
       </c>
-      <c r="B3" s="44">
+      <c r="B3" s="53">
         <v>1</v>
       </c>
       <c r="C3" s="15">
@@ -6375,12 +6385,12 @@
         <v>250</v>
       </c>
       <c r="H3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="57.6">
-      <c r="A4" s="44"/>
-      <c r="B4" s="44"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="60">
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
@@ -6398,12 +6408,12 @@
         <v>250</v>
       </c>
       <c r="H4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="43.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="45">
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -6424,9 +6434,9 @@
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="115.2">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+    <row r="6" spans="1:12" ht="120">
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -6449,9 +6459,9 @@
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
     </row>
-    <row r="7" spans="1:12" ht="72">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44">
+    <row r="7" spans="1:12" ht="90">
+      <c r="A7" s="53"/>
+      <c r="B7" s="53">
         <v>2</v>
       </c>
       <c r="C7" s="15">
@@ -6474,9 +6484,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="57.6">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
+    <row r="8" spans="1:12" ht="60">
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
@@ -6497,9 +6507,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="100.8">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
+    <row r="9" spans="1:12" ht="105">
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
@@ -6520,9 +6530,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="115.2">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
+    <row r="10" spans="1:12" ht="120">
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
@@ -6543,9 +6553,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="100.8">
-      <c r="A11" s="44"/>
-      <c r="B11" s="44"/>
+    <row r="11" spans="1:12" ht="120">
+      <c r="A11" s="53"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
@@ -6566,9 +6576,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="115.2">
-      <c r="A12" s="44"/>
-      <c r="B12" s="44"/>
+    <row r="12" spans="1:12" ht="120">
+      <c r="A12" s="53"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
@@ -6589,9 +6599,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="158.4">
-      <c r="A13" s="44"/>
-      <c r="B13" s="44"/>
+    <row r="13" spans="1:12" ht="165">
+      <c r="A13" s="53"/>
+      <c r="B13" s="53"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -6614,7 +6624,7 @@
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
     </row>
-    <row r="14" spans="1:12" ht="144">
+    <row r="14" spans="1:12" ht="165">
       <c r="C14" s="41">
         <v>2.8</v>
       </c>
@@ -6654,11 +6664,11 @@
       <c r="I15" s="29"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:12" ht="86.4">
-      <c r="A16" s="45">
+    <row r="16" spans="1:12" ht="90">
+      <c r="A16" s="54">
         <v>2</v>
       </c>
-      <c r="B16" s="45">
+      <c r="B16" s="54">
         <v>3</v>
       </c>
       <c r="C16" s="15">
@@ -6668,9 +6678,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="172.8">
-      <c r="A17" s="44"/>
-      <c r="B17" s="44"/>
+    <row r="17" spans="1:4" ht="180">
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="15">
         <v>3.2</v>
       </c>
@@ -6678,9 +6688,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="158.4">
-      <c r="A18" s="44"/>
-      <c r="B18" s="44"/>
+    <row r="18" spans="1:4" ht="165">
+      <c r="A18" s="53"/>
+      <c r="B18" s="53"/>
       <c r="C18" s="15">
         <v>3.3</v>
       </c>
@@ -6688,9 +6698,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="187.2">
-      <c r="A19" s="44"/>
-      <c r="B19" s="44"/>
+    <row r="19" spans="1:4" ht="195">
+      <c r="A19" s="53"/>
+      <c r="B19" s="53"/>
       <c r="C19" s="15">
         <v>3.4</v>
       </c>
@@ -6698,9 +6708,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="129.6">
-      <c r="A20" s="44"/>
-      <c r="B20" s="44"/>
+    <row r="20" spans="1:4" ht="135">
+      <c r="A20" s="53"/>
+      <c r="B20" s="53"/>
       <c r="C20" s="15">
         <v>3.5</v>
       </c>
@@ -6708,9 +6718,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="86.4">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
+    <row r="21" spans="1:4" ht="90">
+      <c r="A21" s="53"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="15">
         <v>3.6</v>
       </c>
@@ -6718,9 +6728,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="158.4">
-      <c r="A22" s="44"/>
-      <c r="B22" s="44"/>
+    <row r="22" spans="1:4" ht="165">
+      <c r="A22" s="53"/>
+      <c r="B22" s="53"/>
       <c r="C22" s="15">
         <v>3.7</v>
       </c>
@@ -6728,9 +6738,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="144">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
+    <row r="23" spans="1:4" ht="150">
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="15">
         <v>3.8</v>
       </c>
@@ -6738,9 +6748,9 @@
         <v>243</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="72">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
+    <row r="24" spans="1:4" ht="75">
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="15">
         <v>3.9</v>
       </c>
@@ -6748,9 +6758,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="216">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
+    <row r="25" spans="1:4" ht="225">
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
       <c r="C25" s="35">
         <v>3.1</v>
       </c>
@@ -6758,9 +6768,9 @@
         <v>245</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="57.6">
-      <c r="A26" s="44"/>
-      <c r="B26" s="44">
+    <row r="26" spans="1:4" ht="60">
+      <c r="A26" s="53"/>
+      <c r="B26" s="53">
         <v>4</v>
       </c>
       <c r="C26" s="15">
@@ -6770,9 +6780,9 @@
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="100.8">
-      <c r="A27" s="44"/>
-      <c r="B27" s="44"/>
+    <row r="27" spans="1:4" ht="105">
+      <c r="A27" s="53"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="15">
         <v>4.2</v>
       </c>
@@ -6780,9 +6790,9 @@
         <v>247</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="86.4">
-      <c r="A28" s="44"/>
-      <c r="B28" s="44"/>
+    <row r="28" spans="1:4" ht="90">
+      <c r="A28" s="53"/>
+      <c r="B28" s="53"/>
       <c r="C28" s="15">
         <v>4.3</v>
       </c>
@@ -6790,9 +6800,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="115.2">
-      <c r="A29" s="44"/>
-      <c r="B29" s="44"/>
+    <row r="29" spans="1:4" ht="120">
+      <c r="A29" s="53"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="15">
         <v>4.4000000000000004</v>
       </c>
@@ -6817,17 +6827,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA087AEC-DE6A-4BD3-B656-5E86DF79D39A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57.6">
+    <row r="1" spans="1:5" ht="60">
       <c r="A1" s="22" t="s">
         <v>216</v>
       </c>
@@ -6891,14 +6901,14 @@
       </c>
       <c r="C4" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E4)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D4" s="12">
         <f>('Updated Sprint'!F15)*(1-(A4-1)/8)</f>
         <v>33.75</v>
       </c>
       <c r="E4" s="28">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6910,7 +6920,7 @@
       </c>
       <c r="C5" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E5)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D5" s="12">
         <f>('Updated Sprint'!F15)*(1-(A5-1)/8)</f>
@@ -6929,7 +6939,7 @@
       </c>
       <c r="C6" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E6)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D6" s="12">
         <f>('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
@@ -6948,7 +6958,7 @@
       </c>
       <c r="C7" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E7)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D7" s="12">
         <f>('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
@@ -6967,7 +6977,7 @@
       </c>
       <c r="C8" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E8)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D8" s="12">
         <f>('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
@@ -6986,7 +6996,7 @@
       </c>
       <c r="C9" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E9)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D9" s="12">
         <f>('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
@@ -7005,7 +7015,7 @@
       </c>
       <c r="C10" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E10)</f>
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D10" s="12">
         <f>('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
@@ -7026,9 +7036,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF11110B-B1A6-47E4-BCEC-C2B4CA62D5BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="55" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3D368C-9D12-4C77-ABFE-CEB94E6E9F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="4" r:id="rId1"/>
@@ -16,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sprint Backlog'!$A$2:$J$181</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="E5" authorId="0" shapeId="0">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -61,12 +62,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -92,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -116,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -140,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -164,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
+    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -188,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -213,7 +214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0">
+    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -237,7 +238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C31" authorId="0" shapeId="0">
+    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -261,7 +262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
+    <comment ref="C38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -285,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C46" authorId="0" shapeId="0">
+    <comment ref="C46" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -309,7 +310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
+    <comment ref="C50" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -333,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C59" authorId="0" shapeId="0">
+    <comment ref="C59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -357,7 +358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C65" authorId="0" shapeId="0">
+    <comment ref="C65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -381,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0">
+    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -405,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C88" authorId="0" shapeId="0">
+    <comment ref="C88" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -429,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0">
+    <comment ref="C101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
       <text>
         <r>
           <rPr>
@@ -453,7 +454,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0">
+    <comment ref="C110" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
       <text>
         <r>
           <rPr>
@@ -477,7 +478,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
+    <comment ref="C116" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
       <text>
         <r>
           <rPr>
@@ -501,7 +502,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
       <text>
         <r>
           <rPr>
@@ -525,7 +526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0">
+    <comment ref="C137" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
       <text>
         <r>
           <rPr>
@@ -549,7 +550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C142" authorId="0" shapeId="0">
+    <comment ref="C142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
       <text>
         <r>
           <rPr>
@@ -573,7 +574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C157" authorId="0" shapeId="0">
+    <comment ref="C157" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
       <text>
         <r>
           <rPr>
@@ -597,7 +598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C161" authorId="0" shapeId="0">
+    <comment ref="C161" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
       <text>
         <r>
           <rPr>
@@ -621,7 +622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C168" authorId="0" shapeId="0">
+    <comment ref="C168" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
       <text>
         <r>
           <rPr>
@@ -645,7 +646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C174" authorId="0" shapeId="0">
+    <comment ref="C174" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
       <text>
         <r>
           <rPr>
@@ -674,12 +675,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -710,14 +711,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -2589,7 +2590,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11">
     <font>
       <sz val="11"/>
@@ -2885,8 +2886,26 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2895,26 +2914,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2951,7 +2952,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3068,19 +3068,19 @@
                   <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>39</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>39</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>39</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>39</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>39</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3278,7 +3278,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3431,7 +3431,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4103,9 +4102,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4143,9 +4142,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4180,7 +4179,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4215,7 +4214,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4387,34 +4386,26 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E5" dT="2026-08-20T15:41:46.67" personId="{00000000-0000-0000-0000-000000000000}" id="{233094A3-3D2A-436A-904F-A8273DA397F5}">
-    <text>Should all skin concerns be listed when we are only addressing top n.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
-    <col min="5" max="5" width="51.140625" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" customWidth="1"/>
+    <col min="5" max="5" width="51.109375" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="10"/>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
     </row>
@@ -4438,7 +4429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="105">
+    <row r="3" spans="1:6" ht="100.8">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -4489,7 +4480,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="90">
+    <row r="6" spans="1:6" ht="86.4">
       <c r="A6" s="15">
         <v>4</v>
       </c>
@@ -4540,32 +4531,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J181"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" s="4" customFormat="1">
       <c r="A2" s="10" t="s">
@@ -4600,7 +4591,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="47">
+      <c r="A3" s="53">
         <v>1</v>
       </c>
       <c r="B3" s="48">
@@ -4612,96 +4603,96 @@
       <c r="D3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="45" cm="1">
+      <c r="F3" s="51" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="47"/>
+      <c r="A4" s="53"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="47"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="47"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="47"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="48"/>
       <c r="C7" s="48"/>
       <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="47"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="48"/>
       <c r="C8" s="48"/>
       <c r="D8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="47"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="48"/>
       <c r="C9" s="48"/>
       <c r="D9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="47"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="48"/>
       <c r="C10" s="48"/>
       <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="47"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="47"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48">
         <v>1.2</v>
@@ -4709,36 +4700,36 @@
       <c r="D12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="45" cm="1">
+      <c r="F12" s="51" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="47"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
       <c r="D13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="47"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
       <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="47"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="48"/>
       <c r="C15" s="48">
         <v>1.3</v>
@@ -4746,33 +4737,33 @@
       <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="45"/>
+      <c r="F15" s="51"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="47"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
       <c r="D16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="47"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="48"/>
       <c r="C17" s="48"/>
       <c r="D17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="47"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48">
         <v>1.4</v>
@@ -4780,84 +4771,84 @@
       <c r="D18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="45" t="s">
+      <c r="E18" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="45"/>
+      <c r="F18" s="51"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="47"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="47"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48"/>
       <c r="D20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="47"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="48"/>
       <c r="C21" s="48"/>
       <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="47"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="48"/>
       <c r="C22" s="48"/>
       <c r="D22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="47"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48"/>
       <c r="D23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="47"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48"/>
       <c r="D24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="47"/>
+      <c r="A25" s="53"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48"/>
       <c r="D25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="47"/>
-      <c r="B26" s="49">
+      <c r="A26" s="53"/>
+      <c r="B26" s="54">
         <v>2</v>
       </c>
       <c r="C26" s="48">
@@ -4866,359 +4857,359 @@
       <c r="D26" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="45"/>
+      <c r="F26" s="51"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="47"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="54"/>
       <c r="C27" s="48"/>
       <c r="D27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="45"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="51"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="47"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="48"/>
       <c r="D28" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="45"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="47"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="51">
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="50">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="45" t="s">
+      <c r="E29" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="45"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="47"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="51"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="50"/>
       <c r="D30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="47"/>
-      <c r="B31" s="49"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="54"/>
       <c r="C31" s="48">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="45" t="s">
+      <c r="E31" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45" t="s">
+      <c r="F31" s="51"/>
+      <c r="G31" s="51" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="47"/>
-      <c r="B32" s="49"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="54"/>
       <c r="C32" s="48"/>
       <c r="D32" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="47"/>
-      <c r="B33" s="49"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="54"/>
       <c r="C33" s="48"/>
       <c r="D33" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="47"/>
-      <c r="B34" s="49"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="54"/>
       <c r="C34" s="48"/>
       <c r="D34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="47"/>
-      <c r="B35" s="49"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="54"/>
       <c r="C35" s="48"/>
       <c r="D35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="47"/>
-      <c r="B36" s="49"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="54"/>
       <c r="C36" s="48"/>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="47"/>
-      <c r="B37" s="49"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="48"/>
       <c r="D37" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="47"/>
-      <c r="B38" s="49"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="54"/>
       <c r="C38" s="48">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="45"/>
+      <c r="F38" s="51"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="47"/>
-      <c r="B39" s="49"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="54"/>
       <c r="C39" s="48"/>
       <c r="D39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="47"/>
-      <c r="B40" s="49"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="54"/>
       <c r="C40" s="48"/>
       <c r="D40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="47"/>
-      <c r="B41" s="49"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="54"/>
       <c r="C41" s="48"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="47"/>
-      <c r="B42" s="49"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="54"/>
       <c r="C42" s="48"/>
       <c r="D42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="47"/>
-      <c r="B43" s="49"/>
+      <c r="A43" s="53"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="48"/>
       <c r="D43" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="47"/>
-      <c r="B44" s="49"/>
+      <c r="A44" s="53"/>
+      <c r="B44" s="54"/>
       <c r="C44" s="48"/>
       <c r="D44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="47"/>
-      <c r="B45" s="49"/>
+      <c r="A45" s="53"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="48"/>
       <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="47"/>
-      <c r="B46" s="49"/>
+      <c r="A46" s="53"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="48">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="46" t="s">
+      <c r="E46" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="45"/>
+      <c r="F46" s="51"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="47"/>
-      <c r="B47" s="49"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="48"/>
       <c r="D47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="46"/>
-      <c r="F47" s="45"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="51"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="47"/>
-      <c r="B48" s="49"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="54"/>
       <c r="C48" s="48"/>
       <c r="D48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="46"/>
-      <c r="F48" s="45"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="51"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="47"/>
-      <c r="B49" s="49"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="54"/>
       <c r="C49" s="48"/>
       <c r="D49" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E49" s="46"/>
-      <c r="F49" s="45"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="51"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="47"/>
-      <c r="B50" s="49"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="54"/>
       <c r="C50" s="48">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="45" t="s">
+      <c r="E50" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="45"/>
+      <c r="F50" s="51"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="47"/>
-      <c r="B51" s="49"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="54"/>
       <c r="C51" s="48"/>
       <c r="D51" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="47"/>
-      <c r="B52" s="49"/>
+      <c r="A52" s="53"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="48"/>
       <c r="D52" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="47"/>
-      <c r="B53" s="49"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="48"/>
       <c r="D53" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="47"/>
-      <c r="B54" s="49"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="54"/>
       <c r="C54" s="48"/>
       <c r="D54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="45"/>
-      <c r="F54" s="45"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="51"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="47"/>
-      <c r="B55" s="49"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="54"/>
       <c r="C55" s="48"/>
       <c r="D55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="47"/>
-      <c r="B56" s="49"/>
+      <c r="A56" s="53"/>
+      <c r="B56" s="54"/>
       <c r="C56" s="48"/>
       <c r="D56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="47"/>
-      <c r="B57" s="49"/>
+      <c r="A57" s="53"/>
+      <c r="B57" s="54"/>
       <c r="C57" s="48"/>
       <c r="D57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="47"/>
-      <c r="B58" s="49"/>
+      <c r="A58" s="53"/>
+      <c r="B58" s="54"/>
       <c r="C58" s="48"/>
       <c r="D58" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="51"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
@@ -5907,7 +5898,7 @@
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
       <c r="B142" s="48"/>
-      <c r="C142" s="52">
+      <c r="C142" s="49">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5917,7 +5908,7 @@
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
       <c r="B143" s="48"/>
-      <c r="C143" s="52"/>
+      <c r="C143" s="49"/>
       <c r="D143" s="7" t="s">
         <v>170</v>
       </c>
@@ -5925,7 +5916,7 @@
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
       <c r="B144" s="48"/>
-      <c r="C144" s="52"/>
+      <c r="C144" s="49"/>
       <c r="D144" s="7" t="s">
         <v>171</v>
       </c>
@@ -5933,7 +5924,7 @@
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
       <c r="B145" s="48"/>
-      <c r="C145" s="52"/>
+      <c r="C145" s="49"/>
       <c r="D145" s="7" t="s">
         <v>172</v>
       </c>
@@ -5941,7 +5932,7 @@
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
       <c r="B146" s="48"/>
-      <c r="C146" s="52"/>
+      <c r="C146" s="49"/>
       <c r="D146" s="7" t="s">
         <v>173</v>
       </c>
@@ -5949,7 +5940,7 @@
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
       <c r="B147" s="48"/>
-      <c r="C147" s="52"/>
+      <c r="C147" s="49"/>
       <c r="D147" s="7" t="s">
         <v>174</v>
       </c>
@@ -5957,7 +5948,7 @@
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
       <c r="B148" s="48"/>
-      <c r="C148" s="52"/>
+      <c r="C148" s="49"/>
       <c r="D148" s="7" t="s">
         <v>175</v>
       </c>
@@ -5965,7 +5956,7 @@
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
       <c r="B149" s="48"/>
-      <c r="C149" s="52"/>
+      <c r="C149" s="49"/>
       <c r="D149" s="7" t="s">
         <v>176</v>
       </c>
@@ -5973,7 +5964,7 @@
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
       <c r="B150" s="48"/>
-      <c r="C150" s="52"/>
+      <c r="C150" s="49"/>
       <c r="D150" s="7" t="s">
         <v>177</v>
       </c>
@@ -5981,7 +5972,7 @@
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
       <c r="B151" s="48"/>
-      <c r="C151" s="52"/>
+      <c r="C151" s="49"/>
       <c r="D151" s="7" t="s">
         <v>178</v>
       </c>
@@ -5989,7 +5980,7 @@
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
       <c r="B152" s="48"/>
-      <c r="C152" s="52"/>
+      <c r="C152" s="49"/>
       <c r="D152" s="7" t="s">
         <v>179</v>
       </c>
@@ -5997,7 +5988,7 @@
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
       <c r="B153" s="48"/>
-      <c r="C153" s="52"/>
+      <c r="C153" s="49"/>
       <c r="D153" s="7" t="s">
         <v>180</v>
       </c>
@@ -6005,7 +5996,7 @@
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
       <c r="B154" s="48"/>
-      <c r="C154" s="52"/>
+      <c r="C154" s="49"/>
       <c r="D154" s="7" t="s">
         <v>181</v>
       </c>
@@ -6013,7 +6004,7 @@
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
       <c r="B155" s="48"/>
-      <c r="C155" s="52"/>
+      <c r="C155" s="49"/>
       <c r="D155" s="7" t="s">
         <v>182</v>
       </c>
@@ -6021,7 +6012,7 @@
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
       <c r="B156" s="48"/>
-      <c r="C156" s="52"/>
+      <c r="C156" s="49"/>
       <c r="D156" s="7" t="s">
         <v>58</v>
       </c>
@@ -6237,8 +6228,43 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J181"/>
+  <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6255,41 +6281,6 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6298,32 +6289,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1">
       <c r="A2" s="32" t="s">
@@ -6361,11 +6352,11 @@
       </c>
       <c r="L2" s="40"/>
     </row>
-    <row r="3" spans="1:12" ht="135">
-      <c r="A3" s="53">
+    <row r="3" spans="1:12" ht="129.6">
+      <c r="A3" s="44">
         <v>1</v>
       </c>
-      <c r="B3" s="53">
+      <c r="B3" s="44">
         <v>1</v>
       </c>
       <c r="C3" s="15">
@@ -6388,9 +6379,9 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="60">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
+    <row r="4" spans="1:12" ht="57.6">
+      <c r="A4" s="44"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="15">
         <v>1.2</v>
       </c>
@@ -6408,12 +6399,12 @@
         <v>250</v>
       </c>
       <c r="H4" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="45">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
       <c r="C5" s="15">
         <v>1.3</v>
       </c>
@@ -6434,9 +6425,9 @@
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="120">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
+    <row r="6" spans="1:12" ht="115.2">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="36">
         <v>1.4</v>
       </c>
@@ -6454,14 +6445,14 @@
         <v>253</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
     </row>
-    <row r="7" spans="1:12" ht="90">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53">
+    <row r="7" spans="1:12" ht="72">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44">
         <v>2</v>
       </c>
       <c r="C7" s="15">
@@ -6484,9 +6475,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="60">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
+    <row r="8" spans="1:12" ht="57.6">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="15">
         <v>2.2000000000000002</v>
       </c>
@@ -6507,9 +6498,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="105">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
+    <row r="9" spans="1:12" ht="100.8">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
       <c r="C9" s="15">
         <v>2.2999999999999998</v>
       </c>
@@ -6530,9 +6521,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="120">
-      <c r="A10" s="53"/>
-      <c r="B10" s="53"/>
+    <row r="10" spans="1:12" ht="115.2">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
       <c r="C10" s="15">
         <v>2.4</v>
       </c>
@@ -6553,9 +6544,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="120">
-      <c r="A11" s="53"/>
-      <c r="B11" s="53"/>
+    <row r="11" spans="1:12" ht="100.8">
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="15">
         <v>2.5</v>
       </c>
@@ -6576,9 +6567,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="120">
-      <c r="A12" s="53"/>
-      <c r="B12" s="53"/>
+    <row r="12" spans="1:12" ht="115.2">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="15">
         <v>2.6</v>
       </c>
@@ -6599,9 +6590,9 @@
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="165">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
+    <row r="13" spans="1:12" ht="158.4">
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="36">
         <v>2.7</v>
       </c>
@@ -6624,7 +6615,7 @@
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
     </row>
-    <row r="14" spans="1:12" ht="165">
+    <row r="14" spans="1:12" ht="144">
       <c r="C14" s="41">
         <v>2.8</v>
       </c>
@@ -6664,11 +6655,11 @@
       <c r="I15" s="29"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:12" ht="90">
-      <c r="A16" s="54">
+    <row r="16" spans="1:12" ht="86.4">
+      <c r="A16" s="45">
         <v>2</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="45">
         <v>3</v>
       </c>
       <c r="C16" s="15">
@@ -6678,9 +6669,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="180">
-      <c r="A17" s="53"/>
-      <c r="B17" s="53"/>
+    <row r="17" spans="1:4" ht="172.8">
+      <c r="A17" s="44"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="15">
         <v>3.2</v>
       </c>
@@ -6688,9 +6679,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="165">
-      <c r="A18" s="53"/>
-      <c r="B18" s="53"/>
+    <row r="18" spans="1:4" ht="158.4">
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
       <c r="C18" s="15">
         <v>3.3</v>
       </c>
@@ -6698,9 +6689,9 @@
         <v>238</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="195">
-      <c r="A19" s="53"/>
-      <c r="B19" s="53"/>
+    <row r="19" spans="1:4" ht="187.2">
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
       <c r="C19" s="15">
         <v>3.4</v>
       </c>
@@ -6708,9 +6699,9 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="135">
-      <c r="A20" s="53"/>
-      <c r="B20" s="53"/>
+    <row r="20" spans="1:4" ht="129.6">
+      <c r="A20" s="44"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="15">
         <v>3.5</v>
       </c>
@@ -6718,9 +6709,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="90">
-      <c r="A21" s="53"/>
-      <c r="B21" s="53"/>
+    <row r="21" spans="1:4" ht="86.4">
+      <c r="A21" s="44"/>
+      <c r="B21" s="44"/>
       <c r="C21" s="15">
         <v>3.6</v>
       </c>
@@ -6728,9 +6719,9 @@
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="165">
-      <c r="A22" s="53"/>
-      <c r="B22" s="53"/>
+    <row r="22" spans="1:4" ht="158.4">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
       <c r="C22" s="15">
         <v>3.7</v>
       </c>
@@ -6738,9 +6729,9 @@
         <v>242</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="150">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
+    <row r="23" spans="1:4" ht="144">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="15">
         <v>3.8</v>
       </c>
@@ -6748,9 +6739,9 @@
         <v>243</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="75">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
+    <row r="24" spans="1:4" ht="72">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
       <c r="C24" s="15">
         <v>3.9</v>
       </c>
@@ -6758,9 +6749,9 @@
         <v>244</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="225">
-      <c r="A25" s="53"/>
-      <c r="B25" s="53"/>
+    <row r="25" spans="1:4" ht="216">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
       <c r="C25" s="35">
         <v>3.1</v>
       </c>
@@ -6768,9 +6759,9 @@
         <v>245</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="60">
-      <c r="A26" s="53"/>
-      <c r="B26" s="53">
+    <row r="26" spans="1:4" ht="57.6">
+      <c r="A26" s="44"/>
+      <c r="B26" s="44">
         <v>4</v>
       </c>
       <c r="C26" s="15">
@@ -6780,9 +6771,9 @@
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="105">
-      <c r="A27" s="53"/>
-      <c r="B27" s="53"/>
+    <row r="27" spans="1:4" ht="100.8">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
       <c r="C27" s="15">
         <v>4.2</v>
       </c>
@@ -6790,9 +6781,9 @@
         <v>247</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="90">
-      <c r="A28" s="53"/>
-      <c r="B28" s="53"/>
+    <row r="28" spans="1:4" ht="86.4">
+      <c r="A28" s="44"/>
+      <c r="B28" s="44"/>
       <c r="C28" s="15">
         <v>4.3</v>
       </c>
@@ -6800,9 +6791,9 @@
         <v>248</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="120">
-      <c r="A29" s="53"/>
-      <c r="B29" s="53"/>
+    <row r="29" spans="1:4" ht="115.2">
+      <c r="A29" s="44"/>
+      <c r="B29" s="44"/>
       <c r="C29" s="15">
         <v>4.4000000000000004</v>
       </c>
@@ -6827,17 +6818,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="60">
+    <row r="1" spans="1:5" ht="57.6">
       <c r="A1" s="22" t="s">
         <v>216</v>
       </c>
@@ -6939,14 +6930,14 @@
       </c>
       <c r="C6" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E6)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D6" s="12">
         <f>('Updated Sprint'!F15)*(1-(A6-1)/8)</f>
         <v>22.5</v>
       </c>
       <c r="E6" s="28">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6958,7 +6949,7 @@
       </c>
       <c r="C7" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E7)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D7" s="12">
         <f>('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
@@ -6977,7 +6968,7 @@
       </c>
       <c r="C8" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E8)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" s="12">
         <f>('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
@@ -6996,7 +6987,7 @@
       </c>
       <c r="C9" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E9)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D9" s="12">
         <f>('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
@@ -7015,7 +7006,7 @@
       </c>
       <c r="C10" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E10)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D10" s="12">
         <f>('Updated Sprint'!F15)*(1-(A10-1)/8)</f>
@@ -7036,9 +7027,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="55" t="s">

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3D368C-9D12-4C77-ABFE-CEB94E6E9F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2EC3B1-8DCA-42F6-9687-7C88CD01700A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -733,7 +733,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="268">
   <si>
     <t>Work Item</t>
   </si>
@@ -2090,9 +2090,6 @@
   </si>
   <si>
     <t>Azad</t>
-  </si>
-  <si>
-    <t>Rajanya</t>
   </si>
   <si>
     <t>Everyone</t>
@@ -2898,15 +2895,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2914,7 +2902,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3056,7 +3053,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>44</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>44</c:v>
@@ -3071,16 +3068,16 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>36</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>36</c:v>
+                  <c:v>31</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>36</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3281,13 +3278,13 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4591,632 +4588,632 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="53">
+      <c r="A3" s="50">
         <v>1</v>
       </c>
-      <c r="B3" s="48">
+      <c r="B3" s="51">
         <v>1</v>
       </c>
-      <c r="C3" s="48">
+      <c r="C3" s="51">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="51" cm="1">
+      <c r="F3" s="48" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="53"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
       <c r="D4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="53"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
+      <c r="A5" s="50"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="53"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
+      <c r="A6" s="50"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="53"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
       <c r="D7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="53"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
       <c r="D8" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="53"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
+      <c r="A9" s="50"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="53"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="48"/>
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="53"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="53"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51">
         <v>1.2</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="51" cm="1">
+      <c r="F12" s="48" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="53"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
+      <c r="A13" s="50"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="53"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
       <c r="D14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="53"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48">
+      <c r="A15" s="50"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51">
         <v>1.3</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="51" t="s">
+      <c r="E15" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="51"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="53"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="53"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
+      <c r="A17" s="50"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="53"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48">
+      <c r="A18" s="50"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51">
         <v>1.4</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="51"/>
+      <c r="F18" s="48"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="53"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
+      <c r="A19" s="50"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
       <c r="D19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="53"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
+      <c r="A20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
       <c r="D20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="53"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
+      <c r="A21" s="50"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
       <c r="D21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="53"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
+      <c r="A22" s="50"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="53"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
+      <c r="A23" s="50"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="53"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
+      <c r="A24" s="50"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
       <c r="D24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="53"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
       <c r="D25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="53"/>
-      <c r="B26" s="54">
+      <c r="A26" s="50"/>
+      <c r="B26" s="52">
         <v>2</v>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="51">
         <v>2.1</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F26" s="51"/>
+      <c r="F26" s="48"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="48"/>
+      <c r="A27" s="50"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="51"/>
       <c r="D27" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="51"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="48"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="53"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="48"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="51"/>
       <c r="D28" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="52"/>
-      <c r="F28" s="51"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="48"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="53"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="50">
+      <c r="A29" s="50"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="53">
         <v>2.2000000000000002</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="51" t="s">
+      <c r="E29" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="F29" s="51"/>
+      <c r="F29" s="48"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="53"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="50"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="53"/>
       <c r="D30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="53"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="48">
+      <c r="A31" s="50"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="51">
         <v>2.2999999999999998</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51" t="s">
+      <c r="F31" s="48"/>
+      <c r="G31" s="48" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="53"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="48"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="51"/>
       <c r="D32" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="53"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="48"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="51"/>
       <c r="D33" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E33" s="51"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="53"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="48"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="51"/>
       <c r="D34" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="48"/>
+      <c r="A35" s="50"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="51"/>
       <c r="D35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="53"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="48"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="51"/>
       <c r="D36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="53"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="48"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="53"/>
-      <c r="B38" s="54"/>
-      <c r="C38" s="48">
+      <c r="A38" s="50"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="51">
         <v>2.4</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="51" t="s">
+      <c r="E38" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F38" s="51"/>
+      <c r="F38" s="48"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="53"/>
-      <c r="B39" s="54"/>
-      <c r="C39" s="48"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="51"/>
       <c r="D39" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="53"/>
-      <c r="B40" s="54"/>
-      <c r="C40" s="48"/>
+      <c r="A40" s="50"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="51"/>
       <c r="D40" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="53"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="48"/>
+      <c r="A41" s="50"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="51"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="53"/>
-      <c r="B42" s="54"/>
-      <c r="C42" s="48"/>
+      <c r="A42" s="50"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="51"/>
       <c r="D42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="53"/>
-      <c r="B43" s="54"/>
-      <c r="C43" s="48"/>
+      <c r="A43" s="50"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="51"/>
       <c r="D43" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="53"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="48"/>
+      <c r="A44" s="50"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="51"/>
       <c r="D44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="53"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="48"/>
+      <c r="A45" s="50"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="51"/>
       <c r="D45" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="53"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="48">
+      <c r="A46" s="50"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="51">
         <v>2.5</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E46" s="52" t="s">
+      <c r="E46" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="51"/>
+      <c r="F46" s="48"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="53"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="48"/>
+      <c r="A47" s="50"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="51"/>
       <c r="D47" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="52"/>
-      <c r="F47" s="51"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="48"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="53"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="48"/>
+      <c r="A48" s="50"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="51"/>
       <c r="D48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="52"/>
-      <c r="F48" s="51"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="48"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="53"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="48"/>
+      <c r="A49" s="50"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="51"/>
       <c r="D49" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E49" s="52"/>
-      <c r="F49" s="51"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="48"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="53"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="48">
+      <c r="A50" s="50"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="51">
         <v>2.7</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="51" t="s">
+      <c r="E50" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="F50" s="51"/>
+      <c r="F50" s="48"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="53"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="48"/>
+      <c r="A51" s="50"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="51"/>
       <c r="D51" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="53"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="48"/>
+      <c r="A52" s="50"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="51"/>
       <c r="D52" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="53"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="48"/>
+      <c r="A53" s="50"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="51"/>
       <c r="D53" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="53"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="48"/>
+      <c r="A54" s="50"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="51"/>
       <c r="D54" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="53"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="48"/>
+      <c r="A55" s="50"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="51"/>
       <c r="D55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="53"/>
-      <c r="B56" s="54"/>
-      <c r="C56" s="48"/>
+      <c r="A56" s="50"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="51"/>
       <c r="D56" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E56" s="51"/>
-      <c r="F56" s="51"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="53"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="48"/>
+      <c r="A57" s="50"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="51"/>
       <c r="D57" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="53"/>
-      <c r="B58" s="54"/>
-      <c r="C58" s="48"/>
+      <c r="A58" s="50"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="51"/>
       <c r="D58" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="51"/>
-      <c r="F58" s="51"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="48">
+      <c r="B59" s="51">
         <v>3</v>
       </c>
-      <c r="C59" s="48">
+      <c r="C59" s="51">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -5225,48 +5222,48 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="48"/>
-      <c r="C60" s="48"/>
+      <c r="B60" s="51"/>
+      <c r="C60" s="51"/>
       <c r="D60" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="48"/>
-      <c r="C61" s="48"/>
+      <c r="B61" s="51"/>
+      <c r="C61" s="51"/>
       <c r="D61" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="48"/>
-      <c r="C62" s="48"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="51"/>
       <c r="D62" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="48"/>
-      <c r="C63" s="48"/>
+      <c r="B63" s="51"/>
+      <c r="C63" s="51"/>
       <c r="D63" s="7" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="48"/>
-      <c r="C64" s="48"/>
+      <c r="B64" s="51"/>
+      <c r="C64" s="51"/>
       <c r="D64" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="48"/>
-      <c r="C65" s="48">
+      <c r="B65" s="51"/>
+      <c r="C65" s="51">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -5275,96 +5272,96 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="48"/>
-      <c r="C66" s="48"/>
+      <c r="B66" s="51"/>
+      <c r="C66" s="51"/>
       <c r="D66" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="48"/>
-      <c r="C67" s="48"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="51"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
+      <c r="B68" s="51"/>
+      <c r="C68" s="51"/>
       <c r="D68" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="51"/>
       <c r="D69" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
       <c r="D70" s="7" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
       <c r="D71" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="51"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="48"/>
-      <c r="C73" s="48"/>
+      <c r="B73" s="51"/>
+      <c r="C73" s="51"/>
       <c r="D73" s="7" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="51"/>
       <c r="D74" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="51"/>
       <c r="D75" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
       <c r="D76" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="48"/>
-      <c r="C77" s="48">
+      <c r="B77" s="51"/>
+      <c r="C77" s="51">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -5373,88 +5370,88 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="48"/>
-      <c r="C78" s="48"/>
+      <c r="B78" s="51"/>
+      <c r="C78" s="51"/>
       <c r="D78" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
+      <c r="B79" s="51"/>
+      <c r="C79" s="51"/>
       <c r="D79" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
+      <c r="B80" s="51"/>
+      <c r="C80" s="51"/>
       <c r="D80" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="48"/>
-      <c r="C81" s="48"/>
+      <c r="B81" s="51"/>
+      <c r="C81" s="51"/>
       <c r="D81" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="48"/>
-      <c r="C82" s="48"/>
+      <c r="B82" s="51"/>
+      <c r="C82" s="51"/>
       <c r="D82" s="7" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="48"/>
-      <c r="C83" s="48"/>
+      <c r="B83" s="51"/>
+      <c r="C83" s="51"/>
       <c r="D83" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="48"/>
-      <c r="C84" s="48"/>
+      <c r="B84" s="51"/>
+      <c r="C84" s="51"/>
       <c r="D84" s="7" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="48"/>
-      <c r="C85" s="48"/>
+      <c r="B85" s="51"/>
+      <c r="C85" s="51"/>
       <c r="D85" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
+      <c r="B86" s="51"/>
+      <c r="C86" s="51"/>
       <c r="D86" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
       <c r="D87" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48">
+      <c r="B88" s="51"/>
+      <c r="C88" s="51">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
@@ -5463,104 +5460,104 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="48"/>
-      <c r="C89" s="48"/>
+      <c r="B89" s="51"/>
+      <c r="C89" s="51"/>
       <c r="D89" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="48"/>
-      <c r="C90" s="48"/>
+      <c r="B90" s="51"/>
+      <c r="C90" s="51"/>
       <c r="D90" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="48"/>
-      <c r="C91" s="48"/>
+      <c r="B91" s="51"/>
+      <c r="C91" s="51"/>
       <c r="D91" s="7" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="48"/>
-      <c r="C92" s="48"/>
+      <c r="B92" s="51"/>
+      <c r="C92" s="51"/>
       <c r="D92" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="48"/>
-      <c r="C93" s="48"/>
+      <c r="B93" s="51"/>
+      <c r="C93" s="51"/>
       <c r="D93" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="48"/>
-      <c r="C94" s="48"/>
+      <c r="B94" s="51"/>
+      <c r="C94" s="51"/>
       <c r="D94" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="48"/>
-      <c r="C95" s="48"/>
+      <c r="B95" s="51"/>
+      <c r="C95" s="51"/>
       <c r="D95" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="48"/>
-      <c r="C96" s="48"/>
+      <c r="B96" s="51"/>
+      <c r="C96" s="51"/>
       <c r="D96" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="48"/>
-      <c r="C97" s="48"/>
+      <c r="B97" s="51"/>
+      <c r="C97" s="51"/>
       <c r="D97" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="48"/>
-      <c r="C98" s="48"/>
+      <c r="B98" s="51"/>
+      <c r="C98" s="51"/>
       <c r="D98" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="48"/>
-      <c r="C99" s="48"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
       <c r="D99" s="7" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="48"/>
-      <c r="C100" s="48"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
       <c r="D100" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="48"/>
-      <c r="C101" s="48">
+      <c r="B101" s="51"/>
+      <c r="C101" s="51">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
@@ -5569,72 +5566,72 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="48"/>
-      <c r="C102" s="48"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="51"/>
       <c r="D102" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="48"/>
-      <c r="C103" s="48"/>
+      <c r="B103" s="51"/>
+      <c r="C103" s="51"/>
       <c r="D103" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="48"/>
-      <c r="C104" s="48"/>
+      <c r="B104" s="51"/>
+      <c r="C104" s="51"/>
       <c r="D104" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="48"/>
-      <c r="C105" s="48"/>
+      <c r="B105" s="51"/>
+      <c r="C105" s="51"/>
       <c r="D105" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="48"/>
-      <c r="C106" s="48"/>
+      <c r="B106" s="51"/>
+      <c r="C106" s="51"/>
       <c r="D106" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="48"/>
-      <c r="C107" s="48"/>
+      <c r="B107" s="51"/>
+      <c r="C107" s="51"/>
       <c r="D107" s="7" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="48"/>
-      <c r="C108" s="48"/>
+      <c r="B108" s="51"/>
+      <c r="C108" s="51"/>
       <c r="D108" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="48"/>
-      <c r="C109" s="48"/>
+      <c r="B109" s="51"/>
+      <c r="C109" s="51"/>
       <c r="D109" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="48"/>
-      <c r="C110" s="48">
+      <c r="B110" s="51"/>
+      <c r="C110" s="51">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -5643,48 +5640,48 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="48"/>
-      <c r="C111" s="48"/>
+      <c r="B111" s="51"/>
+      <c r="C111" s="51"/>
       <c r="D111" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="48"/>
-      <c r="C112" s="48"/>
+      <c r="B112" s="51"/>
+      <c r="C112" s="51"/>
       <c r="D112" s="7" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="48"/>
-      <c r="C113" s="48"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="51"/>
       <c r="D113" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="48"/>
-      <c r="C114" s="48"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="51"/>
       <c r="D114" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="48"/>
-      <c r="C115" s="48"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="51"/>
       <c r="D115" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="48"/>
-      <c r="C116" s="48">
+      <c r="B116" s="51"/>
+      <c r="C116" s="51">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -5693,88 +5690,88 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="48"/>
-      <c r="C117" s="48"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="51"/>
       <c r="D117" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="48"/>
-      <c r="C118" s="48"/>
+      <c r="B118" s="51"/>
+      <c r="C118" s="51"/>
       <c r="D118" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="48"/>
-      <c r="C119" s="48"/>
+      <c r="B119" s="51"/>
+      <c r="C119" s="51"/>
       <c r="D119" s="7" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="48"/>
-      <c r="C120" s="48"/>
+      <c r="B120" s="51"/>
+      <c r="C120" s="51"/>
       <c r="D120" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="48"/>
-      <c r="C121" s="48"/>
+      <c r="B121" s="51"/>
+      <c r="C121" s="51"/>
       <c r="D121" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="48"/>
-      <c r="C122" s="48"/>
+      <c r="B122" s="51"/>
+      <c r="C122" s="51"/>
       <c r="D122" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="48"/>
-      <c r="C123" s="48"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="51"/>
       <c r="D123" s="7" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="48"/>
-      <c r="C124" s="48"/>
+      <c r="B124" s="51"/>
+      <c r="C124" s="51"/>
       <c r="D124" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="48"/>
-      <c r="C125" s="48"/>
+      <c r="B125" s="51"/>
+      <c r="C125" s="51"/>
       <c r="D125" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="48"/>
-      <c r="C126" s="48"/>
+      <c r="B126" s="51"/>
+      <c r="C126" s="51"/>
       <c r="D126" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="48"/>
-      <c r="C127" s="48">
+      <c r="B127" s="51"/>
+      <c r="C127" s="51">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5783,80 +5780,80 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="48"/>
-      <c r="C128" s="48"/>
+      <c r="B128" s="51"/>
+      <c r="C128" s="51"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="48"/>
-      <c r="C129" s="48"/>
+      <c r="B129" s="51"/>
+      <c r="C129" s="51"/>
       <c r="D129" s="7" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="48"/>
-      <c r="C130" s="48"/>
+      <c r="B130" s="51"/>
+      <c r="C130" s="51"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="48"/>
-      <c r="C131" s="48"/>
+      <c r="B131" s="51"/>
+      <c r="C131" s="51"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="48"/>
-      <c r="C132" s="48"/>
+      <c r="B132" s="51"/>
+      <c r="C132" s="51"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="48"/>
-      <c r="C133" s="48"/>
+      <c r="B133" s="51"/>
+      <c r="C133" s="51"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="48"/>
-      <c r="C134" s="48"/>
+      <c r="B134" s="51"/>
+      <c r="C134" s="51"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="48"/>
-      <c r="C135" s="48"/>
+      <c r="B135" s="51"/>
+      <c r="C135" s="51"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="48"/>
-      <c r="C136" s="48"/>
+      <c r="B136" s="51"/>
+      <c r="C136" s="51"/>
       <c r="D136" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="48"/>
-      <c r="C137" s="48">
+      <c r="B137" s="51"/>
+      <c r="C137" s="51">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -5865,40 +5862,40 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="48"/>
-      <c r="C138" s="48"/>
+      <c r="B138" s="51"/>
+      <c r="C138" s="51"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="48"/>
-      <c r="C139" s="48"/>
+      <c r="B139" s="51"/>
+      <c r="C139" s="51"/>
       <c r="D139" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="48"/>
-      <c r="C140" s="48"/>
+      <c r="B140" s="51"/>
+      <c r="C140" s="51"/>
       <c r="D140" s="7" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="48"/>
-      <c r="C141" s="48"/>
+      <c r="B141" s="51"/>
+      <c r="C141" s="51"/>
       <c r="D141" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="48"/>
-      <c r="C142" s="49">
+      <c r="B142" s="51"/>
+      <c r="C142" s="54">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -5907,122 +5904,122 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="48"/>
-      <c r="C143" s="49"/>
+      <c r="B143" s="51"/>
+      <c r="C143" s="54"/>
       <c r="D143" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="48"/>
-      <c r="C144" s="49"/>
+      <c r="B144" s="51"/>
+      <c r="C144" s="54"/>
       <c r="D144" s="7" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="48"/>
-      <c r="C145" s="49"/>
+      <c r="B145" s="51"/>
+      <c r="C145" s="54"/>
       <c r="D145" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="48"/>
-      <c r="C146" s="49"/>
+      <c r="B146" s="51"/>
+      <c r="C146" s="54"/>
       <c r="D146" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="48"/>
-      <c r="C147" s="49"/>
+      <c r="B147" s="51"/>
+      <c r="C147" s="54"/>
       <c r="D147" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="48"/>
-      <c r="C148" s="49"/>
+      <c r="B148" s="51"/>
+      <c r="C148" s="54"/>
       <c r="D148" s="7" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="48"/>
-      <c r="C149" s="49"/>
+      <c r="B149" s="51"/>
+      <c r="C149" s="54"/>
       <c r="D149" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="48"/>
-      <c r="C150" s="49"/>
+      <c r="B150" s="51"/>
+      <c r="C150" s="54"/>
       <c r="D150" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="48"/>
-      <c r="C151" s="49"/>
+      <c r="B151" s="51"/>
+      <c r="C151" s="54"/>
       <c r="D151" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="48"/>
-      <c r="C152" s="49"/>
+      <c r="B152" s="51"/>
+      <c r="C152" s="54"/>
       <c r="D152" s="7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="48"/>
-      <c r="C153" s="49"/>
+      <c r="B153" s="51"/>
+      <c r="C153" s="54"/>
       <c r="D153" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="48"/>
-      <c r="C154" s="49"/>
+      <c r="B154" s="51"/>
+      <c r="C154" s="54"/>
       <c r="D154" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="48"/>
-      <c r="C155" s="49"/>
+      <c r="B155" s="51"/>
+      <c r="C155" s="54"/>
       <c r="D155" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="48"/>
-      <c r="C156" s="49"/>
+      <c r="B156" s="51"/>
+      <c r="C156" s="54"/>
       <c r="D156" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="48">
+      <c r="B157" s="51">
         <v>4</v>
       </c>
-      <c r="C157" s="48">
+      <c r="C157" s="51">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -6031,32 +6028,32 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="48"/>
-      <c r="C158" s="48"/>
+      <c r="B158" s="51"/>
+      <c r="C158" s="51"/>
       <c r="D158" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="48"/>
-      <c r="C159" s="48"/>
+      <c r="B159" s="51"/>
+      <c r="C159" s="51"/>
       <c r="D159" s="7" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="48"/>
-      <c r="C160" s="48"/>
+      <c r="B160" s="51"/>
+      <c r="C160" s="51"/>
       <c r="D160" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="48"/>
-      <c r="C161" s="48">
+      <c r="B161" s="51"/>
+      <c r="C161" s="51">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -6065,56 +6062,56 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="48"/>
-      <c r="C162" s="48"/>
+      <c r="B162" s="51"/>
+      <c r="C162" s="51"/>
       <c r="D162" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="48"/>
-      <c r="C163" s="48"/>
+      <c r="B163" s="51"/>
+      <c r="C163" s="51"/>
       <c r="D163" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="48"/>
-      <c r="C164" s="48"/>
+      <c r="B164" s="51"/>
+      <c r="C164" s="51"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="48"/>
-      <c r="C165" s="48"/>
+      <c r="B165" s="51"/>
+      <c r="C165" s="51"/>
       <c r="D165" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="48"/>
-      <c r="C166" s="48"/>
+      <c r="B166" s="51"/>
+      <c r="C166" s="51"/>
       <c r="D166" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="48"/>
-      <c r="C167" s="48"/>
+      <c r="B167" s="51"/>
+      <c r="C167" s="51"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="48"/>
-      <c r="C168" s="48">
+      <c r="B168" s="51"/>
+      <c r="C168" s="51">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6123,48 +6120,48 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="48"/>
-      <c r="C169" s="48"/>
+      <c r="B169" s="51"/>
+      <c r="C169" s="51"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="48"/>
-      <c r="C170" s="48"/>
+      <c r="B170" s="51"/>
+      <c r="C170" s="51"/>
       <c r="D170" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="48"/>
-      <c r="C171" s="48"/>
+      <c r="B171" s="51"/>
+      <c r="C171" s="51"/>
       <c r="D171" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="48"/>
-      <c r="C172" s="48"/>
+      <c r="B172" s="51"/>
+      <c r="C172" s="51"/>
       <c r="D172" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="48"/>
-      <c r="C173" s="48"/>
+      <c r="B173" s="51"/>
+      <c r="C173" s="51"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="48"/>
-      <c r="C174" s="48">
+      <c r="B174" s="51"/>
+      <c r="C174" s="51">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -6173,56 +6170,56 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="48"/>
-      <c r="C175" s="48"/>
+      <c r="B175" s="51"/>
+      <c r="C175" s="51"/>
       <c r="D175" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="48"/>
-      <c r="C176" s="48"/>
+      <c r="B176" s="51"/>
+      <c r="C176" s="51"/>
       <c r="D176" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="48"/>
-      <c r="C177" s="48"/>
+      <c r="B177" s="51"/>
+      <c r="C177" s="51"/>
       <c r="D177" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="48"/>
-      <c r="C178" s="48"/>
+      <c r="B178" s="51"/>
+      <c r="C178" s="51"/>
       <c r="D178" s="7" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="48"/>
-      <c r="C179" s="48"/>
+      <c r="B179" s="51"/>
+      <c r="C179" s="51"/>
       <c r="D179" s="7" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="48"/>
-      <c r="C180" s="48"/>
+      <c r="B180" s="51"/>
+      <c r="C180" s="51"/>
       <c r="D180" s="7" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="48"/>
-      <c r="C181" s="48"/>
+      <c r="B181" s="51"/>
+      <c r="C181" s="51"/>
       <c r="D181" s="7" t="s">
         <v>59</v>
       </c>
@@ -6230,41 +6227,6 @@
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6281,6 +6243,41 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6348,7 +6345,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L2" s="40"/>
     </row>
@@ -6363,7 +6360,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -6376,7 +6373,7 @@
         <v>250</v>
       </c>
       <c r="H3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="57.6">
@@ -6386,7 +6383,7 @@
         <v>1.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -6399,7 +6396,7 @@
         <v>250</v>
       </c>
       <c r="H4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="43.2">
@@ -6422,7 +6419,7 @@
         <v>251</v>
       </c>
       <c r="H5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="115.2">
@@ -6442,10 +6439,10 @@
         <v>5</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
@@ -6459,7 +6456,7 @@
         <v>2.1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -6468,11 +6465,8 @@
         <f t="array" ref="F7">_xlfn.SWITCH(E7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="G7" t="s">
-        <v>252</v>
-      </c>
       <c r="H7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="57.6">
@@ -6482,7 +6476,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -6495,7 +6489,7 @@
         <v>252</v>
       </c>
       <c r="H8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="100.8">
@@ -6505,7 +6499,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -6518,7 +6512,7 @@
         <v>214</v>
       </c>
       <c r="H9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="115.2">
@@ -6528,7 +6522,7 @@
         <v>2.4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -6538,10 +6532,10 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="100.8">
@@ -6551,7 +6545,7 @@
         <v>2.5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -6560,11 +6554,8 @@
         <f t="array" ref="F11">_xlfn.SWITCH(E11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="G11" t="s">
-        <v>252</v>
-      </c>
       <c r="H11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="115.2">
@@ -6574,7 +6565,7 @@
         <v>2.6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -6584,10 +6575,10 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="158.4">
@@ -6607,10 +6598,10 @@
         <v>5</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
@@ -6620,7 +6611,7 @@
         <v>2.8</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E14" s="43" t="s">
         <v>20</v>
@@ -6630,10 +6621,10 @@
         <v>5</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
@@ -6853,8 +6844,7 @@
         <v>46265</v>
       </c>
       <c r="C2" s="27">
-        <f>('Updated Sprint'!F15)-SUM(E$2:E2)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="12">
         <f>('Updated Sprint'!F15)*(1-(A2-1)/8)</f>
@@ -6949,14 +6939,14 @@
       </c>
       <c r="C7" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E7)</f>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7" s="12">
         <f>('Updated Sprint'!F15)*(1-(A7-1)/8)</f>
         <v>16.875</v>
       </c>
       <c r="E7" s="28">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6968,7 +6958,7 @@
       </c>
       <c r="C8" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E8)</f>
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8" s="12">
         <f>('Updated Sprint'!F15)*(1-(A8-1)/8)</f>
@@ -6987,14 +6977,14 @@
       </c>
       <c r="C9" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E9)</f>
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D9" s="12">
         <f>('Updated Sprint'!F15)*(1-(A9-1)/8)</f>
         <v>5.625</v>
       </c>
       <c r="E9" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7006,7 +6996,7 @@
       </c>
       <c r="C10" s="27">
         <f>('Updated Sprint'!F15)-SUM(E$2:E10)</f>
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D10" s="12">
         <f>('Updated Sprint'!F15)*(1-(A10-1)/8)</f>

--- a/project_plan.xlsx
+++ b/project_plan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2EC3B1-8DCA-42F6-9687-7C88CD01700A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D96847B-E145-484C-AD64-020646FA1A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
+    <author>tc={148E080D-CE22-4CE0-8311-B67C30FEF121}</author>
   </authors>
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -55,6 +56,14 @@
 Comment:
     Should all skin concerns be listed when we are only addressing top n.</t>
         </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="1" shapeId="0" xr:uid="{148E080D-CE22-4CE0-8311-B67C30FEF121}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Get client verification</t>
       </text>
     </comment>
   </commentList>
@@ -733,7 +742,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="270">
   <si>
     <t>Work Item</t>
   </si>
@@ -994,53 +1003,6 @@
 4. A combination of any/all of the above three should be rejected
 4. A proper image should not be rejected</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Detected skin concerns should be from the series:
-SC0001-SC0019 , SC1001-SC1009 &amp;
-SC2001-SC2004.
-2. If no skin concern is detected(perfectly fit skin) then Skin analysis results should show the following message:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"Your skin looks perfect!"
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">3.If the image &amp; questionnaire contains one or multiple particular skin concerns then, all of those should be shown in the Skin analysis results: Primary Concerns.
-4.No other skins concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images and questionnaire.
-5. The total formulation must always weigh 100g total.
-6. The percentage of actives in formulation must be listed.
-7. The formulation explanation must correctly reflect the reason for choosing the actives and bases as per the LLM.
-8. The actives and base comprising the reccomended formulation must be compatible with each other.
-</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view my reccomendation page with the following fields:
-1. Hello "user_full_name"! 
-2. Skin analysis results : Primary Concerns :  those detected through the combination of skin concerns from both image and questionnaire.
-3.Skin analysis results: Skin Type: detected through questionnaire answers.
-4. Skin analysis results: Sensitivity Level: detected through questionnaire answers.
-5. Reccomended for you: Base :
-selected through questionnaire answers.
-6. Reccomended for you : Active Ingredients: those detected through selfie and questionnaire skin concerns.
-7. Reccomended for you: Why this formula: explained by LLM for selected actives detected through selfie and questionnaire skin concerns</t>
   </si>
   <si>
     <r>
@@ -1943,20 +1905,6 @@
 Submit questionnaire for LLM analysis</t>
   </si>
   <si>
-    <t>Define questionnaire-analysis LLM prompt
-Pass questionnaire JSON to LLM
-Define concern extraction rules
-Define skin-type extraction
-Define sensitivity extraction
-Define questionnaire-only concern handling
-Validate LLM response
-Handle malformed LLM response
-Handle LLM/API failure
-Store questionnaire detection result in session_skin_concern_detection
-Store LLM-generated explanations
-Store raw detection JSON</t>
-  </si>
-  <si>
     <t>Retrieve image-based detection results
 Retrieve questionnaire-based detection results
 Match results using skin_concern_id
@@ -1968,32 +1916,6 @@
 Handle concerns detected by both
 Handle no detected concerns
 Validate final combined concern set</t>
-  </si>
-  <si>
-    <t>Retrieve combined skin concerns
-Retrieve relevant concern_benefit mappings
-Retrieve active_benefit_score data
-Calculate/rank active candidates
-Retrieve applicable bases using questionnaire/session information
-Apply age suitability
-Apply skin-type suitability
-Apply climate/location considerations
-Apply acne-suitability requirements
-Apply questionnaire preferences
-Check base-active compatibility
-Produce candidate bases
-Produce candidate actives</t>
-  </si>
-  <si>
-    <t>Pass candidate information and relevant RAG information to LLM
-Generate recommended base
-Generate recommended active ingredients
-Generate explanation for selected base
-Generate explanation for selected actives
-Ensure selected actives address detected concerns
-Ensure selected actives are compatible with selected base
-Generate formulation information
-Validate recommendation output</t>
   </si>
   <si>
     <t>Create recommendation_run
@@ -2582,6 +2504,90 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>I can view my reccomendation page with the following fields:
+1. Hello "user_full_name"! 
+2. Skin analysis results : Primary Concerns :  those detected through the combination of skin concerns from both image and questionnaire.
+3.Skin analysis results: Skin Type: detected through questionnaire answers.
+5. Reccomended for you: Base :
+selected through questionnaire answers.
+6. Reccomended for you : Active Ingredients: those detected through selfie and questionnaire skin concerns.
+7. Reccomended for you: Why this formula: explained by LLM for selected actives detected through selfie and questionnaire skin concerns</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Detected skin concerns should be from the series:
+SC0001-SC0019 , SC1001-SC1009 &amp;
+SC2001-SC2004.
+2. If no skin concern is detected(perfectly fit skin) then Skin analysis results should show the following message:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"No skin concerns detected."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">3.If the image &amp; questionnaire contains one or multiple particular skin concerns then, all of those should be shown in the Skin analysis results: Primary Concerns.
+4.No other skins concerns should be shown in the Skin analysis results: Primary Concerns other than the ones really existing in the images and questionnaire.
+5. The total formulation must always weigh 100g total.
+6. The percentage of actives in formulation must be listed.
+7. The formulation explanation must correctly reflect the reason for choosing the actives and bases as per the LLM.
+8. The actives and base comprising the reccomended formulation must be compatible with each other.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Validate LLM response
+Handle malformed LLM response
+Handle LLM/API failure
+Store questionnaire detection result in session_skin_concern_detection
+Store LLM-generated explanations
+Store raw detection JSON</t>
+  </si>
+  <si>
+    <t>Define questionnaire-analysis LLM prompt
+Pass questionnaire JSON to LLM
+Define concern extraction rules
+Define skin-type extraction
+Define sensitivity extraction
+Define questionnaire-only concern handling</t>
+  </si>
+  <si>
+    <t>Retrieve combined skin concerns
+Retrieve relevant concern_benefit mappings
+Retrieve active_benefit_score data
+Retrieve applicable bases using questionnaire/session information
+Check base-active compatibility
+Produce candidate bases
+Produce candidate actives</t>
+  </si>
+  <si>
+    <t>Validate LLM recommendation output</t>
+  </si>
+  <si>
+    <t>Pass candidate information , along with questionnaire answers to LLM
+Generate recommended base
+Generate recommended active ingredients
+Generate explanation for selected base
+Generate explanation for selected actives
+Ensure selected actives address detected concerns
+Ensure selected actives are compatible with selected base
+Generate formulation information</t>
   </si>
 </sst>
 </file>
@@ -2895,6 +2901,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2902,16 +2917,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4383,6 +4389,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E6" dT="2026-09-10T10:13:35.35" personId="{00000000-0000-0000-0000-000000000000}" id="{148E080D-CE22-4CE0-8311-B67C30FEF121}">
+    <text>Get client verification</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F10"/>
@@ -4451,13 +4465,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" ht="294" customHeight="1">
@@ -4471,10 +4485,10 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>263</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>51</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="86.4">
@@ -4491,7 +4505,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4569,7 +4583,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>7</v>
@@ -4588,1190 +4602,1190 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="50">
+      <c r="A3" s="53">
         <v>1</v>
       </c>
-      <c r="B3" s="51">
+      <c r="B3" s="48">
         <v>1</v>
       </c>
-      <c r="C3" s="51">
+      <c r="C3" s="48">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="48" cm="1">
+      <c r="F3" s="51" cm="1">
         <f t="array" ref="F3">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
       <c r="D4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
+        <v>59</v>
+      </c>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="50"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="50"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="50"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="53"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="53"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="50"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="7" t="s">
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="53"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="7" t="s">
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="53"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="50"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="7" t="s">
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="53"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48">
+        <v>1.2</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="50"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51">
-        <v>1.2</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="48" cm="1">
+      <c r="F12" s="51" cm="1">
         <f t="array" ref="F12">_xlfn.SWITCH(E3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="53"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="53"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48">
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="50"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="7" t="s">
+      <c r="E15" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="51"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="53"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="50"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51">
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="53"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="48" t="s">
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="53"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48">
+        <v>1.4</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="51"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="53"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="53"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="53"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="53"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="53"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="53"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="53"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="53"/>
+      <c r="B26" s="54">
+        <v>2</v>
+      </c>
+      <c r="C26" s="48">
+        <v>2.1</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E26" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="48"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="50"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="50"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51">
-        <v>1.4</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="48" t="s">
+      <c r="F26" s="51"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="53"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E27" s="52"/>
+      <c r="F27" s="51"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="53"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="50">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="51"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="53"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="53"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="48">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="53"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="53"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="53"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="53"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="53"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="53"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="53"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="48">
+        <v>2.4</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="48"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="50"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="50"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="50"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="48"/>
-      <c r="F21" s="48"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="50"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="50"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="50"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="50"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="50"/>
-      <c r="B26" s="52">
-        <v>2</v>
-      </c>
-      <c r="C26" s="51">
-        <v>2.1</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="48"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="50"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E27" s="49"/>
-      <c r="F27" s="48"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="50"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="E28" s="49"/>
-      <c r="F28" s="48"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="50"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="53">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E29" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="48"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="50"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="50"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="51">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="50"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="50"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="50"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="50"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="50"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="50"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="7" t="s">
+      <c r="F38" s="51"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="53"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="50"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="51">
-        <v>2.4</v>
-      </c>
-      <c r="D38" s="7" t="s">
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="53"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E38" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" s="48"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="50"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="50"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="50"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="51"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="48"/>
       <c r="D41" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="50"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="51"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="53"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="53"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="50"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="7" t="s">
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="53"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="50"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="7" t="s">
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="53"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="48">
+        <v>2.5</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="51"/>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="53"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="50"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="7" t="s">
+      <c r="E47" s="52"/>
+      <c r="F47" s="51"/>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="53"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="50"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="51">
-        <v>2.5</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E46" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46" s="48"/>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="50"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="7" t="s">
+      <c r="E48" s="52"/>
+      <c r="F48" s="51"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="53"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E47" s="49"/>
-      <c r="F47" s="48"/>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="50"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="7" t="s">
+      <c r="E49" s="52"/>
+      <c r="F49" s="51"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="53"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="48">
+        <v>2.7</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="49"/>
-      <c r="F48" s="48"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="50"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="7" t="s">
+      <c r="E50" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="51"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="53"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E49" s="49"/>
-      <c r="F49" s="48"/>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="50"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="51">
-        <v>2.7</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="53"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E50" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="F50" s="48"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="50"/>
-      <c r="B51" s="52"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="7" t="s">
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="53"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="50"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="7" t="s">
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="53"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="50"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="7" t="s">
+      <c r="E54" s="51"/>
+      <c r="F54" s="51"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="53"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="50"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="7" t="s">
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="53"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="50"/>
-      <c r="B55" s="52"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="7" t="s">
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="53"/>
+      <c r="B57" s="54"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="50"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="50"/>
-      <c r="B57" s="52"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="50"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="51"/>
+      <c r="A58" s="53"/>
+      <c r="B58" s="54"/>
+      <c r="C58" s="48"/>
       <c r="D58" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
+        <v>55</v>
+      </c>
+      <c r="E58" s="51"/>
+      <c r="F58" s="51"/>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="20"/>
-      <c r="B59" s="51">
+      <c r="B59" s="48">
         <v>3</v>
       </c>
-      <c r="C59" s="51">
+      <c r="C59" s="48">
         <v>3.1</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="19"/>
-      <c r="B60" s="51"/>
-      <c r="C60" s="51"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="48"/>
       <c r="D60" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="19"/>
-      <c r="B61" s="51"/>
-      <c r="C61" s="51"/>
+      <c r="B61" s="48"/>
+      <c r="C61" s="48"/>
       <c r="D61" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="19"/>
-      <c r="B62" s="51"/>
-      <c r="C62" s="51"/>
+      <c r="B62" s="48"/>
+      <c r="C62" s="48"/>
       <c r="D62" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="19"/>
-      <c r="B63" s="51"/>
-      <c r="C63" s="51"/>
+      <c r="B63" s="48"/>
+      <c r="C63" s="48"/>
       <c r="D63" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="19"/>
-      <c r="B64" s="51"/>
-      <c r="C64" s="51"/>
+      <c r="B64" s="48"/>
+      <c r="C64" s="48"/>
       <c r="D64" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="19"/>
-      <c r="B65" s="51"/>
-      <c r="C65" s="51">
+      <c r="B65" s="48"/>
+      <c r="C65" s="48">
         <v>3.2</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="19"/>
-      <c r="B66" s="51"/>
-      <c r="C66" s="51"/>
+      <c r="B66" s="48"/>
+      <c r="C66" s="48"/>
       <c r="D66" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="19"/>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
+      <c r="B67" s="48"/>
+      <c r="C67" s="48"/>
       <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="19"/>
-      <c r="B68" s="51"/>
-      <c r="C68" s="51"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
       <c r="D68" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="19"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
       <c r="D69" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="19"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
       <c r="D70" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="19"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
       <c r="D71" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="19"/>
-      <c r="B72" s="51"/>
-      <c r="C72" s="51"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
       <c r="D72" s="7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="19"/>
-      <c r="B73" s="51"/>
-      <c r="C73" s="51"/>
+      <c r="B73" s="48"/>
+      <c r="C73" s="48"/>
       <c r="D73" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="19"/>
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
       <c r="D74" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="19"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
       <c r="D75" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="19"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
       <c r="D76" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="19"/>
-      <c r="B77" s="51"/>
-      <c r="C77" s="51">
+      <c r="B77" s="48"/>
+      <c r="C77" s="48">
         <v>3.3</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="19"/>
-      <c r="B78" s="51"/>
-      <c r="C78" s="51"/>
+      <c r="B78" s="48"/>
+      <c r="C78" s="48"/>
       <c r="D78" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="19"/>
-      <c r="B79" s="51"/>
-      <c r="C79" s="51"/>
+      <c r="B79" s="48"/>
+      <c r="C79" s="48"/>
       <c r="D79" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="19"/>
-      <c r="B80" s="51"/>
-      <c r="C80" s="51"/>
+      <c r="B80" s="48"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="19"/>
-      <c r="B81" s="51"/>
-      <c r="C81" s="51"/>
+      <c r="B81" s="48"/>
+      <c r="C81" s="48"/>
       <c r="D81" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="19"/>
-      <c r="B82" s="51"/>
-      <c r="C82" s="51"/>
+      <c r="B82" s="48"/>
+      <c r="C82" s="48"/>
       <c r="D82" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="19"/>
-      <c r="B83" s="51"/>
-      <c r="C83" s="51"/>
+      <c r="B83" s="48"/>
+      <c r="C83" s="48"/>
       <c r="D83" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="19"/>
-      <c r="B84" s="51"/>
-      <c r="C84" s="51"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="48"/>
       <c r="D84" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="19"/>
-      <c r="B85" s="51"/>
-      <c r="C85" s="51"/>
+      <c r="B85" s="48"/>
+      <c r="C85" s="48"/>
       <c r="D85" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="19"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
       <c r="D86" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="19"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
       <c r="D87" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="19"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51">
+      <c r="B88" s="48"/>
+      <c r="C88" s="48">
         <v>3.4</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="19"/>
-      <c r="B89" s="51"/>
-      <c r="C89" s="51"/>
+      <c r="B89" s="48"/>
+      <c r="C89" s="48"/>
       <c r="D89" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="19"/>
-      <c r="B90" s="51"/>
-      <c r="C90" s="51"/>
+      <c r="B90" s="48"/>
+      <c r="C90" s="48"/>
       <c r="D90" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="19"/>
-      <c r="B91" s="51"/>
-      <c r="C91" s="51"/>
+      <c r="B91" s="48"/>
+      <c r="C91" s="48"/>
       <c r="D91" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="19"/>
-      <c r="B92" s="51"/>
-      <c r="C92" s="51"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="48"/>
       <c r="D92" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="19"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="51"/>
+      <c r="B93" s="48"/>
+      <c r="C93" s="48"/>
       <c r="D93" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="19"/>
-      <c r="B94" s="51"/>
-      <c r="C94" s="51"/>
+      <c r="B94" s="48"/>
+      <c r="C94" s="48"/>
       <c r="D94" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="19"/>
-      <c r="B95" s="51"/>
-      <c r="C95" s="51"/>
+      <c r="B95" s="48"/>
+      <c r="C95" s="48"/>
       <c r="D95" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="19"/>
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
+      <c r="B96" s="48"/>
+      <c r="C96" s="48"/>
       <c r="D96" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="19"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
+      <c r="B97" s="48"/>
+      <c r="C97" s="48"/>
       <c r="D97" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="19"/>
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
+      <c r="B98" s="48"/>
+      <c r="C98" s="48"/>
       <c r="D98" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="19"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
+      <c r="B99" s="48"/>
+      <c r="C99" s="48"/>
       <c r="D99" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="19"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="48"/>
       <c r="D100" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="19"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51">
+      <c r="B101" s="48"/>
+      <c r="C101" s="48">
         <v>3.5</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="19"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
+      <c r="B102" s="48"/>
+      <c r="C102" s="48"/>
       <c r="D102" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="19"/>
-      <c r="B103" s="51"/>
-      <c r="C103" s="51"/>
+      <c r="B103" s="48"/>
+      <c r="C103" s="48"/>
       <c r="D103" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="19"/>
-      <c r="B104" s="51"/>
-      <c r="C104" s="51"/>
+      <c r="B104" s="48"/>
+      <c r="C104" s="48"/>
       <c r="D104" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="19"/>
-      <c r="B105" s="51"/>
-      <c r="C105" s="51"/>
+      <c r="B105" s="48"/>
+      <c r="C105" s="48"/>
       <c r="D105" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="19"/>
-      <c r="B106" s="51"/>
-      <c r="C106" s="51"/>
+      <c r="B106" s="48"/>
+      <c r="C106" s="48"/>
       <c r="D106" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="19"/>
-      <c r="B107" s="51"/>
-      <c r="C107" s="51"/>
+      <c r="B107" s="48"/>
+      <c r="C107" s="48"/>
       <c r="D107" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="19"/>
-      <c r="B108" s="51"/>
-      <c r="C108" s="51"/>
+      <c r="B108" s="48"/>
+      <c r="C108" s="48"/>
       <c r="D108" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19"/>
-      <c r="B109" s="51"/>
-      <c r="C109" s="51"/>
+      <c r="B109" s="48"/>
+      <c r="C109" s="48"/>
       <c r="D109" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19"/>
-      <c r="B110" s="51"/>
-      <c r="C110" s="51">
+      <c r="B110" s="48"/>
+      <c r="C110" s="48">
         <v>3.6</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19"/>
-      <c r="B111" s="51"/>
-      <c r="C111" s="51"/>
+      <c r="B111" s="48"/>
+      <c r="C111" s="48"/>
       <c r="D111" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19"/>
-      <c r="B112" s="51"/>
-      <c r="C112" s="51"/>
+      <c r="B112" s="48"/>
+      <c r="C112" s="48"/>
       <c r="D112" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="19"/>
-      <c r="B113" s="51"/>
-      <c r="C113" s="51"/>
+      <c r="B113" s="48"/>
+      <c r="C113" s="48"/>
       <c r="D113" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="19"/>
-      <c r="B114" s="51"/>
-      <c r="C114" s="51"/>
+      <c r="B114" s="48"/>
+      <c r="C114" s="48"/>
       <c r="D114" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="19"/>
-      <c r="B115" s="51"/>
-      <c r="C115" s="51"/>
+      <c r="B115" s="48"/>
+      <c r="C115" s="48"/>
       <c r="D115" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="19"/>
-      <c r="B116" s="51"/>
-      <c r="C116" s="51">
+      <c r="B116" s="48"/>
+      <c r="C116" s="48">
         <v>3.7</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="19"/>
-      <c r="B117" s="51"/>
-      <c r="C117" s="51"/>
+      <c r="B117" s="48"/>
+      <c r="C117" s="48"/>
       <c r="D117" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="19"/>
-      <c r="B118" s="51"/>
-      <c r="C118" s="51"/>
+      <c r="B118" s="48"/>
+      <c r="C118" s="48"/>
       <c r="D118" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="19"/>
-      <c r="B119" s="51"/>
-      <c r="C119" s="51"/>
+      <c r="B119" s="48"/>
+      <c r="C119" s="48"/>
       <c r="D119" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="19"/>
-      <c r="B120" s="51"/>
-      <c r="C120" s="51"/>
+      <c r="B120" s="48"/>
+      <c r="C120" s="48"/>
       <c r="D120" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="19"/>
-      <c r="B121" s="51"/>
-      <c r="C121" s="51"/>
+      <c r="B121" s="48"/>
+      <c r="C121" s="48"/>
       <c r="D121" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="19"/>
-      <c r="B122" s="51"/>
-      <c r="C122" s="51"/>
+      <c r="B122" s="48"/>
+      <c r="C122" s="48"/>
       <c r="D122" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="19"/>
-      <c r="B123" s="51"/>
-      <c r="C123" s="51"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="48"/>
       <c r="D123" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="19"/>
-      <c r="B124" s="51"/>
-      <c r="C124" s="51"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="48"/>
       <c r="D124" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="19"/>
-      <c r="B125" s="51"/>
-      <c r="C125" s="51"/>
+      <c r="B125" s="48"/>
+      <c r="C125" s="48"/>
       <c r="D125" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="19"/>
-      <c r="B126" s="51"/>
-      <c r="C126" s="51"/>
+      <c r="B126" s="48"/>
+      <c r="C126" s="48"/>
       <c r="D126" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="19"/>
-      <c r="B127" s="51"/>
-      <c r="C127" s="51">
+      <c r="B127" s="48"/>
+      <c r="C127" s="48">
         <v>3.8</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -5780,338 +5794,338 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="19"/>
-      <c r="B128" s="51"/>
-      <c r="C128" s="51"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="48"/>
       <c r="D128" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="19"/>
-      <c r="B129" s="51"/>
-      <c r="C129" s="51"/>
+      <c r="B129" s="48"/>
+      <c r="C129" s="48"/>
       <c r="D129" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="19"/>
-      <c r="B130" s="51"/>
-      <c r="C130" s="51"/>
+      <c r="B130" s="48"/>
+      <c r="C130" s="48"/>
       <c r="D130" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="19"/>
-      <c r="B131" s="51"/>
-      <c r="C131" s="51"/>
+      <c r="B131" s="48"/>
+      <c r="C131" s="48"/>
       <c r="D131" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="19"/>
-      <c r="B132" s="51"/>
-      <c r="C132" s="51"/>
+      <c r="B132" s="48"/>
+      <c r="C132" s="48"/>
       <c r="D132" s="7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="19"/>
-      <c r="B133" s="51"/>
-      <c r="C133" s="51"/>
+      <c r="B133" s="48"/>
+      <c r="C133" s="48"/>
       <c r="D133" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="19"/>
-      <c r="B134" s="51"/>
-      <c r="C134" s="51"/>
+      <c r="B134" s="48"/>
+      <c r="C134" s="48"/>
       <c r="D134" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="19"/>
-      <c r="B135" s="51"/>
-      <c r="C135" s="51"/>
+      <c r="B135" s="48"/>
+      <c r="C135" s="48"/>
       <c r="D135" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="19"/>
-      <c r="B136" s="51"/>
-      <c r="C136" s="51"/>
+      <c r="B136" s="48"/>
+      <c r="C136" s="48"/>
       <c r="D136" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="19"/>
-      <c r="B137" s="51"/>
-      <c r="C137" s="51">
+      <c r="B137" s="48"/>
+      <c r="C137" s="48">
         <v>3.9</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="19"/>
-      <c r="B138" s="51"/>
-      <c r="C138" s="51"/>
+      <c r="B138" s="48"/>
+      <c r="C138" s="48"/>
       <c r="D138" s="7" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="19"/>
-      <c r="B139" s="51"/>
-      <c r="C139" s="51"/>
+      <c r="B139" s="48"/>
+      <c r="C139" s="48"/>
       <c r="D139" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="19"/>
-      <c r="B140" s="51"/>
-      <c r="C140" s="51"/>
+      <c r="B140" s="48"/>
+      <c r="C140" s="48"/>
       <c r="D140" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="19"/>
-      <c r="B141" s="51"/>
-      <c r="C141" s="51"/>
+      <c r="B141" s="48"/>
+      <c r="C141" s="48"/>
       <c r="D141" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="19"/>
-      <c r="B142" s="51"/>
-      <c r="C142" s="54">
+      <c r="B142" s="48"/>
+      <c r="C142" s="49">
         <v>3.1</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="19"/>
-      <c r="B143" s="51"/>
-      <c r="C143" s="54"/>
+      <c r="B143" s="48"/>
+      <c r="C143" s="49"/>
       <c r="D143" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="19"/>
-      <c r="B144" s="51"/>
-      <c r="C144" s="54"/>
+      <c r="B144" s="48"/>
+      <c r="C144" s="49"/>
       <c r="D144" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="19"/>
-      <c r="B145" s="51"/>
-      <c r="C145" s="54"/>
+      <c r="B145" s="48"/>
+      <c r="C145" s="49"/>
       <c r="D145" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="19"/>
-      <c r="B146" s="51"/>
-      <c r="C146" s="54"/>
+      <c r="B146" s="48"/>
+      <c r="C146" s="49"/>
       <c r="D146" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="19"/>
-      <c r="B147" s="51"/>
-      <c r="C147" s="54"/>
+      <c r="B147" s="48"/>
+      <c r="C147" s="49"/>
       <c r="D147" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="19"/>
-      <c r="B148" s="51"/>
-      <c r="C148" s="54"/>
+      <c r="B148" s="48"/>
+      <c r="C148" s="49"/>
       <c r="D148" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="19"/>
-      <c r="B149" s="51"/>
-      <c r="C149" s="54"/>
+      <c r="B149" s="48"/>
+      <c r="C149" s="49"/>
       <c r="D149" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="19"/>
-      <c r="B150" s="51"/>
-      <c r="C150" s="54"/>
+      <c r="B150" s="48"/>
+      <c r="C150" s="49"/>
       <c r="D150" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="19"/>
-      <c r="B151" s="51"/>
-      <c r="C151" s="54"/>
+      <c r="B151" s="48"/>
+      <c r="C151" s="49"/>
       <c r="D151" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="19"/>
-      <c r="B152" s="51"/>
-      <c r="C152" s="54"/>
+      <c r="B152" s="48"/>
+      <c r="C152" s="49"/>
       <c r="D152" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="19"/>
-      <c r="B153" s="51"/>
-      <c r="C153" s="54"/>
+      <c r="B153" s="48"/>
+      <c r="C153" s="49"/>
       <c r="D153" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="19"/>
-      <c r="B154" s="51"/>
-      <c r="C154" s="54"/>
+      <c r="B154" s="48"/>
+      <c r="C154" s="49"/>
       <c r="D154" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="19"/>
-      <c r="B155" s="51"/>
-      <c r="C155" s="54"/>
+      <c r="B155" s="48"/>
+      <c r="C155" s="49"/>
       <c r="D155" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="19"/>
-      <c r="B156" s="51"/>
-      <c r="C156" s="54"/>
+      <c r="B156" s="48"/>
+      <c r="C156" s="49"/>
       <c r="D156" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="20"/>
-      <c r="B157" s="51">
+      <c r="B157" s="48">
         <v>4</v>
       </c>
-      <c r="C157" s="51">
+      <c r="C157" s="48">
         <v>4.0999999999999996</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="19"/>
-      <c r="B158" s="51"/>
-      <c r="C158" s="51"/>
+      <c r="B158" s="48"/>
+      <c r="C158" s="48"/>
       <c r="D158" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="19"/>
-      <c r="B159" s="51"/>
-      <c r="C159" s="51"/>
+      <c r="B159" s="48"/>
+      <c r="C159" s="48"/>
       <c r="D159" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="19"/>
-      <c r="B160" s="51"/>
-      <c r="C160" s="51"/>
+      <c r="B160" s="48"/>
+      <c r="C160" s="48"/>
       <c r="D160" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="19"/>
-      <c r="B161" s="51"/>
-      <c r="C161" s="51">
+      <c r="B161" s="48"/>
+      <c r="C161" s="48">
         <v>4.2</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="19"/>
-      <c r="B162" s="51"/>
-      <c r="C162" s="51"/>
+      <c r="B162" s="48"/>
+      <c r="C162" s="48"/>
       <c r="D162" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="19"/>
-      <c r="B163" s="51"/>
-      <c r="C163" s="51"/>
+      <c r="B163" s="48"/>
+      <c r="C163" s="48"/>
       <c r="D163" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="19"/>
-      <c r="B164" s="51"/>
-      <c r="C164" s="51"/>
+      <c r="B164" s="48"/>
+      <c r="C164" s="48"/>
       <c r="D164" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="19"/>
-      <c r="B165" s="51"/>
-      <c r="C165" s="51"/>
+      <c r="B165" s="48"/>
+      <c r="C165" s="48"/>
       <c r="D165" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="19"/>
-      <c r="B166" s="51"/>
-      <c r="C166" s="51"/>
+      <c r="B166" s="48"/>
+      <c r="C166" s="48"/>
       <c r="D166" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="19"/>
-      <c r="B167" s="51"/>
-      <c r="C167" s="51"/>
+      <c r="B167" s="48"/>
+      <c r="C167" s="48"/>
       <c r="D167" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="19"/>
-      <c r="B168" s="51"/>
-      <c r="C168" s="51">
+      <c r="B168" s="48"/>
+      <c r="C168" s="48">
         <v>4.3</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -6120,113 +6134,148 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="19"/>
-      <c r="B169" s="51"/>
-      <c r="C169" s="51"/>
+      <c r="B169" s="48"/>
+      <c r="C169" s="48"/>
       <c r="D169" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="19"/>
-      <c r="B170" s="51"/>
-      <c r="C170" s="51"/>
+      <c r="B170" s="48"/>
+      <c r="C170" s="48"/>
       <c r="D170" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="19"/>
-      <c r="B171" s="51"/>
-      <c r="C171" s="51"/>
+      <c r="B171" s="48"/>
+      <c r="C171" s="48"/>
       <c r="D171" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="19"/>
-      <c r="B172" s="51"/>
-      <c r="C172" s="51"/>
+      <c r="B172" s="48"/>
+      <c r="C172" s="48"/>
       <c r="D172" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="19"/>
-      <c r="B173" s="51"/>
-      <c r="C173" s="51"/>
+      <c r="B173" s="48"/>
+      <c r="C173" s="48"/>
       <c r="D173" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="19"/>
-      <c r="B174" s="51"/>
-      <c r="C174" s="51">
+      <c r="B174" s="48"/>
+      <c r="C174" s="48">
         <v>4.4000000000000004</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="19"/>
-      <c r="B175" s="51"/>
-      <c r="C175" s="51"/>
+      <c r="B175" s="48"/>
+      <c r="C175" s="48"/>
       <c r="D175" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="19"/>
-      <c r="B176" s="51"/>
-      <c r="C176" s="51"/>
+      <c r="B176" s="48"/>
+      <c r="C176" s="48"/>
       <c r="D176" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="19"/>
-      <c r="B177" s="51"/>
-      <c r="C177" s="51"/>
+      <c r="B177" s="48"/>
+      <c r="C177" s="48"/>
       <c r="D177" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="19"/>
-      <c r="B178" s="51"/>
-      <c r="C178" s="51"/>
+      <c r="B178" s="48"/>
+      <c r="C178" s="48"/>
       <c r="D178" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="19"/>
-      <c r="B179" s="51"/>
-      <c r="C179" s="51"/>
+      <c r="B179" s="48"/>
+      <c r="C179" s="48"/>
       <c r="D179" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="19"/>
-      <c r="B180" s="51"/>
-      <c r="C180" s="51"/>
+      <c r="B180" s="48"/>
+      <c r="C180" s="48"/>
       <c r="D180" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="19"/>
-      <c r="B181" s="51"/>
-      <c r="C181" s="51"/>
+      <c r="B181" s="48"/>
+      <c r="C181" s="48"/>
       <c r="D181" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:J181" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="51">
+    <mergeCell ref="F50:F58"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F37"/>
+    <mergeCell ref="F38:F45"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E50:E58"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="A3:A58"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="B26:B58"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="C18:C25"/>
+    <mergeCell ref="G31:G37"/>
+    <mergeCell ref="E38:E45"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="E18:E25"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="F18:F25"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F3:F11"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="C110:C115"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C31:C37"/>
+    <mergeCell ref="C38:C45"/>
+    <mergeCell ref="C50:C58"/>
     <mergeCell ref="C168:C173"/>
     <mergeCell ref="C174:C181"/>
     <mergeCell ref="B3:B25"/>
@@ -6243,41 +6292,6 @@
     <mergeCell ref="C77:C87"/>
     <mergeCell ref="C88:C100"/>
     <mergeCell ref="C101:C109"/>
-    <mergeCell ref="C110:C115"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C31:C37"/>
-    <mergeCell ref="C38:C45"/>
-    <mergeCell ref="C50:C58"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F3:F11"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="G31:G37"/>
-    <mergeCell ref="E38:E45"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="E18:E25"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="F18:F25"/>
-    <mergeCell ref="E50:E58"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="A3:A58"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="B26:B58"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="C18:C25"/>
-    <mergeCell ref="F50:F58"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F31:F37"/>
-    <mergeCell ref="F38:F45"/>
-    <mergeCell ref="F46:F49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6287,7 +6301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="15" customWidth="1"/>
@@ -6327,7 +6341,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>7</v>
@@ -6345,7 +6359,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="L2" s="40"/>
     </row>
@@ -6360,7 +6374,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -6370,10 +6384,10 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="57.6">
@@ -6383,7 +6397,7 @@
         <v>1.2</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -6393,10 +6407,10 @@
         <v>3</v>
       </c>
       <c r="G4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="H4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="43.2">
@@ -6406,7 +6420,7 @@
         <v>1.3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -6416,10 +6430,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H5" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="115.2">
@@ -6429,7 +6443,7 @@
         <v>1.4</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E6" s="38" t="s">
         <v>20</v>
@@ -6439,10 +6453,10 @@
         <v>5</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
@@ -6456,7 +6470,7 @@
         <v>2.1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -6466,7 +6480,7 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="57.6">
@@ -6476,7 +6490,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -6486,10 +6500,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H8" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="100.8">
@@ -6499,7 +6513,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -6509,10 +6523,10 @@
         <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="115.2">
@@ -6522,7 +6536,7 @@
         <v>2.4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -6532,10 +6546,10 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H10" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="100.8">
@@ -6545,7 +6559,7 @@
         <v>2.5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -6555,7 +6569,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="115.2">
@@ -6565,7 +6579,7 @@
         <v>2.6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -6575,10 +6589,10 @@
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H12" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="158.4">
@@ -6588,7 +6602,7 @@
         <v>2.7</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E13" s="38" t="s">
         <v>20</v>
@@ -6598,10 +6612,10 @@
         <v>5</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
@@ -6611,7 +6625,7 @@
         <v>2.8</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E14" s="43" t="s">
         <v>20</v>
@@ -6621,10 +6635,10 @@
         <v>5</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H14" s="43" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I14" s="43"/>
       <c r="J14" s="43"/>
@@ -6634,7 +6648,7 @@
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="30" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E15" s="29"/>
       <c r="F15" s="29">
@@ -6657,150 +6671,170 @@
         <v>3.1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="172.8">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="86.4">
       <c r="A17" s="44"/>
       <c r="B17" s="44"/>
       <c r="C17" s="15">
         <v>3.2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="158.4">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="86.4">
       <c r="A18" s="44"/>
       <c r="B18" s="44"/>
       <c r="C18" s="15">
         <v>3.3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="187.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="158.4">
       <c r="A19" s="44"/>
       <c r="B19" s="44"/>
       <c r="C19" s="15">
         <v>3.4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="129.6">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="100.8">
       <c r="A20" s="44"/>
       <c r="B20" s="44"/>
       <c r="C20" s="15">
         <v>3.5</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="86.4">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="115.2">
       <c r="A21" s="44"/>
       <c r="B21" s="44"/>
       <c r="C21" s="15">
         <v>3.6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="158.4">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="44"/>
       <c r="B22" s="44"/>
       <c r="C22" s="15">
         <v>3.7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="144">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="86.4">
       <c r="A23" s="44"/>
       <c r="B23" s="44"/>
       <c r="C23" s="15">
         <v>3.8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="72">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="158.4">
       <c r="A24" s="44"/>
       <c r="B24" s="44"/>
       <c r="C24" s="15">
         <v>3.9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="216">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="144">
       <c r="A25" s="44"/>
       <c r="B25" s="44"/>
       <c r="C25" s="35">
         <v>3.1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="57.6">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="72">
       <c r="A26" s="44"/>
-      <c r="B26" s="44">
-        <v>4</v>
-      </c>
+      <c r="B26" s="44"/>
       <c r="C26" s="15">
-        <v>4.0999999999999996</v>
+        <v>3.11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="100.8">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="216">
       <c r="A27" s="44"/>
       <c r="B27" s="44"/>
-      <c r="C27" s="15">
-        <v>4.2</v>
+      <c r="C27" s="35">
+        <v>3.12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="86.4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="57.6">
       <c r="A28" s="44"/>
-      <c r="B28" s="44"/>
+      <c r="B28" s="44">
+        <v>4</v>
+      </c>
       <c r="C28" s="15">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="115.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="100.8">
       <c r="A29" s="44"/>
       <c r="B29" s="44"/>
       <c r="C29" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="86.4">
+      <c r="A30" s="44"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="115.2">
+      <c r="A31" s="44"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="15">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>249</v>
+      <c r="D31" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A16:A29"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="A16:A31"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:A13"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="B7:B13"/>
-    <mergeCell ref="B16:B25"/>
+    <mergeCell ref="B16:B27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6821,24 +6855,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="57.6">
       <c r="A1" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="D1" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="E1" s="24" t="s">
         <v>218</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="25" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B2" s="26">
         <v>46265</v>
@@ -6856,7 +6890,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B3" s="26">
         <v>46266</v>
@@ -6875,7 +6909,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B4" s="26">
         <v>46267</v>
@@ -6894,7 +6928,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B5" s="26">
         <v>46268</v>
@@ -6913,7 +6947,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B6" s="26">
         <v>46269</v>
@@ -6932,7 +6966,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B7" s="26">
         <v>46272</v>
@@ -6951,7 +6985,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B8" s="26">
         <v>46273</v>
@@ -6970,7 +7004,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="25" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B9" s="26">
         <v>46274</v>
@@ -6989,7 +7023,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B10" s="26">
         <v>46275</v>
